--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -7,15 +7,15 @@
     <sheet state="visible" name="Pitchers" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$39</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$36</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$38</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$35</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
   <si>
     <t>INCENTIVOS DSL 2026</t>
   </si>
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/18/2026</t>
+    <t>Actualización: 6/21/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -104,66 +104,63 @@
     <t>$RD</t>
   </si>
   <si>
+    <t>Celesten, Yeisy</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Flores, Jesus</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Rodriguez, Alex</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>Mateo, Cesar</t>
   </si>
   <si>
-    <t>Celesten, Yeisy</t>
-  </si>
-  <si>
-    <t>Flores, Jesus</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Cavero, Braulio</t>
+  </si>
+  <si>
+    <t>Rosario, Elian</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Rosario, Elian</t>
+    <t>Castillo, Wesly</t>
+  </si>
+  <si>
+    <t>Gonzalez, Victor</t>
+  </si>
+  <si>
+    <t>Abreu, Ariel</t>
+  </si>
+  <si>
+    <t>Benitez, Frainker</t>
   </si>
   <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
-    <t>Cavero, Braulio</t>
-  </si>
-  <si>
-    <t>Castillo, Wesly</t>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
+    <t>Jaquez, Luis</t>
   </si>
   <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
-    <t>Abreu, Ariel</t>
-  </si>
-  <si>
-    <t>Ramirez, Manni</t>
-  </si>
-  <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
-    <t>Jaquez, Luis</t>
-  </si>
-  <si>
-    <t>Gonzalez, Victor</t>
-  </si>
-  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
@@ -176,13 +173,19 @@
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Mosqueda, Juan</t>
+  </si>
+  <si>
+    <t>Rodriguez, Victor</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
-    <t>Mosqueda, Juan</t>
+    <t>Santa, Fraimy</t>
   </si>
   <si>
     <t>Genao, Jhostin</t>
@@ -194,12 +197,6 @@
     <t>Colina, Felix</t>
   </si>
   <si>
-    <t>Rodriguez, Victor</t>
-  </si>
-  <si>
-    <t>Santa, Fraimy</t>
-  </si>
-  <si>
     <t>Montero, Darling</t>
   </si>
   <si>
@@ -251,6 +248,9 @@
     <t>Gamez, Manuel</t>
   </si>
   <si>
+    <t>Medina, Juan</t>
+  </si>
+  <si>
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
@@ -260,7 +260,7 @@
     <t>Santos, Aneudy</t>
   </si>
   <si>
-    <t>Medina, Juan</t>
+    <t>Granado, Argenis</t>
   </si>
   <si>
     <t>Pineda, Frandel</t>
@@ -272,70 +272,64 @@
     <t>Roquez, Yadiel</t>
   </si>
   <si>
+    <t>Pena, Dariel</t>
+  </si>
+  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
-    <t>Pena, Dariel</t>
+    <t>Castillo, Albert</t>
   </si>
   <si>
     <t>Gomez, Manuel</t>
   </si>
   <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
+    <t>Acosta, Isaac</t>
+  </si>
+  <si>
     <t>Alcantara, Jostin</t>
   </si>
   <si>
     <t>Cordero, Albert</t>
   </si>
   <si>
-    <t>Fernandez, Jehiber</t>
+    <t>Lamu, Alex</t>
   </si>
   <si>
     <t>Figuereo, Breyner</t>
   </si>
   <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
     <t>Ramos, Daniel</t>
   </si>
   <si>
-    <t>Castillo, Albert</t>
-  </si>
-  <si>
-    <t>Granado, Argenis</t>
-  </si>
-  <si>
     <t>Ballesteros, Jean</t>
   </si>
   <si>
-    <t>Lamu, Alex</t>
-  </si>
-  <si>
     <t>Perez, Juanangel</t>
   </si>
   <si>
+    <t>Liriano, Edgar</t>
+  </si>
+  <si>
     <t>Peralta, Eddy</t>
   </si>
   <si>
-    <t>Liriano, Edgar</t>
-  </si>
-  <si>
     <t>De Jesus, Yunier</t>
   </si>
   <si>
+    <t>Bautista, Jeyson</t>
+  </si>
+  <si>
     <t>Fernandez, Harley</t>
   </si>
   <si>
+    <t>Medina, Ruben</t>
+  </si>
+  <si>
     <t>Figuereo, Enmanuel</t>
-  </si>
-  <si>
-    <t>Bautista, Jeyson</t>
-  </si>
-  <si>
-    <t>Medina, Ruben</t>
-  </si>
-  <si>
-    <t>Cordova, Jose</t>
   </si>
   <si>
     <t>Gonzalez, Nestor</t>
@@ -388,7 +382,7 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="&quot;Tw Cen MT&quot;"/>
     </font>
     <font>
@@ -399,7 +393,7 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="&quot;Tw Cen MT&quot;"/>
     </font>
     <font>
@@ -819,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -933,26 +927,26 @@
     <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1030,55 +1024,58 @@
     <xf borderId="11" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="33" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="35" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1519,7 +1516,7 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
+    <row r="4">
       <c r="A4" s="28" t="s">
         <v>8</v>
       </c>
@@ -1601,16 +1598,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D5" s="40">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E5" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F5" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G5" s="40">
         <v>3.0</v>
@@ -1619,22 +1616,22 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="39">
         <v>3.0</v>
       </c>
-      <c r="J5" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="K5" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="39">
-        <v>1.0</v>
-      </c>
       <c r="M5" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="N5" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O5" s="40">
         <v>0.0</v>
@@ -1643,20 +1640,20 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="R5" s="40">
         <v>5.0</v>
       </c>
       <c r="S5" s="43">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U5" s="44">
-        <f t="shared" ref="U5:U39" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>2040</v>
+        <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
+        <v>2415</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1673,65 +1670,65 @@
         <v>31</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="39">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="D6" s="40">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E6" s="40">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F6" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H6" s="40">
         <v>0.0</v>
       </c>
       <c r="I6" s="41">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="J6" s="39">
         <v>0.0</v>
       </c>
       <c r="K6" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="L6" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="39">
         <v>5.0</v>
       </c>
-      <c r="M6" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N6" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>7.0</v>
-      </c>
       <c r="R6" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S6" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T6" s="41">
         <v>9.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>1980</v>
+        <v>2295</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1744,23 +1741,23 @@
       <c r="AD6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="s">
-        <v>32</v>
+      <c r="A7" s="46" t="s">
+        <v>33</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="39">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="D7" s="40">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="E7" s="40">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F7" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" s="40">
         <v>3.0</v>
@@ -1769,22 +1766,22 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J7" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K7" s="41">
         <v>0.0</v>
       </c>
       <c r="L7" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M7" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="N7" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O7" s="40">
         <v>0.0</v>
@@ -1799,14 +1796,14 @@
         <v>5.0</v>
       </c>
       <c r="S7" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T7" s="41">
         <v>9.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>1830</v>
+        <v>2130</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1819,69 +1816,69 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="s">
-        <v>33</v>
+      <c r="A8" s="37" t="s">
+        <v>34</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="E8" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="F8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>16.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="M8" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="O8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R8" s="40">
         <v>4.0</v>
       </c>
-      <c r="E8" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R8" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S8" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T8" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>2070</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1894,23 +1891,23 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="45" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="39">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="D9" s="40">
         <v>10.0</v>
       </c>
       <c r="E9" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="40">
         <v>2.0</v>
@@ -1931,7 +1928,7 @@
         <v>3.0</v>
       </c>
       <c r="M9" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="N9" s="40">
         <v>0.0</v>
@@ -1943,20 +1940,20 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R9" s="40">
         <v>4.0</v>
       </c>
       <c r="S9" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T9" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>1620</v>
+        <v>1980</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1969,24 +1966,24 @@
       <c r="AD9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="47">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D10" s="48">
         <v>15.0</v>
       </c>
       <c r="E10" s="48">
+        <v>8.0</v>
+      </c>
+      <c r="F10" s="48">
         <v>6.0</v>
       </c>
-      <c r="F10" s="48">
-        <v>5.0</v>
-      </c>
       <c r="G10" s="48">
         <v>2.0</v>
       </c>
@@ -2012,26 +2009,26 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P10" s="42">
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="R10" s="40">
         <v>6.0</v>
       </c>
       <c r="S10" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T10" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1800</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2044,32 +2041,32 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="39">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="D11" s="40">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E11" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F11" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H11" s="40">
         <v>0.0</v>
       </c>
       <c r="I11" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J11" s="39">
         <v>0.0</v>
@@ -2078,13 +2075,13 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O11" s="40">
         <v>0.0</v>
@@ -2096,17 +2093,17 @@
         <v>6.0</v>
       </c>
       <c r="R11" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S11" s="43">
         <v>2.0</v>
       </c>
       <c r="T11" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1590</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2119,14 +2116,14 @@
       <c r="AD11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="37" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D12" s="40">
         <v>8.0</v>
@@ -2135,10 +2132,10 @@
         <v>3.0</v>
       </c>
       <c r="F12" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H12" s="40">
         <v>0.0</v>
@@ -2156,7 +2153,7 @@
         <v>3.0</v>
       </c>
       <c r="M12" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N12" s="40">
         <v>0.0</v>
@@ -2168,20 +2165,20 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R12" s="40">
         <v>4.0</v>
       </c>
       <c r="S12" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T12" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1545</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2194,23 +2191,23 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="37" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="39">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="D13" s="40">
         <v>8.0</v>
       </c>
       <c r="E13" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" s="40">
         <v>2.0</v>
@@ -2219,7 +2216,7 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J13" s="39">
         <v>0.0</v>
@@ -2228,10 +2225,10 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M13" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="N13" s="40">
         <v>2.0</v>
@@ -2243,7 +2240,7 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R13" s="40">
         <v>4.0</v>
@@ -2252,11 +2249,11 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1530</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2273,31 +2270,31 @@
         <v>40</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="39">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D14" s="40">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="E14" s="40">
         <v>3.0</v>
       </c>
       <c r="F14" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H14" s="40">
         <v>0.0</v>
       </c>
       <c r="I14" s="41">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="J14" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K14" s="41">
         <v>0.0</v>
@@ -2321,7 +2318,7 @@
         <v>4.0</v>
       </c>
       <c r="R14" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S14" s="43">
         <v>1.0</v>
@@ -2331,7 +2328,7 @@
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1530</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2344,32 +2341,32 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="38" t="s">
-        <v>34</v>
+      <c r="B15" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="D15" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E15" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F15" s="40">
         <v>0.0</v>
       </c>
       <c r="G15" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2378,10 +2375,10 @@
         <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M15" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N15" s="40">
         <v>0.0</v>
@@ -2396,17 +2393,17 @@
         <v>3.0</v>
       </c>
       <c r="R15" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S15" s="43">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T15" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1425</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2419,26 +2416,26 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="45" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="D16" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="E16" s="40">
         <v>3.0</v>
       </c>
-      <c r="D16" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E16" s="40">
-        <v>2.0</v>
-      </c>
       <c r="F16" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
@@ -2450,38 +2447,38 @@
         <v>0.0</v>
       </c>
       <c r="K16" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="39">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="M16" s="40">
         <v>0.0</v>
       </c>
       <c r="N16" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O16" s="40">
         <v>1.0</v>
       </c>
       <c r="P16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q16" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R16" s="40">
         <v>4.0</v>
       </c>
-      <c r="R16" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S16" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T16" s="41">
         <v>9.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1305</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2494,20 +2491,20 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="51" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D17" s="40">
         <v>5.0</v>
       </c>
       <c r="E17" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F17" s="40">
         <v>0.0</v>
@@ -2543,20 +2540,20 @@
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R17" s="40">
         <v>3.0</v>
       </c>
       <c r="S17" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T17" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1260</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2569,26 +2566,26 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="51" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C18" s="39">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="D18" s="40">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E18" s="40">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F18" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" s="40">
         <v>0.0</v>
@@ -2603,35 +2600,35 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="39">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="M18" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N18" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P18" s="42">
         <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="R18" s="40">
         <v>4.0</v>
       </c>
       <c r="S18" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T18" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1005</v>
+        <v>1230</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2643,70 +2640,70 @@
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="46" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="D19" s="40">
+        <v>18.0</v>
+      </c>
+      <c r="E19" s="40">
         <v>4.0</v>
       </c>
-      <c r="D19" s="40">
+      <c r="F19" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G19" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="R19" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="S19" s="43">
+        <v>3.0</v>
+      </c>
+      <c r="T19" s="41">
         <v>10.0</v>
-      </c>
-      <c r="E19" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F19" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="G19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="R19" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S19" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="T19" s="41">
-        <v>7.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2719,69 +2716,69 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="45" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D20" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="E20" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="M20" s="40">
         <v>7.0</v>
       </c>
-      <c r="D20" s="40">
-        <v>16.0</v>
-      </c>
-      <c r="E20" s="40">
+      <c r="N20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="39">
         <v>3.0</v>
       </c>
-      <c r="F20" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="39">
-        <v>6.0</v>
-      </c>
       <c r="R20" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S20" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T20" s="41">
         <v>9.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1125</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2798,65 +2795,65 @@
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="D21" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P21" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q21" s="39">
         <v>5.0</v>
       </c>
-      <c r="D21" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="E21" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="M21" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="N21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P21" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q21" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R21" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="S21" s="43">
         <v>0.0</v>
       </c>
       <c r="T21" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>945</v>
+        <v>1065</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2869,32 +2866,32 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="39">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D22" s="40">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E22" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" s="40">
         <v>0.0</v>
       </c>
       <c r="G22" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="40">
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2903,7 +2900,7 @@
         <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M22" s="40">
         <v>2.0</v>
@@ -2918,20 +2915,20 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="R22" s="40">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="S22" s="43">
         <v>2.0</v>
       </c>
       <c r="T22" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>1035</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2948,19 +2945,19 @@
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D23" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="E23" s="40">
         <v>2.0</v>
       </c>
       <c r="F23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="40">
         <v>1.0</v>
@@ -2978,35 +2975,35 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="R23" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S23" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T23" s="41">
         <v>9.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>915</v>
+        <v>975</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3019,32 +3016,32 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>34</v>
+      <c r="B24" s="50" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="39">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="D24" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F24" s="40">
         <v>0.0</v>
       </c>
       <c r="G24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" s="40">
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3056,32 +3053,32 @@
         <v>0.0</v>
       </c>
       <c r="M24" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="40">
         <v>0.0</v>
       </c>
       <c r="O24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R24" s="40">
         <v>1.0</v>
       </c>
       <c r="S24" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T24" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>975</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3097,66 +3094,66 @@
       <c r="A25" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="51" t="s">
-        <v>34</v>
+      <c r="B25" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C25" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
         <v>4.0</v>
       </c>
-      <c r="E25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>3.0</v>
-      </c>
       <c r="R25" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S25" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T25" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>795</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3169,23 +3166,23 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="45" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D26" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E26" s="40">
         <v>0.0</v>
       </c>
       <c r="F26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" s="40">
         <v>0.0</v>
@@ -3194,7 +3191,7 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3203,35 +3200,35 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M26" s="40">
         <v>0.0</v>
       </c>
       <c r="N26" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="39">
         <v>3.0</v>
       </c>
       <c r="R26" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S26" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T26" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>795</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3244,14 +3241,14 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="45" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D27" s="40">
         <v>4.0</v>
@@ -3260,7 +3257,7 @@
         <v>1.0</v>
       </c>
       <c r="F27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" s="40">
         <v>1.0</v>
@@ -3281,10 +3278,10 @@
         <v>1.0</v>
       </c>
       <c r="M27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O27" s="40">
         <v>0.0</v>
@@ -3293,20 +3290,20 @@
         <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R27" s="40">
         <v>1.0</v>
       </c>
       <c r="S27" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>675</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3322,23 +3319,23 @@
       <c r="A28" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>34</v>
+      <c r="B28" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="C28" s="39">
         <v>4.0</v>
       </c>
       <c r="D28" s="40">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E28" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F28" s="40">
         <v>0.0</v>
       </c>
       <c r="G28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" s="40">
         <v>0.0</v>
@@ -3353,13 +3350,13 @@
         <v>0.0</v>
       </c>
       <c r="L28" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="40">
         <v>0.0</v>
@@ -3368,20 +3365,20 @@
         <v>0.0</v>
       </c>
       <c r="Q28" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R28" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="S28" s="43">
         <v>0.0</v>
       </c>
       <c r="T28" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3394,17 +3391,17 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="38" t="s">
-        <v>30</v>
+      <c r="B29" s="50" t="s">
+        <v>32</v>
       </c>
       <c r="C29" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D29" s="40">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="E29" s="40">
         <v>0.0</v>
@@ -3428,13 +3425,13 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M29" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N29" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="40">
         <v>0.0</v>
@@ -3443,10 +3440,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R29" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S29" s="43">
         <v>0.0</v>
@@ -3456,7 +3453,7 @@
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3469,23 +3466,23 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="51" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" s="39">
         <v>3.0</v>
       </c>
       <c r="D30" s="40">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="40">
         <v>0.0</v>
@@ -3494,7 +3491,7 @@
         <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
@@ -3503,13 +3500,13 @@
         <v>0.0</v>
       </c>
       <c r="L30" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O30" s="40">
         <v>0.0</v>
@@ -3518,20 +3515,20 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R30" s="40">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="S30" s="43">
         <v>0.0</v>
       </c>
       <c r="T30" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3544,20 +3541,20 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="45" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C31" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D31" s="40">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="E31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F31" s="40">
         <v>0.0</v>
@@ -3569,7 +3566,7 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3578,13 +3575,13 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="M31" s="40">
         <v>0.0</v>
       </c>
       <c r="N31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O31" s="40">
         <v>0.0</v>
@@ -3593,10 +3590,10 @@
         <v>0.0</v>
       </c>
       <c r="Q31" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R31" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S31" s="43">
         <v>0.0</v>
@@ -3606,7 +3603,7 @@
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3619,17 +3616,17 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="46" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C32" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D32" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E32" s="40">
         <v>0.0</v>
@@ -3653,10 +3650,10 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="40">
         <v>0.0</v>
@@ -3668,20 +3665,20 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R32" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S32" s="43">
         <v>0.0</v>
       </c>
       <c r="T32" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3694,23 +3691,23 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="51" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D33" s="40">
         <v>2.0</v>
       </c>
       <c r="E33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" s="40">
         <v>0.0</v>
@@ -3731,10 +3728,10 @@
         <v>1.0</v>
       </c>
       <c r="M33" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O33" s="40">
         <v>0.0</v>
@@ -3743,20 +3740,20 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R33" s="40">
         <v>1.0</v>
       </c>
       <c r="S33" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T33" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3769,23 +3766,23 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="51" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" s="40">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="E34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" s="40">
         <v>0.0</v>
@@ -3794,7 +3791,7 @@
         <v>0.0</v>
       </c>
       <c r="I34" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J34" s="39">
         <v>0.0</v>
@@ -3803,31 +3800,31 @@
         <v>0.0</v>
       </c>
       <c r="L34" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M34" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="N34" s="40">
         <v>0.0</v>
       </c>
       <c r="O34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P34" s="42">
         <v>0.0</v>
       </c>
       <c r="Q34" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R34" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="S34" s="43">
         <v>0.0</v>
       </c>
       <c r="T34" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
@@ -3844,20 +3841,20 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="37" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C35" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D35" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F35" s="40">
         <v>0.0</v>
@@ -3869,7 +3866,7 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J35" s="39">
         <v>0.0</v>
@@ -3878,31 +3875,31 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M35" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N35" s="40">
         <v>0.0</v>
       </c>
       <c r="O35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P35" s="42">
         <v>0.0</v>
       </c>
       <c r="Q35" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R35" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S35" s="43">
         <v>0.0</v>
       </c>
       <c r="T35" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
@@ -3919,17 +3916,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>30</v>
+      <c r="B36" s="50" t="s">
+        <v>32</v>
       </c>
       <c r="C36" s="39">
         <v>1.0</v>
       </c>
       <c r="D36" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3968,7 +3965,7 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R36" s="40">
         <v>1.0</v>
@@ -3997,14 +3994,14 @@
       <c r="A37" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="51" t="s">
-        <v>34</v>
+      <c r="B37" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="C37" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D37" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="E37" s="40">
         <v>0.0</v>
@@ -4019,7 +4016,7 @@
         <v>0.0</v>
       </c>
       <c r="I37" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J37" s="39">
         <v>0.0</v>
@@ -4028,7 +4025,7 @@
         <v>0.0</v>
       </c>
       <c r="L37" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M37" s="40">
         <v>0.0</v>
@@ -4046,13 +4043,13 @@
         <v>0.0</v>
       </c>
       <c r="R37" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S37" s="43">
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
@@ -4069,11 +4066,11 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="51" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C38" s="39">
         <v>0.0</v>
@@ -4094,7 +4091,7 @@
         <v>0.0</v>
       </c>
       <c r="I38" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J38" s="39">
         <v>0.0</v>
@@ -4102,36 +4099,36 @@
       <c r="K38" s="41">
         <v>0.0</v>
       </c>
-      <c r="L38" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P38" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q38" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="R38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="S38" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="T38" s="41">
-        <v>8.0</v>
+      <c r="L38" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="P38" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q38" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="R38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="S38" s="55">
+        <v>0.0</v>
+      </c>
+      <c r="T38" s="56">
+        <v>9.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4143,90 +4140,16 @@
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
     </row>
-    <row r="39">
-      <c r="A39" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="D39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="E39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K39" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="M39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="N39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="O39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="P39" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q39" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="R39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="S39" s="55">
-        <v>0.0</v>
-      </c>
-      <c r="T39" s="56">
-        <v>8.0</v>
-      </c>
-      <c r="U39" s="44">
-        <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="9"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$4:$U$39">
-    <sortState ref="A4:U39">
-      <sortCondition descending="1" ref="U4:U39"/>
-      <sortCondition ref="A4:A39"/>
-      <sortCondition descending="1" ref="F4:F39"/>
-      <sortCondition descending="1" ref="M4:M39"/>
-      <sortCondition descending="1" ref="G4:G39"/>
-      <sortCondition descending="1" ref="I4:I39"/>
+  <autoFilter ref="$A$4:$U$38">
+    <sortState ref="A4:U38">
+      <sortCondition descending="1" ref="U4:U38"/>
+      <sortCondition descending="1" ref="G4:G38"/>
+      <sortCondition ref="B4:B38"/>
+      <sortCondition ref="A4:A38"/>
+      <sortCondition descending="1" ref="F4:F38"/>
+      <sortCondition descending="1" ref="M4:M38"/>
+      <sortCondition descending="1" ref="I4:I38"/>
     </sortState>
   </autoFilter>
   <mergeCells count="9">
@@ -4240,7 +4163,7 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="U5:U39">
+  <conditionalFormatting sqref="U5:U38">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4252,12 +4175,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B39">
+  <conditionalFormatting sqref="B5:B38">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B39">
+  <conditionalFormatting sqref="B5:B38">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B5))))</formula>
     </cfRule>
@@ -4386,7 +4309,7 @@
     </row>
     <row r="3">
       <c r="A3" s="72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="73" t="s">
         <v>9</v>
@@ -4398,13 +4321,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="G3" s="74" t="s">
         <v>68</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>69</v>
       </c>
       <c r="H3" s="74" t="s">
         <v>19</v>
@@ -4416,19 +4339,19 @@
         <v>22</v>
       </c>
       <c r="K3" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="M3" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="77" t="s">
+      <c r="N3" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="72" t="s">
+      <c r="O3" s="73" t="s">
         <v>73</v>
-      </c>
-      <c r="O3" s="73" t="s">
-        <v>74</v>
       </c>
       <c r="P3" s="73" t="s">
         <v>26</v>
@@ -4450,10 +4373,10 @@
     </row>
     <row r="4">
       <c r="A4" s="78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="80">
         <v>17.0</v>
@@ -4486,7 +4409,7 @@
         <v>0.0</v>
       </c>
       <c r="M4" s="83">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N4" s="82">
         <v>0.0</v>
@@ -4498,16 +4421,16 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R4" s="84">
-        <f t="shared" ref="R4:R8" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>2745</v>
+        <f t="shared" ref="R4:R9" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>2955</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>30</v>
@@ -4537,7 +4460,7 @@
         <v>0.0</v>
       </c>
       <c r="K5" s="82">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L5" s="42">
         <v>1.0</v>
@@ -4555,19 +4478,19 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="83">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R5" s="84">
         <f t="shared" si="1"/>
-        <v>1815</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="82">
         <v>12.0</v>
@@ -4612,37 +4535,37 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R6" s="84">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="86" t="s">
-        <v>78</v>
+      <c r="A7" s="78" t="s">
+        <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="82">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D7" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E7" s="42">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H7" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="81">
         <v>0.0</v>
@@ -4673,33 +4596,33 @@
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>1485</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="87" t="s">
-        <v>79</v>
+      <c r="A8" s="86" t="s">
+        <v>78</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="82">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D8" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E8" s="42">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" s="42">
         <v>0.0</v>
       </c>
       <c r="G8" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H8" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I8" s="81">
         <v>0.0</v>
@@ -4730,84 +4653,84 @@
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>1485</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="82">
+        <v>11.0</v>
+      </c>
+      <c r="D9" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E9" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="F9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q9" s="83">
+        <v>10.0</v>
+      </c>
+      <c r="R9" s="84">
+        <f t="shared" si="1"/>
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="82">
+      <c r="B10" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="82">
         <v>14.0</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D10" s="42">
         <v>6.0</v>
-      </c>
-      <c r="E9" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="F9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q9" s="83">
-        <v>8.0</v>
-      </c>
-      <c r="R9" s="84">
-        <f>C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2</f>
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="78" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="82">
-        <v>11.0</v>
-      </c>
-      <c r="D10" s="42">
-        <v>2.0</v>
       </c>
       <c r="E10" s="42">
         <v>6.0</v>
       </c>
       <c r="F10" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G10" s="42">
         <v>0.0</v>
@@ -4840,82 +4763,82 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="83">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="R10" s="84">
-        <f t="shared" ref="R10:R36" si="2">C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2+I10*$I$2+J10*$J$2</f>
-        <v>1425</v>
+        <f>C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="D11" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="83">
+        <v>9.0</v>
+      </c>
+      <c r="R11" s="84">
+        <f t="shared" ref="R11:R35" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="82">
-        <v>10.0</v>
-      </c>
-      <c r="D11" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="83">
-        <v>8.0</v>
-      </c>
-      <c r="R11" s="84">
-        <f t="shared" si="2"/>
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="86" t="s">
-        <v>83</v>
-      </c>
       <c r="B12" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="82">
         <v>10.0</v>
       </c>
       <c r="D12" s="42">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E12" s="42">
         <v>6.0</v>
@@ -4930,10 +4853,10 @@
         <v>0.0</v>
       </c>
       <c r="I12" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="82">
         <v>1.0</v>
@@ -4951,31 +4874,31 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q12" s="83">
         <v>9.0</v>
       </c>
       <c r="R12" s="84">
         <f t="shared" si="2"/>
-        <v>1395</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="82">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="D13" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E13" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
@@ -4984,16 +4907,16 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="42">
         <v>0.0</v>
@@ -5011,37 +4934,37 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R13" s="84">
         <f t="shared" si="2"/>
-        <v>1320</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85" t="s">
-        <v>85</v>
+      <c r="A14" s="86" t="s">
+        <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C14" s="82">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="D14" s="42">
         <v>7.0</v>
       </c>
       <c r="E14" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="42">
         <v>0.0</v>
       </c>
       <c r="H14" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I14" s="42">
         <v>0.0</v>
@@ -5065,28 +4988,28 @@
         <v>0.0</v>
       </c>
       <c r="P14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q14" s="83">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="R14" s="84">
         <f t="shared" si="2"/>
-        <v>1290</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="82">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="D15" s="42">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E15" s="42">
         <v>4.0</v>
@@ -5122,34 +5045,34 @@
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q15" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R15" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="86" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="79" t="s">
-        <v>34</v>
+      <c r="A16" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>32</v>
       </c>
       <c r="C16" s="82">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D16" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E16" s="42">
         <v>6.0</v>
       </c>
       <c r="F16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="42">
         <v>0.0</v>
@@ -5158,7 +5081,7 @@
         <v>0.0</v>
       </c>
       <c r="I16" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="42">
         <v>0.0</v>
@@ -5182,31 +5105,31 @@
         <v>0.0</v>
       </c>
       <c r="Q16" s="83">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="R16" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="s">
-        <v>88</v>
+      <c r="A17" s="78" t="s">
+        <v>87</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="82">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D17" s="42">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="E17" s="42">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="F17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="42">
         <v>0.0</v>
@@ -5215,7 +5138,7 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5236,43 +5159,43 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R17" s="84">
         <f t="shared" si="2"/>
-        <v>1155</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="88" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>30</v>
+      <c r="A18" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="79" t="s">
+        <v>32</v>
       </c>
       <c r="C18" s="82">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D18" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E18" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F18" s="42">
         <v>0.0</v>
       </c>
       <c r="G18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H18" s="81">
         <v>0.0</v>
       </c>
       <c r="I18" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5281,7 +5204,7 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M18" s="83">
         <v>0.0</v>
@@ -5296,25 +5219,25 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="82">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="D19" s="42">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="E19" s="42">
         <v>4.0</v>
@@ -5353,28 +5276,28 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1005</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="79" t="s">
-        <v>34</v>
+      <c r="A20" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>32</v>
       </c>
       <c r="C20" s="82">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D20" s="42">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E20" s="42">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5407,31 +5330,31 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="83">
         <v>9.0</v>
       </c>
       <c r="R20" s="84">
         <f t="shared" si="2"/>
-        <v>975</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="78" t="s">
-        <v>92</v>
+      <c r="A21" s="88" t="s">
+        <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21" s="82">
         <v>9.0</v>
       </c>
       <c r="D21" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E21" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F21" s="42">
         <v>0.0</v>
@@ -5440,10 +5363,10 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J21" s="42">
         <v>0.0</v>
@@ -5464,28 +5387,28 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q21" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="78" t="s">
-        <v>93</v>
+      <c r="A22" s="88" t="s">
+        <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C22" s="82">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="D22" s="42">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="E22" s="42">
         <v>5.0</v>
@@ -5494,7 +5417,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="81">
         <v>0.0</v>
@@ -5524,31 +5447,31 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R22" s="84">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="78" t="s">
-        <v>94</v>
+      <c r="A23" s="86" t="s">
+        <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="82">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D23" s="42">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E23" s="42">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="42">
         <v>0.0</v>
@@ -5578,22 +5501,22 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>885</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="85" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>30</v>
+      <c r="A24" s="89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="82">
         <v>9.0</v>
@@ -5602,7 +5525,7 @@
         <v>3.0</v>
       </c>
       <c r="E24" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5611,13 +5534,13 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="82">
         <v>0.0</v>
@@ -5635,31 +5558,31 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
-        <v>885</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="s">
-        <v>96</v>
+      <c r="A25" s="78" t="s">
+        <v>95</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25" s="82">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="D25" s="42">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E25" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F25" s="42">
         <v>0.0</v>
@@ -5692,28 +5615,28 @@
         <v>0.0</v>
       </c>
       <c r="P25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q25" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R25" s="84">
         <f t="shared" si="2"/>
-        <v>870</v>
+        <v>990</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="86" t="s">
-        <v>97</v>
+      <c r="A26" s="88" t="s">
+        <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="82">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D26" s="42">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E26" s="42">
         <v>4.0</v>
@@ -5756,24 +5679,24 @@
       </c>
       <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>735</v>
+        <v>990</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" s="82">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D27" s="42">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E27" s="42">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5806,40 +5729,40 @@
         <v>0.0</v>
       </c>
       <c r="P27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q27" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R27" s="84">
         <f t="shared" si="2"/>
-        <v>660</v>
+        <v>765</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="s">
-        <v>99</v>
+      <c r="A28" s="82" t="s">
+        <v>98</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C28" s="82">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D28" s="42">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E28" s="42">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F28" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" s="42">
         <v>0.0</v>
       </c>
       <c r="H28" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28" s="42">
         <v>0.0</v>
@@ -5863,40 +5786,40 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q28" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
-        <v>615</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="82" t="s">
-        <v>100</v>
+      <c r="A29" s="78" t="s">
+        <v>99</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" s="82">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="D29" s="42">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="E29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="42">
         <v>0.0</v>
       </c>
       <c r="H29" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I29" s="42">
         <v>0.0</v>
@@ -5920,22 +5843,22 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q29" s="83">
         <v>9.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>405</v>
+        <v>615</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B30" s="79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" s="82">
         <v>5.0</v>
@@ -5980,28 +5903,28 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R30" s="84">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="82">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D31" s="42">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="E31" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -6034,31 +5957,31 @@
         <v>0.0</v>
       </c>
       <c r="P31" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q31" s="83">
         <v>8.0</v>
       </c>
       <c r="R31" s="84">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="88" t="s">
-        <v>103</v>
+      <c r="A32" s="78" t="s">
+        <v>102</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C32" s="82">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D32" s="42">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="E32" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F32" s="42">
         <v>0.0</v>
@@ -6098,24 +6021,24 @@
       </c>
       <c r="R32" s="84">
         <f t="shared" si="2"/>
-        <v>345</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="91" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" s="92">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="D33" s="91">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="E33" s="91">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F33" s="91">
         <v>0.0</v>
@@ -6124,7 +6047,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="I33" s="91">
         <v>0.0</v>
@@ -6155,24 +6078,24 @@
       </c>
       <c r="R33" s="84">
         <f t="shared" si="2"/>
-        <v>285</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="90" t="s">
-        <v>105</v>
+      <c r="A34" s="94" t="s">
+        <v>104</v>
       </c>
       <c r="B34" s="91" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" s="92">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D34" s="91">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E34" s="91">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="91">
         <v>0.0</v>
@@ -6181,7 +6104,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34" s="91">
         <v>0.0</v>
@@ -6212,128 +6135,71 @@
       </c>
       <c r="R34" s="84">
         <f t="shared" si="2"/>
-        <v>270</v>
-      </c>
-    </row>
-    <row r="35" hidden="1">
-      <c r="A35" s="90" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="91" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="93">
-        <v>7.0</v>
-      </c>
-      <c r="R35" s="84">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="99">
+        <v>8.0</v>
+      </c>
+      <c r="R35" s="100">
         <f t="shared" si="2"/>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="95" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="D36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="G36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q36" s="98">
-        <v>7.0</v>
-      </c>
-      <c r="R36" s="99">
-        <f t="shared" si="2"/>
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$3:$R$36">
-    <sortState ref="A3:R36">
-      <sortCondition descending="1" ref="R3:R36"/>
-      <sortCondition ref="A3:A36"/>
+  <autoFilter ref="$A$3:$R$35">
+    <sortState ref="A3:R35">
+      <sortCondition descending="1" ref="R3:R35"/>
+      <sortCondition ref="A3:A35"/>
     </sortState>
   </autoFilter>
   <mergeCells count="5">
@@ -6343,7 +6209,7 @@
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="R4:R36">
+  <conditionalFormatting sqref="R4:R35">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6355,12 +6221,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B36">
+  <conditionalFormatting sqref="B4:B35">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B36">
+  <conditionalFormatting sqref="B4:B35">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B4))))</formula>
     </cfRule>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -7,15 +7,15 @@
     <sheet state="visible" name="Pitchers" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$38</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$35</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$39</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$36</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
   <si>
     <t>INCENTIVOS DSL 2026</t>
   </si>
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/21/2026</t>
+    <t>Actualización: 6/18/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -104,63 +104,66 @@
     <t>$RD</t>
   </si>
   <si>
+    <t>Rodriguez, Alex</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Mateo, Cesar</t>
+  </si>
+  <si>
     <t>Celesten, Yeisy</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Rodriguez, Alex</t>
-  </si>
-  <si>
-    <t>Mateo, Cesar</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Diaz, David</t>
+  </si>
+  <si>
+    <t>Rosario, Elian</t>
+  </si>
+  <si>
+    <t>Ramirez, Santiago</t>
+  </si>
+  <si>
     <t>Cavero, Braulio</t>
   </si>
   <si>
-    <t>Rosario, Elian</t>
-  </si>
-  <si>
-    <t>Diaz, David</t>
-  </si>
-  <si>
     <t>Castillo, Wesly</t>
   </si>
   <si>
+    <t>Valdes, Abel</t>
+  </si>
+  <si>
+    <t>Benitez, Frainker</t>
+  </si>
+  <si>
+    <t>Abreu, Ariel</t>
+  </si>
+  <si>
+    <t>Ramirez, Manni</t>
+  </si>
+  <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
+    <t>Jaquez, Luis</t>
+  </si>
+  <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
-    <t>Abreu, Ariel</t>
-  </si>
-  <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
-    <t>Ramirez, Santiago</t>
-  </si>
-  <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
-    <t>Jaquez, Luis</t>
-  </si>
-  <si>
-    <t>Valdes, Abel</t>
-  </si>
-  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
@@ -173,30 +176,30 @@
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Chavez, Jesus</t>
+  </si>
+  <si>
+    <t>Pereira, Raul</t>
+  </si>
+  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
+    <t>Genao, Jhostin</t>
+  </si>
+  <si>
+    <t>Ortiz Jr, David</t>
+  </si>
+  <si>
+    <t>Colina, Felix</t>
+  </si>
+  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Chavez, Jesus</t>
-  </si>
-  <si>
-    <t>Pereira, Raul</t>
-  </si>
-  <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
-    <t>Genao, Jhostin</t>
-  </si>
-  <si>
-    <t>Ortiz Jr, David</t>
-  </si>
-  <si>
-    <t>Colina, Felix</t>
-  </si>
-  <si>
     <t>Montero, Darling</t>
   </si>
   <si>
@@ -248,88 +251,91 @@
     <t>Gamez, Manuel</t>
   </si>
   <si>
+    <t>Encarnacion, Jefferson</t>
+  </si>
+  <si>
+    <t>Lara, Carlos</t>
+  </si>
+  <si>
+    <t>Santos, Aneudy</t>
+  </si>
+  <si>
     <t>Medina, Juan</t>
   </si>
   <si>
-    <t>Encarnacion, Jefferson</t>
-  </si>
-  <si>
-    <t>Lara, Carlos</t>
-  </si>
-  <si>
-    <t>Santos, Aneudy</t>
+    <t>Pineda, Frandel</t>
+  </si>
+  <si>
+    <t>Dolsi, Frederik</t>
+  </si>
+  <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
+    <t>Fukuda, Masahiro</t>
+  </si>
+  <si>
+    <t>Pena, Dariel</t>
+  </si>
+  <si>
+    <t>Gomez, Manuel</t>
+  </si>
+  <si>
+    <t>Alcantara, Jostin</t>
+  </si>
+  <si>
+    <t>Cordero, Albert</t>
+  </si>
+  <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
+    <t>Figuereo, Breyner</t>
+  </si>
+  <si>
+    <t>Acosta, Isaac</t>
+  </si>
+  <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
+    <t>Castillo, Albert</t>
   </si>
   <si>
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Pineda, Frandel</t>
-  </si>
-  <si>
-    <t>Dolsi, Frederik</t>
-  </si>
-  <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
-    <t>Pena, Dariel</t>
-  </si>
-  <si>
-    <t>Fukuda, Masahiro</t>
-  </si>
-  <si>
-    <t>Castillo, Albert</t>
-  </si>
-  <si>
-    <t>Gomez, Manuel</t>
-  </si>
-  <si>
-    <t>Fernandez, Jehiber</t>
-  </si>
-  <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
-    <t>Alcantara, Jostin</t>
-  </si>
-  <si>
-    <t>Cordero, Albert</t>
+    <t>Ballesteros, Jean</t>
   </si>
   <si>
     <t>Lamu, Alex</t>
   </si>
   <si>
-    <t>Figuereo, Breyner</t>
-  </si>
-  <si>
-    <t>Ramos, Daniel</t>
-  </si>
-  <si>
-    <t>Ballesteros, Jean</t>
-  </si>
-  <si>
     <t>Perez, Juanangel</t>
   </si>
   <si>
+    <t>Peralta, Eddy</t>
+  </si>
+  <si>
     <t>Liriano, Edgar</t>
   </si>
   <si>
-    <t>Peralta, Eddy</t>
-  </si>
-  <si>
     <t>De Jesus, Yunier</t>
   </si>
   <si>
+    <t>Fernandez, Harley</t>
+  </si>
+  <si>
+    <t>Figuereo, Enmanuel</t>
+  </si>
+  <si>
     <t>Bautista, Jeyson</t>
   </si>
   <si>
-    <t>Fernandez, Harley</t>
-  </si>
-  <si>
     <t>Medina, Ruben</t>
   </si>
   <si>
-    <t>Figuereo, Enmanuel</t>
+    <t>Cordova, Jose</t>
   </si>
   <si>
     <t>Gonzalez, Nestor</t>
@@ -382,7 +388,7 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="&quot;Tw Cen MT&quot;"/>
     </font>
     <font>
@@ -393,7 +399,7 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="&quot;Tw Cen MT&quot;"/>
     </font>
     <font>
@@ -813,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -927,26 +933,26 @@
     <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1024,43 +1030,43 @@
     <xf borderId="11" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="33" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1072,10 +1078,7 @@
     <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="35" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="35" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1516,7 +1519,7 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
     </row>
-    <row r="4">
+    <row r="4" ht="31.5" customHeight="1">
       <c r="A4" s="28" t="s">
         <v>8</v>
       </c>
@@ -1598,16 +1601,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="D5" s="40">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E5" s="40">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" s="40">
         <v>3.0</v>
@@ -1616,22 +1619,22 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J5" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K5" s="41">
         <v>0.0</v>
       </c>
       <c r="L5" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M5" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="N5" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O5" s="40">
         <v>0.0</v>
@@ -1640,20 +1643,20 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="R5" s="40">
         <v>5.0</v>
       </c>
       <c r="S5" s="43">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="T5" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U5" s="44">
-        <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>2415</v>
+        <f t="shared" ref="U5:U39" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
+        <v>2040</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1670,65 +1673,65 @@
         <v>31</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="D6" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="E6" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="F6" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="41">
+        <v>16.0</v>
+      </c>
+      <c r="J6" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="M6" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N6" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R6" s="40">
         <v>4.0</v>
       </c>
-      <c r="E6" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="F6" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J6" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L6" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R6" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S6" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T6" s="41">
         <v>9.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>2295</v>
+        <v>1980</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1741,23 +1744,23 @@
       <c r="AD6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="s">
-        <v>33</v>
+      <c r="A7" s="45" t="s">
+        <v>32</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="39">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="D7" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E7" s="40">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F7" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G7" s="40">
         <v>3.0</v>
@@ -1766,22 +1769,22 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="39">
         <v>3.0</v>
       </c>
-      <c r="J7" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="K7" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="39">
-        <v>2.0</v>
-      </c>
       <c r="M7" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="N7" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O7" s="40">
         <v>0.0</v>
@@ -1796,14 +1799,14 @@
         <v>5.0</v>
       </c>
       <c r="S7" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T7" s="41">
         <v>9.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>2130</v>
+        <v>1830</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1816,69 +1819,69 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>30</v>
-      </c>
       <c r="C8" s="39">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="D8" s="40">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E8" s="40">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L8" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="39">
         <v>3.0</v>
       </c>
-      <c r="G8" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>16.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="39">
+      <c r="R8" s="40">
         <v>5.0</v>
       </c>
-      <c r="M8" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N8" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="O8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="R8" s="40">
-        <v>4.0</v>
-      </c>
       <c r="S8" s="43">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="T8" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>2070</v>
+        <v>1800</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1891,23 +1894,23 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="46" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="39">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="D9" s="40">
         <v>10.0</v>
       </c>
       <c r="E9" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G9" s="40">
         <v>2.0</v>
@@ -1928,7 +1931,7 @@
         <v>3.0</v>
       </c>
       <c r="M9" s="40">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="N9" s="40">
         <v>0.0</v>
@@ -1940,20 +1943,20 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R9" s="40">
         <v>4.0</v>
       </c>
       <c r="S9" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T9" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>1980</v>
+        <v>1620</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1966,23 +1969,23 @@
       <c r="AD9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="45" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="47">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="48">
         <v>15.0</v>
       </c>
       <c r="E10" s="48">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="F10" s="48">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G10" s="48">
         <v>2.0</v>
@@ -2009,26 +2012,26 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P10" s="42">
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="R10" s="40">
         <v>6.0</v>
       </c>
       <c r="S10" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T10" s="41">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>1305</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2041,47 +2044,47 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="45" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="D11" s="40">
         <v>8.0</v>
       </c>
-      <c r="D11" s="40">
+      <c r="E11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J11" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M11" s="40">
         <v>4.0</v>
       </c>
-      <c r="E11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="H11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N11" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O11" s="40">
         <v>0.0</v>
@@ -2093,17 +2096,17 @@
         <v>6.0</v>
       </c>
       <c r="R11" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S11" s="43">
         <v>2.0</v>
       </c>
       <c r="T11" s="41">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>1590</v>
+        <v>1305</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2116,14 +2119,14 @@
       <c r="AD11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="45" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="D12" s="40">
         <v>8.0</v>
@@ -2132,10 +2135,10 @@
         <v>3.0</v>
       </c>
       <c r="F12" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G12" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H12" s="40">
         <v>0.0</v>
@@ -2153,7 +2156,7 @@
         <v>3.0</v>
       </c>
       <c r="M12" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N12" s="40">
         <v>0.0</v>
@@ -2165,20 +2168,20 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="R12" s="40">
         <v>4.0</v>
       </c>
       <c r="S12" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T12" s="41">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>1545</v>
+        <v>1200</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2191,23 +2194,23 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="50" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="39">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="D13" s="40">
         <v>8.0</v>
       </c>
       <c r="E13" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F13" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" s="40">
         <v>2.0</v>
@@ -2216,7 +2219,7 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J13" s="39">
         <v>0.0</v>
@@ -2225,10 +2228,10 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="N13" s="40">
         <v>2.0</v>
@@ -2240,7 +2243,7 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="R13" s="40">
         <v>4.0</v>
@@ -2249,11 +2252,11 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="41">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1110</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2270,31 +2273,31 @@
         <v>40</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D14" s="40">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E14" s="40">
         <v>3.0</v>
       </c>
       <c r="F14" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G14" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H14" s="40">
         <v>0.0</v>
       </c>
       <c r="I14" s="41">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="J14" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K14" s="41">
         <v>0.0</v>
@@ -2318,7 +2321,7 @@
         <v>4.0</v>
       </c>
       <c r="R14" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S14" s="43">
         <v>1.0</v>
@@ -2328,7 +2331,7 @@
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1095</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2341,32 +2344,32 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="50" t="s">
-        <v>30</v>
+      <c r="B15" s="38" t="s">
+        <v>34</v>
       </c>
       <c r="C15" s="39">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="D15" s="40">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E15" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F15" s="40">
         <v>0.0</v>
       </c>
       <c r="G15" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2375,10 +2378,10 @@
         <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M15" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="40">
         <v>0.0</v>
@@ -2393,17 +2396,17 @@
         <v>3.0</v>
       </c>
       <c r="R15" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S15" s="43">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="T15" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1425</v>
+        <v>1065</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2416,26 +2419,26 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="37" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" s="39">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="D16" s="40">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E16" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F16" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
@@ -2447,38 +2450,38 @@
         <v>0.0</v>
       </c>
       <c r="K16" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L16" s="39">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="M16" s="40">
         <v>0.0</v>
       </c>
       <c r="N16" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O16" s="40">
         <v>1.0</v>
       </c>
       <c r="P16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q16" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R16" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S16" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T16" s="41">
         <v>9.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1035</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2491,20 +2494,20 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="50" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="39">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D17" s="40">
         <v>5.0</v>
       </c>
       <c r="E17" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F17" s="40">
         <v>0.0</v>
@@ -2540,20 +2543,20 @@
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R17" s="40">
         <v>3.0</v>
       </c>
       <c r="S17" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T17" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1035</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2566,26 +2569,26 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="46" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C18" s="39">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="D18" s="40">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E18" s="40">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H18" s="40">
         <v>0.0</v>
@@ -2600,35 +2603,35 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="39">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="M18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N18" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O18" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P18" s="42">
         <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="R18" s="40">
         <v>4.0</v>
       </c>
       <c r="S18" s="43">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="T18" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1005</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2640,70 +2643,70 @@
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" hidden="1">
       <c r="A19" s="46" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C19" s="39">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="D19" s="40">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E19" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F19" s="40">
         <v>4.0</v>
       </c>
-      <c r="F19" s="40">
+      <c r="G19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R19" s="40">
         <v>3.0</v>
       </c>
-      <c r="G19" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="R19" s="40">
-        <v>4.0</v>
-      </c>
       <c r="S19" s="43">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="T19" s="41">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2716,69 +2719,69 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="37" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D20" s="40">
+        <v>16.0</v>
+      </c>
+      <c r="E20" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F20" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="39">
         <v>6.0</v>
       </c>
-      <c r="E20" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="39">
-        <v>3.0</v>
-      </c>
       <c r="R20" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S20" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T20" s="41">
         <v>9.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1125</v>
+        <v>990</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2795,19 +2798,19 @@
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C21" s="39">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="D21" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E21" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F21" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" s="40">
         <v>0.0</v>
@@ -2816,7 +2819,7 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J21" s="39">
         <v>0.0</v>
@@ -2825,35 +2828,35 @@
         <v>0.0</v>
       </c>
       <c r="L21" s="39">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="M21" s="40">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="N21" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O21" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q21" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R21" s="40">
         <v>5.0</v>
       </c>
-      <c r="R21" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S21" s="43">
         <v>0.0</v>
       </c>
       <c r="T21" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>945</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2866,69 +2869,69 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="51" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="D22" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="E22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M22" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q22" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="R22" s="40">
         <v>5.0</v>
       </c>
-      <c r="D22" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="E22" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="F22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M22" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q22" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R22" s="40">
-        <v>3.0</v>
-      </c>
       <c r="S22" s="43">
         <v>2.0</v>
       </c>
       <c r="T22" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>930</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2945,19 +2948,19 @@
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D23" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E23" s="40">
         <v>2.0</v>
       </c>
       <c r="F23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="40">
         <v>1.0</v>
@@ -2975,35 +2978,35 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M23" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="R23" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S23" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T23" s="41">
         <v>9.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>975</v>
+        <v>915</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3016,32 +3019,32 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="50" t="s">
-        <v>32</v>
+      <c r="B24" s="38" t="s">
+        <v>34</v>
       </c>
       <c r="C24" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="D24" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="E24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F24" s="40">
         <v>0.0</v>
       </c>
       <c r="G24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" s="40">
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3053,32 +3056,32 @@
         <v>0.0</v>
       </c>
       <c r="M24" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="N24" s="40">
         <v>0.0</v>
       </c>
       <c r="O24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="R24" s="40">
         <v>1.0</v>
       </c>
       <c r="S24" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T24" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>975</v>
+        <v>810</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3094,30 +3097,30 @@
       <c r="A25" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="38" t="s">
-        <v>30</v>
+      <c r="B25" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C25" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D25" s="40">
         <v>4.0</v>
       </c>
-      <c r="D25" s="40">
+      <c r="E25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
         <v>3.0</v>
       </c>
-      <c r="E25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>1.0</v>
-      </c>
       <c r="J25" s="39">
         <v>0.0</v>
       </c>
@@ -3140,20 +3143,20 @@
         <v>0.0</v>
       </c>
       <c r="Q25" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R25" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S25" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T25" s="41">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>735</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3166,23 +3169,23 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="37" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D26" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E26" s="40">
         <v>0.0</v>
       </c>
       <c r="F26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="40">
         <v>0.0</v>
@@ -3191,7 +3194,7 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3200,35 +3203,35 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M26" s="40">
         <v>0.0</v>
       </c>
       <c r="N26" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q26" s="39">
         <v>3.0</v>
       </c>
       <c r="R26" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="S26" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T26" s="41">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>630</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3241,14 +3244,14 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="46" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D27" s="40">
         <v>4.0</v>
@@ -3257,7 +3260,7 @@
         <v>1.0</v>
       </c>
       <c r="F27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" s="40">
         <v>1.0</v>
@@ -3278,10 +3281,10 @@
         <v>1.0</v>
       </c>
       <c r="M27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="40">
         <v>0.0</v>
@@ -3290,20 +3293,20 @@
         <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R27" s="40">
         <v>1.0</v>
       </c>
       <c r="S27" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T27" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>675</v>
+        <v>570</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3319,23 +3322,23 @@
       <c r="A28" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>32</v>
+      <c r="B28" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C28" s="39">
         <v>4.0</v>
       </c>
       <c r="D28" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E28" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" s="40">
         <v>0.0</v>
       </c>
       <c r="G28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H28" s="40">
         <v>0.0</v>
@@ -3350,13 +3353,13 @@
         <v>0.0</v>
       </c>
       <c r="L28" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M28" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O28" s="40">
         <v>0.0</v>
@@ -3365,20 +3368,20 @@
         <v>0.0</v>
       </c>
       <c r="Q28" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R28" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="S28" s="43">
         <v>0.0</v>
       </c>
       <c r="T28" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>570</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3391,17 +3394,17 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="50" t="s">
-        <v>32</v>
+      <c r="B29" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C29" s="39">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D29" s="40">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="E29" s="40">
         <v>0.0</v>
@@ -3425,13 +3428,13 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M29" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O29" s="40">
         <v>0.0</v>
@@ -3440,10 +3443,10 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R29" s="40">
         <v>3.0</v>
-      </c>
-      <c r="R29" s="40">
-        <v>4.0</v>
       </c>
       <c r="S29" s="43">
         <v>0.0</v>
@@ -3453,7 +3456,7 @@
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>525</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3466,23 +3469,23 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="46" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="39">
         <v>3.0</v>
       </c>
       <c r="D30" s="40">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="E30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" s="40">
         <v>0.0</v>
@@ -3491,7 +3494,7 @@
         <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
@@ -3500,13 +3503,13 @@
         <v>0.0</v>
       </c>
       <c r="L30" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="40">
         <v>0.0</v>
@@ -3515,20 +3518,20 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R30" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="S30" s="43">
         <v>0.0</v>
       </c>
       <c r="T30" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3541,20 +3544,20 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="37" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D31" s="40">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="E31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F31" s="40">
         <v>0.0</v>
@@ -3566,7 +3569,7 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3575,13 +3578,13 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M31" s="40">
         <v>0.0</v>
       </c>
       <c r="N31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="40">
         <v>0.0</v>
@@ -3590,10 +3593,10 @@
         <v>0.0</v>
       </c>
       <c r="Q31" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R31" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="S31" s="43">
         <v>0.0</v>
@@ -3603,7 +3606,7 @@
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3616,17 +3619,17 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="50" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C32" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D32" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E32" s="40">
         <v>0.0</v>
@@ -3650,10 +3653,10 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N32" s="40">
         <v>0.0</v>
@@ -3665,20 +3668,20 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R32" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S32" s="43">
         <v>0.0</v>
       </c>
       <c r="T32" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>375</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3691,23 +3694,23 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="46" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D33" s="40">
         <v>2.0</v>
       </c>
       <c r="E33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G33" s="40">
         <v>0.0</v>
@@ -3728,10 +3731,10 @@
         <v>1.0</v>
       </c>
       <c r="M33" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O33" s="40">
         <v>0.0</v>
@@ -3740,20 +3743,20 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="R33" s="40">
         <v>1.0</v>
       </c>
       <c r="S33" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T33" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3766,23 +3769,23 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="50" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D34" s="40">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="E34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="40">
         <v>0.0</v>
@@ -3791,7 +3794,7 @@
         <v>0.0</v>
       </c>
       <c r="I34" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J34" s="39">
         <v>0.0</v>
@@ -3800,31 +3803,31 @@
         <v>0.0</v>
       </c>
       <c r="L34" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M34" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="N34" s="40">
         <v>0.0</v>
       </c>
       <c r="O34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P34" s="42">
         <v>0.0</v>
       </c>
       <c r="Q34" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R34" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="S34" s="43">
         <v>0.0</v>
       </c>
       <c r="T34" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
@@ -3841,20 +3844,20 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="50" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C35" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D35" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F35" s="40">
         <v>0.0</v>
@@ -3866,7 +3869,7 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J35" s="39">
         <v>0.0</v>
@@ -3875,31 +3878,31 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N35" s="40">
         <v>0.0</v>
       </c>
       <c r="O35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P35" s="42">
         <v>0.0</v>
       </c>
       <c r="Q35" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R35" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S35" s="43">
         <v>0.0</v>
       </c>
       <c r="T35" s="41">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
@@ -3916,17 +3919,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="50" t="s">
-        <v>32</v>
+      <c r="B36" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C36" s="39">
         <v>1.0</v>
       </c>
       <c r="D36" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3965,7 +3968,7 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R36" s="40">
         <v>1.0</v>
@@ -3994,14 +3997,14 @@
       <c r="A37" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="38" t="s">
-        <v>32</v>
+      <c r="B37" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C37" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D37" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="E37" s="40">
         <v>0.0</v>
@@ -4016,7 +4019,7 @@
         <v>0.0</v>
       </c>
       <c r="I37" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J37" s="39">
         <v>0.0</v>
@@ -4025,7 +4028,7 @@
         <v>0.0</v>
       </c>
       <c r="L37" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M37" s="40">
         <v>0.0</v>
@@ -4043,13 +4046,13 @@
         <v>0.0</v>
       </c>
       <c r="R37" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S37" s="43">
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
@@ -4066,11 +4069,11 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="46" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C38" s="39">
         <v>0.0</v>
@@ -4091,7 +4094,7 @@
         <v>0.0</v>
       </c>
       <c r="I38" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J38" s="39">
         <v>0.0</v>
@@ -4099,36 +4102,36 @@
       <c r="K38" s="41">
         <v>0.0</v>
       </c>
-      <c r="L38" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="P38" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q38" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="R38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="S38" s="55">
-        <v>0.0</v>
-      </c>
-      <c r="T38" s="56">
-        <v>9.0</v>
+      <c r="L38" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M38" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P38" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q38" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="R38" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="S38" s="43">
+        <v>0.0</v>
+      </c>
+      <c r="T38" s="41">
+        <v>8.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4140,16 +4143,90 @@
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
     </row>
+    <row r="39">
+      <c r="A39" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="D39" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="E39" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F39" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G39" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H39" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J39" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K39" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="P39" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q39" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="R39" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="S39" s="55">
+        <v>0.0</v>
+      </c>
+      <c r="T39" s="56">
+        <v>8.0</v>
+      </c>
+      <c r="U39" s="44">
+        <f t="shared" si="1"/>
+        <v>240</v>
+      </c>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$4:$U$38">
-    <sortState ref="A4:U38">
-      <sortCondition descending="1" ref="U4:U38"/>
-      <sortCondition descending="1" ref="G4:G38"/>
-      <sortCondition ref="B4:B38"/>
-      <sortCondition ref="A4:A38"/>
-      <sortCondition descending="1" ref="F4:F38"/>
-      <sortCondition descending="1" ref="M4:M38"/>
-      <sortCondition descending="1" ref="I4:I38"/>
+  <autoFilter ref="$A$4:$U$39">
+    <sortState ref="A4:U39">
+      <sortCondition descending="1" ref="U4:U39"/>
+      <sortCondition ref="A4:A39"/>
+      <sortCondition descending="1" ref="F4:F39"/>
+      <sortCondition descending="1" ref="M4:M39"/>
+      <sortCondition descending="1" ref="G4:G39"/>
+      <sortCondition descending="1" ref="I4:I39"/>
     </sortState>
   </autoFilter>
   <mergeCells count="9">
@@ -4163,7 +4240,7 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="U5:U38">
+  <conditionalFormatting sqref="U5:U39">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4175,12 +4252,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B38">
+  <conditionalFormatting sqref="B5:B39">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B38">
+  <conditionalFormatting sqref="B5:B39">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B5))))</formula>
     </cfRule>
@@ -4309,7 +4386,7 @@
     </row>
     <row r="3">
       <c r="A3" s="72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="73" t="s">
         <v>9</v>
@@ -4321,13 +4398,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3" s="74" t="s">
         <v>19</v>
@@ -4339,19 +4416,19 @@
         <v>22</v>
       </c>
       <c r="K3" s="72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L3" s="73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M3" s="77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N3" s="72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O3" s="73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P3" s="73" t="s">
         <v>26</v>
@@ -4373,10 +4450,10 @@
     </row>
     <row r="4">
       <c r="A4" s="78" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="80">
         <v>17.0</v>
@@ -4409,7 +4486,7 @@
         <v>0.0</v>
       </c>
       <c r="M4" s="83">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N4" s="82">
         <v>0.0</v>
@@ -4421,16 +4498,16 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="83">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="R4" s="84">
-        <f t="shared" ref="R4:R9" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>2955</v>
+        <f t="shared" ref="R4:R8" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>2745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="85" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>30</v>
@@ -4460,7 +4537,7 @@
         <v>0.0</v>
       </c>
       <c r="K5" s="82">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L5" s="42">
         <v>1.0</v>
@@ -4478,19 +4555,19 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="83">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R5" s="84">
         <f t="shared" si="1"/>
-        <v>2025</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="78" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="82">
         <v>12.0</v>
@@ -4535,37 +4612,37 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="83">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="R6" s="84">
         <f t="shared" si="1"/>
-        <v>1815</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="s">
-        <v>77</v>
+      <c r="A7" s="86" t="s">
+        <v>78</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="82">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="D7" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E7" s="42">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G7" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I7" s="81">
         <v>0.0</v>
@@ -4596,33 +4673,33 @@
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>1680</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="s">
-        <v>78</v>
+      <c r="A8" s="87" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="82">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="D8" s="42">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E8" s="42">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F8" s="42">
         <v>0.0</v>
       </c>
       <c r="G8" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I8" s="81">
         <v>0.0</v>
@@ -4653,84 +4730,84 @@
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>1515</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="87" t="s">
-        <v>79</v>
+      <c r="A9" s="88" t="s">
+        <v>80</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C9" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="D9" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E9" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="F9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q9" s="83">
+        <v>8.0</v>
+      </c>
+      <c r="R9" s="84">
+        <f>C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2</f>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="82">
         <v>11.0</v>
       </c>
-      <c r="D9" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="E9" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="F9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q9" s="83">
-        <v>10.0</v>
-      </c>
-      <c r="R9" s="84">
-        <f t="shared" si="1"/>
-        <v>1515</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="88" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="82">
-        <v>14.0</v>
-      </c>
       <c r="D10" s="42">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="E10" s="42">
         <v>6.0</v>
       </c>
       <c r="F10" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" s="42">
         <v>0.0</v>
@@ -4763,82 +4840,82 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="83">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="R10" s="84">
-        <f>C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2</f>
-        <v>1500</v>
+        <f t="shared" ref="R10:R36" si="2">C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2+I10*$I$2+J10*$J$2</f>
+        <v>1425</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="85" t="s">
-        <v>81</v>
+      <c r="A11" s="78" t="s">
+        <v>82</v>
       </c>
       <c r="B11" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="82">
+        <v>10.0</v>
+      </c>
+      <c r="D11" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="83">
+        <v>8.0</v>
+      </c>
+      <c r="R11" s="84">
+        <f t="shared" si="2"/>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="42" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="82">
-        <v>14.0</v>
-      </c>
-      <c r="D11" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q11" s="83">
-        <v>9.0</v>
-      </c>
-      <c r="R11" s="84">
-        <f t="shared" ref="R11:R35" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="78" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="82">
         <v>10.0</v>
       </c>
       <c r="D12" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E12" s="42">
         <v>6.0</v>
@@ -4853,10 +4930,10 @@
         <v>0.0</v>
       </c>
       <c r="I12" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K12" s="82">
         <v>1.0</v>
@@ -4874,31 +4951,31 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q12" s="83">
         <v>9.0</v>
       </c>
       <c r="R12" s="84">
         <f t="shared" si="2"/>
-        <v>1440</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="82">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D13" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E13" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
@@ -4907,16 +4984,16 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L13" s="42">
         <v>0.0</v>
@@ -4934,37 +5011,37 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="83">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="R13" s="84">
         <f t="shared" si="2"/>
-        <v>1425</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="86" t="s">
-        <v>84</v>
+      <c r="A14" s="85" t="s">
+        <v>85</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C14" s="82">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D14" s="42">
         <v>7.0</v>
       </c>
       <c r="E14" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="42">
         <v>0.0</v>
       </c>
       <c r="H14" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I14" s="42">
         <v>0.0</v>
@@ -4988,28 +5065,28 @@
         <v>0.0</v>
       </c>
       <c r="P14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q14" s="83">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="R14" s="84">
         <f t="shared" si="2"/>
-        <v>1350</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="89" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="82">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="D15" s="42">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E15" s="42">
         <v>4.0</v>
@@ -5045,34 +5122,34 @@
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q15" s="83">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="R15" s="84">
         <f t="shared" si="2"/>
-        <v>1335</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="85" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>32</v>
+      <c r="A16" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>34</v>
       </c>
       <c r="C16" s="82">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="D16" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E16" s="42">
         <v>6.0</v>
       </c>
       <c r="F16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="42">
         <v>0.0</v>
@@ -5081,7 +5158,7 @@
         <v>0.0</v>
       </c>
       <c r="I16" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J16" s="42">
         <v>0.0</v>
@@ -5105,31 +5182,31 @@
         <v>0.0</v>
       </c>
       <c r="Q16" s="83">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="R16" s="84">
         <f t="shared" si="2"/>
-        <v>1320</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="78" t="s">
-        <v>87</v>
+      <c r="A17" s="88" t="s">
+        <v>88</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="82">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="D17" s="42">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E17" s="42">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" s="42">
         <v>0.0</v>
@@ -5138,7 +5215,7 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5159,43 +5236,43 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="R17" s="84">
         <f t="shared" si="2"/>
-        <v>1305</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="86" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="79" t="s">
-        <v>32</v>
+      <c r="A18" s="88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C18" s="82">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="D18" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E18" s="42">
         <v>5.0</v>
       </c>
-      <c r="E18" s="42">
-        <v>6.0</v>
-      </c>
       <c r="F18" s="42">
         <v>0.0</v>
       </c>
       <c r="G18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H18" s="81">
         <v>0.0</v>
       </c>
       <c r="I18" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5204,7 +5281,7 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M18" s="83">
         <v>0.0</v>
@@ -5219,25 +5296,25 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="83">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1425</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="86" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="82">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="D19" s="42">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="E19" s="42">
         <v>4.0</v>
@@ -5276,28 +5353,28 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="83">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>32</v>
+      <c r="A20" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="79" t="s">
+        <v>34</v>
       </c>
       <c r="C20" s="82">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="D20" s="42">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="E20" s="42">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5330,31 +5407,31 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q20" s="83">
         <v>9.0</v>
       </c>
       <c r="R20" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>975</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="88" t="s">
-        <v>91</v>
+      <c r="A21" s="78" t="s">
+        <v>92</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C21" s="82">
         <v>9.0</v>
       </c>
       <c r="D21" s="42">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="E21" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="42">
         <v>0.0</v>
@@ -5363,10 +5440,10 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I21" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J21" s="42">
         <v>0.0</v>
@@ -5387,28 +5464,28 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q21" s="83">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>1185</v>
+        <v>960</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="88" t="s">
-        <v>92</v>
+      <c r="A22" s="78" t="s">
+        <v>93</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C22" s="82">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="D22" s="42">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="E22" s="42">
         <v>5.0</v>
@@ -5417,7 +5494,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H22" s="81">
         <v>0.0</v>
@@ -5447,76 +5524,76 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="83">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="R22" s="84">
         <f t="shared" si="2"/>
-        <v>1185</v>
+        <v>960</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="86" t="s">
-        <v>93</v>
+      <c r="A23" s="78" t="s">
+        <v>94</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="82">
+        <v>7.0</v>
+      </c>
+      <c r="D23" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E23" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="F23" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q23" s="83">
         <v>9.0</v>
-      </c>
-      <c r="D23" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="E23" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="F23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M23" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q23" s="83">
-        <v>10.0</v>
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>885</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="89" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="79" t="s">
-        <v>32</v>
+      <c r="A24" s="85" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C24" s="82">
         <v>9.0</v>
@@ -5525,7 +5602,7 @@
         <v>3.0</v>
       </c>
       <c r="E24" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5534,13 +5611,13 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="82">
         <v>0.0</v>
@@ -5558,31 +5635,31 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
-        <v>1005</v>
+        <v>885</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="s">
-        <v>95</v>
+      <c r="A25" s="88" t="s">
+        <v>96</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" s="82">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="D25" s="42">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="E25" s="42">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F25" s="42">
         <v>0.0</v>
@@ -5615,28 +5692,28 @@
         <v>0.0</v>
       </c>
       <c r="P25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q25" s="83">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="R25" s="84">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>870</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="88" t="s">
-        <v>96</v>
+      <c r="A26" s="86" t="s">
+        <v>97</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="82">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D26" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E26" s="42">
         <v>4.0</v>
@@ -5679,24 +5756,24 @@
       </c>
       <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="78" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" s="82">
+        <v>6.0</v>
+      </c>
+      <c r="D27" s="42">
         <v>7.0</v>
       </c>
-      <c r="D27" s="42">
-        <v>10.0</v>
-      </c>
       <c r="E27" s="42">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5729,40 +5806,40 @@
         <v>0.0</v>
       </c>
       <c r="P27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q27" s="83">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="R27" s="84">
         <f t="shared" si="2"/>
-        <v>765</v>
+        <v>660</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="82" t="s">
-        <v>98</v>
+      <c r="A28" s="78" t="s">
+        <v>99</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C28" s="82">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D28" s="42">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="E28" s="42">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" s="42">
         <v>0.0</v>
       </c>
       <c r="H28" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I28" s="42">
         <v>0.0</v>
@@ -5786,40 +5863,40 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q28" s="83">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
-        <v>645</v>
+        <v>615</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="78" t="s">
-        <v>99</v>
+      <c r="A29" s="82" t="s">
+        <v>100</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="82">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="D29" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G29" s="42">
         <v>0.0</v>
       </c>
       <c r="H29" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29" s="42">
         <v>0.0</v>
@@ -5843,22 +5920,22 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q29" s="83">
         <v>9.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>615</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="88" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B30" s="79" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="82">
         <v>5.0</v>
@@ -5903,28 +5980,28 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="83">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="R30" s="84">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="78" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" s="82">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="D31" s="42">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="E31" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -5957,31 +6034,31 @@
         <v>0.0</v>
       </c>
       <c r="P31" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q31" s="83">
         <v>8.0</v>
       </c>
       <c r="R31" s="84">
         <f t="shared" si="2"/>
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="78" t="s">
-        <v>102</v>
+      <c r="A32" s="88" t="s">
+        <v>103</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" s="82">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D32" s="42">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="E32" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F32" s="42">
         <v>0.0</v>
@@ -6021,24 +6098,24 @@
       </c>
       <c r="R32" s="84">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="90" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B33" s="91" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="92">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="D33" s="91">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="E33" s="91">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="91">
         <v>0.0</v>
@@ -6047,7 +6124,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="I33" s="91">
         <v>0.0</v>
@@ -6078,24 +6155,24 @@
       </c>
       <c r="R33" s="84">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="s">
-        <v>104</v>
+      <c r="A34" s="90" t="s">
+        <v>105</v>
       </c>
       <c r="B34" s="91" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" s="92">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D34" s="91">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="E34" s="91">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F34" s="91">
         <v>0.0</v>
@@ -6104,7 +6181,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="I34" s="91">
         <v>0.0</v>
@@ -6135,71 +6212,128 @@
       </c>
       <c r="R34" s="84">
         <f t="shared" si="2"/>
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="95" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="96" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" hidden="1">
+      <c r="A35" s="90" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="93">
+        <v>7.0</v>
+      </c>
+      <c r="R35" s="84">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="94" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="99">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="99">
-        <v>8.0</v>
-      </c>
-      <c r="R35" s="100">
+      <c r="C36" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="E36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q36" s="98">
+        <v>7.0</v>
+      </c>
+      <c r="R36" s="99">
         <f t="shared" si="2"/>
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$3:$R$35">
-    <sortState ref="A3:R35">
-      <sortCondition descending="1" ref="R3:R35"/>
-      <sortCondition ref="A3:A35"/>
+  <autoFilter ref="$A$3:$R$36">
+    <sortState ref="A3:R36">
+      <sortCondition descending="1" ref="R3:R36"/>
+      <sortCondition ref="A3:A36"/>
     </sortState>
   </autoFilter>
   <mergeCells count="5">
@@ -6209,7 +6343,7 @@
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="R4:R35">
+  <conditionalFormatting sqref="R4:R36">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6221,12 +6355,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B35">
+  <conditionalFormatting sqref="B4:B36">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B35">
+  <conditionalFormatting sqref="B4:B36">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B4))))</formula>
     </cfRule>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -7,15 +7,15 @@
     <sheet state="visible" name="Pitchers" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$39</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$36</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$38</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$35</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
   <si>
     <t>INCENTIVOS DSL 2026</t>
   </si>
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/18/2026</t>
+    <t>Actualización: 6/21/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -104,66 +104,63 @@
     <t>$RD</t>
   </si>
   <si>
+    <t>Celesten, Yeisy</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Flores, Jesus</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Rodriguez, Alex</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>Mateo, Cesar</t>
   </si>
   <si>
-    <t>Celesten, Yeisy</t>
-  </si>
-  <si>
-    <t>Flores, Jesus</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Cavero, Braulio</t>
+  </si>
+  <si>
+    <t>Rosario, Elian</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Rosario, Elian</t>
+    <t>Castillo, Wesly</t>
+  </si>
+  <si>
+    <t>Gonzalez, Victor</t>
+  </si>
+  <si>
+    <t>Abreu, Ariel</t>
+  </si>
+  <si>
+    <t>Benitez, Frainker</t>
   </si>
   <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
-    <t>Cavero, Braulio</t>
-  </si>
-  <si>
-    <t>Castillo, Wesly</t>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
+    <t>Jaquez, Luis</t>
   </si>
   <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
-    <t>Abreu, Ariel</t>
-  </si>
-  <si>
-    <t>Ramirez, Manni</t>
-  </si>
-  <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
-    <t>Jaquez, Luis</t>
-  </si>
-  <si>
-    <t>Gonzalez, Victor</t>
-  </si>
-  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
@@ -176,13 +173,19 @@
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Mosqueda, Juan</t>
+  </si>
+  <si>
+    <t>Rodriguez, Victor</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
-    <t>Mosqueda, Juan</t>
+    <t>Santa, Fraimy</t>
   </si>
   <si>
     <t>Genao, Jhostin</t>
@@ -194,12 +197,6 @@
     <t>Colina, Felix</t>
   </si>
   <si>
-    <t>Rodriguez, Victor</t>
-  </si>
-  <si>
-    <t>Santa, Fraimy</t>
-  </si>
-  <si>
     <t>Montero, Darling</t>
   </si>
   <si>
@@ -248,6 +245,9 @@
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Fukuda, Masahiro</t>
+  </si>
+  <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
@@ -257,85 +257,79 @@
     <t>Lara, Carlos</t>
   </si>
   <si>
+    <t>Medina, Juan</t>
+  </si>
+  <si>
+    <t>Granado, Argenis</t>
+  </si>
+  <si>
     <t>Santos, Aneudy</t>
   </si>
   <si>
-    <t>Medina, Juan</t>
+    <t>Dolsi, Frederik</t>
   </si>
   <si>
     <t>Pineda, Frandel</t>
   </si>
   <si>
-    <t>Dolsi, Frederik</t>
-  </si>
-  <si>
     <t>Roquez, Yadiel</t>
   </si>
   <si>
-    <t>Fukuda, Masahiro</t>
-  </si>
-  <si>
     <t>Pena, Dariel</t>
   </si>
   <si>
     <t>Gomez, Manuel</t>
   </si>
   <si>
+    <t>Castillo, Albert</t>
+  </si>
+  <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
+    <t>Acosta, Isaac</t>
+  </si>
+  <si>
     <t>Alcantara, Jostin</t>
   </si>
   <si>
     <t>Cordero, Albert</t>
   </si>
   <si>
-    <t>Fernandez, Jehiber</t>
+    <t>Lamu, Alex</t>
   </si>
   <si>
     <t>Figuereo, Breyner</t>
   </si>
   <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
     <t>Ramos, Daniel</t>
   </si>
   <si>
-    <t>Castillo, Albert</t>
-  </si>
-  <si>
-    <t>Granado, Argenis</t>
-  </si>
-  <si>
     <t>Ballesteros, Jean</t>
   </si>
   <si>
-    <t>Lamu, Alex</t>
-  </si>
-  <si>
     <t>Perez, Juanangel</t>
   </si>
   <si>
+    <t>Liriano, Edgar</t>
+  </si>
+  <si>
     <t>Peralta, Eddy</t>
   </si>
   <si>
-    <t>Liriano, Edgar</t>
-  </si>
-  <si>
     <t>De Jesus, Yunier</t>
   </si>
   <si>
+    <t>Medina, Ruben</t>
+  </si>
+  <si>
+    <t>Bautista, Jeyson</t>
+  </si>
+  <si>
     <t>Fernandez, Harley</t>
   </si>
   <si>
     <t>Figuereo, Enmanuel</t>
-  </si>
-  <si>
-    <t>Bautista, Jeyson</t>
-  </si>
-  <si>
-    <t>Medina, Ruben</t>
-  </si>
-  <si>
-    <t>Cordova, Jose</t>
   </si>
   <si>
     <t>Gonzalez, Nestor</t>
@@ -388,7 +382,7 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="&quot;Tw Cen MT&quot;"/>
     </font>
     <font>
@@ -399,7 +393,7 @@
     </font>
     <font>
       <sz val="11.0"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="&quot;Tw Cen MT&quot;"/>
     </font>
     <font>
@@ -819,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -933,26 +927,26 @@
     <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1030,55 +1024,61 @@
     <xf borderId="11" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="33" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="35" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1519,7 +1519,7 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
+    <row r="4">
       <c r="A4" s="28" t="s">
         <v>8</v>
       </c>
@@ -1601,16 +1601,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="D5" s="40">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E5" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F5" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G5" s="40">
         <v>3.0</v>
@@ -1619,23 +1619,23 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="41">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="J5" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M5" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N5" s="40">
         <v>2.0</v>
       </c>
-      <c r="K5" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M5" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N5" s="40">
-        <v>0.0</v>
-      </c>
       <c r="O5" s="40">
         <v>0.0</v>
       </c>
@@ -1643,20 +1643,20 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="R5" s="40">
         <v>5.0</v>
       </c>
       <c r="S5" s="43">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U5" s="44">
-        <f t="shared" ref="U5:U39" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>2040</v>
+        <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
+        <v>2490</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1673,65 +1673,65 @@
         <v>31</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="39">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="D6" s="40">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E6" s="40">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F6" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H6" s="40">
         <v>0.0</v>
       </c>
       <c r="I6" s="41">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="J6" s="39">
         <v>0.0</v>
       </c>
       <c r="K6" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="L6" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="39">
         <v>5.0</v>
       </c>
-      <c r="M6" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N6" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>7.0</v>
-      </c>
       <c r="R6" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S6" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T6" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>1980</v>
+        <v>2325</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1744,23 +1744,23 @@
       <c r="AD6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="s">
-        <v>32</v>
+      <c r="A7" s="46" t="s">
+        <v>33</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="39">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="D7" s="40">
         <v>8.0</v>
       </c>
       <c r="E7" s="40">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F7" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" s="40">
         <v>3.0</v>
@@ -1769,22 +1769,22 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J7" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K7" s="41">
         <v>0.0</v>
       </c>
       <c r="L7" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M7" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="N7" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O7" s="40">
         <v>0.0</v>
@@ -1799,14 +1799,14 @@
         <v>5.0</v>
       </c>
       <c r="S7" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T7" s="41">
         <v>9.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>1830</v>
+        <v>2250</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1819,69 +1819,69 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="s">
-        <v>33</v>
+      <c r="A8" s="37" t="s">
+        <v>34</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="E8" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="F8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>16.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="M8" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="O8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R8" s="40">
         <v>4.0</v>
       </c>
-      <c r="E8" s="40">
+      <c r="S8" s="43">
         <v>2.0</v>
       </c>
-      <c r="F8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R8" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S8" s="43">
-        <v>0.0</v>
-      </c>
       <c r="T8" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>2070</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1894,23 +1894,23 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="45" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="39">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="D9" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E9" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F9" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="40">
         <v>2.0</v>
@@ -1928,10 +1928,10 @@
         <v>0.0</v>
       </c>
       <c r="L9" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M9" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="N9" s="40">
         <v>0.0</v>
@@ -1943,20 +1943,20 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R9" s="40">
         <v>4.0</v>
       </c>
       <c r="S9" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T9" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>1620</v>
+        <v>2100</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1969,23 +1969,23 @@
       <c r="AD9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="47">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="D10" s="48">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E10" s="48">
+        <v>8.0</v>
+      </c>
+      <c r="F10" s="48">
         <v>6.0</v>
-      </c>
-      <c r="F10" s="48">
-        <v>5.0</v>
       </c>
       <c r="G10" s="48">
         <v>2.0</v>
@@ -2012,26 +2012,26 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P10" s="42">
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="R10" s="40">
         <v>6.0</v>
       </c>
       <c r="S10" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T10" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1845</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2044,32 +2044,32 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="39">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D11" s="40">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E11" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F11" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H11" s="40">
         <v>0.0</v>
       </c>
       <c r="I11" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J11" s="39">
         <v>0.0</v>
@@ -2078,13 +2078,13 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O11" s="40">
         <v>0.0</v>
@@ -2096,17 +2096,17 @@
         <v>6.0</v>
       </c>
       <c r="R11" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S11" s="43">
         <v>2.0</v>
       </c>
       <c r="T11" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1680</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2119,26 +2119,26 @@
       <c r="AD11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="37" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D12" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E12" s="40">
         <v>3.0</v>
       </c>
       <c r="F12" s="40">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G12" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H12" s="40">
         <v>0.0</v>
@@ -2156,7 +2156,7 @@
         <v>3.0</v>
       </c>
       <c r="M12" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N12" s="40">
         <v>0.0</v>
@@ -2168,20 +2168,20 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R12" s="40">
         <v>4.0</v>
       </c>
       <c r="S12" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T12" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2194,23 +2194,23 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="37" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="39">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="D13" s="40">
         <v>8.0</v>
       </c>
       <c r="E13" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" s="40">
         <v>2.0</v>
@@ -2219,7 +2219,7 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J13" s="39">
         <v>0.0</v>
@@ -2228,10 +2228,10 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M13" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="N13" s="40">
         <v>2.0</v>
@@ -2243,7 +2243,7 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R13" s="40">
         <v>4.0</v>
@@ -2252,11 +2252,11 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1530</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2273,31 +2273,31 @@
         <v>40</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="39">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="D14" s="40">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="E14" s="40">
         <v>3.0</v>
       </c>
       <c r="F14" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H14" s="40">
         <v>0.0</v>
       </c>
       <c r="I14" s="41">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="J14" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K14" s="41">
         <v>0.0</v>
@@ -2321,17 +2321,17 @@
         <v>4.0</v>
       </c>
       <c r="R14" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S14" s="43">
         <v>1.0</v>
       </c>
       <c r="T14" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1785</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2344,17 +2344,17 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="38" t="s">
-        <v>34</v>
+      <c r="B15" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="D15" s="40">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E15" s="40">
         <v>2.0</v>
@@ -2363,13 +2363,13 @@
         <v>0.0</v>
       </c>
       <c r="G15" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2378,10 +2378,10 @@
         <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="M15" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N15" s="40">
         <v>0.0</v>
@@ -2396,17 +2396,17 @@
         <v>3.0</v>
       </c>
       <c r="R15" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S15" s="43">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T15" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1440</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2419,26 +2419,26 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="45" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="D16" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="E16" s="40">
         <v>3.0</v>
       </c>
-      <c r="D16" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E16" s="40">
-        <v>2.0</v>
-      </c>
       <c r="F16" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
@@ -2450,38 +2450,38 @@
         <v>0.0</v>
       </c>
       <c r="K16" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="39">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="M16" s="40">
         <v>0.0</v>
       </c>
       <c r="N16" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O16" s="40">
         <v>1.0</v>
       </c>
       <c r="P16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q16" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R16" s="40">
         <v>4.0</v>
       </c>
-      <c r="R16" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S16" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T16" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1335</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2494,20 +2494,20 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="51" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D17" s="40">
         <v>5.0</v>
       </c>
       <c r="E17" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F17" s="40">
         <v>0.0</v>
@@ -2543,20 +2543,20 @@
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R17" s="40">
         <v>3.0</v>
       </c>
       <c r="S17" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T17" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1290</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2569,26 +2569,26 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="51" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C18" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D18" s="40">
         <v>9.0</v>
       </c>
-      <c r="D18" s="40">
-        <v>5.0</v>
-      </c>
       <c r="E18" s="40">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F18" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" s="40">
         <v>0.0</v>
@@ -2603,35 +2603,35 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="39">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="M18" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N18" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P18" s="42">
         <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="R18" s="40">
         <v>4.0</v>
       </c>
       <c r="S18" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T18" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1005</v>
+        <v>1260</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2643,70 +2643,70 @@
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="46" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="D19" s="40">
+        <v>18.0</v>
+      </c>
+      <c r="E19" s="40">
         <v>4.0</v>
       </c>
-      <c r="D19" s="40">
+      <c r="F19" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G19" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="R19" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="S19" s="43">
+        <v>3.0</v>
+      </c>
+      <c r="T19" s="41">
         <v>10.0</v>
-      </c>
-      <c r="E19" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F19" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="G19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="R19" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S19" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="T19" s="41">
-        <v>7.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2719,69 +2719,69 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="45" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D20" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="E20" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>3.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="M20" s="40">
         <v>7.0</v>
       </c>
-      <c r="D20" s="40">
-        <v>16.0</v>
-      </c>
-      <c r="E20" s="40">
+      <c r="N20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="39">
         <v>3.0</v>
       </c>
-      <c r="F20" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="39">
-        <v>6.0</v>
-      </c>
       <c r="R20" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S20" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T20" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1185</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2798,65 +2798,65 @@
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="D21" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P21" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q21" s="39">
         <v>5.0</v>
       </c>
-      <c r="D21" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="E21" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="M21" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="N21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P21" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q21" s="39">
+      <c r="R21" s="40">
         <v>2.0</v>
       </c>
-      <c r="R21" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S21" s="43">
         <v>0.0</v>
       </c>
       <c r="T21" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>945</v>
+        <v>1065</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2869,32 +2869,32 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="39">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D22" s="40">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E22" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" s="40">
         <v>0.0</v>
       </c>
       <c r="G22" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="40">
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2903,7 +2903,7 @@
         <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M22" s="40">
         <v>2.0</v>
@@ -2918,20 +2918,20 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="R22" s="40">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="S22" s="43">
         <v>2.0</v>
       </c>
       <c r="T22" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>1035</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2948,19 +2948,19 @@
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D23" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="E23" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="40">
         <v>1.0</v>
@@ -2978,35 +2978,35 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="R23" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S23" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T23" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>915</v>
+        <v>1065</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3019,32 +3019,32 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>34</v>
+      <c r="B24" s="50" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="39">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="D24" s="40">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="E24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F24" s="40">
         <v>0.0</v>
       </c>
       <c r="G24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" s="40">
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3056,32 +3056,32 @@
         <v>0.0</v>
       </c>
       <c r="M24" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="40">
         <v>0.0</v>
       </c>
       <c r="O24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R24" s="40">
         <v>1.0</v>
       </c>
       <c r="S24" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T24" s="41">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>1020</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3097,66 +3097,66 @@
       <c r="A25" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="51" t="s">
-        <v>34</v>
+      <c r="B25" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C25" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
         <v>4.0</v>
       </c>
-      <c r="E25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>3.0</v>
-      </c>
       <c r="R25" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S25" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T25" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>795</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3169,23 +3169,23 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="45" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D26" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E26" s="40">
         <v>0.0</v>
       </c>
       <c r="F26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" s="40">
         <v>0.0</v>
@@ -3194,7 +3194,7 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3203,35 +3203,35 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M26" s="40">
         <v>0.0</v>
       </c>
       <c r="N26" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="39">
         <v>3.0</v>
       </c>
       <c r="R26" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S26" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T26" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>795</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3244,11 +3244,11 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="45" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" s="39">
         <v>4.0</v>
@@ -3260,7 +3260,7 @@
         <v>1.0</v>
       </c>
       <c r="F27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" s="40">
         <v>1.0</v>
@@ -3269,7 +3269,7 @@
         <v>0.0</v>
       </c>
       <c r="I27" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J27" s="39">
         <v>0.0</v>
@@ -3281,10 +3281,10 @@
         <v>1.0</v>
       </c>
       <c r="M27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O27" s="40">
         <v>0.0</v>
@@ -3293,20 +3293,20 @@
         <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R27" s="40">
         <v>1.0</v>
       </c>
       <c r="S27" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>810</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3322,23 +3322,23 @@
       <c r="A28" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>34</v>
+      <c r="B28" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="C28" s="39">
         <v>4.0</v>
       </c>
       <c r="D28" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E28" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F28" s="40">
         <v>0.0</v>
       </c>
       <c r="G28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" s="40">
         <v>0.0</v>
@@ -3353,13 +3353,13 @@
         <v>0.0</v>
       </c>
       <c r="L28" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="40">
         <v>0.0</v>
@@ -3368,20 +3368,20 @@
         <v>0.0</v>
       </c>
       <c r="Q28" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R28" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="S28" s="43">
         <v>0.0</v>
       </c>
       <c r="T28" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3394,17 +3394,17 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="38" t="s">
-        <v>30</v>
+      <c r="B29" s="50" t="s">
+        <v>32</v>
       </c>
       <c r="C29" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D29" s="40">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="E29" s="40">
         <v>0.0</v>
@@ -3419,7 +3419,7 @@
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3428,13 +3428,13 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M29" s="40">
         <v>2.0</v>
       </c>
-      <c r="M29" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N29" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="40">
         <v>0.0</v>
@@ -3443,20 +3443,20 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R29" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S29" s="43">
         <v>0.0</v>
       </c>
       <c r="T29" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3469,69 +3469,69 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="51" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" s="39">
         <v>3.0</v>
       </c>
       <c r="D30" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="E30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F30" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J30" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M30" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P30" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q30" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="S30" s="43">
+        <v>0.0</v>
+      </c>
+      <c r="T30" s="41">
         <v>10.0</v>
-      </c>
-      <c r="E30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J30" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P30" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q30" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="R30" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S30" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="T30" s="41">
-        <v>8.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>570</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3544,69 +3544,69 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="45" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C31" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="D31" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E31" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I31" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J31" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P31" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q31" s="39">
         <v>2.0</v>
       </c>
-      <c r="D31" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I31" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J31" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L31" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P31" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q31" s="39">
-        <v>1.0</v>
-      </c>
       <c r="R31" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S31" s="43">
         <v>0.0</v>
       </c>
       <c r="T31" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3619,17 +3619,17 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="46" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C32" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D32" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E32" s="40">
         <v>0.0</v>
@@ -3653,10 +3653,10 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="40">
         <v>0.0</v>
@@ -3668,20 +3668,20 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="R32" s="40">
         <v>2.0</v>
       </c>
-      <c r="R32" s="40">
-        <v>1.0</v>
-      </c>
       <c r="S32" s="43">
         <v>0.0</v>
       </c>
       <c r="T32" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3694,23 +3694,23 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="51" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D33" s="40">
         <v>2.0</v>
       </c>
       <c r="E33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" s="40">
         <v>0.0</v>
@@ -3731,10 +3731,10 @@
         <v>1.0</v>
       </c>
       <c r="M33" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O33" s="40">
         <v>0.0</v>
@@ -3743,20 +3743,20 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R33" s="40">
         <v>1.0</v>
       </c>
       <c r="S33" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T33" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3769,23 +3769,23 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="51" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" s="40">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="E34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" s="40">
         <v>0.0</v>
@@ -3794,7 +3794,7 @@
         <v>0.0</v>
       </c>
       <c r="I34" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J34" s="39">
         <v>0.0</v>
@@ -3803,35 +3803,35 @@
         <v>0.0</v>
       </c>
       <c r="L34" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M34" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="N34" s="40">
         <v>0.0</v>
       </c>
       <c r="O34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P34" s="42">
         <v>0.0</v>
       </c>
       <c r="Q34" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R34" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="S34" s="43">
         <v>0.0</v>
       </c>
       <c r="T34" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3844,20 +3844,20 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="37" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C35" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D35" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F35" s="40">
         <v>0.0</v>
@@ -3869,40 +3869,40 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="39">
         <v>2.0</v>
       </c>
-      <c r="J35" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M35" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N35" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P35" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="39">
-        <v>1.0</v>
-      </c>
       <c r="R35" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S35" s="43">
         <v>0.0</v>
       </c>
       <c r="T35" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
@@ -3919,17 +3919,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>30</v>
+      <c r="B36" s="50" t="s">
+        <v>32</v>
       </c>
       <c r="C36" s="39">
         <v>1.0</v>
       </c>
       <c r="D36" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3968,7 +3968,7 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R36" s="40">
         <v>1.0</v>
@@ -3977,11 +3977,11 @@
         <v>0.0</v>
       </c>
       <c r="T36" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3997,14 +3997,14 @@
       <c r="A37" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="51" t="s">
-        <v>34</v>
+      <c r="B37" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="C37" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D37" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="E37" s="40">
         <v>0.0</v>
@@ -4019,7 +4019,7 @@
         <v>0.0</v>
       </c>
       <c r="I37" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J37" s="39">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>0.0</v>
       </c>
       <c r="L37" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M37" s="40">
         <v>0.0</v>
@@ -4046,17 +4046,17 @@
         <v>0.0</v>
       </c>
       <c r="R37" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S37" s="43">
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4069,11 +4069,11 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="51" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C38" s="39">
         <v>0.0</v>
@@ -4094,7 +4094,7 @@
         <v>0.0</v>
       </c>
       <c r="I38" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J38" s="39">
         <v>0.0</v>
@@ -4102,36 +4102,36 @@
       <c r="K38" s="41">
         <v>0.0</v>
       </c>
-      <c r="L38" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P38" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q38" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="R38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="S38" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="T38" s="41">
-        <v>8.0</v>
+      <c r="L38" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="P38" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q38" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="R38" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="S38" s="55">
+        <v>0.0</v>
+      </c>
+      <c r="T38" s="56">
+        <v>10.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4143,90 +4143,16 @@
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
     </row>
-    <row r="39">
-      <c r="A39" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="D39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="E39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H39" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K39" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="M39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="N39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="O39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="P39" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q39" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="R39" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="S39" s="55">
-        <v>0.0</v>
-      </c>
-      <c r="T39" s="56">
-        <v>8.0</v>
-      </c>
-      <c r="U39" s="44">
-        <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="9"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$4:$U$39">
-    <sortState ref="A4:U39">
-      <sortCondition descending="1" ref="U4:U39"/>
-      <sortCondition ref="A4:A39"/>
-      <sortCondition descending="1" ref="F4:F39"/>
-      <sortCondition descending="1" ref="M4:M39"/>
-      <sortCondition descending="1" ref="G4:G39"/>
-      <sortCondition descending="1" ref="I4:I39"/>
+  <autoFilter ref="$A$4:$U$38">
+    <sortState ref="A4:U38">
+      <sortCondition descending="1" ref="U4:U38"/>
+      <sortCondition descending="1" ref="G4:G38"/>
+      <sortCondition ref="B4:B38"/>
+      <sortCondition ref="A4:A38"/>
+      <sortCondition descending="1" ref="F4:F38"/>
+      <sortCondition descending="1" ref="M4:M38"/>
+      <sortCondition descending="1" ref="I4:I38"/>
     </sortState>
   </autoFilter>
   <mergeCells count="9">
@@ -4240,7 +4166,7 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="U5:U39">
+  <conditionalFormatting sqref="U5:U38">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4252,12 +4178,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B39">
+  <conditionalFormatting sqref="B5:B38">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B39">
+  <conditionalFormatting sqref="B5:B38">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B5))))</formula>
     </cfRule>
@@ -4386,7 +4312,7 @@
     </row>
     <row r="3">
       <c r="A3" s="72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="73" t="s">
         <v>9</v>
@@ -4398,13 +4324,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="G3" s="74" t="s">
         <v>68</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>69</v>
       </c>
       <c r="H3" s="74" t="s">
         <v>19</v>
@@ -4416,19 +4342,19 @@
         <v>22</v>
       </c>
       <c r="K3" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="M3" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="77" t="s">
+      <c r="N3" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="72" t="s">
+      <c r="O3" s="73" t="s">
         <v>73</v>
-      </c>
-      <c r="O3" s="73" t="s">
-        <v>74</v>
       </c>
       <c r="P3" s="73" t="s">
         <v>26</v>
@@ -4450,10 +4376,10 @@
     </row>
     <row r="4">
       <c r="A4" s="78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="80">
         <v>17.0</v>
@@ -4486,7 +4412,7 @@
         <v>0.0</v>
       </c>
       <c r="M4" s="83">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N4" s="82">
         <v>0.0</v>
@@ -4498,47 +4424,47 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="83">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R4" s="84">
-        <f t="shared" ref="R4:R8" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>2745</v>
+        <f t="shared" ref="R4:R11" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>2985</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="85" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="B5" s="79" t="s">
+        <v>32</v>
       </c>
       <c r="C5" s="82">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="D5" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="F5" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G5" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="82">
         <v>2.0</v>
       </c>
-      <c r="E5" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="F5" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="82">
-        <v>1.0</v>
-      </c>
       <c r="L5" s="42">
         <v>1.0</v>
       </c>
@@ -4555,34 +4481,34 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="83">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="R5" s="84">
         <f t="shared" si="1"/>
-        <v>1815</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="s">
-        <v>77</v>
+      <c r="A6" s="85" t="s">
+        <v>76</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="82">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="D6" s="42">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E6" s="42">
         <v>9.0</v>
       </c>
       <c r="F6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="81">
         <v>0.0</v>
@@ -4591,7 +4517,7 @@
         <v>0.0</v>
       </c>
       <c r="J6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K6" s="82">
         <v>0.0</v>
@@ -4609,46 +4535,46 @@
         <v>0.0</v>
       </c>
       <c r="P6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q6" s="83">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="R6" s="84">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="86" t="s">
-        <v>78</v>
+      <c r="A7" s="78" t="s">
+        <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="82">
         <v>12.0</v>
       </c>
       <c r="D7" s="42">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E7" s="42">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="F7" s="42">
         <v>0.0</v>
       </c>
       <c r="G7" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H7" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="81">
         <v>0.0</v>
       </c>
       <c r="J7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K7" s="82">
         <v>0.0</v>
@@ -4669,37 +4595,37 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="87" t="s">
-        <v>79</v>
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="8" hidden="1">
+      <c r="A8" s="86" t="s">
+        <v>78</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="82">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="D8" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E8" s="42">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="F8" s="42">
         <v>0.0</v>
       </c>
       <c r="G8" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H8" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I8" s="81">
         <v>0.0</v>
@@ -4730,24 +4656,24 @@
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="88" t="s">
-        <v>80</v>
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="87" t="s">
+        <v>79</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" s="82">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="D9" s="42">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E9" s="42">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F9" s="42">
         <v>0.0</v>
@@ -4780,139 +4706,139 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q9" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R9" s="84">
-        <f>C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2</f>
-        <v>1470</v>
+        <f t="shared" si="1"/>
+        <v>1515</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="D10" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="E10" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="F10" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q10" s="83">
+        <v>9.0</v>
+      </c>
+      <c r="R10" s="84">
+        <f t="shared" si="1"/>
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="82">
-        <v>11.0</v>
-      </c>
-      <c r="D10" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="E10" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="F10" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q10" s="83">
-        <v>7.0</v>
-      </c>
-      <c r="R10" s="84">
-        <f t="shared" ref="R10:R36" si="2">C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2+I10*$I$2+J10*$J$2</f>
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="78" t="s">
+      <c r="B11" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="D11" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="83">
+        <v>9.0</v>
+      </c>
+      <c r="R11" s="84">
+        <f t="shared" si="1"/>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="88" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="82">
-        <v>10.0</v>
-      </c>
-      <c r="D11" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="83">
-        <v>8.0</v>
-      </c>
-      <c r="R11" s="84">
-        <f t="shared" si="2"/>
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="86" t="s">
-        <v>83</v>
-      </c>
       <c r="B12" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="82">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="D12" s="42">
         <v>6.0</v>
@@ -4933,10 +4859,10 @@
         <v>0.0</v>
       </c>
       <c r="J12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L12" s="42">
         <v>0.0</v>
@@ -4951,31 +4877,31 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q12" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R12" s="84">
-        <f t="shared" si="2"/>
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="13">
+        <f>C12*$C$2+D12*$D$2+E12*$E$2+F12*$F$2+G12*$G$2+H12*$H$2+K12*$K$2+L12*$L$2+M12*$M$2+N12*$N$2+O12*$O$2+P12*$P$2+Q12*$Q$2</f>
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="13" hidden="1">
       <c r="A13" s="86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="82">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="D13" s="42">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E13" s="42">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
@@ -4984,16 +4910,16 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="42">
         <v>0.0</v>
@@ -5011,31 +4937,31 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R13" s="84">
-        <f t="shared" si="2"/>
-        <v>1320</v>
+        <f t="shared" ref="R13:R35" si="2">C13*$C$2+D13*$D$2+E13*$E$2+F13*$F$2+G13*$G$2+H13*$H$2+K13*$K$2+L13*$L$2+M13*$M$2+N13*$N$2+O13*$O$2+P13*$P$2+Q13*$Q$2+I13*$I$2+J13*$J$2</f>
+        <v>1710</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85" t="s">
-        <v>85</v>
+      <c r="A14" s="78" t="s">
+        <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="82">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="D14" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E14" s="42">
         <v>6.0</v>
       </c>
       <c r="F14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="42">
         <v>0.0</v>
@@ -5044,13 +4970,13 @@
         <v>0.0</v>
       </c>
       <c r="I14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J14" s="42">
         <v>0.0</v>
       </c>
       <c r="K14" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L14" s="42">
         <v>0.0</v>
@@ -5068,37 +4994,37 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="83">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="R14" s="84">
         <f t="shared" si="2"/>
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="89" t="s">
-        <v>86</v>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="86" t="s">
+        <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="82">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="D15" s="42">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="E15" s="42">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="F15" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="42">
         <v>0.0</v>
       </c>
       <c r="H15" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I15" s="81">
         <v>0.0</v>
@@ -5122,34 +5048,34 @@
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q15" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R15" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="86" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="79" t="s">
-        <v>34</v>
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="D16" s="42">
         <v>9.0</v>
       </c>
-      <c r="D16" s="42">
-        <v>5.0</v>
-      </c>
       <c r="E16" s="42">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="42">
         <v>0.0</v>
@@ -5158,7 +5084,7 @@
         <v>0.0</v>
       </c>
       <c r="I16" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="42">
         <v>0.0</v>
@@ -5179,31 +5105,31 @@
         <v>0.0</v>
       </c>
       <c r="P16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q16" s="83">
         <v>9.0</v>
       </c>
       <c r="R16" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>30</v>
+      <c r="A17" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="79" t="s">
+        <v>32</v>
       </c>
       <c r="C17" s="82">
         <v>9.0</v>
       </c>
       <c r="D17" s="42">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="E17" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="42">
         <v>0.0</v>
@@ -5215,7 +5141,7 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5224,7 +5150,7 @@
         <v>0.0</v>
       </c>
       <c r="L17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M17" s="83">
         <v>0.0</v>
@@ -5236,37 +5162,37 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R17" s="84">
         <f t="shared" si="2"/>
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="88" t="s">
-        <v>89</v>
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" s="78" t="s">
+        <v>88</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="82">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="D18" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E18" s="42">
         <v>4.0</v>
       </c>
-      <c r="E18" s="42">
-        <v>5.0</v>
-      </c>
       <c r="F18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H18" s="81">
         <v>0.0</v>
@@ -5296,25 +5222,25 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="19" hidden="1">
       <c r="A19" s="86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="82">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="D19" s="42">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="E19" s="42">
         <v>4.0</v>
@@ -5353,28 +5279,28 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1005</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="79" t="s">
-        <v>34</v>
+      <c r="A20" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>32</v>
       </c>
       <c r="C20" s="82">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D20" s="42">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E20" s="42">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5407,31 +5333,31 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R20" s="84">
         <f t="shared" si="2"/>
-        <v>975</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="78" t="s">
-        <v>92</v>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="21" hidden="1">
+      <c r="A21" s="88" t="s">
+        <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21" s="82">
         <v>9.0</v>
       </c>
       <c r="D21" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E21" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F21" s="42">
         <v>0.0</v>
@@ -5440,10 +5366,10 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J21" s="42">
         <v>0.0</v>
@@ -5464,28 +5390,28 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q21" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>960</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="78" t="s">
-        <v>93</v>
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="22" hidden="1">
+      <c r="A22" s="88" t="s">
+        <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C22" s="82">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="D22" s="42">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="E22" s="42">
         <v>5.0</v>
@@ -5494,7 +5420,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="81">
         <v>0.0</v>
@@ -5524,31 +5450,31 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R22" s="84">
         <f t="shared" si="2"/>
-        <v>960</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="78" t="s">
-        <v>94</v>
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="23" hidden="1">
+      <c r="A23" s="86" t="s">
+        <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="82">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D23" s="42">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E23" s="42">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="42">
         <v>0.0</v>
@@ -5578,22 +5504,22 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>885</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="85" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>30</v>
+      <c r="A24" s="89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="82">
         <v>9.0</v>
@@ -5602,7 +5528,7 @@
         <v>3.0</v>
       </c>
       <c r="E24" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5611,13 +5537,13 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="82">
         <v>0.0</v>
@@ -5635,31 +5561,31 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
-        <v>885</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="s">
-        <v>96</v>
+      <c r="A25" s="78" t="s">
+        <v>95</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25" s="82">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="D25" s="42">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E25" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F25" s="42">
         <v>0.0</v>
@@ -5692,28 +5618,28 @@
         <v>0.0</v>
       </c>
       <c r="P25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q25" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R25" s="84">
         <f t="shared" si="2"/>
-        <v>870</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="86" t="s">
-        <v>97</v>
+      <c r="A26" s="88" t="s">
+        <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="82">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D26" s="42">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E26" s="42">
         <v>4.0</v>
@@ -5752,28 +5678,28 @@
         <v>0.0</v>
       </c>
       <c r="Q26" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>735</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" s="82">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D27" s="42">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E27" s="42">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5806,40 +5732,40 @@
         <v>0.0</v>
       </c>
       <c r="P27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q27" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R27" s="84">
         <f t="shared" si="2"/>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="78" t="s">
-        <v>99</v>
+        <v>795</v>
+      </c>
+    </row>
+    <row r="28" hidden="1">
+      <c r="A28" s="82" t="s">
+        <v>98</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C28" s="82">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D28" s="42">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E28" s="42">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F28" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" s="42">
         <v>0.0</v>
       </c>
       <c r="H28" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28" s="42">
         <v>0.0</v>
@@ -5863,40 +5789,40 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q28" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
-        <v>615</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="82" t="s">
-        <v>100</v>
+      <c r="A29" s="78" t="s">
+        <v>99</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" s="82">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="D29" s="42">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="E29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="42">
         <v>0.0</v>
       </c>
       <c r="H29" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I29" s="42">
         <v>0.0</v>
@@ -5920,22 +5846,22 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q29" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>405</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B30" s="79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30" s="82">
         <v>5.0</v>
@@ -5980,29 +5906,29 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="83">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R30" s="84">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="82">
+        <v>6.0</v>
+      </c>
+      <c r="D31" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="E31" s="42">
         <v>2.0</v>
       </c>
-      <c r="D31" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="E31" s="42">
-        <v>0.0</v>
-      </c>
       <c r="F31" s="42">
         <v>0.0</v>
       </c>
@@ -6010,7 +5936,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="I31" s="42">
         <v>0.0</v>
@@ -6037,25 +5963,25 @@
         <v>0.0</v>
       </c>
       <c r="Q31" s="83">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R31" s="84">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="88" t="s">
-        <v>103</v>
+      <c r="A32" s="78" t="s">
+        <v>102</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C32" s="82">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="D32" s="42">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="E32" s="42">
         <v>1.0</v>
@@ -6091,31 +6017,31 @@
         <v>0.0</v>
       </c>
       <c r="P32" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q32" s="83">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R32" s="84">
         <f t="shared" si="2"/>
-        <v>345</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="91" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" s="92">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D33" s="91">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="E33" s="91">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F33" s="91">
         <v>0.0</v>
@@ -6151,28 +6077,28 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="93">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R33" s="84">
         <f t="shared" si="2"/>
-        <v>285</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="91" t="s">
-        <v>34</v>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="34" hidden="1">
+      <c r="A34" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="95" t="s">
+        <v>30</v>
       </c>
       <c r="C34" s="92">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D34" s="91">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E34" s="91">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="91">
         <v>0.0</v>
@@ -6181,7 +6107,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34" s="91">
         <v>0.0</v>
@@ -6212,128 +6138,76 @@
       </c>
       <c r="R34" s="84">
         <f t="shared" si="2"/>
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" hidden="1">
-      <c r="A35" s="90" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="91" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="93">
-        <v>7.0</v>
-      </c>
-      <c r="R35" s="84">
+      <c r="A35" s="96" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="100">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="100">
+        <v>8.0</v>
+      </c>
+      <c r="R35" s="101">
         <f t="shared" si="2"/>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="95" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="D36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="G36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q36" s="98">
-        <v>7.0</v>
-      </c>
-      <c r="R36" s="99">
-        <f t="shared" si="2"/>
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$3:$R$36">
-    <sortState ref="A3:R36">
-      <sortCondition descending="1" ref="R3:R36"/>
-      <sortCondition ref="A3:A36"/>
+  <autoFilter ref="$A$3:$R$35">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="B"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A3:R35">
+      <sortCondition descending="1" ref="R3:R35"/>
+      <sortCondition ref="A3:A35"/>
     </sortState>
   </autoFilter>
   <mergeCells count="5">
@@ -6343,7 +6217,7 @@
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="R4:R36">
+  <conditionalFormatting sqref="R4:R35">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6355,12 +6229,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B36">
+  <conditionalFormatting sqref="B4:B35">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B36">
+  <conditionalFormatting sqref="B4:B35">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B4))))</formula>
     </cfRule>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/21/2026</t>
+    <t>Actualización: 6/22/2026</t>
   </si>
   <si>
     <t>Players</t>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/22/2026</t>
+    <t>Actualización: 6/23/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -119,15 +119,18 @@
     <t>Rodriguez, Alex</t>
   </si>
   <si>
+    <t>Guerrero, Oliver</t>
+  </si>
+  <si>
     <t>Mateo, Cesar</t>
   </si>
   <si>
-    <t>Guerrero, Oliver</t>
-  </si>
-  <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Castillo, Wesly</t>
+  </si>
+  <si>
     <t>Cavero, Braulio</t>
   </si>
   <si>
@@ -137,15 +140,12 @@
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Castillo, Wesly</t>
+    <t>Abreu, Ariel</t>
   </si>
   <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
-    <t>Abreu, Ariel</t>
-  </si>
-  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
@@ -161,34 +161,37 @@
     <t>Valdes, Abel</t>
   </si>
   <si>
+    <t>Marcano, Jose</t>
+  </si>
+  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
-    <t>Marcano, Jose</t>
-  </si>
-  <si>
     <t>Pinder, Jayln</t>
   </si>
   <si>
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Rodriguez, Victor</t>
+  </si>
+  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
-    <t>Rodriguez, Victor</t>
+    <t>Pereira, Raul</t>
   </si>
   <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
-    <t>Pereira, Raul</t>
+    <t>Genao, Jhostin</t>
   </si>
   <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
-    <t>Genao, Jhostin</t>
+    <t>Montero, Darling</t>
   </si>
   <si>
     <t>Ortiz Jr, David</t>
@@ -197,7 +200,7 @@
     <t>Colina, Felix</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
+    <t>Coronado, Francisco</t>
   </si>
   <si>
     <t>Seminiel, Cristian</t>
@@ -206,9 +209,6 @@
     <t>Cedeno, Luis</t>
   </si>
   <si>
-    <t>Coronado, Francisco</t>
-  </si>
-  <si>
     <t>Simon, Jhon</t>
   </si>
   <si>
@@ -245,6 +245,12 @@
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Pineda, Frandel</t>
+  </si>
+  <si>
+    <t>Gomez, Manuel</t>
+  </si>
+  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
@@ -254,33 +260,27 @@
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
+    <t>Dolsi, Frederik</t>
+  </si>
+  <si>
+    <t>Medina, Juan</t>
+  </si>
+  <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
+    <t>Santos, Aneudy</t>
+  </si>
+  <si>
     <t>Lara, Carlos</t>
   </si>
   <si>
-    <t>Medina, Juan</t>
-  </si>
-  <si>
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Santos, Aneudy</t>
-  </si>
-  <si>
-    <t>Dolsi, Frederik</t>
-  </si>
-  <si>
-    <t>Pineda, Frandel</t>
-  </si>
-  <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Pena, Dariel</t>
   </si>
   <si>
-    <t>Gomez, Manuel</t>
-  </si>
-  <si>
     <t>Castillo, Albert</t>
   </si>
   <si>
@@ -299,22 +299,22 @@
     <t>Lamu, Alex</t>
   </si>
   <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
     <t>Figuereo, Breyner</t>
   </si>
   <si>
-    <t>Ramos, Daniel</t>
-  </si>
-  <si>
     <t>Ballesteros, Jean</t>
   </si>
   <si>
+    <t>Peralta, Eddy</t>
+  </si>
+  <si>
     <t>Perez, Juanangel</t>
   </si>
   <si>
     <t>Liriano, Edgar</t>
-  </si>
-  <si>
-    <t>Peralta, Eddy</t>
   </si>
   <si>
     <t>De Jesus, Yunier</t>
@@ -1051,10 +1051,10 @@
     <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1601,13 +1601,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D5" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E5" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F5" s="40">
         <v>5.0</v>
@@ -1631,7 +1631,7 @@
         <v>4.0</v>
       </c>
       <c r="M5" s="40">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="N5" s="40">
         <v>2.0</v>
@@ -1652,11 +1652,11 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>2490</v>
+        <v>2655</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1676,10 +1676,10 @@
         <v>32</v>
       </c>
       <c r="C6" s="39">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D6" s="40">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E6" s="40">
         <v>3.0</v>
@@ -1724,14 +1724,14 @@
         <v>5.0</v>
       </c>
       <c r="S6" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T6" s="41">
         <v>10.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>2325</v>
+        <v>2370</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1802,11 +1802,11 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="41">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>2250</v>
+        <v>2310</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1819,47 +1819,47 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="45" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="39">
+        <v>19.0</v>
+      </c>
+      <c r="D8" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E8" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F8" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M8" s="40">
         <v>7.0</v>
       </c>
-      <c r="D8" s="40">
-        <v>9.0</v>
-      </c>
-      <c r="E8" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="F8" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G8" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>16.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="M8" s="40">
-        <v>2.0</v>
-      </c>
       <c r="N8" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="O8" s="40">
         <v>0.0</v>
@@ -1868,7 +1868,7 @@
         <v>0.0</v>
       </c>
       <c r="Q8" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="R8" s="40">
         <v>4.0</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>2070</v>
+        <v>2145</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1894,65 +1894,65 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="37" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="39">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="D9" s="40">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="E9" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="F9" s="40">
         <v>3.0</v>
       </c>
-      <c r="F9" s="40">
+      <c r="G9" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="41">
+        <v>16.0</v>
+      </c>
+      <c r="J9" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="39">
         <v>5.0</v>
       </c>
-      <c r="G9" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J9" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="39">
-        <v>4.0</v>
-      </c>
       <c r="M9" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N9" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="O9" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q9" s="39">
         <v>7.0</v>
-      </c>
-      <c r="N9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q9" s="39">
-        <v>4.0</v>
       </c>
       <c r="R9" s="40">
         <v>4.0</v>
       </c>
       <c r="S9" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T9" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
@@ -1976,16 +1976,16 @@
         <v>30</v>
       </c>
       <c r="C10" s="47">
+        <v>10.0</v>
+      </c>
+      <c r="D10" s="48">
+        <v>17.0</v>
+      </c>
+      <c r="E10" s="48">
         <v>9.0</v>
       </c>
-      <c r="D10" s="48">
-        <v>16.0</v>
-      </c>
-      <c r="E10" s="48">
-        <v>8.0</v>
-      </c>
       <c r="F10" s="48">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G10" s="48">
         <v>2.0</v>
@@ -2027,11 +2027,11 @@
         <v>3.0</v>
       </c>
       <c r="T10" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>1845</v>
+        <v>2025</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2044,59 +2044,59 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="45" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="39">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="D11" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E11" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F11" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="41">
+        <v>6.0</v>
+      </c>
+      <c r="J11" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="K11" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="39">
         <v>4.0</v>
       </c>
-      <c r="E11" s="40">
+      <c r="R11" s="40">
         <v>4.0</v>
-      </c>
-      <c r="F11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="H11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="40">
-        <v>2.0</v>
       </c>
       <c r="S11" s="43">
         <v>2.0</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>1680</v>
+        <v>1935</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2129,59 +2129,59 @@
         <v>9.0</v>
       </c>
       <c r="D12" s="40">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E12" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F12" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="H12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J12" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="39">
         <v>6.0</v>
       </c>
-      <c r="G12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="39">
-        <v>7.0</v>
-      </c>
       <c r="R12" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S12" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T12" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>1560</v>
+        <v>1740</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2201,25 +2201,25 @@
         <v>30</v>
       </c>
       <c r="C13" s="39">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="D13" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E13" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F13" s="40">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G13" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H13" s="40">
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J13" s="39">
         <v>0.0</v>
@@ -2228,13 +2228,13 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M13" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="N13" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O13" s="40">
         <v>0.0</v>
@@ -2249,14 +2249,14 @@
         <v>4.0</v>
       </c>
       <c r="S13" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T13" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1665</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2269,47 +2269,47 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="37" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="D14" s="40">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="E14" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F14" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H14" s="40">
         <v>0.0</v>
       </c>
       <c r="I14" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J14" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M14" s="40">
         <v>6.0</v>
       </c>
-      <c r="J14" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="K14" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M14" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N14" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O14" s="40">
         <v>0.0</v>
@@ -2318,20 +2318,20 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="39">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="R14" s="40">
         <v>4.0</v>
       </c>
       <c r="S14" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T14" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1545</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2347,66 +2347,66 @@
       <c r="A15" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="50" t="s">
-        <v>30</v>
+      <c r="B15" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="C15" s="39">
         <v>13.0</v>
       </c>
       <c r="D15" s="40">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="E15" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F15" s="40">
         <v>0.0</v>
       </c>
       <c r="G15" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L15" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="M15" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q15" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R15" s="40">
         <v>4.0</v>
       </c>
-      <c r="J15" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M15" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q15" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R15" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S15" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T15" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1440</v>
+        <v>1485</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2422,66 +2422,66 @@
       <c r="A16" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>32</v>
+      <c r="B16" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="39">
+        <v>13.0</v>
+      </c>
+      <c r="D16" s="40">
+        <v>15.0</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J16" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M16" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="N16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="R16" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S16" s="43">
+        <v>3.0</v>
+      </c>
+      <c r="T16" s="41">
         <v>11.0</v>
-      </c>
-      <c r="D16" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="E16" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="F16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>10.0</v>
-      </c>
-      <c r="M16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R16" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S16" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="T16" s="41">
-        <v>10.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1335</v>
+        <v>1470</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2501,10 +2501,10 @@
         <v>32</v>
       </c>
       <c r="C17" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D17" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E17" s="40">
         <v>3.0</v>
@@ -2549,14 +2549,14 @@
         <v>3.0</v>
       </c>
       <c r="S17" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T17" s="41">
         <v>10.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1365</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2576,10 +2576,10 @@
         <v>30</v>
       </c>
       <c r="C18" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D18" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E18" s="40">
         <v>6.0</v>
@@ -2627,11 +2627,11 @@
         <v>2.0</v>
       </c>
       <c r="T18" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1335</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2669,7 +2669,7 @@
         <v>0.0</v>
       </c>
       <c r="I19" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J19" s="39">
         <v>0.0</v>
@@ -2702,11 +2702,11 @@
         <v>3.0</v>
       </c>
       <c r="T19" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1260</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2852,11 +2852,11 @@
         <v>0.0</v>
       </c>
       <c r="T21" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1095</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2869,23 +2869,23 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="45" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D22" s="40">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="E22" s="40">
         <v>3.0</v>
       </c>
       <c r="F22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="40">
         <v>1.0</v>
@@ -2903,35 +2903,35 @@
         <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M22" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N22" s="40">
         <v>0.0</v>
       </c>
       <c r="O22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="R22" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S22" s="43">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="T22" s="41">
         <v>10.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1065</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2944,23 +2944,23 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="37" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D23" s="40">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E23" s="40">
         <v>3.0</v>
       </c>
       <c r="F23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="40">
         <v>1.0</v>
@@ -2978,35 +2978,35 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M23" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="R23" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S23" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T23" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3026,10 +3026,10 @@
         <v>32</v>
       </c>
       <c r="C24" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D24" s="40">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E24" s="40">
         <v>0.0</v>
@@ -3074,14 +3074,14 @@
         <v>1.0</v>
       </c>
       <c r="S24" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T24" s="41">
         <v>11.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>1035</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3101,10 +3101,10 @@
         <v>30</v>
       </c>
       <c r="C25" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D25" s="40">
         <v>4.0</v>
-      </c>
-      <c r="D25" s="40">
-        <v>3.0</v>
       </c>
       <c r="E25" s="40">
         <v>0.0</v>
@@ -3152,11 +3152,11 @@
         <v>1.0</v>
       </c>
       <c r="T25" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>870</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3173,28 +3173,28 @@
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="39">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D26" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" s="40">
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3203,25 +3203,25 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N26" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q26" s="39">
         <v>3.0</v>
       </c>
       <c r="R26" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S26" s="43">
         <v>1.0</v>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3248,28 +3248,28 @@
         <v>53</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" s="39">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D27" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" s="40">
         <v>0.0</v>
       </c>
       <c r="I27" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="39">
         <v>0.0</v>
@@ -3278,25 +3278,25 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q27" s="39">
         <v>3.0</v>
       </c>
       <c r="R27" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S27" s="43">
         <v>1.0</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3319,32 +3319,32 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="50" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D28" s="40">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E28" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" s="40">
         <v>0.0</v>
       </c>
       <c r="G28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H28" s="40">
         <v>0.0</v>
       </c>
       <c r="I28" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J28" s="39">
         <v>0.0</v>
@@ -3356,10 +3356,10 @@
         <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O28" s="40">
         <v>0.0</v>
@@ -3371,7 +3371,7 @@
         <v>3.0</v>
       </c>
       <c r="R28" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="S28" s="43">
         <v>0.0</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3394,32 +3394,32 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="38" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D29" s="40">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E29" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F29" s="40">
         <v>0.0</v>
       </c>
       <c r="G29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="40">
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3431,10 +3431,10 @@
         <v>1.0</v>
       </c>
       <c r="M29" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O29" s="40">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>3.0</v>
       </c>
       <c r="R29" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="S29" s="43">
         <v>0.0</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3469,47 +3469,47 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="45" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="D30" s="40">
+        <v>14.0</v>
+      </c>
+      <c r="E30" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J30" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="39">
         <v>3.0</v>
       </c>
-      <c r="D30" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J30" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="39">
-        <v>1.0</v>
-      </c>
       <c r="M30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="40">
         <v>0.0</v>
@@ -3521,17 +3521,17 @@
         <v>2.0</v>
       </c>
       <c r="R30" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="S30" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T30" s="41">
         <v>10.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3544,7 +3544,7 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="51" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
@@ -3554,13 +3554,13 @@
         <v>3.0</v>
       </c>
       <c r="D31" s="40">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="E31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="40">
         <v>0.0</v>
@@ -3569,7 +3569,7 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3578,13 +3578,13 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="40">
         <v>0.0</v>
@@ -3596,7 +3596,7 @@
         <v>2.0</v>
       </c>
       <c r="R31" s="40">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="S31" s="43">
         <v>0.0</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3619,20 +3619,20 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="51" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D32" s="40">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="E32" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F32" s="40">
         <v>0.0</v>
@@ -3644,7 +3644,7 @@
         <v>0.0</v>
       </c>
       <c r="I32" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J32" s="39">
         <v>0.0</v>
@@ -3653,35 +3653,35 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M32" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P32" s="42">
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R32" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S32" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="41">
         <v>10.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>555</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3694,14 +3694,14 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="46" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D33" s="40">
         <v>2.0</v>
@@ -3728,10 +3728,10 @@
         <v>0.0</v>
       </c>
       <c r="L33" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M33" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N33" s="40">
         <v>0.0</v>
@@ -3743,13 +3743,13 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="R33" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S33" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T33" s="41">
         <v>10.0</v>
@@ -3776,13 +3776,13 @@
         <v>32</v>
       </c>
       <c r="C34" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D34" s="40">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="E34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F34" s="40">
         <v>0.0</v>
@@ -3794,7 +3794,7 @@
         <v>0.0</v>
       </c>
       <c r="I34" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J34" s="39">
         <v>0.0</v>
@@ -3803,35 +3803,35 @@
         <v>0.0</v>
       </c>
       <c r="L34" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M34" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="39">
         <v>3.0</v>
       </c>
-      <c r="N34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P34" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R34" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S34" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T34" s="41">
         <v>10.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3844,17 +3844,17 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="45" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C35" s="39">
         <v>1.0</v>
       </c>
       <c r="D35" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E35" s="40">
         <v>0.0</v>
@@ -3869,7 +3869,7 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J35" s="39">
         <v>0.0</v>
@@ -3878,7 +3878,7 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" s="40">
         <v>0.0</v>
@@ -3893,20 +3893,20 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S35" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T35" s="41">
         <v>10.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3922,14 +3922,14 @@
       <c r="A36" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="50" t="s">
-        <v>32</v>
+      <c r="B36" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C36" s="39">
         <v>1.0</v>
       </c>
       <c r="D36" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3968,7 +3968,7 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R36" s="40">
         <v>1.0</v>
@@ -3994,17 +3994,17 @@
       <c r="AD36" s="9"/>
     </row>
     <row r="37">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="50" t="s">
         <v>32</v>
       </c>
       <c r="C37" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D37" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="E37" s="40">
         <v>0.0</v>
@@ -4019,7 +4019,7 @@
         <v>0.0</v>
       </c>
       <c r="I37" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J37" s="39">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>0.0</v>
       </c>
       <c r="L37" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M37" s="40">
         <v>0.0</v>
@@ -4046,7 +4046,7 @@
         <v>0.0</v>
       </c>
       <c r="R37" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S37" s="43">
         <v>0.0</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4379,16 +4379,16 @@
         <v>74</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="80">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="D4" s="81">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E4" s="81">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="F4" s="81">
         <v>0.0</v>
@@ -4397,7 +4397,7 @@
         <v>1.0</v>
       </c>
       <c r="H4" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I4" s="81">
         <v>0.0</v>
@@ -4424,11 +4424,11 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R4" s="84">
-        <f t="shared" ref="R4:R11" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>2985</v>
+        <f t="shared" ref="R4:R13" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>3420</v>
       </c>
     </row>
     <row r="5">
@@ -4489,23 +4489,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="78" t="s">
         <v>76</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="D6" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E6" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" s="42">
         <v>0.0</v>
@@ -4514,13 +4514,13 @@
         <v>0.0</v>
       </c>
       <c r="I6" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J6" s="42">
         <v>0.0</v>
       </c>
       <c r="K6" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L6" s="42">
         <v>0.0</v>
@@ -4535,97 +4535,97 @@
         <v>0.0</v>
       </c>
       <c r="P6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q6" s="83">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="R6" s="84">
         <f t="shared" si="1"/>
-        <v>1905</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>32</v>
+      <c r="B7" s="79" t="s">
+        <v>30</v>
       </c>
       <c r="C7" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="D7" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E7" s="42">
+        <v>10.0</v>
+      </c>
+      <c r="F7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="81">
+        <v>2.0</v>
+      </c>
+      <c r="J7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="M7" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q7" s="83">
         <v>12.0</v>
-      </c>
-      <c r="D7" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="E7" s="42">
-        <v>9.0</v>
-      </c>
-      <c r="F7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H7" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K7" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M7" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q7" s="83">
-        <v>10.0</v>
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="8" hidden="1">
-      <c r="A8" s="86" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="85" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="82">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="D8" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E8" s="42">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="F8" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I8" s="81">
         <v>0.0</v>
@@ -4649,37 +4649,37 @@
         <v>0.0</v>
       </c>
       <c r="P8" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q8" s="83">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="9" hidden="1">
-      <c r="A9" s="87" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="78" t="s">
         <v>79</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="82">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D9" s="42">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="E9" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F9" s="42">
         <v>0.0</v>
       </c>
       <c r="G9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H9" s="81">
         <v>0.0</v>
@@ -4688,7 +4688,7 @@
         <v>0.0</v>
       </c>
       <c r="J9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K9" s="82">
         <v>0.0</v>
@@ -4713,33 +4713,33 @@
       </c>
       <c r="R9" s="84">
         <f t="shared" si="1"/>
-        <v>1515</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="86" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="82">
         <v>14.0</v>
       </c>
       <c r="D10" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E10" s="42">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="F10" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G10" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H10" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I10" s="42">
         <v>0.0</v>
@@ -4766,28 +4766,28 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R10" s="84">
         <f t="shared" si="1"/>
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="11" hidden="1">
-      <c r="A11" s="85" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="86" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="82">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="D11" s="42">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E11" s="42">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="F11" s="42">
         <v>0.0</v>
@@ -4802,10 +4802,10 @@
         <v>0.0</v>
       </c>
       <c r="J11" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K11" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L11" s="42">
         <v>0.0</v>
@@ -4823,15 +4823,15 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="83">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R11" s="84">
         <f t="shared" si="1"/>
-        <v>1470</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="78" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="42" t="s">
@@ -4841,13 +4841,13 @@
         <v>14.0</v>
       </c>
       <c r="D12" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E12" s="42">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="42">
         <v>0.0</v>
@@ -4877,17 +4877,17 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q12" s="83">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="R12" s="84">
-        <f>C12*$C$2+D12*$D$2+E12*$E$2+F12*$F$2+G12*$G$2+H12*$H$2+K12*$K$2+L12*$L$2+M12*$M$2+N12*$N$2+O12*$O$2+P12*$P$2+Q12*$Q$2</f>
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="13" hidden="1">
+        <f t="shared" si="1"/>
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="86" t="s">
         <v>83</v>
       </c>
@@ -4895,13 +4895,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D13" s="42">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E13" s="42">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
@@ -4910,16 +4910,16 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L13" s="42">
         <v>0.0</v>
@@ -4937,25 +4937,25 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R13" s="84">
-        <f t="shared" ref="R13:R35" si="2">C13*$C$2+D13*$D$2+E13*$E$2+F13*$F$2+G13*$G$2+H13*$H$2+K13*$K$2+L13*$L$2+M13*$M$2+N13*$N$2+O13*$O$2+P13*$P$2+Q13*$Q$2+I13*$I$2+J13*$J$2</f>
+        <f t="shared" si="1"/>
         <v>1710</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="87" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="82">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="D14" s="42">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E14" s="42">
         <v>6.0</v>
@@ -4970,13 +4970,13 @@
         <v>0.0</v>
       </c>
       <c r="I14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J14" s="42">
         <v>0.0</v>
       </c>
       <c r="K14" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L14" s="42">
         <v>0.0</v>
@@ -4991,28 +4991,28 @@
         <v>0.0</v>
       </c>
       <c r="P14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q14" s="83">
         <v>10.0</v>
       </c>
       <c r="R14" s="84">
-        <f t="shared" si="2"/>
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="15" hidden="1">
-      <c r="A15" s="86" t="s">
+        <f>C14*$C$2+D14*$D$2+E14*$E$2+F14*$F$2+G14*$G$2+H14*$H$2+K14*$K$2+L14*$L$2+M14*$M$2+N14*$N$2+O14*$O$2+P14*$P$2+Q14*$Q$2</f>
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="88" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="82">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="D15" s="42">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E15" s="42">
         <v>8.0</v>
@@ -5024,7 +5024,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I15" s="81">
         <v>0.0</v>
@@ -5051,31 +5051,31 @@
         <v>1.0</v>
       </c>
       <c r="Q15" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R15" s="84">
-        <f t="shared" si="2"/>
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="16" hidden="1">
-      <c r="A16" s="89" t="s">
+        <f t="shared" ref="R15:R35" si="2">C15*$C$2+D15*$D$2+E15*$E$2+F15*$F$2+G15*$G$2+H15*$H$2+K15*$K$2+L15*$L$2+M15*$M$2+N15*$N$2+O15*$O$2+P15*$P$2+Q15*$Q$2+I15*$I$2+J15*$J$2</f>
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="85" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="82">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D16" s="42">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E16" s="42">
         <v>4.0</v>
       </c>
       <c r="F16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="42">
         <v>0.0</v>
@@ -5108,31 +5108,31 @@
         <v>1.0</v>
       </c>
       <c r="Q16" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R16" s="84">
         <f t="shared" si="2"/>
-        <v>1335</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="79" t="s">
-        <v>32</v>
+      <c r="B17" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C17" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="D17" s="42">
         <v>9.0</v>
       </c>
-      <c r="D17" s="42">
-        <v>5.0</v>
-      </c>
       <c r="E17" s="42">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="42">
         <v>0.0</v>
@@ -5141,7 +5141,7 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5150,7 +5150,7 @@
         <v>0.0</v>
       </c>
       <c r="L17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M17" s="83">
         <v>0.0</v>
@@ -5162,17 +5162,17 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="R17" s="84">
         <f t="shared" si="2"/>
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="18" hidden="1">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="78" t="s">
         <v>88</v>
       </c>
@@ -5222,14 +5222,14 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="19" hidden="1">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="86" t="s">
         <v>89</v>
       </c>
@@ -5279,11 +5279,11 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="20">
@@ -5343,8 +5343,8 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="21" hidden="1">
-      <c r="A21" s="88" t="s">
+    <row r="21">
+      <c r="A21" s="87" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
@@ -5393,15 +5393,15 @@
         <v>1.0</v>
       </c>
       <c r="Q21" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="22" hidden="1">
-      <c r="A22" s="88" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="87" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
@@ -5450,14 +5450,14 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="83">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R22" s="84">
         <f t="shared" si="2"/>
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="23" hidden="1">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="86" t="s">
         <v>93</v>
       </c>
@@ -5507,28 +5507,28 @@
         <v>1.0</v>
       </c>
       <c r="Q23" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="82">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D24" s="42">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="E24" s="42">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5537,13 +5537,13 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="82">
         <v>0.0</v>
@@ -5561,31 +5561,31 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
-        <v>1035</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="79" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="82">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D25" s="42">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E25" s="42">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F25" s="42">
         <v>0.0</v>
@@ -5594,13 +5594,13 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I25" s="81">
         <v>0.0</v>
       </c>
       <c r="J25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K25" s="82">
         <v>0.0</v>
@@ -5621,15 +5621,15 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R25" s="84">
         <f t="shared" si="2"/>
-        <v>1020</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="87" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
@@ -5693,13 +5693,13 @@
         <v>32</v>
       </c>
       <c r="C27" s="82">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="D27" s="42">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E27" s="42">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5708,7 +5708,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I27" s="42">
         <v>0.0</v>
@@ -5739,27 +5739,27 @@
       </c>
       <c r="R27" s="84">
         <f t="shared" si="2"/>
-        <v>795</v>
-      </c>
-    </row>
-    <row r="28" hidden="1">
-      <c r="A28" s="82" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="78" t="s">
         <v>98</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C28" s="82">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D28" s="42">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E28" s="42">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F28" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" s="42">
         <v>0.0</v>
@@ -5796,33 +5796,33 @@
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
-        <v>645</v>
+        <v>795</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="78" t="s">
+      <c r="A29" s="82" t="s">
         <v>99</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="82">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D29" s="42">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E29" s="42">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G29" s="42">
         <v>0.0</v>
       </c>
       <c r="H29" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29" s="42">
         <v>0.0</v>
@@ -5846,18 +5846,18 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q29" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>645</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="88" t="s">
+      <c r="A30" s="87" t="s">
         <v>100</v>
       </c>
       <c r="B30" s="79" t="s">
@@ -6084,7 +6084,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="34" hidden="1">
+    <row r="34">
       <c r="A34" s="94" t="s">
         <v>104</v>
       </c>
@@ -6134,14 +6134,14 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="93">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R34" s="84">
         <f t="shared" si="2"/>
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35" hidden="1">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="96" t="s">
         <v>105</v>
       </c>
@@ -6191,20 +6191,15 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="100">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R35" s="101">
         <f t="shared" si="2"/>
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="$A$3:$R$35">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="B"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A3:R35">
       <sortCondition descending="1" ref="R3:R35"/>
       <sortCondition ref="A3:A35"/>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/23/2026</t>
+    <t>Actualización: 6/24/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -128,39 +128,39 @@
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Cavero, Braulio</t>
+  </si>
+  <si>
     <t>Castillo, Wesly</t>
   </si>
   <si>
-    <t>Cavero, Braulio</t>
-  </si>
-  <si>
     <t>Rosario, Elian</t>
   </si>
   <si>
     <t>Diaz, David</t>
   </si>
   <si>
+    <t>Ramirez, Santiago</t>
+  </si>
+  <si>
+    <t>Benitez, Frainker</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
-    <t>Ramirez, Santiago</t>
-  </si>
-  <si>
     <t>Done, Carlos</t>
   </si>
   <si>
+    <t>Valdes, Abel</t>
+  </si>
+  <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
-    <t>Valdes, Abel</t>
-  </si>
-  <si>
     <t>Marcano, Jose</t>
   </si>
   <si>
@@ -170,18 +170,21 @@
     <t>Pinder, Jayln</t>
   </si>
   <si>
+    <t>Rodriguez, Victor</t>
+  </si>
+  <si>
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
-    <t>Rodriguez, Victor</t>
-  </si>
-  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
+    <t>Montero, Darling</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
@@ -191,9 +194,6 @@
     <t>Santa, Fraimy</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
-  </si>
-  <si>
     <t>Ortiz Jr, David</t>
   </si>
   <si>
@@ -245,6 +245,9 @@
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Gamez, Manuel</t>
+  </si>
+  <si>
     <t>Pineda, Frandel</t>
   </si>
   <si>
@@ -254,21 +257,18 @@
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
-    <t>Gamez, Manuel</t>
-  </si>
-  <si>
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
     <t>Medina, Juan</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Santos, Aneudy</t>
   </si>
   <si>
@@ -278,13 +278,16 @@
     <t>Granado, Argenis</t>
   </si>
   <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
     <t>Pena, Dariel</t>
   </si>
   <si>
     <t>Castillo, Albert</t>
   </si>
   <si>
-    <t>Fernandez, Jehiber</t>
+    <t>Ballesteros, Jean</t>
   </si>
   <si>
     <t>Acosta, Isaac</t>
@@ -296,24 +299,24 @@
     <t>Cordero, Albert</t>
   </si>
   <si>
+    <t>Figuereo, Breyner</t>
+  </si>
+  <si>
     <t>Lamu, Alex</t>
   </si>
   <si>
     <t>Ramos, Daniel</t>
   </si>
   <si>
-    <t>Figuereo, Breyner</t>
-  </si>
-  <si>
-    <t>Ballesteros, Jean</t>
-  </si>
-  <si>
     <t>Peralta, Eddy</t>
   </si>
   <si>
     <t>Perez, Juanangel</t>
   </si>
   <si>
+    <t>Figuereo, Enmanuel</t>
+  </si>
+  <si>
     <t>Liriano, Edgar</t>
   </si>
   <si>
@@ -327,9 +330,6 @@
   </si>
   <si>
     <t>Fernandez, Harley</t>
-  </si>
-  <si>
-    <t>Figuereo, Enmanuel</t>
   </si>
   <si>
     <t>Gonzalez, Nestor</t>
@@ -813,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="100">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -942,11 +942,11 @@
     <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1070,12 +1070,6 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="35" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1601,16 +1595,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="D5" s="40">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E5" s="40">
         <v>8.0</v>
       </c>
       <c r="F5" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G5" s="40">
         <v>3.0</v>
@@ -1631,7 +1625,7 @@
         <v>4.0</v>
       </c>
       <c r="M5" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="N5" s="40">
         <v>2.0</v>
@@ -1643,7 +1637,7 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R5" s="40">
         <v>5.0</v>
@@ -1652,11 +1646,11 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>2655</v>
+        <v>2790</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1676,13 +1670,13 @@
         <v>32</v>
       </c>
       <c r="C6" s="39">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D6" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E6" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F6" s="40">
         <v>2.0</v>
@@ -1727,11 +1721,11 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>2370</v>
+        <v>2580</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1802,11 +1796,11 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>2310</v>
+        <v>2340</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1826,16 +1820,16 @@
         <v>32</v>
       </c>
       <c r="C8" s="39">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D8" s="40">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E8" s="40">
         <v>3.0</v>
       </c>
       <c r="F8" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G8" s="40">
         <v>2.0</v>
@@ -1856,7 +1850,7 @@
         <v>4.0</v>
       </c>
       <c r="M8" s="40">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="N8" s="40">
         <v>0.0</v>
@@ -1877,11 +1871,11 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>2145</v>
+        <v>2310</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1901,10 +1895,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D9" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E9" s="40">
         <v>7.0</v>
@@ -1919,7 +1913,7 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="41">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="J9" s="39">
         <v>0.0</v>
@@ -1931,7 +1925,7 @@
         <v>5.0</v>
       </c>
       <c r="M9" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N9" s="40">
         <v>3.0</v>
@@ -1943,7 +1937,7 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R9" s="40">
         <v>4.0</v>
@@ -1952,11 +1946,11 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>2100</v>
+        <v>2280</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1976,16 +1970,16 @@
         <v>30</v>
       </c>
       <c r="C10" s="47">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D10" s="48">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E10" s="48">
         <v>9.0</v>
       </c>
       <c r="F10" s="48">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G10" s="48">
         <v>2.0</v>
@@ -1994,7 +1988,7 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="49">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="J10" s="39">
         <v>0.0</v>
@@ -2018,7 +2012,7 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R10" s="40">
         <v>6.0</v>
@@ -2027,11 +2021,11 @@
         <v>3.0</v>
       </c>
       <c r="T10" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>2025</v>
+        <v>2175</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2044,35 +2038,35 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="39">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="D11" s="40">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="E11" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F11" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H11" s="40">
         <v>0.0</v>
       </c>
       <c r="I11" s="41">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="J11" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K11" s="41">
         <v>0.0</v>
@@ -2084,7 +2078,7 @@
         <v>0.0</v>
       </c>
       <c r="N11" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O11" s="40">
         <v>0.0</v>
@@ -2093,20 +2087,20 @@
         <v>0.0</v>
       </c>
       <c r="Q11" s="39">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="R11" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S11" s="43">
         <v>2.0</v>
       </c>
       <c r="T11" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>1935</v>
+        <v>1995</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2119,59 +2113,59 @@
       <c r="AD11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="45" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="39">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="D12" s="40">
+        <v>17.0</v>
+      </c>
+      <c r="E12" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F12" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="41">
+        <v>6.0</v>
+      </c>
+      <c r="J12" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="K12" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="39">
         <v>4.0</v>
       </c>
-      <c r="E12" s="40">
+      <c r="R12" s="40">
         <v>4.0</v>
-      </c>
-      <c r="F12" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="G12" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="H12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J12" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R12" s="40">
-        <v>2.0</v>
       </c>
       <c r="S12" s="43">
         <v>2.0</v>
@@ -2181,7 +2175,7 @@
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>1740</v>
+        <v>1845</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2234,7 +2228,7 @@
         <v>1.0</v>
       </c>
       <c r="N13" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O13" s="40">
         <v>0.0</v>
@@ -2243,7 +2237,7 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R13" s="40">
         <v>4.0</v>
@@ -2252,11 +2246,11 @@
         <v>3.0</v>
       </c>
       <c r="T13" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1665</v>
+        <v>1755</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2279,7 +2273,7 @@
         <v>11.0</v>
       </c>
       <c r="D14" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E14" s="40">
         <v>1.0</v>
@@ -2306,7 +2300,7 @@
         <v>2.0</v>
       </c>
       <c r="M14" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="N14" s="40">
         <v>2.0</v>
@@ -2318,7 +2312,7 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R14" s="40">
         <v>4.0</v>
@@ -2327,11 +2321,11 @@
         <v>2.0</v>
       </c>
       <c r="T14" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1545</v>
+        <v>1590</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2344,26 +2338,26 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="50" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="D15" s="40">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E15" s="40">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F15" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
@@ -2375,25 +2369,25 @@
         <v>0.0</v>
       </c>
       <c r="K15" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="M15" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N15" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O15" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="42">
         <v>0.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R15" s="40">
         <v>4.0</v>
@@ -2402,11 +2396,11 @@
         <v>2.0</v>
       </c>
       <c r="T15" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1485</v>
+        <v>1575</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2419,32 +2413,32 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="50" t="s">
-        <v>30</v>
+      <c r="B16" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="C16" s="39">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="D16" s="40">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="E16" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F16" s="40">
         <v>0.0</v>
       </c>
       <c r="G16" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
       </c>
       <c r="I16" s="41">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="J16" s="39">
         <v>0.0</v>
@@ -2456,32 +2450,32 @@
         <v>3.0</v>
       </c>
       <c r="M16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="R16" s="40">
         <v>3.0</v>
       </c>
-      <c r="N16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R16" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S16" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T16" s="41">
         <v>11.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1470</v>
+        <v>1575</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2494,17 +2488,17 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="39">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="D17" s="40">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="E17" s="40">
         <v>3.0</v>
@@ -2513,50 +2507,50 @@
         <v>0.0</v>
       </c>
       <c r="G17" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L17" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="M17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q17" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R17" s="40">
         <v>4.0</v>
       </c>
-      <c r="H17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J17" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q17" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="R17" s="40">
-        <v>3.0</v>
-      </c>
       <c r="S17" s="43">
         <v>2.0</v>
       </c>
       <c r="T17" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1365</v>
+        <v>1515</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2569,32 +2563,32 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="51" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="39">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="D18" s="40">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E18" s="40">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H18" s="40">
         <v>0.0</v>
       </c>
       <c r="I18" s="41">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="J18" s="39">
         <v>0.0</v>
@@ -2603,13 +2597,13 @@
         <v>0.0</v>
       </c>
       <c r="L18" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M18" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="N18" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O18" s="40">
         <v>0.0</v>
@@ -2618,20 +2612,20 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="R18" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S18" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1335</v>
+        <v>1500</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2651,7 +2645,7 @@
         <v>30</v>
       </c>
       <c r="C19" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D19" s="40">
         <v>18.0</v>
@@ -2693,7 +2687,7 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R19" s="40">
         <v>4.0</v>
@@ -2702,11 +2696,11 @@
         <v>3.0</v>
       </c>
       <c r="T19" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1395</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2719,69 +2713,69 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="46" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D20" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="E20" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F20" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q20" s="39">
         <v>6.0</v>
       </c>
-      <c r="E20" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="39">
-        <v>3.0</v>
-      </c>
       <c r="R20" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="S20" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T20" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1185</v>
+        <v>1245</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2794,69 +2788,69 @@
       <c r="AD20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="45" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C21" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D21" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="E21" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="41">
         <v>3.0</v>
       </c>
-      <c r="D21" s="40">
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="M21" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="N21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q21" s="39">
         <v>3.0</v>
       </c>
-      <c r="E21" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="F21" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="G21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P21" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q21" s="39">
+      <c r="R21" s="40">
         <v>5.0</v>
       </c>
-      <c r="R21" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S21" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T21" s="41">
         <v>11.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2927,11 +2921,11 @@
         <v>0.0</v>
       </c>
       <c r="T22" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1095</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -3002,11 +2996,11 @@
         <v>2.0</v>
       </c>
       <c r="T23" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3022,7 +3016,7 @@
       <c r="A24" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="51" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="39">
@@ -3077,11 +3071,11 @@
         <v>2.0</v>
       </c>
       <c r="T24" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1065</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3094,32 +3088,32 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="45" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C25" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D25" s="40">
         <v>4.0</v>
       </c>
       <c r="E25" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F25" s="40">
         <v>1.0</v>
       </c>
       <c r="G25" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H25" s="40">
         <v>0.0</v>
       </c>
       <c r="I25" s="41">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J25" s="39">
         <v>0.0</v>
@@ -3128,13 +3122,13 @@
         <v>0.0</v>
       </c>
       <c r="L25" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M25" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N25" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O25" s="40">
         <v>0.0</v>
@@ -3143,10 +3137,10 @@
         <v>0.0</v>
       </c>
       <c r="Q25" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R25" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S25" s="43">
         <v>1.0</v>
@@ -3156,7 +3150,7 @@
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>870</v>
+        <v>1020</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3169,26 +3163,26 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="46" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D26" s="40">
         <v>4.0</v>
       </c>
       <c r="E26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F26" s="40">
         <v>1.0</v>
       </c>
       <c r="G26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="40">
         <v>0.0</v>
@@ -3203,13 +3197,13 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="40">
         <v>0.0</v>
@@ -3218,20 +3212,20 @@
         <v>0.0</v>
       </c>
       <c r="Q26" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R26" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S26" s="43">
         <v>1.0</v>
       </c>
       <c r="T26" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>900</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3302,11 +3296,11 @@
         <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>855</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3322,14 +3316,14 @@
       <c r="A28" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="51" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D28" s="40">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E28" s="40">
         <v>0.0</v>
@@ -3356,13 +3350,13 @@
         <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N28" s="40">
         <v>1.0</v>
       </c>
       <c r="O28" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P28" s="42">
         <v>0.0</v>
@@ -3377,11 +3371,11 @@
         <v>0.0</v>
       </c>
       <c r="T28" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>735</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3394,17 +3388,17 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="50" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="39">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D29" s="40">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="E29" s="40">
         <v>2.0</v>
@@ -3413,13 +3407,13 @@
         <v>0.0</v>
       </c>
       <c r="G29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="40">
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3428,35 +3422,35 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M29" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="N29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P29" s="42">
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R29" s="40">
         <v>3.0</v>
       </c>
-      <c r="R29" s="40">
-        <v>1.0</v>
-      </c>
       <c r="S29" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T29" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3479,22 +3473,22 @@
         <v>4.0</v>
       </c>
       <c r="D30" s="40">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="E30" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F30" s="40">
         <v>0.0</v>
       </c>
       <c r="G30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H30" s="40">
         <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
@@ -3503,35 +3497,35 @@
         <v>0.0</v>
       </c>
       <c r="L30" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P30" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q30" s="39">
         <v>3.0</v>
       </c>
-      <c r="M30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P30" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q30" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R30" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="S30" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T30" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>630</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3544,50 +3538,50 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="45" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D31" s="40">
+        <v>16.0</v>
+      </c>
+      <c r="E31" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I31" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J31" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="39">
         <v>3.0</v>
       </c>
-      <c r="D31" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F31" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I31" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J31" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L31" s="39">
-        <v>1.0</v>
-      </c>
       <c r="M31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P31" s="42">
         <v>0.0</v>
@@ -3596,17 +3590,17 @@
         <v>2.0</v>
       </c>
       <c r="R31" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="S31" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T31" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3619,23 +3613,23 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="50" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
         <v>32</v>
       </c>
       <c r="C32" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D32" s="40">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="E32" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G32" s="40">
         <v>0.0</v>
@@ -3644,7 +3638,7 @@
         <v>0.0</v>
       </c>
       <c r="I32" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J32" s="39">
         <v>0.0</v>
@@ -3653,16 +3647,16 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M32" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="N32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P32" s="42">
         <v>0.0</v>
@@ -3671,17 +3665,17 @@
         <v>2.0</v>
       </c>
       <c r="R32" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="S32" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T32" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>555</v>
+        <v>600</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3752,11 +3746,11 @@
         <v>0.0</v>
       </c>
       <c r="T33" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3769,7 +3763,7 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="50" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
@@ -3827,11 +3821,11 @@
         <v>1.0</v>
       </c>
       <c r="T34" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3902,11 +3896,11 @@
         <v>1.0</v>
       </c>
       <c r="T35" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3977,11 +3971,11 @@
         <v>0.0</v>
       </c>
       <c r="T36" s="41">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3997,7 +3991,7 @@
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="51" t="s">
         <v>32</v>
       </c>
       <c r="C37" s="39">
@@ -4052,11 +4046,11 @@
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4069,7 +4063,7 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="50" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
@@ -4127,11 +4121,11 @@
         <v>0.0</v>
       </c>
       <c r="T38" s="56">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4147,8 +4141,8 @@
   <autoFilter ref="$A$4:$U$38">
     <sortState ref="A4:U38">
       <sortCondition descending="1" ref="U4:U38"/>
+      <sortCondition ref="B4:B38"/>
       <sortCondition descending="1" ref="G4:G38"/>
-      <sortCondition ref="B4:B38"/>
       <sortCondition ref="A4:A38"/>
       <sortCondition descending="1" ref="F4:F38"/>
       <sortCondition descending="1" ref="M4:M38"/>
@@ -4221,8 +4215,7 @@
     <col customWidth="1" min="17" max="17" width="5.13"/>
     <col customWidth="1" min="18" max="18" width="6.88"/>
     <col customWidth="1" min="19" max="19" width="4.75"/>
-    <col customWidth="1" min="20" max="20" width="4.0"/>
-    <col customWidth="1" min="21" max="21" width="3.38"/>
+    <col customWidth="1" min="20" max="21" width="5.63"/>
     <col customWidth="1" min="22" max="22" width="3.75"/>
     <col customWidth="1" min="23" max="23" width="5.0"/>
     <col customWidth="1" min="24" max="24" width="3.0"/>
@@ -4424,11 +4417,11 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="83">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R4" s="84">
         <f t="shared" ref="R4:R13" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>3420</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="5">
@@ -4481,11 +4474,11 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="83">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R5" s="84">
         <f t="shared" si="1"/>
-        <v>2475</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="6">
@@ -4496,31 +4489,31 @@
         <v>32</v>
       </c>
       <c r="C6" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D6" s="42">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E6" s="42">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="F6" s="42">
         <v>0.0</v>
       </c>
       <c r="G6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H6" s="81">
         <v>0.0</v>
       </c>
       <c r="I6" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K6" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L6" s="42">
         <v>0.0</v>
@@ -4538,25 +4531,25 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R6" s="84">
         <f t="shared" si="1"/>
-        <v>2085</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="79" t="s">
-        <v>30</v>
+      <c r="B7" s="42" t="s">
+        <v>32</v>
       </c>
       <c r="C7" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D7" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E7" s="42">
         <v>10.0</v>
@@ -4571,16 +4564,16 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="81">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J7" s="42">
         <v>0.0</v>
       </c>
       <c r="K7" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="83">
         <v>0.0</v>
@@ -4592,34 +4585,34 @@
         <v>0.0</v>
       </c>
       <c r="P7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q7" s="83">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>2025</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>32</v>
+      <c r="B8" s="79" t="s">
+        <v>30</v>
       </c>
       <c r="C8" s="82">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="D8" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E8" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F8" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G8" s="42">
         <v>0.0</v>
@@ -4628,7 +4621,7 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J8" s="42">
         <v>0.0</v>
@@ -4637,7 +4630,7 @@
         <v>0.0</v>
       </c>
       <c r="L8" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M8" s="83">
         <v>0.0</v>
@@ -4652,34 +4645,34 @@
         <v>0.0</v>
       </c>
       <c r="Q8" s="83">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>1905</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="85" t="s">
         <v>79</v>
       </c>
       <c r="B9" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="82">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="D9" s="42">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E9" s="42">
         <v>9.0</v>
       </c>
       <c r="F9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" s="81">
         <v>0.0</v>
@@ -4688,7 +4681,7 @@
         <v>0.0</v>
       </c>
       <c r="J9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K9" s="82">
         <v>0.0</v>
@@ -4706,14 +4699,14 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q9" s="83">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R9" s="84">
         <f t="shared" si="1"/>
-        <v>1845</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="10">
@@ -4727,10 +4720,10 @@
         <v>14.0</v>
       </c>
       <c r="D10" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E10" s="42">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
@@ -4766,11 +4759,11 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R10" s="84">
         <f t="shared" si="1"/>
-        <v>1755</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="11">
@@ -4823,37 +4816,37 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R11" s="84">
         <f t="shared" si="1"/>
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="86" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D12" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E12" s="42">
         <v>8.0</v>
       </c>
       <c r="F12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" s="42">
         <v>0.0</v>
       </c>
       <c r="H12" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I12" s="81">
         <v>0.0</v>
@@ -4880,37 +4873,37 @@
         <v>1.0</v>
       </c>
       <c r="Q12" s="83">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="R12" s="84">
         <f t="shared" si="1"/>
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="78" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="D13" s="42">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="E13" s="42">
         <v>8.0</v>
       </c>
       <c r="F13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" s="42">
         <v>0.0</v>
       </c>
       <c r="H13" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
@@ -4937,11 +4930,11 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="83">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="R13" s="84">
         <f t="shared" si="1"/>
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="14">
@@ -4994,11 +4987,11 @@
         <v>1.0</v>
       </c>
       <c r="Q14" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R14" s="84">
         <f>C14*$C$2+D14*$D$2+E14*$E$2+F14*$F$2+G14*$G$2+H14*$H$2+K14*$K$2+L14*$L$2+M14*$M$2+N14*$N$2+O14*$O$2+P14*$P$2+Q14*$Q$2</f>
-        <v>1695</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="15">
@@ -5009,10 +5002,10 @@
         <v>30</v>
       </c>
       <c r="C15" s="82">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="D15" s="42">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="E15" s="42">
         <v>8.0</v>
@@ -5024,7 +5017,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I15" s="81">
         <v>0.0</v>
@@ -5051,11 +5044,11 @@
         <v>1.0</v>
       </c>
       <c r="Q15" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R15" s="84">
         <f t="shared" ref="R15:R35" si="2">C15*$C$2+D15*$D$2+E15*$E$2+F15*$F$2+G15*$G$2+H15*$H$2+K15*$K$2+L15*$L$2+M15*$M$2+N15*$N$2+O15*$O$2+P15*$P$2+Q15*$Q$2+I15*$I$2+J15*$J$2</f>
-        <v>1545</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="16">
@@ -5108,40 +5101,40 @@
         <v>1.0</v>
       </c>
       <c r="Q16" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R16" s="84">
         <f t="shared" si="2"/>
-        <v>1500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="86" t="s">
         <v>87</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D17" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E17" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" s="42">
         <v>0.0</v>
       </c>
       <c r="H17" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5162,28 +5155,28 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R17" s="84">
         <f t="shared" si="2"/>
-        <v>1365</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="89" t="s">
         <v>88</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="82">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="D18" s="42">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E18" s="42">
         <v>4.0</v>
@@ -5219,43 +5212,43 @@
         <v>0.0</v>
       </c>
       <c r="P18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q18" s="83">
         <v>11.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1335</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="78" t="s">
         <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="82">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="D19" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E19" s="42">
         <v>4.0</v>
       </c>
       <c r="F19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G19" s="42">
         <v>0.0</v>
       </c>
       <c r="H19" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J19" s="42">
         <v>0.0</v>
@@ -5279,85 +5272,85 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="87" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="82">
+        <v>10.0</v>
+      </c>
+      <c r="D20" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E20" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="F20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="83">
         <v>11.0</v>
-      </c>
-      <c r="D20" s="42">
-        <v>11.0</v>
-      </c>
-      <c r="E20" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="F20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I20" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K20" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="83">
-        <v>10.0</v>
       </c>
       <c r="R20" s="84">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="87" t="s">
+      <c r="A21" s="78" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C21" s="82">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D21" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E21" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F21" s="42">
         <v>0.0</v>
@@ -5366,13 +5359,13 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I21" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K21" s="82">
         <v>0.0</v>
@@ -5390,14 +5383,14 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q21" s="83">
         <v>11.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="22">
@@ -5408,25 +5401,25 @@
         <v>30</v>
       </c>
       <c r="C22" s="82">
+        <v>9.0</v>
+      </c>
+      <c r="D22" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="E22" s="42">
         <v>7.0</v>
       </c>
-      <c r="D22" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="E22" s="42">
-        <v>5.0</v>
-      </c>
       <c r="F22" s="42">
         <v>0.0</v>
       </c>
       <c r="G22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H22" s="81">
         <v>0.0</v>
       </c>
       <c r="I22" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J22" s="42">
         <v>0.0</v>
@@ -5450,25 +5443,25 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="83">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R22" s="84">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="87" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="82">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="D23" s="42">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E23" s="42">
         <v>5.0</v>
@@ -5477,7 +5470,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H23" s="81">
         <v>0.0</v>
@@ -5511,24 +5504,24 @@
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>1155</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="79" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="82">
         <v>12.0</v>
       </c>
       <c r="D24" s="42">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="E24" s="42">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5537,13 +5530,13 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="82">
         <v>0.0</v>
@@ -5561,31 +5554,31 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="79" t="s">
-        <v>32</v>
+      <c r="B25" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C25" s="82">
         <v>9.0</v>
       </c>
       <c r="D25" s="42">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="E25" s="42">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F25" s="42">
         <v>0.0</v>
@@ -5594,13 +5587,13 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I25" s="81">
         <v>0.0</v>
       </c>
       <c r="J25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K25" s="82">
         <v>0.0</v>
@@ -5621,28 +5614,28 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R25" s="84">
         <f t="shared" si="2"/>
-        <v>1035</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="87" t="s">
+      <c r="A26" s="78" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="82">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="D26" s="42">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="E26" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
@@ -5675,14 +5668,14 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q26" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>1020</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="27">
@@ -5735,11 +5728,11 @@
         <v>1.0</v>
       </c>
       <c r="Q27" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R27" s="84">
         <f t="shared" si="2"/>
-        <v>930</v>
+        <v>960</v>
       </c>
     </row>
     <row r="28">
@@ -5753,7 +5746,7 @@
         <v>7.0</v>
       </c>
       <c r="D28" s="42">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E28" s="42">
         <v>4.0</v>
@@ -5792,7 +5785,7 @@
         <v>1.0</v>
       </c>
       <c r="Q28" s="83">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
@@ -5800,23 +5793,23 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="82" t="s">
+      <c r="A29" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="79" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="82">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D29" s="42">
         <v>11.0</v>
       </c>
       <c r="E29" s="42">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="42">
         <v>0.0</v>
@@ -5846,40 +5839,40 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q29" s="83">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>675</v>
+        <v>735</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="79" t="s">
-        <v>32</v>
+      <c r="B30" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C30" s="82">
         <v>5.0</v>
       </c>
       <c r="D30" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E30" s="42">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F30" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="42">
         <v>0.0</v>
       </c>
       <c r="H30" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30" s="42">
         <v>0.0</v>
@@ -5903,31 +5896,31 @@
         <v>0.0</v>
       </c>
       <c r="P30" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q30" s="83">
         <v>12.0</v>
       </c>
       <c r="R30" s="84">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>705</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="79" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="82">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D31" s="42">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="E31" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -5936,7 +5929,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="81">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I31" s="42">
         <v>0.0</v>
@@ -5963,11 +5956,11 @@
         <v>0.0</v>
       </c>
       <c r="Q31" s="83">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="R31" s="84">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32">
@@ -5978,53 +5971,53 @@
         <v>32</v>
       </c>
       <c r="C32" s="82">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D32" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="E32" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="F32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="81">
+        <v>2.0</v>
+      </c>
+      <c r="I32" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q32" s="83">
         <v>11.0</v>
-      </c>
-      <c r="E32" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="F32" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q32" s="83">
-        <v>9.0</v>
       </c>
       <c r="R32" s="84">
         <f t="shared" si="2"/>
-        <v>405</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33">
@@ -6035,13 +6028,13 @@
         <v>32</v>
       </c>
       <c r="C33" s="92">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D33" s="91">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="E33" s="91">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="91">
         <v>0.0</v>
@@ -6074,31 +6067,31 @@
         <v>0.0</v>
       </c>
       <c r="P33" s="91">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q33" s="93">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R33" s="84">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="95" t="s">
-        <v>30</v>
+      <c r="B34" s="91" t="s">
+        <v>32</v>
       </c>
       <c r="C34" s="92">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D34" s="91">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="E34" s="91">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F34" s="91">
         <v>0.0</v>
@@ -6134,21 +6127,21 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="93">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R34" s="84">
         <f t="shared" si="2"/>
-        <v>375</v>
+        <v>420</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="96" t="s">
+      <c r="A35" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="98">
+      <c r="C35" s="96">
         <v>0.0</v>
       </c>
       <c r="D35" s="54">
@@ -6163,25 +6156,25 @@
       <c r="G35" s="54">
         <v>0.0</v>
       </c>
-      <c r="H35" s="99">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="99">
+      <c r="H35" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="97">
         <v>0.0</v>
       </c>
       <c r="J35" s="54">
         <v>0.0</v>
       </c>
-      <c r="K35" s="98">
+      <c r="K35" s="96">
         <v>0.0</v>
       </c>
       <c r="L35" s="54">
         <v>0.0</v>
       </c>
-      <c r="M35" s="100">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="98">
+      <c r="M35" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="96">
         <v>0.0</v>
       </c>
       <c r="O35" s="54">
@@ -6190,12 +6183,12 @@
       <c r="P35" s="54">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="100">
-        <v>9.0</v>
-      </c>
-      <c r="R35" s="101">
+      <c r="Q35" s="98">
+        <v>10.0</v>
+      </c>
+      <c r="R35" s="99">
         <f t="shared" si="2"/>
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -110,66 +110,66 @@
     <t>R</t>
   </si>
   <si>
+    <t>Mateo, Cesar</t>
+  </si>
+  <si>
+    <t>Rodriguez, Alex</t>
+  </si>
+  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Rodriguez, Alex</t>
+    <t>Zayas, Saivel</t>
+  </si>
+  <si>
+    <t>Cavero, Braulio</t>
   </si>
   <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
-    <t>Mateo, Cesar</t>
-  </si>
-  <si>
-    <t>Zayas, Saivel</t>
-  </si>
-  <si>
-    <t>Cavero, Braulio</t>
+    <t>Rosario, Elian</t>
   </si>
   <si>
     <t>Castillo, Wesly</t>
   </si>
   <si>
-    <t>Rosario, Elian</t>
-  </si>
-  <si>
     <t>Diaz, David</t>
   </si>
   <si>
+    <t>Gonzalez, Victor</t>
+  </si>
+  <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
-    <t>Gonzalez, Victor</t>
-  </si>
-  <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
+    <t>Marcano, Jose</t>
+  </si>
+  <si>
+    <t>Pinder, Jayln</t>
+  </si>
+  <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
-    <t>Marcano, Jose</t>
-  </si>
-  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
-    <t>Pinder, Jayln</t>
-  </si>
-  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
@@ -185,27 +185,27 @@
     <t>Montero, Darling</t>
   </si>
   <si>
+    <t>Ortiz Jr, David</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Genao, Jhostin</t>
   </si>
   <si>
+    <t>Colina, Felix</t>
+  </si>
+  <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
-    <t>Ortiz Jr, David</t>
-  </si>
-  <si>
-    <t>Colina, Felix</t>
+    <t>Seminiel, Cristian</t>
   </si>
   <si>
     <t>Coronado, Francisco</t>
   </si>
   <si>
-    <t>Seminiel, Cristian</t>
-  </si>
-  <si>
     <t>Cedeno, Luis</t>
   </si>
   <si>
@@ -245,6 +245,9 @@
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Medina, Juan</t>
+  </si>
+  <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
@@ -254,28 +257,34 @@
     <t>Gomez, Manuel</t>
   </si>
   <si>
+    <t>Granado, Argenis</t>
+  </si>
+  <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
+    <t>Castillo, Albert</t>
+  </si>
+  <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
-    <t>Medina, Juan</t>
-  </si>
-  <si>
     <t>Santos, Aneudy</t>
   </si>
   <si>
     <t>Lara, Carlos</t>
   </si>
   <si>
-    <t>Granado, Argenis</t>
+    <t>Alcantara, Jostin</t>
+  </si>
+  <si>
+    <t>Acosta, Isaac</t>
   </si>
   <si>
     <t>Fernandez, Jehiber</t>
@@ -284,33 +293,24 @@
     <t>Pena, Dariel</t>
   </si>
   <si>
-    <t>Castillo, Albert</t>
+    <t>Peralta, Eddy</t>
   </si>
   <si>
     <t>Ballesteros, Jean</t>
   </si>
   <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
-    <t>Alcantara, Jostin</t>
-  </si>
-  <si>
     <t>Cordero, Albert</t>
   </si>
   <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
+    <t>Lamu, Alex</t>
+  </si>
+  <si>
     <t>Figuereo, Breyner</t>
   </si>
   <si>
-    <t>Lamu, Alex</t>
-  </si>
-  <si>
-    <t>Ramos, Daniel</t>
-  </si>
-  <si>
-    <t>Peralta, Eddy</t>
-  </si>
-  <si>
     <t>Perez, Juanangel</t>
   </si>
   <si>
@@ -320,13 +320,13 @@
     <t>Liriano, Edgar</t>
   </si>
   <si>
+    <t>Medina, Ruben</t>
+  </si>
+  <si>
+    <t>Bautista, Jeyson</t>
+  </si>
+  <si>
     <t>De Jesus, Yunier</t>
-  </si>
-  <si>
-    <t>Medina, Ruben</t>
-  </si>
-  <si>
-    <t>Bautista, Jeyson</t>
   </si>
   <si>
     <t>Fernandez, Harley</t>
@@ -813,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -927,12 +927,12 @@
     <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -942,11 +942,11 @@
     <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1060,17 +1060,23 @@
     <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="35" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1595,19 +1601,19 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="D5" s="40">
         <v>13.0</v>
       </c>
       <c r="E5" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F5" s="40">
         <v>6.0</v>
       </c>
       <c r="G5" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="40">
         <v>0.0</v>
@@ -1616,7 +1622,7 @@
         <v>0.0</v>
       </c>
       <c r="J5" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K5" s="41">
         <v>0.0</v>
@@ -1625,7 +1631,7 @@
         <v>4.0</v>
       </c>
       <c r="M5" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="N5" s="40">
         <v>2.0</v>
@@ -1637,7 +1643,7 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R5" s="40">
         <v>5.0</v>
@@ -1646,11 +1652,11 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>2790</v>
+        <v>3270</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1663,69 +1669,69 @@
       <c r="AD5" s="9"/>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="37" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="D6" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="E6" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="F6" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="41">
+        <v>23.0</v>
+      </c>
+      <c r="J6" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="39">
         <v>7.0</v>
       </c>
-      <c r="E6" s="40">
+      <c r="M6" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="N6" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>9.0</v>
+      </c>
+      <c r="R6" s="40">
         <v>4.0</v>
       </c>
-      <c r="F6" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J6" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L6" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R6" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S6" s="43">
         <v>2.0</v>
       </c>
       <c r="T6" s="41">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>2580</v>
+        <v>2745</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1738,14 +1744,14 @@
       <c r="AD6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="s">
-        <v>33</v>
+      <c r="A7" s="45" t="s">
+        <v>32</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="39">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="D7" s="40">
         <v>8.0</v>
@@ -1763,7 +1769,7 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="41">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="J7" s="39">
         <v>2.0</v>
@@ -1778,7 +1784,7 @@
         <v>1.0</v>
       </c>
       <c r="N7" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O7" s="40">
         <v>0.0</v>
@@ -1796,11 +1802,11 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>2340</v>
+        <v>2745</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1813,44 +1819,44 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>32</v>
-      </c>
       <c r="C8" s="39">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="D8" s="40">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="E8" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L8" s="39">
         <v>3.0</v>
       </c>
-      <c r="F8" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="G8" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>4.0</v>
-      </c>
       <c r="M8" s="40">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="N8" s="40">
         <v>0.0</v>
@@ -1862,20 +1868,20 @@
         <v>0.0</v>
       </c>
       <c r="Q8" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R8" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S8" s="43">
         <v>2.0</v>
       </c>
       <c r="T8" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>2310</v>
+        <v>2625</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1894,63 +1900,63 @@
       <c r="B9" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="D9" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="E9" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="F9" s="40">
+      <c r="C9" s="47">
+        <v>11.0</v>
+      </c>
+      <c r="D9" s="48">
+        <v>19.0</v>
+      </c>
+      <c r="E9" s="48">
+        <v>9.0</v>
+      </c>
+      <c r="F9" s="48">
+        <v>9.0</v>
+      </c>
+      <c r="G9" s="48">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="49">
+        <v>4.0</v>
+      </c>
+      <c r="J9" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L9" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q9" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R9" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="S9" s="43">
         <v>3.0</v>
       </c>
-      <c r="G9" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="41">
-        <v>18.0</v>
-      </c>
-      <c r="J9" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="M9" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N9" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="O9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q9" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="R9" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S9" s="43">
-        <v>2.0</v>
-      </c>
       <c r="T9" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>2280</v>
+        <v>2520</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1969,63 +1975,63 @@
       <c r="B10" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="47">
-        <v>11.0</v>
-      </c>
-      <c r="D10" s="48">
-        <v>19.0</v>
-      </c>
-      <c r="E10" s="48">
-        <v>9.0</v>
-      </c>
-      <c r="F10" s="48">
+      <c r="C10" s="39">
+        <v>13.0</v>
+      </c>
+      <c r="D10" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="E10" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="F10" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="G10" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="H10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="J10" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" s="39">
         <v>8.0</v>
       </c>
-      <c r="G10" s="48">
-        <v>2.0</v>
-      </c>
-      <c r="H10" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="49">
-        <v>3.0</v>
-      </c>
-      <c r="J10" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q10" s="39">
-        <v>10.0</v>
-      </c>
       <c r="R10" s="40">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="S10" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T10" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>2175</v>
+        <v>2475</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2038,59 +2044,59 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="46" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" s="39">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="D11" s="40">
+        <v>15.0</v>
+      </c>
+      <c r="E11" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F11" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="G11" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J11" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="39">
         <v>4.0</v>
       </c>
-      <c r="E11" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F11" s="40">
+      <c r="M11" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="N11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="39">
         <v>4.0</v>
       </c>
-      <c r="G11" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="H11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="39">
-        <v>7.0</v>
-      </c>
       <c r="R11" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S11" s="43">
         <v>2.0</v>
@@ -2100,7 +2106,7 @@
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>1995</v>
+        <v>2310</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2113,47 +2119,47 @@
       <c r="AD11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="37" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="D12" s="40">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="E12" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F12" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="39">
         <v>3.0</v>
       </c>
-      <c r="F12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="41">
-        <v>6.0</v>
-      </c>
-      <c r="J12" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="K12" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="39">
-        <v>0.0</v>
-      </c>
       <c r="M12" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N12" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O12" s="40">
         <v>0.0</v>
@@ -2162,20 +2168,20 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="R12" s="40">
         <v>4.0</v>
       </c>
       <c r="S12" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T12" s="41">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>1845</v>
+        <v>2040</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2188,47 +2194,47 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="46" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" s="39">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="D13" s="40">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
       <c r="E13" s="40">
         <v>3.0</v>
       </c>
       <c r="F13" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="41">
         <v>6.0</v>
       </c>
-      <c r="G13" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H13" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J13" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="41">
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O13" s="40">
         <v>0.0</v>
@@ -2237,20 +2243,20 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="R13" s="40">
         <v>4.0</v>
       </c>
       <c r="S13" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T13" s="41">
         <v>12.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1755</v>
+        <v>1845</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2273,7 +2279,7 @@
         <v>11.0</v>
       </c>
       <c r="D14" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E14" s="40">
         <v>1.0</v>
@@ -2282,7 +2288,7 @@
         <v>0.0</v>
       </c>
       <c r="G14" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H14" s="40">
         <v>0.0</v>
@@ -2300,10 +2306,10 @@
         <v>2.0</v>
       </c>
       <c r="M14" s="40">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="N14" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="O14" s="40">
         <v>0.0</v>
@@ -2312,7 +2318,7 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R14" s="40">
         <v>4.0</v>
@@ -2321,11 +2327,11 @@
         <v>2.0</v>
       </c>
       <c r="T14" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1590</v>
+        <v>1725</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2338,32 +2344,32 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="D15" s="40">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E15" s="40">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F15" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2372,13 +2378,13 @@
         <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M15" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="N15" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O15" s="40">
         <v>0.0</v>
@@ -2387,20 +2393,20 @@
         <v>0.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="R15" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S15" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T15" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1575</v>
+        <v>1650</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2413,32 +2419,32 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="51" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" s="39">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="D16" s="40">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="E16" s="40">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
       </c>
       <c r="I16" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="39">
         <v>0.0</v>
@@ -2450,10 +2456,10 @@
         <v>3.0</v>
       </c>
       <c r="M16" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N16" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O16" s="40">
         <v>0.0</v>
@@ -2462,20 +2468,20 @@
         <v>0.0</v>
       </c>
       <c r="Q16" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="R16" s="40">
         <v>4.0</v>
       </c>
-      <c r="R16" s="40">
-        <v>3.0</v>
-      </c>
       <c r="S16" s="43">
         <v>2.0</v>
       </c>
       <c r="T16" s="41">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1575</v>
+        <v>1605</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2488,17 +2494,17 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="51" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="39">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="D17" s="40">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="E17" s="40">
         <v>3.0</v>
@@ -2507,22 +2513,22 @@
         <v>0.0</v>
       </c>
       <c r="G17" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H17" s="40">
         <v>0.0</v>
       </c>
       <c r="I17" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J17" s="39">
         <v>0.0</v>
       </c>
       <c r="K17" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L17" s="39">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="M17" s="40">
         <v>0.0</v>
@@ -2531,26 +2537,26 @@
         <v>0.0</v>
       </c>
       <c r="O17" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P17" s="42">
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R17" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="S17" s="43">
         <v>2.0</v>
       </c>
       <c r="T17" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1515</v>
+        <v>1575</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2566,66 +2572,66 @@
       <c r="A18" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="39">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="D18" s="40">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E18" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F18" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G18" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="41">
         <v>3.0</v>
       </c>
-      <c r="H18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="41">
+      <c r="J18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="R18" s="40">
         <v>4.0</v>
-      </c>
-      <c r="J18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M18" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R18" s="40">
-        <v>5.0</v>
       </c>
       <c r="S18" s="43">
         <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1455</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2642,40 +2648,40 @@
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C19" s="39">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="D19" s="40">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="E19" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F19" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" s="40">
         <v>0.0</v>
       </c>
       <c r="I19" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J19" s="39">
         <v>0.0</v>
       </c>
       <c r="K19" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L19" s="39">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="M19" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N19" s="40">
         <v>0.0</v>
@@ -2687,20 +2693,20 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="39">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="R19" s="40">
         <v>4.0</v>
       </c>
       <c r="S19" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T19" s="41">
         <v>12.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1440</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2713,7 +2719,7 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="45" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -2771,11 +2777,11 @@
         <v>0.0</v>
       </c>
       <c r="T20" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1245</v>
+        <v>1305</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2788,23 +2794,23 @@
       <c r="AD20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="46" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D21" s="40">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E21" s="40">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F21" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" s="40">
         <v>1.0</v>
@@ -2813,7 +2819,7 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="41">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="J21" s="39">
         <v>0.0</v>
@@ -2822,35 +2828,35 @@
         <v>0.0</v>
       </c>
       <c r="L21" s="39">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M21" s="40">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="N21" s="40">
         <v>0.0</v>
       </c>
       <c r="O21" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P21" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q21" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="R21" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="S21" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T21" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1125</v>
+        <v>1275</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2863,33 +2869,33 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>32</v>
+      <c r="B22" s="50" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="D22" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="E22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="41">
         <v>4.0</v>
       </c>
-      <c r="D22" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E22" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="F22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J22" s="39">
         <v>0.0</v>
       </c>
@@ -2900,32 +2906,32 @@
         <v>0.0</v>
       </c>
       <c r="M22" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="40">
         <v>0.0</v>
       </c>
       <c r="O22" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="R22" s="40">
         <v>1.0</v>
       </c>
       <c r="S22" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T22" s="41">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1185</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2938,33 +2944,33 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C23" s="39">
         <v>5.0</v>
       </c>
       <c r="D23" s="40">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E23" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="41">
         <v>3.0</v>
       </c>
-      <c r="F23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J23" s="39">
         <v>0.0</v>
       </c>
@@ -2972,10 +2978,10 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="M23" s="40">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
@@ -2987,20 +2993,20 @@
         <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="R23" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S23" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T23" s="41">
         <v>12.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1155</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3013,44 +3019,44 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="51" t="s">
-        <v>32</v>
+      <c r="B24" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C24" s="39">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="D24" s="40">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="E24" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F24" s="40">
         <v>0.0</v>
       </c>
       <c r="G24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" s="40">
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J24" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="39">
         <v>3.0</v>
       </c>
-      <c r="J24" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="39">
-        <v>0.0</v>
-      </c>
       <c r="M24" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N24" s="40">
         <v>0.0</v>
@@ -3062,20 +3068,20 @@
         <v>0.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R24" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="S24" s="43">
         <v>2.0</v>
       </c>
       <c r="T24" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1155</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3088,20 +3094,20 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="46" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" s="39">
         <v>6.0</v>
       </c>
       <c r="D25" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E25" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F25" s="40">
         <v>1.0</v>
@@ -3146,11 +3152,11 @@
         <v>1.0</v>
       </c>
       <c r="T25" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3163,14 +3169,14 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="45" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D26" s="40">
         <v>4.0</v>
@@ -3188,7 +3194,7 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3221,11 +3227,11 @@
         <v>1.0</v>
       </c>
       <c r="T26" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>1065</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3238,14 +3244,14 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="46" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D27" s="40">
         <v>2.0</v>
@@ -3272,7 +3278,7 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M27" s="40">
         <v>0.0</v>
@@ -3296,11 +3302,11 @@
         <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>855</v>
+        <v>975</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3316,14 +3322,14 @@
       <c r="A28" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>32</v>
+      <c r="B28" s="50" t="s">
+        <v>34</v>
       </c>
       <c r="C28" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D28" s="40">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E28" s="40">
         <v>0.0</v>
@@ -3350,7 +3356,7 @@
         <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="N28" s="40">
         <v>1.0</v>
@@ -3371,11 +3377,11 @@
         <v>0.0</v>
       </c>
       <c r="T28" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>810</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3388,11 +3394,11 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="51" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" s="39">
         <v>2.0</v>
@@ -3401,10 +3407,10 @@
         <v>7.0</v>
       </c>
       <c r="E29" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G29" s="40">
         <v>0.0</v>
@@ -3431,7 +3437,7 @@
         <v>1.0</v>
       </c>
       <c r="O29" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P29" s="42">
         <v>0.0</v>
@@ -3446,11 +3452,11 @@
         <v>1.0</v>
       </c>
       <c r="T29" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>810</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3467,22 +3473,22 @@
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" s="39">
         <v>4.0</v>
       </c>
       <c r="D30" s="40">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="E30" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" s="40">
         <v>0.0</v>
       </c>
       <c r="G30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" s="40">
         <v>0.0</v>
@@ -3497,7 +3503,7 @@
         <v>0.0</v>
       </c>
       <c r="L30" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M30" s="40">
         <v>0.0</v>
@@ -3512,20 +3518,20 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="R30" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S30" s="43">
         <v>0.0</v>
       </c>
       <c r="T30" s="41">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>810</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3538,32 +3544,32 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="46" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D31" s="40">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="E31" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F31" s="40">
         <v>0.0</v>
       </c>
       <c r="G31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H31" s="40">
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3572,35 +3578,35 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P31" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q31" s="39">
         <v>3.0</v>
       </c>
-      <c r="M31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N31" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O31" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P31" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q31" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R31" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T31" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>780</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3613,50 +3619,50 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="46" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D32" s="40">
+        <v>16.0</v>
+      </c>
+      <c r="E32" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J32" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="39">
         <v>3.0</v>
       </c>
-      <c r="D32" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="39">
-        <v>1.0</v>
-      </c>
       <c r="M32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P32" s="42">
         <v>0.0</v>
@@ -3665,17 +3671,17 @@
         <v>2.0</v>
       </c>
       <c r="R32" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="S32" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3688,20 +3694,20 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="51" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C33" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D33" s="40">
         <v>2.0</v>
       </c>
       <c r="E33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="40">
         <v>0.0</v>
@@ -3722,10 +3728,10 @@
         <v>0.0</v>
       </c>
       <c r="L33" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M33" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N33" s="40">
         <v>0.0</v>
@@ -3737,20 +3743,20 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R33" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S33" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T33" s="41">
         <v>12.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>615</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3763,23 +3769,23 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="51" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D34" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E34" s="40">
         <v>0.0</v>
       </c>
       <c r="F34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="40">
         <v>0.0</v>
@@ -3800,7 +3806,7 @@
         <v>1.0</v>
       </c>
       <c r="M34" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N34" s="40">
         <v>0.0</v>
@@ -3812,20 +3818,20 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S34" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T34" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3838,17 +3844,17 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="45" t="s">
+      <c r="A35" s="37" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C35" s="39">
         <v>1.0</v>
       </c>
       <c r="D35" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="E35" s="40">
         <v>0.0</v>
@@ -3863,7 +3869,7 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J35" s="39">
         <v>0.0</v>
@@ -3872,7 +3878,7 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M35" s="40">
         <v>0.0</v>
@@ -3887,20 +3893,20 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S35" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T35" s="41">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3913,17 +3919,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="46" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C36" s="39">
         <v>1.0</v>
       </c>
       <c r="D36" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3938,7 +3944,7 @@
         <v>0.0</v>
       </c>
       <c r="I36" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J36" s="39">
         <v>0.0</v>
@@ -3947,7 +3953,7 @@
         <v>0.0</v>
       </c>
       <c r="L36" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M36" s="40">
         <v>0.0</v>
@@ -3962,20 +3968,20 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R36" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S36" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T36" s="41">
         <v>12.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3991,8 +3997,8 @@
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="51" t="s">
-        <v>32</v>
+      <c r="B37" s="50" t="s">
+        <v>34</v>
       </c>
       <c r="C37" s="39">
         <v>1.0</v>
@@ -4046,11 +4052,11 @@
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4063,11 +4069,11 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="51" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C38" s="39">
         <v>0.0</v>
@@ -4121,11 +4127,11 @@
         <v>0.0</v>
       </c>
       <c r="T38" s="56">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4417,11 +4423,11 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="83">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="R4" s="84">
-        <f t="shared" ref="R4:R13" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>3450</v>
+        <f t="shared" ref="R4:R15" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>3510</v>
       </c>
     </row>
     <row r="5">
@@ -4429,7 +4435,7 @@
         <v>75</v>
       </c>
       <c r="B5" s="79" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="82">
         <v>17.0</v>
@@ -4474,11 +4480,11 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="83">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R5" s="84">
         <f t="shared" si="1"/>
-        <v>2505</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="6">
@@ -4486,22 +4492,22 @@
         <v>76</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="82">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D6" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E6" s="42">
         <v>12.0</v>
       </c>
       <c r="F6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="81">
         <v>0.0</v>
@@ -4510,13 +4516,13 @@
         <v>0.0</v>
       </c>
       <c r="J6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K6" s="82">
         <v>0.0</v>
       </c>
       <c r="L6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M6" s="83">
         <v>0.0</v>
@@ -4535,7 +4541,7 @@
       </c>
       <c r="R6" s="84">
         <f t="shared" si="1"/>
-        <v>2295</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="7">
@@ -4543,34 +4549,34 @@
         <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D7" s="42">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E7" s="42">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="F7" s="42">
         <v>0.0</v>
       </c>
       <c r="G7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H7" s="81">
         <v>0.0</v>
       </c>
       <c r="I7" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K7" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" s="42">
         <v>0.0</v>
@@ -4588,25 +4594,25 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>2115</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="79" t="s">
-        <v>30</v>
+      <c r="B8" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D8" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E8" s="42">
         <v>10.0</v>
@@ -4621,19 +4627,19 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="81">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J8" s="42">
         <v>0.0</v>
       </c>
       <c r="K8" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L8" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M8" s="83">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N8" s="82">
         <v>0.0</v>
@@ -4642,34 +4648,34 @@
         <v>0.0</v>
       </c>
       <c r="P8" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q8" s="83">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>2055</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>32</v>
+      <c r="B9" s="79" t="s">
+        <v>30</v>
       </c>
       <c r="C9" s="82">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="D9" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E9" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G9" s="42">
         <v>0.0</v>
@@ -4678,7 +4684,7 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J9" s="42">
         <v>0.0</v>
@@ -4687,7 +4693,7 @@
         <v>0.0</v>
       </c>
       <c r="L9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M9" s="83">
         <v>0.0</v>
@@ -4702,37 +4708,37 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="83">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="R9" s="84">
         <f t="shared" si="1"/>
-        <v>1935</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="85" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="82">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="D10" s="42">
         <v>7.0</v>
       </c>
       <c r="E10" s="42">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
       </c>
       <c r="G10" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H10" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="42">
         <v>0.0</v>
@@ -4759,11 +4765,11 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="83">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="R10" s="84">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="11">
@@ -4774,13 +4780,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D11" s="42">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E11" s="42">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="F11" s="42">
         <v>0.0</v>
@@ -4789,13 +4795,13 @@
         <v>0.0</v>
       </c>
       <c r="H11" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I11" s="81">
         <v>0.0</v>
       </c>
       <c r="J11" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K11" s="82">
         <v>1.0</v>
@@ -4816,37 +4822,37 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="83">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R11" s="84">
         <f t="shared" si="1"/>
-        <v>1770</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="85" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="D12" s="42">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="E12" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="42">
         <v>0.0</v>
       </c>
       <c r="H12" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="81">
         <v>0.0</v>
@@ -4870,22 +4876,22 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q12" s="83">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="R12" s="84">
         <f t="shared" si="1"/>
-        <v>1740</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="86" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="82">
         <v>14.0</v>
@@ -4894,16 +4900,16 @@
         <v>7.0</v>
       </c>
       <c r="E13" s="42">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="F13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H13" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
@@ -4930,31 +4936,31 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="83">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="R13" s="84">
         <f t="shared" si="1"/>
-        <v>1740</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="78" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="D14" s="42">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E14" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="42">
         <v>0.0</v>
@@ -4984,145 +4990,145 @@
         <v>0.0</v>
       </c>
       <c r="P14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q14" s="83">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="R14" s="84">
-        <f>C14*$C$2+D14*$D$2+E14*$E$2+F14*$F$2+G14*$G$2+H14*$H$2+K14*$K$2+L14*$L$2+M14*$M$2+N14*$N$2+O14*$O$2+P14*$P$2+Q14*$Q$2</f>
-        <v>1725</v>
+        <f t="shared" si="1"/>
+        <v>1845</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="86" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="D15" s="42">
+        <v>10.0</v>
+      </c>
+      <c r="E15" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="F15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="K15" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="L15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q15" s="83">
         <v>14.0</v>
       </c>
-      <c r="D15" s="42">
-        <v>7.0</v>
-      </c>
-      <c r="E15" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="F15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I15" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M15" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q15" s="83">
+      <c r="R15" s="84">
+        <f t="shared" si="1"/>
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="82">
+        <v>17.0</v>
+      </c>
+      <c r="D16" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="E16" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="F16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q16" s="83">
         <v>12.0</v>
       </c>
-      <c r="R15" s="84">
-        <f t="shared" ref="R15:R35" si="2">C15*$C$2+D15*$D$2+E15*$E$2+F15*$F$2+G15*$G$2+H15*$H$2+K15*$K$2+L15*$L$2+M15*$M$2+N15*$N$2+O15*$O$2+P15*$P$2+Q15*$Q$2+I15*$I$2+J15*$J$2</f>
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="85" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="82">
-        <v>14.0</v>
-      </c>
-      <c r="D16" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="E16" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="F16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q16" s="83">
-        <v>11.0</v>
-      </c>
       <c r="R16" s="84">
-        <f t="shared" si="2"/>
-        <v>1530</v>
+        <f>C16*$C$2+D16*$D$2+E16*$E$2+F16*$F$2+G16*$G$2+H16*$H$2+K16*$K$2+L16*$L$2+M16*$M$2+N16*$N$2+O16*$O$2+P16*$P$2+Q16*$Q$2</f>
+        <v>1755</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="88" t="s">
         <v>87</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="D17" s="42">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="E17" s="42">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F17" s="42">
         <v>0.0</v>
@@ -5134,7 +5140,7 @@
         <v>1.0</v>
       </c>
       <c r="I17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5155,34 +5161,34 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R17" s="84">
-        <f t="shared" si="2"/>
-        <v>1470</v>
+        <f t="shared" ref="R17:R35" si="2">C17*$C$2+D17*$D$2+E17*$E$2+F17*$F$2+G17*$G$2+H17*$H$2+K17*$K$2+L17*$L$2+M17*$M$2+N17*$N$2+O17*$O$2+P17*$P$2+Q17*$Q$2+I17*$I$2+J17*$J$2</f>
+        <v>1755</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="87" t="s">
         <v>88</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D18" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E18" s="42">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="F18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" s="42">
         <v>0.0</v>
@@ -5191,7 +5197,7 @@
         <v>0.0</v>
       </c>
       <c r="I18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5215,11 +5221,11 @@
         <v>1.0</v>
       </c>
       <c r="Q18" s="83">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1395</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="19">
@@ -5227,31 +5233,31 @@
         <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C19" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="D19" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="E19" s="42">
         <v>11.0</v>
       </c>
-      <c r="D19" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="E19" s="42">
-        <v>4.0</v>
-      </c>
       <c r="F19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="42">
         <v>0.0</v>
       </c>
       <c r="H19" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I19" s="42">
         <v>0.0</v>
       </c>
       <c r="J19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K19" s="82">
         <v>0.0</v>
@@ -5276,24 +5282,24 @@
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1365</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="86" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="82">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="D20" s="42">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="E20" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5302,10 +5308,10 @@
         <v>0.0</v>
       </c>
       <c r="H20" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J20" s="42">
         <v>0.0</v>
@@ -5329,43 +5335,43 @@
         <v>0.0</v>
       </c>
       <c r="Q20" s="83">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="R20" s="84">
         <f t="shared" si="2"/>
-        <v>1320</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="89" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" s="82">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="D21" s="42">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E21" s="42">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" s="42">
         <v>0.0</v>
       </c>
       <c r="H21" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21" s="81">
         <v>0.0</v>
       </c>
       <c r="J21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K21" s="82">
         <v>0.0</v>
@@ -5383,31 +5389,31 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q21" s="83">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="78" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C22" s="82">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="D22" s="42">
         <v>9.0</v>
       </c>
       <c r="E22" s="42">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" s="42">
         <v>0.0</v>
@@ -5416,10 +5422,10 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="81">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="I22" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J22" s="42">
         <v>0.0</v>
@@ -5447,7 +5453,7 @@
       </c>
       <c r="R22" s="84">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="23">
@@ -5455,22 +5461,22 @@
         <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C23" s="82">
+        <v>10.0</v>
+      </c>
+      <c r="D23" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E23" s="42">
         <v>7.0</v>
       </c>
-      <c r="D23" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="E23" s="42">
-        <v>5.0</v>
-      </c>
       <c r="F23" s="42">
         <v>0.0</v>
       </c>
       <c r="G23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" s="81">
         <v>0.0</v>
@@ -5497,46 +5503,46 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="79" t="s">
-        <v>32</v>
+      <c r="B24" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C24" s="82">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="D24" s="42">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E24" s="42">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
       </c>
       <c r="G24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="82">
         <v>0.0</v>
@@ -5557,28 +5563,28 @@
         <v>1.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
-        <v>1200</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="78" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C25" s="82">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D25" s="42">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="E25" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F25" s="42">
         <v>0.0</v>
@@ -5611,28 +5617,28 @@
         <v>0.0</v>
       </c>
       <c r="P25" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q25" s="83">
         <v>12.0</v>
       </c>
       <c r="R25" s="84">
         <f t="shared" si="2"/>
-        <v>1185</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="86" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="82">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="D26" s="42">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="E26" s="42">
         <v>5.0</v>
@@ -5668,31 +5674,31 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="83">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>1140</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="78" t="s">
+      <c r="A27" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="42" t="s">
-        <v>32</v>
+      <c r="B27" s="79" t="s">
+        <v>34</v>
       </c>
       <c r="C27" s="82">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D27" s="42">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="E27" s="42">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5707,7 +5713,7 @@
         <v>0.0</v>
       </c>
       <c r="J27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K27" s="82">
         <v>0.0</v>
@@ -5728,28 +5734,28 @@
         <v>1.0</v>
       </c>
       <c r="Q27" s="83">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="R27" s="84">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="42" t="s">
-        <v>32</v>
+      <c r="B28" s="79" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="82">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="D28" s="42">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E28" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="42">
         <v>0.0</v>
@@ -5785,11 +5791,11 @@
         <v>1.0</v>
       </c>
       <c r="Q28" s="83">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
-        <v>795</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="29">
@@ -5842,11 +5848,11 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="83">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>735</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30">
@@ -5857,10 +5863,10 @@
         <v>30</v>
       </c>
       <c r="C30" s="82">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D30" s="42">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E30" s="42">
         <v>3.0</v>
@@ -5899,28 +5905,28 @@
         <v>1.0</v>
       </c>
       <c r="Q30" s="83">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R30" s="84">
         <f t="shared" si="2"/>
-        <v>705</v>
+        <v>765</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="79" t="s">
-        <v>32</v>
+      <c r="B31" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="C31" s="82">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D31" s="42">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
       <c r="E31" s="42">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -5929,7 +5935,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="81">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I31" s="42">
         <v>0.0</v>
@@ -5956,28 +5962,28 @@
         <v>0.0</v>
       </c>
       <c r="Q31" s="83">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="R31" s="84">
         <f t="shared" si="2"/>
-        <v>480</v>
+        <v>690</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="42" t="s">
-        <v>32</v>
+      <c r="B32" s="79" t="s">
+        <v>30</v>
       </c>
       <c r="C32" s="82">
         <v>6.0</v>
       </c>
       <c r="D32" s="42">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="E32" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F32" s="42">
         <v>0.0</v>
@@ -5986,7 +5992,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="I32" s="81">
         <v>0.0</v>
@@ -6010,14 +6016,14 @@
         <v>0.0</v>
       </c>
       <c r="P32" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q32" s="83">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R32" s="84">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>570</v>
       </c>
     </row>
     <row r="33">
@@ -6025,27 +6031,27 @@
         <v>103</v>
       </c>
       <c r="B33" s="91" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="92">
         <v>5.0</v>
       </c>
-      <c r="D33" s="91">
-        <v>11.0</v>
-      </c>
-      <c r="E33" s="91">
-        <v>1.0</v>
-      </c>
-      <c r="F33" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="91">
+      <c r="D33" s="93">
+        <v>9.0</v>
+      </c>
+      <c r="E33" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="93">
         <v>0.0</v>
       </c>
       <c r="H33" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="91">
+        <v>1.0</v>
+      </c>
+      <c r="I33" s="93">
         <v>0.0</v>
       </c>
       <c r="J33" s="42">
@@ -6054,55 +6060,55 @@
       <c r="K33" s="92">
         <v>0.0</v>
       </c>
-      <c r="L33" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="93">
+      <c r="L33" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="94">
         <v>0.0</v>
       </c>
       <c r="N33" s="92">
         <v>0.0</v>
       </c>
-      <c r="O33" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="91">
-        <v>1.0</v>
-      </c>
-      <c r="Q33" s="93">
-        <v>10.0</v>
+      <c r="O33" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="Q33" s="94">
+        <v>14.0</v>
       </c>
       <c r="R33" s="84">
         <f t="shared" si="2"/>
-        <v>435</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="90" t="s">
+      <c r="A34" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="91" t="s">
-        <v>32</v>
+      <c r="B34" s="93" t="s">
+        <v>34</v>
       </c>
       <c r="C34" s="92">
         <v>2.0</v>
       </c>
-      <c r="D34" s="91">
-        <v>1.0</v>
-      </c>
-      <c r="E34" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="91">
+      <c r="D34" s="93">
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="93">
         <v>0.0</v>
       </c>
       <c r="H34" s="81">
         <v>0.0</v>
       </c>
-      <c r="I34" s="91">
+      <c r="I34" s="93">
         <v>0.0</v>
       </c>
       <c r="J34" s="42">
@@ -6111,37 +6117,37 @@
       <c r="K34" s="92">
         <v>0.0</v>
       </c>
-      <c r="L34" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="93">
+      <c r="L34" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="94">
         <v>0.0</v>
       </c>
       <c r="N34" s="92">
         <v>0.0</v>
       </c>
-      <c r="O34" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="91">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="93">
-        <v>10.0</v>
+      <c r="O34" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="93">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="94">
+        <v>11.0</v>
       </c>
       <c r="R34" s="84">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="95" t="s">
+      <c r="B35" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="96">
+      <c r="C35" s="98">
         <v>0.0</v>
       </c>
       <c r="D35" s="54">
@@ -6156,25 +6162,25 @@
       <c r="G35" s="54">
         <v>0.0</v>
       </c>
-      <c r="H35" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="97">
+      <c r="H35" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="99">
         <v>0.0</v>
       </c>
       <c r="J35" s="54">
         <v>0.0</v>
       </c>
-      <c r="K35" s="96">
+      <c r="K35" s="98">
         <v>0.0</v>
       </c>
       <c r="L35" s="54">
         <v>0.0</v>
       </c>
-      <c r="M35" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="96">
+      <c r="M35" s="100">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="98">
         <v>0.0</v>
       </c>
       <c r="O35" s="54">
@@ -6183,12 +6189,12 @@
       <c r="P35" s="54">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="98">
-        <v>10.0</v>
-      </c>
-      <c r="R35" s="99">
+      <c r="Q35" s="100">
+        <v>12.0</v>
+      </c>
+      <c r="R35" s="101">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/24/2026</t>
+    <t>Actualización: 6/30/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -137,24 +137,24 @@
     <t>Castillo, Wesly</t>
   </si>
   <si>
+    <t>Gonzalez, Victor</t>
+  </si>
+  <si>
+    <t>Ramirez, Santiago</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Gonzalez, Victor</t>
-  </si>
-  <si>
-    <t>Ramirez, Santiago</t>
-  </si>
-  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
+    <t>Abreu, Ariel</t>
+  </si>
+  <si>
     <t>Done, Carlos</t>
   </si>
   <si>
-    <t>Abreu, Ariel</t>
-  </si>
-  <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
@@ -164,33 +164,33 @@
     <t>Pinder, Jayln</t>
   </si>
   <si>
+    <t>Volquez, Fabelin</t>
+  </si>
+  <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
-    <t>Volquez, Fabelin</t>
+    <t>Alarcon, Rosnel</t>
   </si>
   <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Alarcon, Rosnel</t>
-  </si>
-  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
+    <t>Ortiz Jr, David</t>
+  </si>
+  <si>
+    <t>Chavez, Jesus</t>
+  </si>
+  <si>
+    <t>Montero, Darling</t>
+  </si>
+  <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
-  </si>
-  <si>
-    <t>Ortiz Jr, David</t>
-  </si>
-  <si>
-    <t>Chavez, Jesus</t>
-  </si>
-  <si>
     <t>Genao, Jhostin</t>
   </si>
   <si>
@@ -248,21 +248,27 @@
     <t>Medina, Juan</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
+    <t>Dolsi, Frederik</t>
+  </si>
+  <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
     <t>Pineda, Frandel</t>
   </si>
   <si>
+    <t>Santos, Aneudy</t>
+  </si>
+  <si>
     <t>Gomez, Manuel</t>
   </si>
   <si>
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
@@ -272,34 +278,28 @@
     <t>Castillo, Albert</t>
   </si>
   <si>
-    <t>Dolsi, Frederik</t>
-  </si>
-  <si>
-    <t>Santos, Aneudy</t>
-  </si>
-  <si>
     <t>Lara, Carlos</t>
   </si>
   <si>
     <t>Alcantara, Jostin</t>
   </si>
   <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
     <t>Acosta, Isaac</t>
   </si>
   <si>
-    <t>Fernandez, Jehiber</t>
-  </si>
-  <si>
     <t>Pena, Dariel</t>
   </si>
   <si>
     <t>Peralta, Eddy</t>
   </si>
   <si>
+    <t>Cordero, Albert</t>
+  </si>
+  <si>
     <t>Ballesteros, Jean</t>
-  </si>
-  <si>
-    <t>Cordero, Albert</t>
   </si>
   <si>
     <t>Ramos, Daniel</t>
@@ -1601,16 +1601,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="D5" s="40">
         <v>13.0</v>
       </c>
       <c r="E5" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F5" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G5" s="40">
         <v>4.0</v>
@@ -1643,7 +1643,7 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R5" s="40">
         <v>5.0</v>
@@ -1652,11 +1652,11 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>3270</v>
+        <v>3585</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1676,10 +1676,10 @@
         <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D6" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E6" s="40">
         <v>9.0</v>
@@ -1694,7 +1694,7 @@
         <v>0.0</v>
       </c>
       <c r="I6" s="41">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="J6" s="39">
         <v>0.0</v>
@@ -1718,7 +1718,7 @@
         <v>0.0</v>
       </c>
       <c r="Q6" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R6" s="40">
         <v>4.0</v>
@@ -1727,11 +1727,11 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>2745</v>
+        <v>2880</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1751,10 +1751,10 @@
         <v>30</v>
       </c>
       <c r="C7" s="39">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D7" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E7" s="40">
         <v>1.0</v>
@@ -1793,7 +1793,7 @@
         <v>0.0</v>
       </c>
       <c r="Q7" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="R7" s="40">
         <v>5.0</v>
@@ -1802,11 +1802,11 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>2745</v>
+        <v>2850</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1826,16 +1826,16 @@
         <v>34</v>
       </c>
       <c r="C8" s="39">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D8" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E8" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F8" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" s="40">
         <v>2.0</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>2625</v>
+        <v>2775</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1901,10 +1901,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="47">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="D9" s="48">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E9" s="48">
         <v>9.0</v>
@@ -1943,7 +1943,7 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R9" s="40">
         <v>6.0</v>
@@ -1952,11 +1952,11 @@
         <v>3.0</v>
       </c>
       <c r="T9" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>2520</v>
+        <v>2700</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1982,7 +1982,7 @@
         <v>5.0</v>
       </c>
       <c r="E10" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F10" s="40">
         <v>5.0</v>
@@ -2018,7 +2018,7 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="R10" s="40">
         <v>2.0</v>
@@ -2027,11 +2027,11 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>2475</v>
+        <v>2595</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2054,7 +2054,7 @@
         <v>20.0</v>
       </c>
       <c r="D11" s="40">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E11" s="40">
         <v>3.0</v>
@@ -2081,13 +2081,13 @@
         <v>4.0</v>
       </c>
       <c r="M11" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="N11" s="40">
         <v>0.0</v>
       </c>
       <c r="O11" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P11" s="42">
         <v>0.0</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2310</v>
+        <v>2280</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2126,19 +2126,19 @@
         <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D12" s="40">
         <v>10.0</v>
       </c>
       <c r="E12" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="40">
         <v>6.0</v>
       </c>
       <c r="G12" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H12" s="40">
         <v>0.0</v>
@@ -2153,7 +2153,7 @@
         <v>0.0</v>
       </c>
       <c r="L12" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M12" s="40">
         <v>1.0</v>
@@ -2168,7 +2168,7 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R12" s="40">
         <v>4.0</v>
@@ -2177,11 +2177,11 @@
         <v>3.0</v>
       </c>
       <c r="T12" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2040</v>
+        <v>2235</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2228,7 +2228,7 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M13" s="40">
         <v>0.0</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1845</v>
+        <v>1830</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2269,23 +2269,23 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="D14" s="40">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="E14" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="40">
         <v>3.0</v>
@@ -2294,7 +2294,7 @@
         <v>0.0</v>
       </c>
       <c r="I14" s="41">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="J14" s="39">
         <v>0.0</v>
@@ -2303,35 +2303,35 @@
         <v>0.0</v>
       </c>
       <c r="L14" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M14" s="40">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="N14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q14" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R14" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S14" s="43">
         <v>3.0</v>
       </c>
-      <c r="O14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P14" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q14" s="39">
-        <v>9.0</v>
-      </c>
-      <c r="R14" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S14" s="43">
-        <v>2.0</v>
-      </c>
       <c r="T14" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1725</v>
+        <v>1830</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2344,32 +2344,32 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="D15" s="40">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E15" s="40">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F15" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2378,13 +2378,13 @@
         <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M15" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="N15" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O15" s="40">
         <v>0.0</v>
@@ -2393,20 +2393,20 @@
         <v>0.0</v>
       </c>
       <c r="Q15" s="39">
+        <v>9.0</v>
+      </c>
+      <c r="R15" s="40">
         <v>4.0</v>
       </c>
-      <c r="R15" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S15" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T15" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1650</v>
+        <v>1755</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2419,32 +2419,32 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="37" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="39">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="D16" s="40">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E16" s="40">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="F16" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
       </c>
       <c r="I16" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J16" s="39">
         <v>0.0</v>
@@ -2453,14 +2453,14 @@
         <v>0.0</v>
       </c>
       <c r="L16" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M16" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="N16" s="40">
         <v>3.0</v>
       </c>
-      <c r="M16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N16" s="40">
-        <v>2.0</v>
-      </c>
       <c r="O16" s="40">
         <v>0.0</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>0.0</v>
       </c>
       <c r="Q16" s="39">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R16" s="40">
         <v>4.0</v>
@@ -2477,11 +2477,11 @@
         <v>2.0</v>
       </c>
       <c r="T16" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1605</v>
+        <v>1725</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2569,44 +2569,44 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="46" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C18" s="39">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="D18" s="40">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="E18" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F18" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H18" s="40">
         <v>0.0</v>
       </c>
       <c r="I18" s="41">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="J18" s="39">
         <v>0.0</v>
       </c>
       <c r="K18" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L18" s="39">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="M18" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N18" s="40">
         <v>0.0</v>
@@ -2618,20 +2618,20 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="R18" s="40">
         <v>4.0</v>
       </c>
       <c r="S18" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T18" s="41">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1455</v>
+        <v>1560</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2644,69 +2644,69 @@
       <c r="AD18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="45" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19" s="39">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="D19" s="40">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E19" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F19" s="40">
         <v>3.0</v>
       </c>
-      <c r="F19" s="40">
-        <v>0.0</v>
-      </c>
       <c r="G19" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H19" s="40">
         <v>0.0</v>
       </c>
       <c r="I19" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J19" s="39">
         <v>0.0</v>
       </c>
       <c r="K19" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="39">
         <v>10.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>5.0</v>
       </c>
       <c r="R19" s="40">
         <v>4.0</v>
       </c>
       <c r="S19" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T19" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1440</v>
+        <v>1485</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2777,11 +2777,11 @@
         <v>0.0</v>
       </c>
       <c r="T20" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1335</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2944,20 +2944,20 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="37" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C23" s="39">
         <v>5.0</v>
       </c>
       <c r="D23" s="40">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E23" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F23" s="40">
         <v>0.0</v>
@@ -2969,19 +2969,19 @@
         <v>0.0</v>
       </c>
       <c r="I23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="39">
         <v>3.0</v>
       </c>
-      <c r="J23" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="39">
-        <v>7.0</v>
-      </c>
       <c r="M23" s="40">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
@@ -2993,20 +2993,20 @@
         <v>0.0</v>
       </c>
       <c r="Q23" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="R23" s="40">
         <v>3.0</v>
       </c>
-      <c r="R23" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S23" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T23" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1155</v>
+        <v>1185</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3019,21 +3019,21 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="46" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C24" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="D24" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="E24" s="40">
         <v>5.0</v>
       </c>
-      <c r="D24" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="E24" s="40">
-        <v>4.0</v>
-      </c>
       <c r="F24" s="40">
         <v>0.0</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3053,35 +3053,35 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="M24" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="N24" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q24" s="39">
         <v>3.0</v>
       </c>
-      <c r="M24" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N24" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q24" s="39">
-        <v>6.0</v>
-      </c>
       <c r="R24" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S24" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T24" s="41">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1155</v>
+        <v>1170</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3094,26 +3094,26 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="45" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C25" s="39">
         <v>6.0</v>
       </c>
       <c r="D25" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E25" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F25" s="40">
         <v>1.0</v>
       </c>
       <c r="G25" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H25" s="40">
         <v>0.0</v>
@@ -3128,13 +3128,13 @@
         <v>0.0</v>
       </c>
       <c r="L25" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M25" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N25" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O25" s="40">
         <v>0.0</v>
@@ -3143,20 +3143,20 @@
         <v>0.0</v>
       </c>
       <c r="Q25" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R25" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S25" s="43">
         <v>1.0</v>
       </c>
       <c r="T25" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3169,26 +3169,26 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="46" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C26" s="39">
         <v>6.0</v>
       </c>
       <c r="D26" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E26" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F26" s="40">
         <v>1.0</v>
       </c>
       <c r="G26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" s="40">
         <v>0.0</v>
@@ -3203,13 +3203,13 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O26" s="40">
         <v>0.0</v>
@@ -3218,20 +3218,20 @@
         <v>0.0</v>
       </c>
       <c r="Q26" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R26" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S26" s="43">
         <v>1.0</v>
       </c>
       <c r="T26" s="41">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1080</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3302,11 +3302,11 @@
         <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>975</v>
+        <v>1005</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3319,69 +3319,69 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="50" t="s">
-        <v>34</v>
+      <c r="B28" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="39">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="D28" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="E28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J28" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P28" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="R28" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="S28" s="43">
+        <v>0.0</v>
+      </c>
+      <c r="T28" s="41">
         <v>15.0</v>
-      </c>
-      <c r="E28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J28" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M28" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="N28" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O28" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P28" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q28" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R28" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S28" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="T28" s="41">
-        <v>12.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3394,69 +3394,69 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="39">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="D29" s="40">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E29" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I29" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J29" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P29" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q29" s="39">
         <v>3.0</v>
       </c>
-      <c r="F29" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G29" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H29" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I29" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J29" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M29" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="N29" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O29" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P29" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q29" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R29" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="S29" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T29" s="41">
         <v>12.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3469,23 +3469,23 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="51" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C30" s="39">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D30" s="40">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="E30" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="40">
         <v>0.0</v>
@@ -3494,7 +3494,7 @@
         <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
@@ -3503,31 +3503,31 @@
         <v>0.0</v>
       </c>
       <c r="L30" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M30" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="N30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P30" s="42">
         <v>0.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R30" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S30" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T30" s="41">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
@@ -3544,50 +3544,50 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="50" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="D31" s="40">
+        <v>16.0</v>
+      </c>
+      <c r="E31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I31" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J31" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M31" s="40">
         <v>6.0</v>
       </c>
-      <c r="D31" s="40">
-        <v>9.0</v>
-      </c>
-      <c r="E31" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="F31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H31" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I31" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J31" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L31" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M31" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O31" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P31" s="42">
         <v>0.0</v>
@@ -3596,7 +3596,7 @@
         <v>3.0</v>
       </c>
       <c r="R31" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="S31" s="43">
         <v>0.0</v>
@@ -3629,7 +3629,7 @@
         <v>5.0</v>
       </c>
       <c r="D32" s="40">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="E32" s="40">
         <v>1.0</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>645</v>
+        <v>615</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3902,11 +3902,11 @@
         <v>0.0</v>
       </c>
       <c r="T35" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -4426,7 +4426,7 @@
         <v>15.0</v>
       </c>
       <c r="R4" s="84">
-        <f t="shared" ref="R4:R15" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <f t="shared" ref="R4:R10" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
         <v>3510</v>
       </c>
     </row>
@@ -4438,19 +4438,19 @@
         <v>34</v>
       </c>
       <c r="C5" s="82">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
       <c r="D5" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E5" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F5" s="42">
         <v>1.0</v>
       </c>
       <c r="G5" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H5" s="81">
         <v>0.0</v>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="R5" s="84">
         <f t="shared" si="1"/>
-        <v>2535</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="6">
@@ -4545,17 +4545,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="86" t="s">
         <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C7" s="82">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D7" s="42">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E7" s="42">
         <v>12.0</v>
@@ -4564,19 +4564,19 @@
         <v>0.0</v>
       </c>
       <c r="G7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H7" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I7" s="81">
         <v>0.0</v>
       </c>
       <c r="J7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K7" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="42">
         <v>0.0</v>
@@ -4594,106 +4594,106 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="83">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="R7" s="84">
         <f t="shared" si="1"/>
-        <v>2325</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="86" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="82">
+        <v>19.0</v>
+      </c>
+      <c r="D8" s="42">
+        <v>12.0</v>
+      </c>
+      <c r="E8" s="42">
+        <v>11.0</v>
+      </c>
+      <c r="F8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="K8" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="L8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q8" s="83">
         <v>15.0</v>
-      </c>
-      <c r="D8" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="E8" s="42">
-        <v>10.0</v>
-      </c>
-      <c r="F8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="83">
-        <v>1.0</v>
-      </c>
-      <c r="N8" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q8" s="83">
-        <v>12.0</v>
       </c>
       <c r="R8" s="84">
         <f t="shared" si="1"/>
-        <v>2325</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="79" t="s">
-        <v>30</v>
+      <c r="B9" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="82">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="D9" s="42">
         <v>5.0</v>
       </c>
       <c r="E9" s="42">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="F9" s="42">
         <v>0.0</v>
       </c>
       <c r="G9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H9" s="81">
         <v>0.0</v>
       </c>
       <c r="I9" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K9" s="82">
         <v>0.0</v>
       </c>
       <c r="L9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="83">
         <v>0.0</v>
@@ -4705,31 +4705,31 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q9" s="83">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="R9" s="84">
         <f t="shared" si="1"/>
-        <v>2115</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="78" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="82">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="D10" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E10" s="42">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
@@ -4741,19 +4741,19 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
       </c>
       <c r="K10" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L10" s="42">
         <v>0.0</v>
       </c>
       <c r="M10" s="83">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="82">
         <v>0.0</v>
@@ -4765,151 +4765,151 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="83">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="R10" s="84">
         <f t="shared" si="1"/>
-        <v>1995</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="87" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="82">
+        <v>21.0</v>
+      </c>
+      <c r="D11" s="42">
+        <v>11.0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>10.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="83">
+        <v>12.0</v>
+      </c>
+      <c r="R11" s="84">
+        <f>C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2</f>
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="82">
+      <c r="C12" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="D12" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E12" s="42">
+        <v>10.0</v>
+      </c>
+      <c r="F12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="81">
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="M12" s="83">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="83">
         <v>15.0</v>
       </c>
-      <c r="D11" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q11" s="83">
-        <v>14.0</v>
-      </c>
-      <c r="R11" s="84">
-        <f t="shared" si="1"/>
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="82">
-        <v>17.0</v>
-      </c>
-      <c r="D12" s="42">
-        <v>7.0</v>
-      </c>
-      <c r="E12" s="42">
-        <v>9.0</v>
-      </c>
-      <c r="F12" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="83">
-        <v>9.0</v>
-      </c>
       <c r="R12" s="84">
-        <f t="shared" si="1"/>
-        <v>1965</v>
+        <f t="shared" ref="R12:R35" si="2">C12*$C$2+D12*$D$2+E12*$E$2+F12*$F$2+G12*$G$2+H12*$H$2+K12*$K$2+L12*$L$2+M12*$M$2+N12*$N$2+O12*$O$2+P12*$P$2+Q12*$Q$2+I12*$I$2+J12*$J$2</f>
+        <v>2115</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="85" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="82">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="D13" s="42">
         <v>7.0</v>
       </c>
       <c r="E13" s="42">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
       </c>
       <c r="G13" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H13" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="81">
         <v>0.0</v>
@@ -4939,25 +4939,25 @@
         <v>13.0</v>
       </c>
       <c r="R13" s="84">
-        <f t="shared" si="1"/>
-        <v>1845</v>
+        <f t="shared" si="2"/>
+        <v>1995</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="85" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C14" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="D14" s="42">
         <v>7.0</v>
       </c>
       <c r="E14" s="42">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="F14" s="42">
         <v>1.0</v>
@@ -4993,11 +4993,11 @@
         <v>0.0</v>
       </c>
       <c r="Q14" s="83">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="R14" s="84">
-        <f t="shared" si="1"/>
-        <v>1845</v>
+        <f t="shared" si="2"/>
+        <v>1965</v>
       </c>
     </row>
     <row r="15">
@@ -5008,31 +5008,31 @@
         <v>30</v>
       </c>
       <c r="C15" s="82">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D15" s="42">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="E15" s="42">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="F15" s="42">
         <v>0.0</v>
       </c>
       <c r="G15" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I15" s="81">
         <v>0.0</v>
       </c>
       <c r="J15" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15" s="42">
         <v>0.0</v>
@@ -5053,28 +5053,28 @@
         <v>14.0</v>
       </c>
       <c r="R15" s="84">
-        <f t="shared" si="1"/>
-        <v>1830</v>
+        <f t="shared" si="2"/>
+        <v>1875</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="78" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C16" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="D16" s="42">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E16" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="42">
         <v>0.0</v>
@@ -5104,14 +5104,14 @@
         <v>0.0</v>
       </c>
       <c r="P16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q16" s="83">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="R16" s="84">
-        <f>C16*$C$2+D16*$D$2+E16*$E$2+F16*$F$2+G16*$G$2+H16*$H$2+K16*$K$2+L16*$L$2+M16*$M$2+N16*$N$2+O16*$O$2+P16*$P$2+Q16*$Q$2</f>
-        <v>1755</v>
+        <f t="shared" si="2"/>
+        <v>1875</v>
       </c>
     </row>
     <row r="17">
@@ -5164,11 +5164,11 @@
         <v>1.0</v>
       </c>
       <c r="Q17" s="83">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R17" s="84">
-        <f t="shared" ref="R17:R35" si="2">C17*$C$2+D17*$D$2+E17*$E$2+F17*$F$2+G17*$G$2+H17*$H$2+K17*$K$2+L17*$L$2+M17*$M$2+N17*$N$2+O17*$O$2+P17*$P$2+Q17*$Q$2+I17*$I$2+J17*$J$2</f>
-        <v>1755</v>
+        <f t="shared" si="2"/>
+        <v>1785</v>
       </c>
     </row>
     <row r="18">
@@ -5221,28 +5221,28 @@
         <v>1.0</v>
       </c>
       <c r="Q18" s="83">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R18" s="84">
         <f t="shared" si="2"/>
-        <v>1755</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="86" t="s">
         <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19" s="82">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D19" s="42">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="E19" s="42">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="42">
         <v>0.0</v>
@@ -5254,10 +5254,10 @@
         <v>1.0</v>
       </c>
       <c r="I19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K19" s="82">
         <v>0.0</v>
@@ -5278,29 +5278,29 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="83">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="R19" s="84">
         <f t="shared" si="2"/>
-        <v>1545</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="78" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C20" s="82">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="D20" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="E20" s="42">
         <v>11.0</v>
       </c>
-      <c r="E20" s="42">
-        <v>5.0</v>
-      </c>
       <c r="F20" s="42">
         <v>0.0</v>
       </c>
@@ -5311,10 +5311,10 @@
         <v>1.0</v>
       </c>
       <c r="I20" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K20" s="82">
         <v>0.0</v>
@@ -5335,11 +5335,11 @@
         <v>0.0</v>
       </c>
       <c r="Q20" s="83">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="R20" s="84">
         <f t="shared" si="2"/>
-        <v>1530</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="21">
@@ -5392,11 +5392,11 @@
         <v>1.0</v>
       </c>
       <c r="Q21" s="83">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R21" s="84">
         <f t="shared" si="2"/>
-        <v>1485</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="22">
@@ -5461,22 +5461,22 @@
         <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C23" s="82">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="D23" s="42">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E23" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="42">
         <v>0.0</v>
       </c>
       <c r="G23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H23" s="81">
         <v>0.0</v>
@@ -5503,14 +5503,14 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="83">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R23" s="84">
         <f t="shared" si="2"/>
-        <v>1350</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="24">
@@ -5518,22 +5518,22 @@
         <v>94</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C24" s="82">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D24" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E24" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
       </c>
       <c r="G24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" s="81">
         <v>0.0</v>
@@ -5560,10 +5560,10 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="83">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="R24" s="84">
         <f t="shared" si="2"/>
@@ -5677,11 +5677,11 @@
         <v>1.0</v>
       </c>
       <c r="Q26" s="83">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R26" s="84">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="27">
@@ -5791,11 +5791,11 @@
         <v>1.0</v>
       </c>
       <c r="Q28" s="83">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R28" s="84">
         <f t="shared" si="2"/>
-        <v>1080</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="29">
@@ -5848,11 +5848,11 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="83">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R29" s="84">
         <f t="shared" si="2"/>
-        <v>795</v>
+        <v>825</v>
       </c>
     </row>
     <row r="30">
@@ -5905,11 +5905,11 @@
         <v>1.0</v>
       </c>
       <c r="Q30" s="83">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R30" s="84">
         <f t="shared" si="2"/>
-        <v>765</v>
+        <v>795</v>
       </c>
     </row>
     <row r="31">
@@ -5974,10 +5974,10 @@
         <v>102</v>
       </c>
       <c r="B32" s="79" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C32" s="82">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D32" s="42">
         <v>11.0</v>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="R32" s="84">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>645</v>
       </c>
     </row>
     <row r="33">
@@ -6190,11 +6190,11 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="100">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R35" s="101">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -8,14 +8,14 @@
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$38</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$35</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$36</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="107">
   <si>
     <t>INCENTIVOS DSL 2026</t>
   </si>
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/30/2026</t>
+    <t>Actualización: 6/2/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -110,21 +110,21 @@
     <t>R</t>
   </si>
   <si>
+    <t>Zayas, Saivel</t>
+  </si>
+  <si>
+    <t>Flores, Jesus</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Mateo, Cesar</t>
   </si>
   <si>
     <t>Rodriguez, Alex</t>
   </si>
   <si>
-    <t>Flores, Jesus</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Zayas, Saivel</t>
-  </si>
-  <si>
     <t>Cavero, Braulio</t>
   </si>
   <si>
@@ -146,34 +146,37 @@
     <t>Diaz, David</t>
   </si>
   <si>
+    <t>Abreu, Ariel</t>
+  </si>
+  <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
-    <t>Abreu, Ariel</t>
-  </si>
-  <si>
-    <t>Done, Carlos</t>
+    <t>Marcano, Jose</t>
+  </si>
+  <si>
+    <t>Volquez, Fabelin</t>
+  </si>
+  <si>
+    <t>Rodriguez, Victor</t>
   </si>
   <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
-    <t>Marcano, Jose</t>
+    <t>Jaquez, Luis</t>
+  </si>
+  <si>
+    <t>Alarcon, Rosnel</t>
   </si>
   <si>
     <t>Pinder, Jayln</t>
   </si>
   <si>
-    <t>Volquez, Fabelin</t>
-  </si>
-  <si>
-    <t>Jaquez, Luis</t>
-  </si>
-  <si>
-    <t>Alarcon, Rosnel</t>
-  </si>
-  <si>
-    <t>Rodriguez, Victor</t>
+    <t>Pereira, Raul</t>
   </si>
   <si>
     <t>Mosqueda, Juan</t>
@@ -182,13 +185,13 @@
     <t>Ortiz Jr, David</t>
   </si>
   <si>
+    <t>Montero, Darling</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
-  </si>
-  <si>
-    <t>Pereira, Raul</t>
+    <t>Coronado, Francisco</t>
   </si>
   <si>
     <t>Genao, Jhostin</t>
@@ -203,9 +206,6 @@
     <t>Seminiel, Cristian</t>
   </si>
   <si>
-    <t>Coronado, Francisco</t>
-  </si>
-  <si>
     <t>Cedeno, Luis</t>
   </si>
   <si>
@@ -248,63 +248,63 @@
     <t>Medina, Juan</t>
   </si>
   <si>
+    <t>Pineda, Frandel</t>
+  </si>
+  <si>
+    <t>Fukuda, Masahiro</t>
+  </si>
+  <si>
+    <t>Gomez, Manuel</t>
+  </si>
+  <si>
     <t>Roquez, Yadiel</t>
   </si>
   <si>
+    <t>Gamez, Manuel</t>
+  </si>
+  <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
-    <t>Gamez, Manuel</t>
-  </si>
-  <si>
-    <t>Pineda, Frandel</t>
-  </si>
-  <si>
     <t>Santos, Aneudy</t>
   </si>
   <si>
-    <t>Gomez, Manuel</t>
+    <t>Encarnacion, Jefferson</t>
+  </si>
+  <si>
+    <t>Lara, Carlos</t>
+  </si>
+  <si>
+    <t>Alcantara, Jostin</t>
+  </si>
+  <si>
+    <t>Fernandez, Jehiber</t>
   </si>
   <si>
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Fukuda, Masahiro</t>
-  </si>
-  <si>
-    <t>Encarnacion, Jefferson</t>
-  </si>
-  <si>
     <t>Castillo, Albert</t>
   </si>
   <si>
-    <t>Lara, Carlos</t>
-  </si>
-  <si>
-    <t>Alcantara, Jostin</t>
-  </si>
-  <si>
-    <t>Fernandez, Jehiber</t>
+    <t>Pena, Dariel</t>
   </si>
   <si>
     <t>Acosta, Isaac</t>
   </si>
   <si>
-    <t>Pena, Dariel</t>
+    <t>Ramos, Daniel</t>
   </si>
   <si>
     <t>Peralta, Eddy</t>
   </si>
   <si>
+    <t>Ballesteros, Jean</t>
+  </si>
+  <si>
     <t>Cordero, Albert</t>
   </si>
   <si>
-    <t>Ballesteros, Jean</t>
-  </si>
-  <si>
-    <t>Ramos, Daniel</t>
-  </si>
-  <si>
     <t>Lamu, Alex</t>
   </si>
   <si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>Gonzalez, Nestor</t>
+  </si>
+  <si>
+    <t>Mendez, Eithan</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="37">
     <border/>
     <border>
       <left style="medium">
@@ -721,20 +724,6 @@
     </border>
     <border>
       <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -813,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -927,21 +916,21 @@
     <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -960,9 +949,6 @@
     <xf borderId="29" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="30" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -972,10 +958,10 @@
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="31" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="30" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="32" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -1024,7 +1010,7 @@
     <xf borderId="11" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="33" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="32" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1036,64 +1022,58 @@
     <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="32" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="32" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="32" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="32" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="32" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="32" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="34" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="34" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="33" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="35" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="35" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="36" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="37" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="36" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1601,16 +1581,16 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="D5" s="40">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="E5" s="40">
         <v>10.0</v>
       </c>
       <c r="F5" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G5" s="40">
         <v>4.0</v>
@@ -1619,7 +1599,7 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J5" s="39">
         <v>1.0</v>
@@ -1631,7 +1611,7 @@
         <v>4.0</v>
       </c>
       <c r="M5" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="N5" s="40">
         <v>2.0</v>
@@ -1643,20 +1623,20 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R5" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S5" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T5" s="41">
         <v>14.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>3585</v>
+        <v>4110</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1675,63 +1655,63 @@
       <c r="B6" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="39">
-        <v>11.0</v>
-      </c>
-      <c r="D6" s="40">
-        <v>12.0</v>
-      </c>
-      <c r="E6" s="40">
+      <c r="C6" s="45">
+        <v>18.0</v>
+      </c>
+      <c r="D6" s="46">
+        <v>21.0</v>
+      </c>
+      <c r="E6" s="46">
+        <v>10.0</v>
+      </c>
+      <c r="F6" s="46">
         <v>9.0</v>
       </c>
-      <c r="F6" s="40">
+      <c r="G6" s="46">
         <v>3.0</v>
       </c>
-      <c r="G6" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="41">
-        <v>24.0</v>
+      <c r="H6" s="46">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="47">
+        <v>7.0</v>
       </c>
       <c r="J6" s="39">
         <v>0.0</v>
       </c>
       <c r="K6" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L6" s="39">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M6" s="40">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="N6" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="O6" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P6" s="42">
         <v>0.0</v>
       </c>
       <c r="Q6" s="39">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="R6" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="S6" s="43">
         <v>4.0</v>
-      </c>
-      <c r="S6" s="43">
-        <v>2.0</v>
       </c>
       <c r="T6" s="41">
         <v>15.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>2880</v>
+        <v>3360</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1744,69 +1724,69 @@
       <c r="AD6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="48" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7" s="39">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="D7" s="40">
         <v>9.0</v>
       </c>
       <c r="E7" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F7" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G7" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H7" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="41">
         <v>2.0</v>
       </c>
-      <c r="G7" s="40">
+      <c r="J7" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L7" s="39">
         <v>3.0</v>
       </c>
-      <c r="H7" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="41">
+      <c r="M7" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q7" s="39">
         <v>6.0</v>
       </c>
-      <c r="J7" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="K7" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M7" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N7" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O7" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q7" s="39">
-        <v>8.0</v>
-      </c>
       <c r="R7" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S7" s="43">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T7" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>2850</v>
+        <v>3240</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1819,69 +1799,69 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="s">
-        <v>33</v>
+      <c r="A8" s="37" t="s">
+        <v>34</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="D8" s="40">
+        <v>14.0</v>
+      </c>
+      <c r="E8" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>26.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="39">
         <v>9.0</v>
       </c>
-      <c r="E8" s="40">
+      <c r="M8" s="40">
         <v>6.0</v>
       </c>
-      <c r="F8" s="40">
+      <c r="N8" s="40">
         <v>3.0</v>
       </c>
-      <c r="G8" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="40">
-        <v>0.0</v>
-      </c>
       <c r="O8" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P8" s="42">
         <v>0.0</v>
       </c>
       <c r="Q8" s="39">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="R8" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S8" s="43">
         <v>2.0</v>
       </c>
       <c r="T8" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>2775</v>
+        <v>3195</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1894,69 +1874,69 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="49" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="47">
-        <v>13.0</v>
-      </c>
-      <c r="D9" s="48">
-        <v>20.0</v>
-      </c>
-      <c r="E9" s="48">
+      <c r="C9" s="39">
+        <v>23.0</v>
+      </c>
+      <c r="D9" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="E9" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="41">
+        <v>7.0</v>
+      </c>
+      <c r="J9" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="K9" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M9" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N9" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O9" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q9" s="39">
         <v>9.0</v>
       </c>
-      <c r="F9" s="48">
-        <v>9.0</v>
-      </c>
-      <c r="G9" s="48">
+      <c r="R9" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S9" s="43">
         <v>2.0</v>
-      </c>
-      <c r="H9" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="49">
-        <v>4.0</v>
-      </c>
-      <c r="J9" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L9" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q9" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R9" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S9" s="43">
-        <v>3.0</v>
       </c>
       <c r="T9" s="41">
         <v>15.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>2700</v>
+        <v>3195</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1976,13 +1956,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="39">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D10" s="40">
         <v>5.0</v>
       </c>
       <c r="E10" s="40">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="F10" s="40">
         <v>5.0</v>
@@ -2018,7 +1998,7 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R10" s="40">
         <v>2.0</v>
@@ -2031,7 +2011,7 @@
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>2595</v>
+        <v>2925</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2044,17 +2024,17 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="48" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="39">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="D11" s="40">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="E11" s="40">
         <v>3.0</v>
@@ -2093,20 +2073,20 @@
         <v>0.0</v>
       </c>
       <c r="Q11" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R11" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S11" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T11" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2280</v>
+        <v>2445</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2126,19 +2106,19 @@
         <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D12" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E12" s="40">
         <v>5.0</v>
       </c>
       <c r="F12" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G12" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H12" s="40">
         <v>0.0</v>
@@ -2153,7 +2133,7 @@
         <v>0.0</v>
       </c>
       <c r="L12" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M12" s="40">
         <v>1.0</v>
@@ -2168,7 +2148,7 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="R12" s="40">
         <v>4.0</v>
@@ -2181,7 +2161,7 @@
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2235</v>
+        <v>2385</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2194,14 +2174,14 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="48" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="39">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="D13" s="40">
         <v>18.0</v>
@@ -2219,7 +2199,7 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J13" s="39">
         <v>1.0</v>
@@ -2243,20 +2223,20 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R13" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S13" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T13" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>1830</v>
+        <v>2160</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2269,17 +2249,17 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="48" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D14" s="40">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E14" s="40">
         <v>2.0</v>
@@ -2321,17 +2301,17 @@
         <v>5.0</v>
       </c>
       <c r="R14" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S14" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T14" s="41">
         <v>15.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1830</v>
+        <v>1935</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2351,10 +2331,10 @@
         <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D15" s="40">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E15" s="40">
         <v>8.0</v>
@@ -2393,7 +2373,7 @@
         <v>0.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R15" s="40">
         <v>4.0</v>
@@ -2406,7 +2386,7 @@
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1755</v>
+        <v>1875</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2426,10 +2406,10 @@
         <v>30</v>
       </c>
       <c r="C16" s="39">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D16" s="40">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E16" s="40">
         <v>1.0</v>
@@ -2456,7 +2436,7 @@
         <v>2.0</v>
       </c>
       <c r="M16" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="N16" s="40">
         <v>3.0</v>
@@ -2468,7 +2448,7 @@
         <v>0.0</v>
       </c>
       <c r="Q16" s="39">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R16" s="40">
         <v>4.0</v>
@@ -2481,7 +2461,7 @@
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1725</v>
+        <v>1815</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2494,69 +2474,69 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="48" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="39">
+        <v>16.0</v>
+      </c>
+      <c r="D17" s="40">
+        <v>15.0</v>
+      </c>
+      <c r="E17" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L17" s="39">
         <v>12.0</v>
       </c>
-      <c r="D17" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="E17" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="F17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="H17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J17" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="39">
-        <v>3.0</v>
-      </c>
       <c r="M17" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N17" s="40">
         <v>0.0</v>
       </c>
       <c r="O17" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P17" s="42">
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="R17" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S17" s="43">
         <v>2.0</v>
       </c>
       <c r="T17" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1575</v>
+        <v>1815</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2569,69 +2549,69 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="49" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C18" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="D18" s="40">
+        <v>28.0</v>
+      </c>
+      <c r="E18" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G18" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="J18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R18" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="S18" s="43">
+        <v>4.0</v>
+      </c>
+      <c r="T18" s="41">
         <v>15.0</v>
-      </c>
-      <c r="D18" s="40">
-        <v>15.0</v>
-      </c>
-      <c r="E18" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="F18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="M18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R18" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S18" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="T18" s="41">
-        <v>12.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1560</v>
+        <v>1800</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2644,33 +2624,33 @@
       <c r="AD18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="51" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C19" s="39">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D19" s="40">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="E19" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="40">
         <v>4.0</v>
       </c>
-      <c r="F19" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G19" s="40">
+      <c r="H19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="41">
         <v>2.0</v>
       </c>
-      <c r="H19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="41">
-        <v>3.0</v>
-      </c>
       <c r="J19" s="39">
         <v>0.0</v>
       </c>
@@ -2678,7 +2658,7 @@
         <v>0.0</v>
       </c>
       <c r="L19" s="39">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="M19" s="40">
         <v>0.0</v>
@@ -2687,26 +2667,26 @@
         <v>0.0</v>
       </c>
       <c r="O19" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P19" s="42">
         <v>0.0</v>
       </c>
       <c r="Q19" s="39">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="R19" s="40">
         <v>4.0</v>
       </c>
       <c r="S19" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T19" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1485</v>
+        <v>1650</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2719,69 +2699,69 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="48" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C20" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="D20" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E20" s="40">
         <v>4.0</v>
       </c>
-      <c r="D20" s="40">
+      <c r="F20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="40">
         <v>4.0</v>
       </c>
-      <c r="E20" s="40">
+      <c r="N20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P20" s="42">
         <v>2.0</v>
       </c>
-      <c r="F20" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>1.0</v>
-      </c>
       <c r="Q20" s="39">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="R20" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S20" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T20" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1335</v>
+        <v>1575</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2794,69 +2774,69 @@
       <c r="AD20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="37" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="D21" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="E21" s="40">
         <v>4.0</v>
       </c>
-      <c r="D21" s="40">
+      <c r="F21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="39">
         <v>3.0</v>
       </c>
-      <c r="E21" s="40">
+      <c r="M21" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="N21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q21" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R21" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S21" s="43">
         <v>3.0</v>
       </c>
-      <c r="F21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="N21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P21" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="Q21" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="R21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="S21" s="43">
-        <v>0.0</v>
-      </c>
       <c r="T21" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1275</v>
+        <v>1395</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2869,23 +2849,23 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="50" t="s">
-        <v>34</v>
+      <c r="B22" s="38" t="s">
+        <v>33</v>
       </c>
       <c r="C22" s="39">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="D22" s="40">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E22" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="40">
         <v>1.0</v>
@@ -2894,44 +2874,44 @@
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q22" s="39">
         <v>4.0</v>
       </c>
-      <c r="J22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q22" s="39">
-        <v>5.0</v>
-      </c>
       <c r="R22" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S22" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T22" s="41">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1185</v>
+        <v>1380</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2944,69 +2924,69 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="49" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D23" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="E23" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F23" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q23" s="39">
         <v>7.0</v>
       </c>
-      <c r="E23" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M23" s="40">
+      <c r="R23" s="40">
         <v>2.0</v>
       </c>
-      <c r="N23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q23" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R23" s="40">
-        <v>3.0</v>
-      </c>
       <c r="S23" s="43">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="T23" s="41">
         <v>15.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1185</v>
+        <v>1365</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3019,11 +2999,11 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="48" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="39">
         <v>6.0</v>
@@ -3032,7 +3012,7 @@
         <v>11.0</v>
       </c>
       <c r="E24" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F24" s="40">
         <v>0.0</v>
@@ -3068,20 +3048,20 @@
         <v>0.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R24" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S24" s="43">
         <v>1.0</v>
       </c>
       <c r="T24" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1170</v>
+        <v>1350</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3094,14 +3074,14 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="49" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D25" s="40">
         <v>4.0</v>
@@ -3119,7 +3099,7 @@
         <v>0.0</v>
       </c>
       <c r="I25" s="41">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="J25" s="39">
         <v>0.0</v>
@@ -3146,17 +3126,17 @@
         <v>4.0</v>
       </c>
       <c r="R25" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="S25" s="43">
         <v>2.0</v>
-      </c>
-      <c r="S25" s="43">
-        <v>1.0</v>
       </c>
       <c r="T25" s="41">
         <v>15.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1290</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3169,69 +3149,69 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>34</v>
+      <c r="B26" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="C26" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="D26" s="40">
+        <v>15.0</v>
+      </c>
+      <c r="E26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J26" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P26" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q26" s="39">
         <v>6.0</v>
       </c>
-      <c r="D26" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="E26" s="40">
+      <c r="R26" s="40">
         <v>2.0</v>
       </c>
-      <c r="F26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J26" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P26" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q26" s="39">
+      <c r="S26" s="43">
         <v>3.0</v>
       </c>
-      <c r="R26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="S26" s="43">
-        <v>1.0</v>
-      </c>
       <c r="T26" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1230</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3244,69 +3224,69 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>30</v>
+      <c r="B27" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="C27" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="D27" s="40">
+        <v>18.0</v>
+      </c>
+      <c r="E27" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J27" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M27" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N27" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O27" s="40">
         <v>3.0</v>
       </c>
-      <c r="D27" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O27" s="40">
-        <v>1.0</v>
-      </c>
       <c r="P27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R27" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S27" s="43">
         <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1005</v>
+        <v>1215</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3319,7 +3299,7 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="48" t="s">
         <v>54</v>
       </c>
       <c r="B28" s="38" t="s">
@@ -3329,59 +3309,59 @@
         <v>4.0</v>
       </c>
       <c r="D28" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J28" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="40">
         <v>2.0</v>
       </c>
-      <c r="E28" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J28" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="40">
-        <v>0.0</v>
-      </c>
       <c r="O28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P28" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q28" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R28" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="S28" s="43">
         <v>2.0</v>
-      </c>
-      <c r="S28" s="43">
-        <v>0.0</v>
       </c>
       <c r="T28" s="41">
         <v>15.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>1110</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3394,17 +3374,17 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="49" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C29" s="39">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D29" s="40">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E29" s="40">
         <v>2.0</v>
@@ -3413,7 +3393,7 @@
         <v>0.0</v>
       </c>
       <c r="G29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="40">
         <v>0.0</v>
@@ -3428,7 +3408,7 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M29" s="40">
         <v>0.0</v>
@@ -3443,20 +3423,20 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="R29" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S29" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T29" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>825</v>
+        <v>1080</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3473,13 +3453,13 @@
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="39">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D30" s="40">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="E30" s="40">
         <v>3.0</v>
@@ -3524,14 +3504,14 @@
         <v>3.0</v>
       </c>
       <c r="S30" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T30" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3544,32 +3524,32 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="50" t="s">
-        <v>34</v>
+      <c r="B31" s="38" t="s">
+        <v>33</v>
       </c>
       <c r="C31" s="39">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D31" s="40">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E31" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F31" s="40">
         <v>0.0</v>
       </c>
       <c r="G31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H31" s="40">
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3578,16 +3558,16 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M31" s="40">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="N31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P31" s="42">
         <v>0.0</v>
@@ -3596,17 +3576,17 @@
         <v>3.0</v>
       </c>
       <c r="R31" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="43">
         <v>0.0</v>
       </c>
       <c r="T31" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>885</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3619,20 +3599,20 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="48" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D32" s="40">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="E32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F32" s="40">
         <v>0.0</v>
@@ -3644,7 +3624,7 @@
         <v>0.0</v>
       </c>
       <c r="I32" s="41">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="J32" s="39">
         <v>0.0</v>
@@ -3653,35 +3633,35 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M32" s="40">
         <v>0.0</v>
       </c>
       <c r="N32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P32" s="42">
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="R32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="S32" s="43">
         <v>2.0</v>
       </c>
-      <c r="R32" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S32" s="43">
-        <v>1.0</v>
-      </c>
       <c r="T32" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>735</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3694,69 +3674,69 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="48" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D33" s="40">
+        <v>17.0</v>
+      </c>
+      <c r="E33" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F33" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="I33" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J33" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M33" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O33" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q33" s="39">
         <v>2.0</v>
       </c>
-      <c r="E33" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M33" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q33" s="39">
-        <v>3.0</v>
-      </c>
       <c r="R33" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S33" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T33" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>690</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3773,65 +3753,65 @@
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="D34" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="E34" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M34" s="40">
         <v>3.0</v>
       </c>
-      <c r="D34" s="40">
+      <c r="N34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="39">
         <v>3.0</v>
       </c>
-      <c r="E34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M34" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S34" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T34" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3844,23 +3824,23 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="51" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C35" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D35" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="E35" s="40">
         <v>0.0</v>
       </c>
       <c r="F35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" s="40">
         <v>0.0</v>
@@ -3878,10 +3858,10 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N35" s="40">
         <v>0.0</v>
@@ -3896,17 +3876,17 @@
         <v>2.0</v>
       </c>
       <c r="R35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S35" s="43">
         <v>0.0</v>
       </c>
       <c r="T35" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>495</v>
+        <v>660</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3919,17 +3899,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="37" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C36" s="39">
         <v>1.0</v>
       </c>
       <c r="D36" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3944,7 +3924,7 @@
         <v>0.0</v>
       </c>
       <c r="I36" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J36" s="39">
         <v>0.0</v>
@@ -3953,7 +3933,7 @@
         <v>0.0</v>
       </c>
       <c r="L36" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M36" s="40">
         <v>0.0</v>
@@ -3968,20 +3948,20 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R36" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S36" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T36" s="41">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3998,7 +3978,7 @@
         <v>63</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="39">
         <v>1.0</v>
@@ -4052,11 +4032,11 @@
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4073,7 +4053,7 @@
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="39">
         <v>0.0</v>
@@ -4126,12 +4106,12 @@
       <c r="S38" s="55">
         <v>0.0</v>
       </c>
-      <c r="T38" s="56">
-        <v>12.0</v>
+      <c r="T38" s="41">
+        <v>14.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4230,15 +4210,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.0" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="58"/>
-      <c r="J1" s="59"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="12" t="s">
         <v>6</v>
       </c>
@@ -4253,167 +4233,167 @@
       <c r="R1" s="8"/>
     </row>
     <row r="2" ht="18.0" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61">
         <v>75.0</v>
       </c>
-      <c r="D2" s="63">
+      <c r="D2" s="62">
         <v>-30.0</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="63">
         <v>60.0</v>
       </c>
-      <c r="F2" s="64">
+      <c r="F2" s="63">
         <v>90.0</v>
       </c>
-      <c r="G2" s="64">
+      <c r="G2" s="63">
         <v>180.0</v>
       </c>
-      <c r="H2" s="63">
+      <c r="H2" s="62">
         <v>-15.0</v>
       </c>
-      <c r="I2" s="65">
+      <c r="I2" s="64">
         <v>30.0</v>
       </c>
-      <c r="J2" s="66">
+      <c r="J2" s="65">
         <v>-15.0</v>
       </c>
-      <c r="K2" s="67">
+      <c r="K2" s="66">
         <v>180.0</v>
       </c>
-      <c r="L2" s="67">
+      <c r="L2" s="66">
         <v>180.0</v>
       </c>
-      <c r="M2" s="68">
+      <c r="M2" s="67">
         <v>180.0</v>
       </c>
-      <c r="N2" s="69">
+      <c r="N2" s="68">
         <v>60.0</v>
       </c>
       <c r="O2" s="23">
         <v>180.0</v>
       </c>
-      <c r="P2" s="67">
+      <c r="P2" s="66">
         <v>30.0</v>
       </c>
-      <c r="Q2" s="68">
+      <c r="Q2" s="67">
         <v>30.0</v>
       </c>
-      <c r="R2" s="70"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="74" t="s">
+      <c r="G3" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="74" t="s">
+      <c r="H3" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="75" t="s">
+      <c r="I3" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="76" t="s">
+      <c r="J3" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="72" t="s">
+      <c r="K3" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="L3" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="77" t="s">
+      <c r="M3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="72" t="s">
+      <c r="N3" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="73" t="s">
+      <c r="O3" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="73" t="s">
+      <c r="P3" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="77" t="s">
+      <c r="Q3" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="77" t="s">
+      <c r="R3" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="70"/>
+      <c r="U3" s="70"/>
+      <c r="V3" s="70"/>
+      <c r="W3" s="70"/>
+      <c r="X3" s="70"/>
+      <c r="Y3" s="70"/>
+      <c r="Z3" s="70"/>
     </row>
     <row r="4">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="80">
-        <v>21.0</v>
-      </c>
-      <c r="D4" s="81">
-        <v>4.0</v>
-      </c>
-      <c r="E4" s="81">
-        <v>12.0</v>
-      </c>
-      <c r="F4" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="H4" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I4" s="81">
+      <c r="C4" s="79">
+        <v>24.0</v>
+      </c>
+      <c r="D4" s="80">
+        <v>5.0</v>
+      </c>
+      <c r="E4" s="80">
+        <v>13.0</v>
+      </c>
+      <c r="F4" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="H4" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="80">
         <v>0.0</v>
       </c>
       <c r="J4" s="42">
         <v>0.0</v>
       </c>
-      <c r="K4" s="82">
+      <c r="K4" s="81">
         <v>1.0</v>
       </c>
       <c r="L4" s="42">
         <v>0.0</v>
       </c>
-      <c r="M4" s="83">
+      <c r="M4" s="82">
         <v>3.0</v>
       </c>
-      <c r="N4" s="82">
+      <c r="N4" s="81">
         <v>0.0</v>
       </c>
       <c r="O4" s="42">
@@ -4422,22 +4402,22 @@
       <c r="P4" s="42">
         <v>0.0</v>
       </c>
-      <c r="Q4" s="83">
+      <c r="Q4" s="82">
         <v>15.0</v>
       </c>
-      <c r="R4" s="84">
-        <f t="shared" ref="R4:R10" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>3510</v>
+      <c r="R4" s="83">
+        <f t="shared" ref="R4:R12" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>3765</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="82">
+      <c r="B5" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="81">
         <v>24.0</v>
       </c>
       <c r="D5" s="42">
@@ -4452,7 +4432,7 @@
       <c r="G5" s="42">
         <v>1.0</v>
       </c>
-      <c r="H5" s="81">
+      <c r="H5" s="80">
         <v>0.0</v>
       </c>
       <c r="I5" s="42">
@@ -4461,16 +4441,16 @@
       <c r="J5" s="42">
         <v>0.0</v>
       </c>
-      <c r="K5" s="82">
+      <c r="K5" s="81">
         <v>2.0</v>
       </c>
       <c r="L5" s="42">
         <v>1.0</v>
       </c>
-      <c r="M5" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N5" s="82">
+      <c r="M5" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N5" s="81">
         <v>0.0</v>
       </c>
       <c r="O5" s="42">
@@ -4479,454 +4459,454 @@
       <c r="P5" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q5" s="83">
+      <c r="Q5" s="82">
+        <v>10.0</v>
+      </c>
+      <c r="R5" s="83">
+        <f t="shared" si="1"/>
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="81">
+        <v>22.0</v>
+      </c>
+      <c r="D6" s="42">
         <v>8.0</v>
       </c>
-      <c r="R5" s="84">
+      <c r="E6" s="42">
+        <v>15.0</v>
+      </c>
+      <c r="F6" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="M6" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q6" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="78" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="82">
-        <v>18.0</v>
-      </c>
-      <c r="D6" s="42">
-        <v>7.0</v>
-      </c>
-      <c r="E6" s="42">
-        <v>12.0</v>
-      </c>
-      <c r="F6" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L6" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="M6" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q6" s="83">
-        <v>11.0</v>
-      </c>
-      <c r="R6" s="84">
-        <f t="shared" si="1"/>
-        <v>2490</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="77" t="s">
         <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="82">
+        <v>33</v>
+      </c>
+      <c r="C7" s="81">
         <v>18.0</v>
       </c>
       <c r="D7" s="42">
         <v>8.0</v>
       </c>
       <c r="E7" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="F7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="J7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="L7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="N7" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q7" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R7" s="83">
+        <f t="shared" si="1"/>
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="81">
+        <v>22.0</v>
+      </c>
+      <c r="D8" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="E8" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="F8" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="82">
+        <v>11.0</v>
+      </c>
+      <c r="R8" s="83">
+        <f t="shared" si="1"/>
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="81">
+        <v>18.0</v>
+      </c>
+      <c r="D9" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E9" s="42">
         <v>12.0</v>
       </c>
-      <c r="F7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M7" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q7" s="83">
+      <c r="F9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="80">
+        <v>2.0</v>
+      </c>
+      <c r="J9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="M9" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q9" s="82">
         <v>15.0</v>
       </c>
-      <c r="R7" s="84">
+      <c r="R9" s="83">
+        <f t="shared" si="1"/>
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="81">
+        <v>18.0</v>
+      </c>
+      <c r="D10" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="E10" s="42">
+        <v>12.0</v>
+      </c>
+      <c r="F10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="L10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q10" s="82">
+        <v>15.0</v>
+      </c>
+      <c r="R10" s="83">
         <f t="shared" si="1"/>
         <v>2475</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="86" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="42" t="s">
+    <row r="11">
+      <c r="A11" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="81">
+        <v>16.0</v>
+      </c>
+      <c r="D11" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>12.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="K11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R11" s="83">
+        <f t="shared" si="1"/>
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="82">
+      <c r="C12" s="81">
         <v>19.0</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D12" s="42">
         <v>12.0</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E12" s="42">
         <v>11.0</v>
       </c>
-      <c r="F8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K8" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q8" s="83">
+      <c r="F12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="K12" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="L12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q12" s="82">
         <v>15.0</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R12" s="83">
         <f t="shared" si="1"/>
         <v>2355</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="82">
-        <v>16.0</v>
-      </c>
-      <c r="D9" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="E9" s="42">
-        <v>12.0</v>
-      </c>
-      <c r="F9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K9" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q9" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R9" s="84">
-        <f t="shared" si="1"/>
-        <v>2325</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="82">
-        <v>15.0</v>
-      </c>
-      <c r="D10" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="E10" s="42">
+    <row r="13">
+      <c r="A13" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="81">
+        <v>21.0</v>
+      </c>
+      <c r="D13" s="42">
+        <v>11.0</v>
+      </c>
+      <c r="E13" s="42">
         <v>10.0</v>
       </c>
-      <c r="F10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="J10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="L10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="83">
-        <v>1.0</v>
-      </c>
-      <c r="N10" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q10" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R10" s="84">
-        <f t="shared" si="1"/>
-        <v>2325</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="82">
-        <v>21.0</v>
-      </c>
-      <c r="D11" s="42">
-        <v>11.0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>10.0</v>
-      </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q11" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R11" s="84">
-        <f>C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2</f>
-        <v>2235</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="86" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="82">
-        <v>13.0</v>
-      </c>
-      <c r="D12" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="E12" s="42">
-        <v>10.0</v>
-      </c>
-      <c r="F12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="81">
-        <v>2.0</v>
-      </c>
-      <c r="J12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="M12" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="83">
-        <v>15.0</v>
-      </c>
-      <c r="R12" s="84">
-        <f t="shared" ref="R12:R35" si="2">C12*$C$2+D12*$D$2+E12*$E$2+F12*$F$2+G12*$G$2+H12*$H$2+K12*$K$2+L12*$L$2+M12*$M$2+N12*$N$2+O12*$O$2+P12*$P$2+Q12*$Q$2+I12*$I$2+J12*$J$2</f>
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="85" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="82">
-        <v>19.0</v>
-      </c>
-      <c r="D13" s="42">
-        <v>7.0</v>
-      </c>
-      <c r="E13" s="42">
-        <v>6.0</v>
-      </c>
       <c r="F13" s="42">
         <v>0.0</v>
       </c>
       <c r="G13" s="42">
         <v>0.0</v>
       </c>
-      <c r="H13" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="81">
+      <c r="H13" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="80">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
         <v>0.0</v>
       </c>
-      <c r="K13" s="82">
+      <c r="K13" s="81">
         <v>0.0</v>
       </c>
       <c r="L13" s="42">
         <v>0.0</v>
       </c>
-      <c r="M13" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N13" s="82">
+      <c r="M13" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="81">
         <v>0.0</v>
       </c>
       <c r="O13" s="42">
@@ -4935,12 +4915,12 @@
       <c r="P13" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q13" s="83">
-        <v>13.0</v>
-      </c>
-      <c r="R13" s="84">
-        <f t="shared" si="2"/>
-        <v>1995</v>
+      <c r="Q13" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R13" s="83">
+        <f>C13*$C$2+D13*$D$2+E13*$E$2+F13*$F$2+G13*$G$2+H13*$H$2+K13*$K$2+L13*$L$2+M13*$M$2+N13*$N$2+O13*$O$2+P13*$P$2+Q13*$Q$2</f>
+        <v>2295</v>
       </c>
     </row>
     <row r="14">
@@ -4948,693 +4928,693 @@
         <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="82">
-        <v>17.0</v>
+        <v>30</v>
+      </c>
+      <c r="C14" s="81">
+        <v>18.0</v>
       </c>
       <c r="D14" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E14" s="42">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="F14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="H14" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I14" s="80">
         <v>0.0</v>
       </c>
       <c r="J14" s="42">
         <v>0.0</v>
       </c>
-      <c r="K14" s="82">
+      <c r="K14" s="81">
         <v>0.0</v>
       </c>
       <c r="L14" s="42">
         <v>0.0</v>
       </c>
-      <c r="M14" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N14" s="82">
+      <c r="M14" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="81">
         <v>0.0</v>
       </c>
       <c r="O14" s="42">
         <v>0.0</v>
       </c>
       <c r="P14" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q14" s="83">
-        <v>9.0</v>
-      </c>
-      <c r="R14" s="84">
-        <f t="shared" si="2"/>
-        <v>1965</v>
+        <v>1.0</v>
+      </c>
+      <c r="Q14" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R14" s="83">
+        <f t="shared" ref="R14:R36" si="2">C14*$C$2+D14*$D$2+E14*$E$2+F14*$F$2+G14*$G$2+H14*$H$2+K14*$K$2+L14*$L$2+M14*$M$2+N14*$N$2+O14*$O$2+P14*$P$2+Q14*$Q$2+I14*$I$2+J14*$J$2</f>
+        <v>2265</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="87" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="82">
-        <v>14.0</v>
+      <c r="C15" s="81">
+        <v>19.0</v>
       </c>
       <c r="D15" s="42">
+        <v>10.0</v>
+      </c>
+      <c r="E15" s="42">
+        <v>10.0</v>
+      </c>
+      <c r="F15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q15" s="82">
+        <v>15.0</v>
+      </c>
+      <c r="R15" s="83">
+        <f t="shared" si="2"/>
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="81">
+        <v>17.0</v>
+      </c>
+      <c r="D16" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="E16" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="F16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="J16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q16" s="82">
+        <v>15.0</v>
+      </c>
+      <c r="R16" s="83">
+        <f t="shared" si="2"/>
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="81">
+        <v>19.0</v>
+      </c>
+      <c r="D17" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="E17" s="42">
         <v>7.0</v>
       </c>
-      <c r="E15" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="F15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="H15" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I15" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M15" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q15" s="83">
-        <v>14.0</v>
-      </c>
-      <c r="R15" s="84">
+      <c r="F17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I17" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="J17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M17" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q17" s="82">
+        <v>15.0</v>
+      </c>
+      <c r="R17" s="83">
+        <f t="shared" si="2"/>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="81">
+        <v>19.0</v>
+      </c>
+      <c r="D18" s="42">
+        <v>11.0</v>
+      </c>
+      <c r="E18" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="F18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q18" s="82">
+        <v>13.0</v>
+      </c>
+      <c r="R18" s="83">
         <f t="shared" si="2"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="78" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="42" t="s">
+    <row r="19">
+      <c r="A19" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="82">
+      <c r="C19" s="81">
         <v>15.0</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D19" s="42">
         <v>7.0</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E19" s="42">
         <v>7.0</v>
       </c>
-      <c r="F16" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="83">
+      <c r="F19" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="82">
         <v>15.0</v>
       </c>
-      <c r="R16" s="84">
+      <c r="R19" s="83">
         <f t="shared" si="2"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="42" t="s">
+    <row r="20">
+      <c r="A20" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="82">
+      <c r="C20" s="81">
+        <v>19.0</v>
+      </c>
+      <c r="D20" s="42">
+        <v>18.0</v>
+      </c>
+      <c r="E20" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="F20" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q20" s="82">
         <v>14.0</v>
       </c>
-      <c r="D17" s="42">
+      <c r="R20" s="83">
+        <f t="shared" si="2"/>
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="81">
+        <v>13.0</v>
+      </c>
+      <c r="D21" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="E21" s="42">
+        <v>11.0</v>
+      </c>
+      <c r="F21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I21" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="K21" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M21" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q21" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R21" s="83">
+        <f t="shared" si="2"/>
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="81">
+        <v>15.0</v>
+      </c>
+      <c r="D22" s="42">
+        <v>17.0</v>
+      </c>
+      <c r="E22" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="F22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M22" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="Q22" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R22" s="83">
+        <f t="shared" si="2"/>
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="81">
+        <v>15.0</v>
+      </c>
+      <c r="D23" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="E23" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="F23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="80">
+        <v>2.0</v>
+      </c>
+      <c r="I23" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q23" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R23" s="83">
+        <f t="shared" si="2"/>
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="86" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="81">
+        <v>10.0</v>
+      </c>
+      <c r="D24" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E24" s="42">
         <v>7.0</v>
       </c>
-      <c r="E17" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="F17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M17" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P17" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q17" s="83">
-        <v>15.0</v>
-      </c>
-      <c r="R17" s="84">
+      <c r="F24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M24" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q24" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="42" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="82">
-        <v>15.0</v>
-      </c>
-      <c r="D18" s="42">
-        <v>11.0</v>
-      </c>
-      <c r="E18" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="F18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="J18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P18" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q18" s="83">
-        <v>15.0</v>
-      </c>
-      <c r="R18" s="84">
-        <f t="shared" si="2"/>
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="86" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="82">
-        <v>15.0</v>
-      </c>
-      <c r="D19" s="42">
-        <v>11.0</v>
-      </c>
-      <c r="E19" s="42">
+      <c r="C25" s="81">
+        <v>9.0</v>
+      </c>
+      <c r="D25" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="E25" s="42">
         <v>5.0</v>
       </c>
-      <c r="F19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I19" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="J19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="83">
-        <v>15.0</v>
-      </c>
-      <c r="R19" s="84">
-        <f t="shared" si="2"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="78" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="82">
-        <v>13.0</v>
-      </c>
-      <c r="D20" s="42">
+      <c r="F25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q25" s="82">
         <v>14.0</v>
       </c>
-      <c r="E20" s="42">
-        <v>11.0</v>
-      </c>
-      <c r="F20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I20" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K20" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R20" s="84">
-        <f t="shared" si="2"/>
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="82">
-        <v>15.0</v>
-      </c>
-      <c r="D21" s="42">
-        <v>15.0</v>
-      </c>
-      <c r="E21" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G21" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P21" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q21" s="83">
-        <v>14.0</v>
-      </c>
-      <c r="R21" s="84">
-        <f t="shared" si="2"/>
-        <v>1515</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="82">
-        <v>15.0</v>
-      </c>
-      <c r="D22" s="42">
-        <v>9.0</v>
-      </c>
-      <c r="E22" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="F22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="81">
-        <v>2.0</v>
-      </c>
-      <c r="I22" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P22" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q22" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R22" s="84">
+      <c r="R25" s="83">
         <f t="shared" si="2"/>
         <v>1395</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="82">
-        <v>8.0</v>
-      </c>
-      <c r="D23" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="E23" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="F23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M23" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q23" s="83">
-        <v>14.0</v>
-      </c>
-      <c r="R23" s="84">
-        <f t="shared" si="2"/>
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="87" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="82">
-        <v>10.0</v>
-      </c>
-      <c r="D24" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="E24" s="42">
-        <v>7.0</v>
-      </c>
-      <c r="F24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M24" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P24" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q24" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R24" s="84">
-        <f t="shared" si="2"/>
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="82">
-        <v>12.0</v>
-      </c>
-      <c r="D25" s="42">
-        <v>15.0</v>
-      </c>
-      <c r="E25" s="42">
-        <v>7.0</v>
-      </c>
-      <c r="F25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="Q25" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R25" s="84">
-        <f t="shared" si="2"/>
-        <v>1290</v>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="85" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="82">
+      <c r="C26" s="81">
         <v>9.0</v>
       </c>
       <c r="D26" s="42">
@@ -5649,25 +5629,25 @@
       <c r="G26" s="42">
         <v>0.0</v>
       </c>
-      <c r="H26" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="42">
+      <c r="H26" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="80">
         <v>0.0</v>
       </c>
       <c r="J26" s="42">
         <v>0.0</v>
       </c>
-      <c r="K26" s="82">
+      <c r="K26" s="81">
         <v>0.0</v>
       </c>
       <c r="L26" s="42">
         <v>0.0</v>
       </c>
-      <c r="M26" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="82">
+      <c r="M26" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="81">
         <v>0.0</v>
       </c>
       <c r="O26" s="42">
@@ -5676,22 +5656,22 @@
       <c r="P26" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q26" s="83">
+      <c r="Q26" s="82">
         <v>15.0</v>
       </c>
-      <c r="R26" s="84">
+      <c r="R26" s="83">
         <f t="shared" si="2"/>
         <v>1275</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="89" t="s">
+      <c r="A27" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="82">
+      <c r="B27" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="81">
         <v>12.0</v>
       </c>
       <c r="D27" s="42">
@@ -5706,7 +5686,7 @@
       <c r="G27" s="42">
         <v>0.0</v>
       </c>
-      <c r="H27" s="81">
+      <c r="H27" s="80">
         <v>1.0</v>
       </c>
       <c r="I27" s="42">
@@ -5715,16 +5695,16 @@
       <c r="J27" s="42">
         <v>1.0</v>
       </c>
-      <c r="K27" s="82">
+      <c r="K27" s="81">
         <v>0.0</v>
       </c>
       <c r="L27" s="42">
         <v>0.0</v>
       </c>
-      <c r="M27" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="82">
+      <c r="M27" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="81">
         <v>0.0</v>
       </c>
       <c r="O27" s="42">
@@ -5733,22 +5713,22 @@
       <c r="P27" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q27" s="83">
-        <v>13.0</v>
-      </c>
-      <c r="R27" s="84">
+      <c r="Q27" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1230</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="82">
+      <c r="C28" s="81">
         <v>10.0</v>
       </c>
       <c r="D28" s="42">
@@ -5763,7 +5743,7 @@
       <c r="G28" s="42">
         <v>0.0</v>
       </c>
-      <c r="H28" s="81">
+      <c r="H28" s="80">
         <v>0.0</v>
       </c>
       <c r="I28" s="42">
@@ -5772,16 +5752,16 @@
       <c r="J28" s="42">
         <v>0.0</v>
       </c>
-      <c r="K28" s="82">
+      <c r="K28" s="81">
         <v>0.0</v>
       </c>
       <c r="L28" s="42">
         <v>0.0</v>
       </c>
-      <c r="M28" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="82">
+      <c r="M28" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="81">
         <v>0.0</v>
       </c>
       <c r="O28" s="42">
@@ -5790,29 +5770,29 @@
       <c r="P28" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q28" s="83">
+      <c r="Q28" s="82">
         <v>14.0</v>
       </c>
-      <c r="R28" s="84">
+      <c r="R28" s="83">
         <f t="shared" si="2"/>
         <v>1110</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="87" t="s">
+      <c r="A29" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="79" t="s">
+      <c r="B29" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="82">
-        <v>7.0</v>
+      <c r="C29" s="81">
+        <v>9.0</v>
       </c>
       <c r="D29" s="42">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E29" s="42">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F29" s="42">
         <v>0.0</v>
@@ -5820,7 +5800,7 @@
       <c r="G29" s="42">
         <v>0.0</v>
       </c>
-      <c r="H29" s="81">
+      <c r="H29" s="80">
         <v>0.0</v>
       </c>
       <c r="I29" s="42">
@@ -5829,16 +5809,16 @@
       <c r="J29" s="42">
         <v>0.0</v>
       </c>
-      <c r="K29" s="82">
+      <c r="K29" s="81">
         <v>0.0</v>
       </c>
       <c r="L29" s="42">
         <v>0.0</v>
       </c>
-      <c r="M29" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="82">
+      <c r="M29" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="81">
         <v>0.0</v>
       </c>
       <c r="O29" s="42">
@@ -5847,22 +5827,22 @@
       <c r="P29" s="42">
         <v>0.0</v>
       </c>
-      <c r="Q29" s="83">
+      <c r="Q29" s="82">
         <v>13.0</v>
       </c>
-      <c r="R29" s="84">
+      <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>825</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="81" t="s">
         <v>100</v>
       </c>
       <c r="B30" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="82">
+      <c r="C30" s="81">
         <v>7.0</v>
       </c>
       <c r="D30" s="42">
@@ -5877,7 +5857,7 @@
       <c r="G30" s="42">
         <v>0.0</v>
       </c>
-      <c r="H30" s="81">
+      <c r="H30" s="80">
         <v>0.0</v>
       </c>
       <c r="I30" s="42">
@@ -5886,16 +5866,16 @@
       <c r="J30" s="42">
         <v>0.0</v>
       </c>
-      <c r="K30" s="82">
+      <c r="K30" s="81">
         <v>0.0</v>
       </c>
       <c r="L30" s="42">
         <v>0.0</v>
       </c>
-      <c r="M30" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="82">
+      <c r="M30" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="81">
         <v>0.0</v>
       </c>
       <c r="O30" s="42">
@@ -5904,22 +5884,22 @@
       <c r="P30" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q30" s="83">
+      <c r="Q30" s="82">
         <v>15.0</v>
       </c>
-      <c r="R30" s="84">
+      <c r="R30" s="83">
         <f t="shared" si="2"/>
         <v>795</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="77" t="s">
         <v>101</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="82">
+        <v>33</v>
+      </c>
+      <c r="C31" s="81">
         <v>8.0</v>
       </c>
       <c r="D31" s="42">
@@ -5934,7 +5914,7 @@
       <c r="G31" s="42">
         <v>0.0</v>
       </c>
-      <c r="H31" s="81">
+      <c r="H31" s="80">
         <v>2.0</v>
       </c>
       <c r="I31" s="42">
@@ -5943,16 +5923,16 @@
       <c r="J31" s="42">
         <v>0.0</v>
       </c>
-      <c r="K31" s="82">
+      <c r="K31" s="81">
         <v>0.0</v>
       </c>
       <c r="L31" s="42">
         <v>0.0</v>
       </c>
-      <c r="M31" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N31" s="82">
+      <c r="M31" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="81">
         <v>0.0</v>
       </c>
       <c r="O31" s="42">
@@ -5961,22 +5941,22 @@
       <c r="P31" s="42">
         <v>0.0</v>
       </c>
-      <c r="Q31" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R31" s="84">
+      <c r="Q31" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>690</v>
+        <v>750</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="78" t="s">
+      <c r="A32" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="82">
+      <c r="B32" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="81">
         <v>7.0</v>
       </c>
       <c r="D32" s="42">
@@ -5991,25 +5971,25 @@
       <c r="G32" s="42">
         <v>0.0</v>
       </c>
-      <c r="H32" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="81">
+      <c r="H32" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="42">
         <v>0.0</v>
       </c>
       <c r="J32" s="42">
         <v>0.0</v>
       </c>
-      <c r="K32" s="82">
+      <c r="K32" s="81">
         <v>0.0</v>
       </c>
       <c r="L32" s="42">
         <v>0.0</v>
       </c>
-      <c r="M32" s="83">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="82">
+      <c r="M32" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="81">
         <v>0.0</v>
       </c>
       <c r="O32" s="42">
@@ -6018,190 +5998,247 @@
       <c r="P32" s="42">
         <v>1.0</v>
       </c>
-      <c r="Q32" s="83">
-        <v>12.0</v>
-      </c>
-      <c r="R32" s="84">
+      <c r="Q32" s="82">
+        <v>14.0</v>
+      </c>
+      <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>645</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="90" t="s">
+      <c r="A33" s="86" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="91" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="92">
+      <c r="B33" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="81">
         <v>5.0</v>
       </c>
-      <c r="D33" s="93">
+      <c r="D33" s="42">
         <v>9.0</v>
       </c>
-      <c r="E33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="I33" s="93">
+      <c r="E33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I33" s="80">
         <v>0.0</v>
       </c>
       <c r="J33" s="42">
         <v>0.0</v>
       </c>
-      <c r="K33" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="Q33" s="94">
-        <v>14.0</v>
-      </c>
-      <c r="R33" s="84">
+      <c r="K33" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q33" s="82">
+        <v>16.0</v>
+      </c>
+      <c r="R33" s="83">
+        <f t="shared" si="2"/>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="91">
+        <v>2.0</v>
+      </c>
+      <c r="D34" s="90">
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="92">
+        <v>13.0</v>
+      </c>
+      <c r="R34" s="83">
         <f t="shared" si="2"/>
         <v>510</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="95" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="93" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="92">
-        <v>2.0</v>
-      </c>
-      <c r="D34" s="93">
-        <v>1.0</v>
-      </c>
-      <c r="E34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="92">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="94">
-        <v>11.0</v>
-      </c>
-      <c r="R34" s="84">
-        <f t="shared" si="2"/>
-        <v>450</v>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="96" t="s">
+      <c r="A35" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="99">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="99">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="100">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="98">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="100">
+      <c r="C35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="91">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="92">
         <v>13.0</v>
       </c>
-      <c r="R35" s="101">
+      <c r="R35" s="83">
         <f t="shared" si="2"/>
         <v>390</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="95">
+        <v>1.0</v>
+      </c>
+      <c r="D36" s="54">
+        <v>6.0</v>
+      </c>
+      <c r="E36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="95">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="95">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q36" s="97">
+        <v>1.0</v>
+      </c>
+      <c r="R36" s="98">
+        <f t="shared" si="2"/>
+        <v>-75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$3:$R$35">
-    <sortState ref="A3:R35">
-      <sortCondition descending="1" ref="R3:R35"/>
-      <sortCondition ref="A3:A35"/>
+  <autoFilter ref="$A$3:$R$36">
+    <sortState ref="A3:R36">
+      <sortCondition descending="1" ref="R3:R36"/>
+      <sortCondition ref="A3:A36"/>
     </sortState>
   </autoFilter>
   <mergeCells count="5">
@@ -6211,7 +6248,7 @@
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="R4:R35">
+  <conditionalFormatting sqref="R4:R36">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6223,12 +6260,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B35">
+  <conditionalFormatting sqref="B4:B36">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B35">
+  <conditionalFormatting sqref="B4:B36">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B4))))</formula>
     </cfRule>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -143,10 +143,10 @@
     <t>Ramirez, Santiago</t>
   </si>
   <si>
+    <t>Abreu, Ariel</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
-  </si>
-  <si>
-    <t>Abreu, Ariel</t>
   </si>
   <si>
     <t>Done, Carlos</t>
@@ -2399,65 +2399,65 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="48" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C16" s="39">
+        <v>16.0</v>
+      </c>
+      <c r="D16" s="40">
+        <v>15.0</v>
+      </c>
+      <c r="E16" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L16" s="39">
         <v>12.0</v>
       </c>
-      <c r="D16" s="40">
-        <v>14.0</v>
-      </c>
-      <c r="E16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>2.0</v>
-      </c>
       <c r="M16" s="40">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="N16" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="O16" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P16" s="42">
         <v>0.0</v>
       </c>
       <c r="Q16" s="39">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="R16" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S16" s="43">
         <v>2.0</v>
       </c>
       <c r="T16" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
@@ -2474,65 +2474,65 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="37" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C17" s="39">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="D17" s="40">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="E17" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J17" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M17" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="N17" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="O17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q17" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R17" s="40">
         <v>4.0</v>
-      </c>
-      <c r="F17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L17" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="M17" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P17" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q17" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R17" s="40">
-        <v>5.0</v>
       </c>
       <c r="S17" s="43">
         <v>2.0</v>
       </c>
       <c r="T17" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
@@ -2742,7 +2742,7 @@
         <v>0.0</v>
       </c>
       <c r="O20" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P20" s="42">
         <v>2.0</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1575</v>
+        <v>1590</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -4127,6 +4127,7 @@
   <autoFilter ref="$A$4:$U$38">
     <sortState ref="A4:U38">
       <sortCondition descending="1" ref="U4:U38"/>
+      <sortCondition descending="1" ref="O4:O38"/>
       <sortCondition ref="B4:B38"/>
       <sortCondition descending="1" ref="G4:G38"/>
       <sortCondition ref="A4:A38"/>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -1692,7 +1692,7 @@
         <v>0.0</v>
       </c>
       <c r="O6" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="P6" s="42">
         <v>0.0</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>3360</v>
+        <v>3345</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1914,7 +1914,7 @@
         <v>1.0</v>
       </c>
       <c r="N9" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O9" s="40">
         <v>0.0</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3195</v>
+        <v>3225</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -2193,7 +2193,7 @@
         <v>1.0</v>
       </c>
       <c r="G13" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H13" s="40">
         <v>0.0</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2160</v>
+        <v>2175</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2292,7 +2292,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P14" s="42">
         <v>0.0</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1935</v>
+        <v>1920</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2592,7 +2592,7 @@
         <v>1.0</v>
       </c>
       <c r="O18" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P18" s="42">
         <v>0.0</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>1785</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2664,7 +2664,7 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O19" s="40">
         <v>0.0</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1650</v>
+        <v>1680</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -3042,7 +3042,7 @@
         <v>0.0</v>
       </c>
       <c r="O24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P24" s="42">
         <v>0.0</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1335</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/2/2026</t>
+    <t>Actualización: 6/5/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -113,15 +113,15 @@
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Mateo, Cesar</t>
+  </si>
+  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Mateo, Cesar</t>
-  </si>
-  <si>
     <t>Rodriguez, Alex</t>
   </si>
   <si>
@@ -137,36 +137,36 @@
     <t>Castillo, Wesly</t>
   </si>
   <si>
+    <t>Diaz, David</t>
+  </si>
+  <si>
+    <t>Ramirez, Santiago</t>
+  </si>
+  <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
-    <t>Ramirez, Santiago</t>
+    <t>Benitez, Frainker</t>
   </si>
   <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
-    <t>Diaz, David</t>
-  </si>
-  <si>
     <t>Done, Carlos</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
     <t>Marcano, Jose</t>
   </si>
   <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
+    <t>Valdes, Abel</t>
+  </si>
+  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Valdes, Abel</t>
-  </si>
-  <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
@@ -176,33 +176,33 @@
     <t>Pinder, Jayln</t>
   </si>
   <si>
+    <t>Ortiz Jr, David</t>
+  </si>
+  <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
+    <t>Montero, Darling</t>
+  </si>
+  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
-    <t>Ortiz Jr, David</t>
-  </si>
-  <si>
-    <t>Montero, Darling</t>
-  </si>
-  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
+    <t>Santa, Fraimy</t>
+  </si>
+  <si>
     <t>Coronado, Francisco</t>
   </si>
   <si>
+    <t>Colina, Felix</t>
+  </si>
+  <si>
     <t>Genao, Jhostin</t>
   </si>
   <si>
-    <t>Colina, Felix</t>
-  </si>
-  <si>
-    <t>Santa, Fraimy</t>
-  </si>
-  <si>
     <t>Seminiel, Cristian</t>
   </si>
   <si>
@@ -251,15 +251,15 @@
     <t>Pineda, Frandel</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
     <t>Gomez, Manuel</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
@@ -275,6 +275,9 @@
     <t>Lara, Carlos</t>
   </si>
   <si>
+    <t>Peralta, Eddy</t>
+  </si>
+  <si>
     <t>Alcantara, Jostin</t>
   </si>
   <si>
@@ -293,16 +296,19 @@
     <t>Acosta, Isaac</t>
   </si>
   <si>
+    <t>Liriano, Edgar</t>
+  </si>
+  <si>
     <t>Ramos, Daniel</t>
   </si>
   <si>
-    <t>Peralta, Eddy</t>
+    <t>Cordero, Albert</t>
   </si>
   <si>
     <t>Ballesteros, Jean</t>
   </si>
   <si>
-    <t>Cordero, Albert</t>
+    <t>Perez, Juanangel</t>
   </si>
   <si>
     <t>Lamu, Alex</t>
@@ -311,13 +317,7 @@
     <t>Figuereo, Breyner</t>
   </si>
   <si>
-    <t>Perez, Juanangel</t>
-  </si>
-  <si>
     <t>Figuereo, Enmanuel</t>
-  </si>
-  <si>
-    <t>Liriano, Edgar</t>
   </si>
   <si>
     <t>Medina, Ruben</t>
@@ -931,11 +931,11 @@
     <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1581,10 +1581,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="D5" s="40">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="E5" s="40">
         <v>10.0</v>
@@ -1608,7 +1608,7 @@
         <v>0.0</v>
       </c>
       <c r="L5" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M5" s="40">
         <v>11.0</v>
@@ -1626,17 +1626,17 @@
         <v>14.0</v>
       </c>
       <c r="R5" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="S5" s="43">
         <v>4.0</v>
       </c>
       <c r="T5" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4110</v>
+        <v>4200</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1662,7 +1662,7 @@
         <v>21.0</v>
       </c>
       <c r="E6" s="46">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F6" s="46">
         <v>9.0</v>
@@ -1680,7 +1680,7 @@
         <v>0.0</v>
       </c>
       <c r="K6" s="41">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L6" s="39">
         <v>0.0</v>
@@ -1701,17 +1701,17 @@
         <v>14.0</v>
       </c>
       <c r="R6" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="S6" s="43">
         <v>4.0</v>
       </c>
       <c r="T6" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>3345</v>
+        <v>3645</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1724,23 +1724,23 @@
       <c r="AD6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="37" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" s="39">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="D7" s="40">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="E7" s="40">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F7" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" s="40">
         <v>4.0</v>
@@ -1749,44 +1749,44 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="41">
+        <v>27.0</v>
+      </c>
+      <c r="J7" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="39">
+        <v>9.0</v>
+      </c>
+      <c r="M7" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N7" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="O7" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q7" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R7" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S7" s="43">
         <v>2.0</v>
       </c>
-      <c r="J7" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L7" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M7" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O7" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q7" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R7" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S7" s="43">
-        <v>3.0</v>
-      </c>
       <c r="T7" s="41">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>3240</v>
+        <v>3480</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1799,23 +1799,23 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>30</v>
-      </c>
       <c r="C8" s="39">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
       <c r="D8" s="40">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="E8" s="40">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F8" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" s="40">
         <v>4.0</v>
@@ -1824,44 +1824,44 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="41">
-        <v>26.0</v>
+        <v>2.0</v>
       </c>
       <c r="J8" s="39">
         <v>0.0</v>
       </c>
       <c r="K8" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="L8" s="39">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="M8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="39">
         <v>6.0</v>
       </c>
-      <c r="N8" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="O8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="39">
-        <v>12.0</v>
-      </c>
       <c r="R8" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="S8" s="43">
         <v>4.0</v>
       </c>
-      <c r="S8" s="43">
-        <v>2.0</v>
-      </c>
       <c r="T8" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3195</v>
+        <v>3270</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1932,11 +1932,11 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3225</v>
+        <v>3255</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1956,7 +1956,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="39">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="D10" s="40">
         <v>5.0</v>
@@ -1968,13 +1968,13 @@
         <v>5.0</v>
       </c>
       <c r="G10" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="H10" s="40">
         <v>0.0</v>
       </c>
       <c r="I10" s="41">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="J10" s="39">
         <v>0.0</v>
@@ -2001,17 +2001,17 @@
         <v>11.0</v>
       </c>
       <c r="R10" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S10" s="43">
         <v>2.0</v>
       </c>
       <c r="T10" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>2925</v>
+        <v>3195</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2028,13 +2028,13 @@
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="39">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="D11" s="40">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E11" s="40">
         <v>3.0</v>
@@ -2079,14 +2079,14 @@
         <v>5.0</v>
       </c>
       <c r="S11" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T11" s="41">
         <v>14.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2445</v>
+        <v>2520</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2109,13 +2109,13 @@
         <v>14.0</v>
       </c>
       <c r="D12" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E12" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F12" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G12" s="40">
         <v>4.0</v>
@@ -2151,17 +2151,17 @@
         <v>12.0</v>
       </c>
       <c r="R12" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S12" s="43">
         <v>3.0</v>
       </c>
       <c r="T12" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2385</v>
+        <v>2520</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2178,13 +2178,13 @@
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="39">
         <v>17.0</v>
       </c>
       <c r="D13" s="40">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E13" s="40">
         <v>3.0</v>
@@ -2199,10 +2199,10 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J13" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K13" s="41">
         <v>0.0</v>
@@ -2229,14 +2229,14 @@
         <v>5.0</v>
       </c>
       <c r="S13" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T13" s="41">
         <v>14.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2175</v>
+        <v>2385</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2249,23 +2249,23 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="D14" s="40">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="E14" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F14" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="40">
         <v>3.0</v>
@@ -2274,7 +2274,7 @@
         <v>0.0</v>
       </c>
       <c r="I14" s="41">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="J14" s="39">
         <v>0.0</v>
@@ -2283,35 +2283,35 @@
         <v>0.0</v>
       </c>
       <c r="L14" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M14" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="N14" s="40">
         <v>3.0</v>
       </c>
-      <c r="M14" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N14" s="40">
-        <v>0.0</v>
-      </c>
       <c r="O14" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P14" s="42">
         <v>0.0</v>
       </c>
       <c r="Q14" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R14" s="40">
         <v>5.0</v>
       </c>
-      <c r="R14" s="40">
-        <v>7.0</v>
-      </c>
       <c r="S14" s="43">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="T14" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>2025</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2324,17 +2324,17 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="50" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D15" s="40">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E15" s="40">
         <v>8.0</v>
@@ -2376,17 +2376,17 @@
         <v>11.0</v>
       </c>
       <c r="R15" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S15" s="43">
         <v>2.0</v>
       </c>
       <c r="T15" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1875</v>
+        <v>1980</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2402,66 +2402,66 @@
       <c r="A16" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>33</v>
+      <c r="B16" s="51" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="39">
+        <v>17.0</v>
+      </c>
+      <c r="D16" s="40">
+        <v>22.0</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>6.0</v>
+      </c>
+      <c r="J16" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M16" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="N16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R16" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S16" s="43">
+        <v>4.0</v>
+      </c>
+      <c r="T16" s="41">
         <v>16.0</v>
-      </c>
-      <c r="D16" s="40">
-        <v>15.0</v>
-      </c>
-      <c r="E16" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="M16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R16" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S16" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="T16" s="41">
-        <v>14.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1815</v>
+        <v>1950</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2474,26 +2474,26 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="50" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C17" s="39">
         <v>12.0</v>
       </c>
       <c r="D17" s="40">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="E17" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F17" s="40">
         <v>0.0</v>
       </c>
       <c r="G17" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H17" s="40">
         <v>0.0</v>
@@ -2508,35 +2508,35 @@
         <v>0.0</v>
       </c>
       <c r="L17" s="39">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M17" s="40">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="N17" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="O17" s="40">
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="R17" s="40">
         <v>4.0</v>
       </c>
       <c r="S17" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T17" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1815</v>
+        <v>1950</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2549,69 +2549,69 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="48" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C18" s="39">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="D18" s="40">
-        <v>28.0</v>
+        <v>17.0</v>
       </c>
       <c r="E18" s="40">
         <v>5.0</v>
       </c>
       <c r="F18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L18" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="M18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="R18" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S18" s="43">
         <v>3.0</v>
       </c>
-      <c r="G18" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="J18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O18" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R18" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S18" s="43">
-        <v>4.0</v>
-      </c>
       <c r="T18" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1920</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2624,69 +2624,69 @@
       <c r="AD18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="49" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="39">
         <v>12.0</v>
       </c>
       <c r="D19" s="40">
-        <v>8.0</v>
+        <v>28.0</v>
       </c>
       <c r="E19" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F19" s="40">
         <v>3.0</v>
       </c>
-      <c r="F19" s="40">
-        <v>0.0</v>
-      </c>
       <c r="G19" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="J19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R19" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="S19" s="43">
         <v>4.0</v>
       </c>
-      <c r="H19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R19" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S19" s="43">
-        <v>2.0</v>
-      </c>
       <c r="T19" s="41">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1680</v>
+        <v>1815</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2703,7 +2703,7 @@
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="39">
         <v>6.0</v>
@@ -2832,11 +2832,11 @@
         <v>3.0</v>
       </c>
       <c r="T21" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2849,14 +2849,14 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="49" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C22" s="39">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="D22" s="40">
         <v>6.0</v>
@@ -2865,53 +2865,53 @@
         <v>3.0</v>
       </c>
       <c r="F22" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G22" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H22" s="40">
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="40">
         <v>2.0</v>
       </c>
-      <c r="J22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N22" s="40">
-        <v>1.0</v>
-      </c>
       <c r="O22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="R22" s="40">
         <v>2.0</v>
       </c>
       <c r="S22" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T22" s="41">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1395</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2924,32 +2924,32 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="48" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C23" s="39">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="D23" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E23" s="40">
         <v>3.0</v>
       </c>
       <c r="F23" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H23" s="40">
         <v>0.0</v>
       </c>
       <c r="I23" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J23" s="39">
         <v>0.0</v>
@@ -2961,32 +2961,32 @@
         <v>1.0</v>
       </c>
       <c r="M23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N23" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="R23" s="40">
         <v>2.0</v>
       </c>
       <c r="S23" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T23" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1365</v>
+        <v>1380</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3003,13 +3003,13 @@
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D24" s="40">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E24" s="40">
         <v>6.0</v>
@@ -3054,14 +3054,14 @@
         <v>6.0</v>
       </c>
       <c r="S24" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T24" s="41">
         <v>14.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1335</v>
+        <v>1350</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3084,7 +3084,7 @@
         <v>7.0</v>
       </c>
       <c r="D25" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E25" s="40">
         <v>0.0</v>
@@ -3117,7 +3117,7 @@
         <v>0.0</v>
       </c>
       <c r="O25" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P25" s="42">
         <v>0.0</v>
@@ -3126,17 +3126,17 @@
         <v>4.0</v>
       </c>
       <c r="R25" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S25" s="43">
         <v>2.0</v>
       </c>
       <c r="T25" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1305</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3152,8 +3152,8 @@
       <c r="A26" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="50" t="s">
-        <v>33</v>
+      <c r="B26" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C26" s="39">
         <v>10.0</v>
@@ -3224,20 +3224,20 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="50" t="s">
-        <v>33</v>
+      <c r="B27" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C27" s="39">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="D27" s="40">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E27" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F27" s="40">
         <v>0.0</v>
@@ -3249,7 +3249,7 @@
         <v>0.0</v>
       </c>
       <c r="I27" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="39">
         <v>0.0</v>
@@ -3258,35 +3258,35 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="40">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P27" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q27" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="R27" s="40">
         <v>3.0</v>
       </c>
-      <c r="P27" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q27" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="R27" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S27" s="43">
         <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1215</v>
+        <v>1230</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3299,69 +3299,69 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>30</v>
+      <c r="B28" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C28" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="D28" s="40">
+        <v>18.0</v>
+      </c>
+      <c r="E28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J28" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M28" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O28" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="P28" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" s="39">
         <v>4.0</v>
       </c>
-      <c r="D28" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="E28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J28" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O28" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P28" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q28" s="39">
-        <v>3.0</v>
-      </c>
       <c r="R28" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S28" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T28" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1215</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3374,69 +3374,69 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="50" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C29" s="39">
         <v>6.0</v>
       </c>
       <c r="D29" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="E29" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F29" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I29" s="41">
         <v>2.0</v>
       </c>
-      <c r="E29" s="40">
+      <c r="J29" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="39">
         <v>2.0</v>
       </c>
-      <c r="F29" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G29" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H29" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I29" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J29" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="39">
-        <v>0.0</v>
-      </c>
       <c r="M29" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="N29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P29" s="42">
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R29" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S29" s="43">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T29" s="41">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3449,56 +3449,56 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="48" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C30" s="39">
         <v>4.0</v>
       </c>
       <c r="D30" s="40">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J30" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="39">
         <v>3.0</v>
       </c>
-      <c r="F30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="41">
+      <c r="M30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="40">
         <v>2.0</v>
       </c>
-      <c r="J30" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M30" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="N30" s="40">
-        <v>1.0</v>
-      </c>
       <c r="O30" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P30" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R30" s="40">
         <v>3.0</v>
@@ -3507,11 +3507,11 @@
         <v>2.0</v>
       </c>
       <c r="T30" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1110</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3528,13 +3528,13 @@
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="39">
         <v>7.0</v>
       </c>
       <c r="D31" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E31" s="40">
         <v>2.0</v>
@@ -3579,7 +3579,7 @@
         <v>1.0</v>
       </c>
       <c r="S31" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T31" s="41">
         <v>14.0</v>
@@ -3599,69 +3599,69 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="s">
+      <c r="A32" s="50" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" s="39">
         <v>4.0</v>
       </c>
       <c r="D32" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J32" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M32" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q32" s="39">
         <v>2.0</v>
       </c>
-      <c r="E32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J32" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q32" s="39">
-        <v>0.0</v>
-      </c>
       <c r="R32" s="40">
         <v>0.0</v>
       </c>
       <c r="S32" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T32" s="41">
         <v>14.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>795</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3678,16 +3678,16 @@
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33" s="39">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D33" s="40">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="E33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F33" s="40">
         <v>0.0</v>
@@ -3696,10 +3696,10 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I33" s="41">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="J33" s="39">
         <v>0.0</v>
@@ -3708,25 +3708,25 @@
         <v>0.0</v>
       </c>
       <c r="L33" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M33" s="40">
         <v>0.0</v>
       </c>
       <c r="N33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P33" s="42">
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R33" s="40">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="S33" s="43">
         <v>2.0</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3749,11 +3749,11 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="50" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C34" s="39">
         <v>1.0</v>
@@ -3824,50 +3824,50 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="s">
+      <c r="A35" s="48" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="D35" s="40">
+        <v>19.0</v>
+      </c>
+      <c r="E35" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F35" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="I35" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J35" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="39">
         <v>3.0</v>
       </c>
-      <c r="D35" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="E35" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G35" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="39">
-        <v>1.0</v>
-      </c>
       <c r="M35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P35" s="42">
         <v>0.0</v>
@@ -3876,10 +3876,10 @@
         <v>2.0</v>
       </c>
       <c r="R35" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="S35" s="43">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T35" s="41">
         <v>14.0</v>
@@ -3977,8 +3977,8 @@
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="50" t="s">
-        <v>33</v>
+      <c r="B37" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C37" s="39">
         <v>1.0</v>
@@ -4049,11 +4049,11 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="50" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" s="39">
         <v>0.0</v>
@@ -4404,11 +4404,11 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R4" s="83">
         <f t="shared" ref="R4:R12" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>3765</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="5">
@@ -4416,7 +4416,7 @@
         <v>75</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="81">
         <v>24.0</v>
@@ -4473,7 +4473,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="81">
         <v>22.0</v>
@@ -4530,7 +4530,7 @@
         <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="81">
         <v>18.0</v>
@@ -4583,29 +4583,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="85" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="81">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="D8" s="42">
         <v>8.0</v>
       </c>
       <c r="E8" s="42">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="F8" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G8" s="42">
         <v>0.0</v>
       </c>
       <c r="H8" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I8" s="80">
         <v>0.0</v>
@@ -4614,13 +4614,13 @@
         <v>0.0</v>
       </c>
       <c r="K8" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L8" s="42">
         <v>0.0</v>
       </c>
       <c r="M8" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N8" s="81">
         <v>0.0</v>
@@ -4629,34 +4629,34 @@
         <v>0.0</v>
       </c>
       <c r="P8" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q8" s="82">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="R8" s="83">
         <f t="shared" si="1"/>
-        <v>2610</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="78" t="s">
-        <v>30</v>
+      <c r="B9" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="81">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="D9" s="42">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="E9" s="42">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" s="42">
         <v>0.0</v>
@@ -4665,7 +4665,7 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="80">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J9" s="42">
         <v>0.0</v>
@@ -4674,7 +4674,7 @@
         <v>0.0</v>
       </c>
       <c r="L9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="82">
         <v>0.0</v>
@@ -4689,25 +4689,25 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="82">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="R9" s="83">
         <f t="shared" si="1"/>
-        <v>2580</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="81">
         <v>18.0</v>
       </c>
       <c r="D10" s="42">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E10" s="42">
         <v>12.0</v>
@@ -4719,19 +4719,19 @@
         <v>0.0</v>
       </c>
       <c r="H10" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="80">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
       </c>
       <c r="K10" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L10" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M10" s="82">
         <v>0.0</v>
@@ -4743,14 +4743,14 @@
         <v>0.0</v>
       </c>
       <c r="P10" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q10" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R10" s="83">
         <f t="shared" si="1"/>
-        <v>2475</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="11">
@@ -4758,7 +4758,7 @@
         <v>81</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="81">
         <v>16.0</v>
@@ -4860,11 +4860,11 @@
         <v>1.0</v>
       </c>
       <c r="Q12" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R12" s="83">
         <f t="shared" si="1"/>
-        <v>2355</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="13">
@@ -4872,7 +4872,7 @@
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="81">
         <v>21.0</v>
@@ -4974,11 +4974,11 @@
         <v>1.0</v>
       </c>
       <c r="Q14" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R14" s="83">
         <f t="shared" ref="R14:R36" si="2">C14*$C$2+D14*$D$2+E14*$E$2+F14*$F$2+G14*$G$2+H14*$H$2+K14*$K$2+L14*$L$2+M14*$M$2+N14*$N$2+O14*$O$2+P14*$P$2+Q14*$Q$2+I14*$I$2+J14*$J$2</f>
-        <v>2265</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="15">
@@ -5031,28 +5031,28 @@
         <v>1.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2190</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="77" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" s="81">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="D16" s="42">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="E16" s="42">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="F16" s="42">
         <v>0.0</v>
@@ -5061,16 +5061,16 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="80">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="42">
         <v>0.0</v>
       </c>
       <c r="K16" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="42">
         <v>0.0</v>
@@ -5085,31 +5085,31 @@
         <v>0.0</v>
       </c>
       <c r="P16" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="86" t="s">
         <v>87</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="81">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="D17" s="42">
         <v>13.0</v>
       </c>
       <c r="E17" s="42">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="F17" s="42">
         <v>0.0</v>
@@ -5118,7 +5118,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I17" s="80">
         <v>1.0</v>
@@ -5142,18 +5142,18 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q17" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>1920</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="85" t="s">
         <v>88</v>
       </c>
       <c r="B18" s="42" t="s">
@@ -5163,10 +5163,10 @@
         <v>19.0</v>
       </c>
       <c r="D18" s="42">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E18" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F18" s="42">
         <v>0.0</v>
@@ -5175,10 +5175,10 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5199,34 +5199,34 @@
         <v>0.0</v>
       </c>
       <c r="P18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>1875</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="84" t="s">
         <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="81">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="D19" s="42">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E19" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="42">
         <v>0.0</v>
@@ -5256,28 +5256,28 @@
         <v>0.0</v>
       </c>
       <c r="P19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>1875</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="77" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="81">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="D20" s="42">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="E20" s="42">
         <v>7.0</v>
@@ -5313,46 +5313,46 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="82">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>1845</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="88" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" s="81">
-        <v>13.0</v>
+        <v>19.0</v>
       </c>
       <c r="D21" s="42">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="E21" s="42">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="F21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" s="42">
         <v>0.0</v>
       </c>
       <c r="H21" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21" s="80">
         <v>0.0</v>
       </c>
       <c r="J21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K21" s="81">
         <v>0.0</v>
@@ -5370,14 +5370,14 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>1605</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="22">
@@ -5385,16 +5385,16 @@
         <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" s="81">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="D22" s="42">
         <v>17.0</v>
       </c>
       <c r="E22" s="42">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="F22" s="42">
         <v>0.0</v>
@@ -5403,13 +5403,13 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I22" s="80">
         <v>0.0</v>
       </c>
       <c r="J22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K22" s="81">
         <v>0.0</v>
@@ -5427,40 +5427,40 @@
         <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q22" s="82">
         <v>14.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>1575</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="81" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C23" s="81">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="D23" s="42">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
       <c r="E23" s="42">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="42">
         <v>0.0</v>
       </c>
       <c r="H23" s="80">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="I23" s="80">
         <v>0.0</v>
@@ -5472,7 +5472,7 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M23" s="82">
         <v>0.0</v>
@@ -5487,28 +5487,28 @@
         <v>1.0</v>
       </c>
       <c r="Q23" s="82">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>1455</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="77" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="81">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="D24" s="42">
-        <v>6.0</v>
+        <v>17.0</v>
       </c>
       <c r="E24" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5541,14 +5541,14 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q24" s="82">
         <v>14.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1410</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="25">
@@ -5601,28 +5601,28 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1395</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="86" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C26" s="81">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D26" s="42">
         <v>6.0</v>
       </c>
       <c r="E26" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
@@ -5655,31 +5655,31 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q26" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="77" t="s">
         <v>97</v>
       </c>
       <c r="B27" s="78" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C27" s="81">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D27" s="42">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="E27" s="42">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5688,13 +5688,13 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I27" s="42">
         <v>0.0</v>
       </c>
       <c r="J27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" s="81">
         <v>0.0</v>
@@ -5715,25 +5715,25 @@
         <v>1.0</v>
       </c>
       <c r="Q27" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1260</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="81">
         <v>10.0</v>
       </c>
       <c r="D28" s="42">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="E28" s="42">
         <v>5.0</v>
@@ -5772,28 +5772,28 @@
         <v>1.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="86" t="s">
+      <c r="A29" s="88" t="s">
         <v>99</v>
       </c>
       <c r="B29" s="78" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C29" s="81">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D29" s="42">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="E29" s="42">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F29" s="42">
         <v>0.0</v>
@@ -5802,13 +5802,13 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I29" s="42">
         <v>0.0</v>
       </c>
       <c r="J29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K29" s="81">
         <v>0.0</v>
@@ -5826,34 +5826,34 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1005</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="s">
+      <c r="A30" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="81">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D30" s="42">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E30" s="42">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F30" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" s="42">
         <v>0.0</v>
@@ -5883,14 +5883,14 @@
         <v>0.0</v>
       </c>
       <c r="P30" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q30" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>795</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="31">
@@ -5898,16 +5898,16 @@
         <v>101</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="81">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D31" s="42">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="E31" s="42">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -5940,14 +5940,14 @@
         <v>0.0</v>
       </c>
       <c r="P31" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q31" s="82">
         <v>14.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>960</v>
       </c>
     </row>
     <row r="32">
@@ -5955,16 +5955,16 @@
         <v>102</v>
       </c>
       <c r="B32" s="78" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C32" s="81">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D32" s="42">
         <v>11.0</v>
       </c>
       <c r="E32" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F32" s="42">
         <v>0.0</v>
@@ -6000,11 +6000,11 @@
         <v>1.0</v>
       </c>
       <c r="Q32" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>705</v>
+        <v>945</v>
       </c>
     </row>
     <row r="33">
@@ -6012,13 +6012,13 @@
         <v>103</v>
       </c>
       <c r="B33" s="78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33" s="81">
         <v>5.0</v>
       </c>
       <c r="D33" s="42">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E33" s="42">
         <v>0.0</v>
@@ -6054,14 +6054,14 @@
         <v>0.0</v>
       </c>
       <c r="P33" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q33" s="82">
         <v>16.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34">
@@ -6069,7 +6069,7 @@
         <v>104</v>
       </c>
       <c r="B34" s="90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C34" s="91">
         <v>2.0</v>
@@ -6171,11 +6171,11 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="92">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R35" s="83">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36">
@@ -6183,7 +6183,7 @@
         <v>106</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C36" s="95">
         <v>1.0</v>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -110,24 +110,24 @@
     <t>R</t>
   </si>
   <si>
+    <t>Mateo, Cesar</t>
+  </si>
+  <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
-    <t>Mateo, Cesar</t>
-  </si>
-  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>Cavero, Braulio</t>
+  </si>
+  <si>
     <t>Rodriguez, Alex</t>
   </si>
   <si>
-    <t>Cavero, Braulio</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
@@ -140,15 +140,15 @@
     <t>Diaz, David</t>
   </si>
   <si>
+    <t>Benitez, Frainker</t>
+  </si>
+  <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
@@ -161,27 +161,27 @@
     <t>Volquez, Fabelin</t>
   </si>
   <si>
+    <t>Rodriguez, Victor</t>
+  </si>
+  <si>
+    <t>Jaquez, Luis</t>
+  </si>
+  <si>
+    <t>Alarcon, Rosnel</t>
+  </si>
+  <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
-    <t>Rodriguez, Victor</t>
-  </si>
-  <si>
-    <t>Jaquez, Luis</t>
-  </si>
-  <si>
-    <t>Alarcon, Rosnel</t>
-  </si>
-  <si>
     <t>Pinder, Jayln</t>
   </si>
   <si>
+    <t>Pereira, Raul</t>
+  </si>
+  <si>
     <t>Ortiz Jr, David</t>
   </si>
   <si>
-    <t>Pereira, Raul</t>
-  </si>
-  <si>
     <t>Montero, Darling</t>
   </si>
   <si>
@@ -203,15 +203,15 @@
     <t>Genao, Jhostin</t>
   </si>
   <si>
+    <t>Simon, Jhon</t>
+  </si>
+  <si>
     <t>Seminiel, Cristian</t>
   </si>
   <si>
     <t>Cedeno, Luis</t>
   </si>
   <si>
-    <t>Simon, Jhon</t>
-  </si>
-  <si>
     <t>Pitchers</t>
   </si>
   <si>
@@ -245,15 +245,21 @@
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
     <t>Medina, Juan</t>
   </si>
   <si>
+    <t>Santos, Aneudy</t>
+  </si>
+  <si>
+    <t>Dolsi, Frederik</t>
+  </si>
+  <si>
     <t>Pineda, Frandel</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
@@ -263,12 +269,6 @@
     <t>Gamez, Manuel</t>
   </si>
   <si>
-    <t>Dolsi, Frederik</t>
-  </si>
-  <si>
-    <t>Santos, Aneudy</t>
-  </si>
-  <si>
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
@@ -296,16 +296,16 @@
     <t>Acosta, Isaac</t>
   </si>
   <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
+    <t>Ballesteros, Jean</t>
+  </si>
+  <si>
     <t>Liriano, Edgar</t>
   </si>
   <si>
-    <t>Ramos, Daniel</t>
-  </si>
-  <si>
     <t>Cordero, Albert</t>
-  </si>
-  <si>
-    <t>Ballesteros, Jean</t>
   </si>
   <si>
     <t>Perez, Juanangel</t>
@@ -1629,14 +1629,14 @@
         <v>8.0</v>
       </c>
       <c r="S5" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T5" s="41">
         <v>15.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4200</v>
+        <v>4230</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1655,56 +1655,56 @@
       <c r="B6" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="45">
-        <v>18.0</v>
-      </c>
-      <c r="D6" s="46">
-        <v>21.0</v>
-      </c>
-      <c r="E6" s="46">
+      <c r="C6" s="39">
+        <v>16.0</v>
+      </c>
+      <c r="D6" s="40">
+        <v>15.0</v>
+      </c>
+      <c r="E6" s="40">
         <v>11.0</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="G6" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="41">
+        <v>27.0</v>
+      </c>
+      <c r="J6" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="39">
         <v>9.0</v>
       </c>
-      <c r="G6" s="46">
+      <c r="M6" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N6" s="40">
         <v>3.0</v>
       </c>
-      <c r="H6" s="46">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="47">
-        <v>7.0</v>
-      </c>
-      <c r="J6" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="41">
+      <c r="O6" s="40">
         <v>2.0</v>
       </c>
-      <c r="L6" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O6" s="40">
+      <c r="P6" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R6" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S6" s="43">
         <v>3.0</v>
-      </c>
-      <c r="P6" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>14.0</v>
-      </c>
-      <c r="R6" s="40">
-        <v>9.0</v>
-      </c>
-      <c r="S6" s="43">
-        <v>4.0</v>
       </c>
       <c r="T6" s="41">
         <v>16.0</v>
@@ -1730,63 +1730,63 @@
       <c r="B7" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="39">
-        <v>15.0</v>
-      </c>
-      <c r="D7" s="40">
+      <c r="C7" s="45">
+        <v>18.0</v>
+      </c>
+      <c r="D7" s="46">
+        <v>24.0</v>
+      </c>
+      <c r="E7" s="46">
+        <v>11.0</v>
+      </c>
+      <c r="F7" s="46">
+        <v>9.0</v>
+      </c>
+      <c r="G7" s="46">
+        <v>3.0</v>
+      </c>
+      <c r="H7" s="46">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="47">
+        <v>7.0</v>
+      </c>
+      <c r="J7" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L7" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="P7" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q7" s="39">
         <v>14.0</v>
       </c>
-      <c r="E7" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="F7" s="40">
+      <c r="R7" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="S7" s="43">
         <v>5.0</v>
-      </c>
-      <c r="G7" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="H7" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="41">
-        <v>27.0</v>
-      </c>
-      <c r="J7" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="39">
-        <v>9.0</v>
-      </c>
-      <c r="M7" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="N7" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="O7" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P7" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q7" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R7" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S7" s="43">
-        <v>2.0</v>
       </c>
       <c r="T7" s="41">
         <v>16.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>3480</v>
+        <v>3585</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1857,11 +1857,11 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3270</v>
+        <v>3300</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1874,44 +1874,44 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="37" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="39">
-        <v>23.0</v>
+        <v>18.0</v>
       </c>
       <c r="D9" s="40">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E9" s="40">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="F9" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="40">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="40">
         <v>0.0</v>
       </c>
       <c r="I9" s="41">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="J9" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K9" s="41">
         <v>0.0</v>
       </c>
       <c r="L9" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N9" s="40">
         <v>2.0</v>
@@ -1923,20 +1923,20 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R9" s="40">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="S9" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T9" s="41">
         <v>16.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3255</v>
+        <v>3285</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1949,44 +1949,44 @@
       <c r="AD9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="49" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="39">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="D10" s="40">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="E10" s="40">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G10" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="41">
         <v>7.0</v>
       </c>
-      <c r="H10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="41">
-        <v>6.0</v>
-      </c>
       <c r="J10" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K10" s="41">
         <v>0.0</v>
       </c>
       <c r="L10" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M10" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="40">
         <v>2.0</v>
@@ -1998,10 +1998,10 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="R10" s="40">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="S10" s="43">
         <v>2.0</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3195</v>
+        <v>3255</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2031,7 +2031,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="39">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="D11" s="40">
         <v>19.0</v>
@@ -2082,11 +2082,11 @@
         <v>4.0</v>
       </c>
       <c r="T11" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2520</v>
+        <v>2775</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2109,7 +2109,7 @@
         <v>14.0</v>
       </c>
       <c r="D12" s="40">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E12" s="40">
         <v>6.0</v>
@@ -2154,14 +2154,14 @@
         <v>5.0</v>
       </c>
       <c r="S12" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T12" s="41">
         <v>16.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2520</v>
+        <v>2490</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2181,10 +2181,10 @@
         <v>34</v>
       </c>
       <c r="C13" s="39">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="D13" s="40">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E13" s="40">
         <v>3.0</v>
@@ -2232,11 +2232,11 @@
         <v>4.0</v>
       </c>
       <c r="T13" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2385</v>
+        <v>2460</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2262,7 +2262,7 @@
         <v>15.0</v>
       </c>
       <c r="E14" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="40">
         <v>0.0</v>
@@ -2304,14 +2304,14 @@
         <v>5.0</v>
       </c>
       <c r="S14" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T14" s="41">
         <v>16.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>2025</v>
+        <v>2115</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2328,28 +2328,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C15" s="39">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="D15" s="40">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="E15" s="40">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F15" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H15" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="41">
         <v>2.0</v>
-      </c>
-      <c r="G15" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="41">
-        <v>0.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2361,32 +2361,32 @@
         <v>4.0</v>
       </c>
       <c r="M15" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O15" s="40">
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="R15" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S15" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T15" s="41">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>1980</v>
+        <v>2115</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2399,69 +2399,69 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="D16" s="40">
         <v>17.0</v>
       </c>
-      <c r="D16" s="40">
-        <v>22.0</v>
-      </c>
       <c r="E16" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="F16" s="40">
         <v>2.0</v>
       </c>
-      <c r="F16" s="40">
-        <v>1.0</v>
-      </c>
       <c r="G16" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M16" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N16" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R16" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S16" s="43">
         <v>3.0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="41">
-        <v>6.0</v>
-      </c>
-      <c r="J16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M16" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="N16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R16" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="S16" s="43">
-        <v>4.0</v>
       </c>
       <c r="T16" s="41">
         <v>16.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>1950</v>
+        <v>2055</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2474,32 +2474,32 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>34</v>
+      <c r="B17" s="51" t="s">
+        <v>30</v>
       </c>
       <c r="C17" s="39">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="D17" s="40">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
       <c r="E17" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F17" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H17" s="40">
         <v>0.0</v>
       </c>
       <c r="I17" s="41">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="J17" s="39">
         <v>0.0</v>
@@ -2508,31 +2508,31 @@
         <v>0.0</v>
       </c>
       <c r="L17" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M17" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N17" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O17" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q17" s="39">
         <v>5.0</v>
       </c>
       <c r="R17" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S17" s="43">
         <v>4.0</v>
       </c>
-      <c r="S17" s="43">
-        <v>3.0</v>
-      </c>
       <c r="T17" s="41">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
@@ -2559,7 +2559,7 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="40">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E18" s="40">
         <v>5.0</v>
@@ -2607,11 +2607,11 @@
         <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>1890</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2634,7 +2634,7 @@
         <v>12.0</v>
       </c>
       <c r="D19" s="40">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E19" s="40">
         <v>5.0</v>
@@ -2679,14 +2679,14 @@
         <v>6.0</v>
       </c>
       <c r="S19" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T19" s="41">
         <v>16.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1815</v>
+        <v>1785</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2757,11 +2757,11 @@
         <v>1.0</v>
       </c>
       <c r="T20" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1590</v>
+        <v>1620</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2849,32 +2849,32 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="48" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C22" s="39">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="D22" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E22" s="40">
         <v>3.0</v>
       </c>
       <c r="F22" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="40">
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2886,32 +2886,32 @@
         <v>1.0</v>
       </c>
       <c r="M22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N22" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O22" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="R22" s="40">
         <v>2.0</v>
       </c>
       <c r="S22" s="43">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T22" s="41">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1410</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2931,26 +2931,26 @@
         <v>34</v>
       </c>
       <c r="C23" s="39">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D23" s="40">
+        <v>14.0</v>
+      </c>
+      <c r="E23" s="40">
         <v>7.0</v>
       </c>
-      <c r="E23" s="40">
+      <c r="F23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="41">
         <v>3.0</v>
       </c>
-      <c r="F23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="41">
-        <v>2.0</v>
-      </c>
       <c r="J23" s="39">
         <v>0.0</v>
       </c>
@@ -2958,16 +2958,16 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="M23" s="40">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="N23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P23" s="42">
         <v>0.0</v>
@@ -2976,17 +2976,17 @@
         <v>4.0</v>
       </c>
       <c r="R23" s="40">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="S23" s="43">
         <v>2.0</v>
       </c>
       <c r="T23" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -2999,26 +2999,26 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="49" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D24" s="40">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="E24" s="40">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="F24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" s="40">
         <v>0.0</v>
@@ -3033,10 +3033,10 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="39">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="M24" s="40">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="40">
         <v>0.0</v>
@@ -3051,17 +3051,17 @@
         <v>4.0</v>
       </c>
       <c r="R24" s="40">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="S24" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T24" s="41">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1410</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3081,62 +3081,62 @@
         <v>30</v>
       </c>
       <c r="C25" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="D25" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="E25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q25" s="39">
         <v>7.0</v>
       </c>
-      <c r="D25" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="E25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>4.0</v>
-      </c>
       <c r="R25" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="S25" s="43">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="T25" s="41">
         <v>16.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1395</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3207,11 +3207,11 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1260</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3224,59 +3224,59 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>30</v>
+      <c r="B27" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="C27" s="39">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="D27" s="40">
+        <v>18.0</v>
+      </c>
+      <c r="E27" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J27" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M27" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N27" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O27" s="40">
         <v>3.0</v>
       </c>
-      <c r="E27" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="F27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O27" s="40">
-        <v>0.0</v>
-      </c>
       <c r="P27" s="42">
         <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="R27" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S27" s="43">
         <v>1.0</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1245</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3299,20 +3299,20 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>34</v>
+      <c r="B28" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="39">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="D28" s="40">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E28" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F28" s="40">
         <v>0.0</v>
@@ -3324,7 +3324,7 @@
         <v>0.0</v>
       </c>
       <c r="I28" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J28" s="39">
         <v>0.0</v>
@@ -3333,35 +3333,35 @@
         <v>0.0</v>
       </c>
       <c r="L28" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M28" s="40">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P28" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="R28" s="40">
         <v>3.0</v>
       </c>
-      <c r="P28" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q28" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="R28" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S28" s="43">
         <v>1.0</v>
       </c>
       <c r="T28" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1215</v>
+        <v>1230</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3432,11 +3432,11 @@
         <v>3.0</v>
       </c>
       <c r="T29" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1140</v>
+        <v>1170</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3531,16 +3531,16 @@
         <v>34</v>
       </c>
       <c r="C31" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D31" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E31" s="40">
         <v>2.0</v>
       </c>
       <c r="F31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="40">
         <v>1.0</v>
@@ -3582,11 +3582,11 @@
         <v>1.0</v>
       </c>
       <c r="T31" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>885</v>
+        <v>1005</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3657,11 +3657,11 @@
         <v>1.0</v>
       </c>
       <c r="T32" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3732,11 +3732,11 @@
         <v>2.0</v>
       </c>
       <c r="T33" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>765</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3807,11 +3807,11 @@
         <v>1.0</v>
       </c>
       <c r="T34" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>675</v>
+        <v>705</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3834,13 +3834,13 @@
         <v>5.0</v>
       </c>
       <c r="D35" s="40">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E35" s="40">
         <v>1.0</v>
       </c>
       <c r="F35" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" s="40">
         <v>0.0</v>
@@ -3882,11 +3882,11 @@
         <v>3.0</v>
       </c>
       <c r="T35" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>705</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3899,17 +3899,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="50" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C36" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D36" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3942,16 +3942,16 @@
         <v>0.0</v>
       </c>
       <c r="O36" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P36" s="42">
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="R36" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S36" s="43">
         <v>0.0</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>495</v>
+        <v>585</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3977,54 +3977,54 @@
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="51" t="s">
-        <v>34</v>
+      <c r="B37" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C37" s="39">
         <v>1.0</v>
       </c>
       <c r="D37" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="E37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I37" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J37" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P37" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q37" s="39">
         <v>2.0</v>
       </c>
-      <c r="E37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I37" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J37" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P37" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q37" s="39">
-        <v>0.0</v>
-      </c>
       <c r="R37" s="40">
         <v>1.0</v>
       </c>
@@ -4032,11 +4032,11 @@
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4049,17 +4049,17 @@
       <c r="AD37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="51" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D38" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="E38" s="40">
         <v>0.0</v>
@@ -4101,17 +4101,17 @@
         <v>0.0</v>
       </c>
       <c r="R38" s="53">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S38" s="55">
         <v>0.0</v>
       </c>
       <c r="T38" s="41">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U38" s="44">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>495</v>
       </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
@@ -4407,7 +4407,7 @@
         <v>16.0</v>
       </c>
       <c r="R4" s="83">
-        <f t="shared" ref="R4:R12" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <f t="shared" ref="R4:R7" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
         <v>3795</v>
       </c>
     </row>
@@ -4419,10 +4419,10 @@
         <v>34</v>
       </c>
       <c r="C5" s="81">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="D5" s="42">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E5" s="42">
         <v>10.0</v>
@@ -4461,37 +4461,37 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="82">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R5" s="83">
         <f t="shared" si="1"/>
-        <v>3390</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="85" t="s">
         <v>76</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C6" s="81">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="D6" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E6" s="42">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="F6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" s="42">
         <v>0.0</v>
       </c>
       <c r="H6" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I6" s="80">
         <v>0.0</v>
@@ -4500,13 +4500,13 @@
         <v>0.0</v>
       </c>
       <c r="K6" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M6" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N6" s="81">
         <v>0.0</v>
@@ -4518,11 +4518,11 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3000</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="7">
@@ -4533,16 +4533,16 @@
         <v>34</v>
       </c>
       <c r="C7" s="81">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="D7" s="42">
         <v>8.0</v>
       </c>
       <c r="E7" s="42">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="F7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" s="42">
         <v>0.0</v>
@@ -4551,19 +4551,19 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J7" s="42">
         <v>0.0</v>
       </c>
       <c r="K7" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M7" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N7" s="81">
         <v>0.0</v>
@@ -4579,99 +4579,99 @@
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>2730</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="86" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="81">
+        <v>28.0</v>
+      </c>
+      <c r="D8" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="E8" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="F8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q8" s="82">
+        <v>15.0</v>
+      </c>
+      <c r="R8" s="83">
+        <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="42" t="s">
         <v>30</v>
-      </c>
-      <c r="C8" s="81">
-        <v>18.0</v>
-      </c>
-      <c r="D8" s="42">
-        <v>8.0</v>
-      </c>
-      <c r="E8" s="42">
-        <v>12.0</v>
-      </c>
-      <c r="F8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="80">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="L8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="N8" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q8" s="82">
-        <v>16.0</v>
-      </c>
-      <c r="R8" s="83">
-        <f t="shared" si="1"/>
-        <v>2685</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="84" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>34</v>
       </c>
       <c r="C9" s="81">
         <v>22.0</v>
       </c>
       <c r="D9" s="42">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E9" s="42">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="F9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G9" s="42">
         <v>0.0</v>
       </c>
       <c r="H9" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I9" s="80">
         <v>0.0</v>
       </c>
       <c r="J9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K9" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L9" s="42">
         <v>0.0</v>
@@ -4686,31 +4686,31 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q9" s="82">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="R9" s="83">
-        <f t="shared" si="1"/>
-        <v>2610</v>
+        <f t="shared" ref="R9:R36" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
+        <v>2850</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="78" t="s">
-        <v>30</v>
+      <c r="B10" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="C10" s="81">
         <v>18.0</v>
       </c>
       <c r="D10" s="42">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="E10" s="42">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
@@ -4722,19 +4722,19 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="80">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
       </c>
       <c r="K10" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L10" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M10" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="81">
         <v>0.0</v>
@@ -4743,89 +4743,89 @@
         <v>0.0</v>
       </c>
       <c r="P10" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q10" s="82">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="R10" s="83">
-        <f t="shared" si="1"/>
-        <v>2610</v>
+        <f t="shared" si="2"/>
+        <v>2760</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="84" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="81">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="D11" s="42">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E11" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="82">
         <v>12.0</v>
       </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H11" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q11" s="82">
-        <v>14.0</v>
-      </c>
       <c r="R11" s="83">
-        <f t="shared" si="1"/>
-        <v>2385</v>
+        <f t="shared" si="2"/>
+        <v>2640</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="81">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="D12" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E12" s="42">
         <v>12.0</v>
       </c>
-      <c r="E12" s="42">
-        <v>11.0</v>
-      </c>
       <c r="F12" s="42">
         <v>0.0</v>
       </c>
@@ -4833,19 +4833,19 @@
         <v>0.0</v>
       </c>
       <c r="H12" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="80">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M12" s="82">
         <v>0.0</v>
@@ -4857,37 +4857,37 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q12" s="82">
         <v>16.0</v>
       </c>
       <c r="R12" s="83">
-        <f t="shared" si="1"/>
-        <v>2385</v>
+        <f t="shared" si="2"/>
+        <v>2610</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="77" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="81">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="D13" s="42">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="E13" s="42">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
       </c>
       <c r="G13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H13" s="80">
         <v>0.0</v>
@@ -4896,7 +4896,7 @@
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="81">
         <v>0.0</v>
@@ -4917,11 +4917,11 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R13" s="83">
-        <f>C13*$C$2+D13*$D$2+E13*$E$2+F13*$F$2+G13*$G$2+H13*$H$2+K13*$K$2+L13*$L$2+M13*$M$2+N13*$N$2+O13*$O$2+P13*$P$2+Q13*$Q$2</f>
-        <v>2295</v>
+        <f t="shared" si="2"/>
+        <v>2415</v>
       </c>
     </row>
     <row r="14">
@@ -4977,7 +4977,7 @@
         <v>15.0</v>
       </c>
       <c r="R14" s="83">
-        <f t="shared" ref="R14:R36" si="2">C14*$C$2+D14*$D$2+E14*$E$2+F14*$F$2+G14*$G$2+H14*$H$2+K14*$K$2+L14*$L$2+M14*$M$2+N14*$N$2+O14*$O$2+P14*$P$2+Q14*$Q$2+I14*$I$2+J14*$J$2</f>
+        <f t="shared" si="2"/>
         <v>2295</v>
       </c>
     </row>
@@ -5088,11 +5088,11 @@
         <v>2.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>2040</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="17">
@@ -5430,31 +5430,31 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="81" t="s">
+      <c r="A23" s="77" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C23" s="81">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="D23" s="42">
         <v>17.0</v>
       </c>
       <c r="E23" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="42">
         <v>0.0</v>
@@ -5472,7 +5472,7 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="82">
         <v>0.0</v>
@@ -5484,28 +5484,28 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q23" s="82">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>1590</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="86" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="42" t="s">
         <v>34</v>
       </c>
       <c r="C24" s="81">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="D24" s="42">
-        <v>17.0</v>
+        <v>7.0</v>
       </c>
       <c r="E24" s="42">
         <v>8.0</v>
@@ -5517,7 +5517,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
@@ -5541,37 +5541,37 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1575</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="81" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="81">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D25" s="42">
+        <v>17.0</v>
+      </c>
+      <c r="E25" s="42">
         <v>7.0</v>
       </c>
-      <c r="E25" s="42">
-        <v>5.0</v>
-      </c>
       <c r="F25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H25" s="80">
         <v>0.0</v>
@@ -5586,7 +5586,7 @@
         <v>0.0</v>
       </c>
       <c r="L25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M25" s="82">
         <v>0.0</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1455</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="26">
@@ -5613,22 +5613,22 @@
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C26" s="81">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D26" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E26" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
       </c>
       <c r="G26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" s="80">
         <v>0.0</v>
@@ -5655,14 +5655,14 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="82">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1410</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="27">
@@ -5829,11 +5829,11 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1260</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="30">
@@ -5943,11 +5943,11 @@
         <v>1.0</v>
       </c>
       <c r="Q31" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>990</v>
       </c>
     </row>
     <row r="32">
@@ -6057,11 +6057,11 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>510</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34">
@@ -6114,11 +6114,11 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="92">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R34" s="83">
         <f t="shared" si="2"/>
-        <v>510</v>
+        <v>540</v>
       </c>
     </row>
     <row r="35">
@@ -6228,11 +6228,11 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="97">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R36" s="98">
         <f t="shared" si="2"/>
-        <v>-75</v>
+        <v>-45</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -116,18 +116,18 @@
     <t>Zayas, Saivel</t>
   </si>
   <si>
+    <t>Cavero, Braulio</t>
+  </si>
+  <si>
+    <t>Rodriguez, Alex</t>
+  </si>
+  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Cavero, Braulio</t>
-  </si>
-  <si>
-    <t>Rodriguez, Alex</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
@@ -137,15 +137,15 @@
     <t>Castillo, Wesly</t>
   </si>
   <si>
+    <t>Benitez, Frainker</t>
+  </si>
+  <si>
+    <t>Ramirez, Santiago</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
-    <t>Ramirez, Santiago</t>
-  </si>
-  <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
@@ -158,22 +158,25 @@
     <t>Marcano, Jose</t>
   </si>
   <si>
+    <t>Jaquez, Luis</t>
+  </si>
+  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
+    <t>Pinder, Jayln</t>
+  </si>
+  <si>
+    <t>Alarcon, Rosnel</t>
+  </si>
+  <si>
+    <t>Valdes, Abel</t>
+  </si>
+  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Jaquez, Luis</t>
-  </si>
-  <si>
-    <t>Alarcon, Rosnel</t>
-  </si>
-  <si>
-    <t>Valdes, Abel</t>
-  </si>
-  <si>
-    <t>Pinder, Jayln</t>
+    <t>Montero, Darling</t>
   </si>
   <si>
     <t>Pereira, Raul</t>
@@ -182,9 +185,6 @@
     <t>Ortiz Jr, David</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
-  </si>
-  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
@@ -197,12 +197,12 @@
     <t>Coronado, Francisco</t>
   </si>
   <si>
+    <t>Genao, Jhostin</t>
+  </si>
+  <si>
     <t>Colina, Felix</t>
   </si>
   <si>
-    <t>Genao, Jhostin</t>
-  </si>
-  <si>
     <t>Simon, Jhon</t>
   </si>
   <si>
@@ -248,6 +248,12 @@
     <t>Roquez, Yadiel</t>
   </si>
   <si>
+    <t>Pineda, Frandel</t>
+  </si>
+  <si>
+    <t>Gomez, Manuel</t>
+  </si>
+  <si>
     <t>Medina, Juan</t>
   </si>
   <si>
@@ -257,21 +263,15 @@
     <t>Dolsi, Frederik</t>
   </si>
   <si>
-    <t>Pineda, Frandel</t>
-  </si>
-  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
-    <t>Gomez, Manuel</t>
+    <t>Encarnacion, Jefferson</t>
   </si>
   <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
-    <t>Encarnacion, Jefferson</t>
-  </si>
-  <si>
     <t>Lara, Carlos</t>
   </si>
   <si>
@@ -293,19 +293,19 @@
     <t>Pena, Dariel</t>
   </si>
   <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
     <t>Acosta, Isaac</t>
   </si>
   <si>
-    <t>Ramos, Daniel</t>
+    <t>Cordero, Albert</t>
+  </si>
+  <si>
+    <t>Liriano, Edgar</t>
   </si>
   <si>
     <t>Ballesteros, Jean</t>
-  </si>
-  <si>
-    <t>Liriano, Edgar</t>
-  </si>
-  <si>
-    <t>Cordero, Albert</t>
   </si>
   <si>
     <t>Perez, Juanangel</t>
@@ -925,10 +925,10 @@
     <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1632,11 +1632,11 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4230</v>
+        <v>4260</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1656,19 +1656,19 @@
         <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D6" s="40">
         <v>15.0</v>
       </c>
       <c r="E6" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F6" s="40">
         <v>6.0</v>
       </c>
       <c r="G6" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H6" s="40">
         <v>0.0</v>
@@ -1686,7 +1686,7 @@
         <v>9.0</v>
       </c>
       <c r="M6" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="N6" s="40">
         <v>3.0</v>
@@ -1701,17 +1701,17 @@
         <v>12.0</v>
       </c>
       <c r="R6" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S6" s="43">
         <v>3.0</v>
       </c>
       <c r="T6" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>3645</v>
+        <v>3945</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1782,11 +1782,11 @@
         <v>5.0</v>
       </c>
       <c r="T7" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>3585</v>
+        <v>3615</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1799,69 +1799,69 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="37" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="D8" s="40">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E8" s="40">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F8" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>6.0</v>
+      </c>
+      <c r="J8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M8" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N8" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O8" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R8" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="S8" s="43">
         <v>3.0</v>
       </c>
-      <c r="G8" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J8" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L8" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R8" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S8" s="43">
-        <v>4.0</v>
-      </c>
       <c r="T8" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3300</v>
+        <v>3480</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1874,44 +1874,44 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="s">
-        <v>35</v>
+      <c r="A9" s="48" t="s">
+        <v>34</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="39">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="D9" s="40">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E9" s="40">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" s="40">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H9" s="40">
         <v>0.0</v>
       </c>
       <c r="I9" s="41">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J9" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K9" s="41">
         <v>0.0</v>
       </c>
       <c r="L9" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M9" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N9" s="40">
         <v>2.0</v>
@@ -1923,20 +1923,20 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="R9" s="40">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="S9" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T9" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3285</v>
+        <v>3330</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1950,46 +1950,46 @@
     </row>
     <row r="10">
       <c r="A10" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>30</v>
-      </c>
       <c r="C10" s="39">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="D10" s="40">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E10" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F10" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G10" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="41">
         <v>2.0</v>
       </c>
-      <c r="G10" s="40">
+      <c r="J10" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L10" s="39">
         <v>3.0</v>
       </c>
-      <c r="H10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="41">
-        <v>7.0</v>
-      </c>
-      <c r="J10" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="K10" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="39">
-        <v>2.0</v>
-      </c>
       <c r="M10" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O10" s="40">
         <v>0.0</v>
@@ -1998,20 +1998,20 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="R10" s="40">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="S10" s="43">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="T10" s="41">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3255</v>
+        <v>3300</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2024,17 +2024,17 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="49" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="39">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="D11" s="40">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E11" s="40">
         <v>3.0</v>
@@ -2061,7 +2061,7 @@
         <v>4.0</v>
       </c>
       <c r="M11" s="40">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="N11" s="40">
         <v>0.0</v>
@@ -2073,20 +2073,20 @@
         <v>0.0</v>
       </c>
       <c r="Q11" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R11" s="40">
         <v>5.0</v>
       </c>
       <c r="S11" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T11" s="41">
         <v>15.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2775</v>
+        <v>2895</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2106,7 +2106,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="39">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="D12" s="40">
         <v>14.0</v>
@@ -2118,7 +2118,7 @@
         <v>8.0</v>
       </c>
       <c r="G12" s="40">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H12" s="40">
         <v>0.0</v>
@@ -2151,17 +2151,17 @@
         <v>12.0</v>
       </c>
       <c r="R12" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S12" s="43">
         <v>4.0</v>
       </c>
       <c r="T12" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2490</v>
+        <v>2805</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2174,14 +2174,14 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="49" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="39">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D13" s="40">
         <v>20.0</v>
@@ -2223,20 +2223,20 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R13" s="40">
         <v>5.0</v>
       </c>
       <c r="S13" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T13" s="41">
         <v>15.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2460</v>
+        <v>2595</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2249,69 +2249,69 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="50" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C14" s="39">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="D14" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="E14" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="F14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J14" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q14" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="R14" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="S14" s="43">
+        <v>4.0</v>
+      </c>
+      <c r="T14" s="41">
         <v>15.0</v>
-      </c>
-      <c r="E14" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="F14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J14" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="M14" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="N14" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="O14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P14" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q14" s="39">
-        <v>11.0</v>
-      </c>
-      <c r="R14" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S14" s="43">
-        <v>3.0</v>
-      </c>
-      <c r="T14" s="41">
-        <v>16.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>2115</v>
+        <v>2235</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2328,28 +2328,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="D15" s="40">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="E15" s="40">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F15" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2361,32 +2361,32 @@
         <v>4.0</v>
       </c>
       <c r="M15" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N15" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O15" s="40">
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="R15" s="40">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="S15" s="43">
         <v>3.0</v>
       </c>
       <c r="T15" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2115</v>
+        <v>2175</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2399,47 +2399,47 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="37" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="39">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D16" s="40">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="E16" s="40">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>3.0</v>
+      </c>
+      <c r="J16" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="39">
         <v>2.0</v>
       </c>
-      <c r="G16" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>4.0</v>
-      </c>
       <c r="M16" s="40">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="N16" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="O16" s="40">
         <v>0.0</v>
@@ -2457,11 +2457,11 @@
         <v>3.0</v>
       </c>
       <c r="T16" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2055</v>
+        <v>2145</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2474,17 +2474,17 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="49" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="39">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="D17" s="40">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="E17" s="40">
         <v>2.0</v>
@@ -2526,17 +2526,17 @@
         <v>5.0</v>
       </c>
       <c r="R17" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="S17" s="43">
         <v>4.0</v>
       </c>
       <c r="T17" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>1950</v>
+        <v>2070</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2549,11 +2549,11 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="49" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="39">
         <v>17.0</v>
@@ -2598,20 +2598,20 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R18" s="40">
         <v>5.0</v>
       </c>
       <c r="S18" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T18" s="41">
         <v>15.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1890</v>
+        <v>1950</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2624,20 +2624,20 @@
       <c r="AD18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="48" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="39">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D19" s="40">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="E19" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F19" s="40">
         <v>3.0</v>
@@ -2676,17 +2676,17 @@
         <v>12.0</v>
       </c>
       <c r="R19" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S19" s="43">
         <v>5.0</v>
       </c>
       <c r="T19" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1920</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2699,11 +2699,11 @@
       <c r="AD19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" s="39">
         <v>6.0</v>
@@ -2774,20 +2774,20 @@
       <c r="AD20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="49" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C21" s="39">
         <v>7.0</v>
       </c>
       <c r="D21" s="40">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="E21" s="40">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F21" s="40">
         <v>0.0</v>
@@ -2799,7 +2799,7 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J21" s="39">
         <v>0.0</v>
@@ -2808,35 +2808,35 @@
         <v>0.0</v>
       </c>
       <c r="L21" s="39">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="M21" s="40">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="N21" s="40">
         <v>0.0</v>
       </c>
       <c r="O21" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P21" s="42">
         <v>0.0</v>
       </c>
       <c r="Q21" s="39">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="R21" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S21" s="43">
         <v>3.0</v>
       </c>
       <c r="T21" s="41">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1425</v>
+        <v>1485</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2849,69 +2849,69 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="37" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C22" s="39">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D22" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="E22" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M22" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q22" s="39">
         <v>7.0</v>
       </c>
-      <c r="E22" s="40">
+      <c r="R22" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="S22" s="43">
         <v>3.0</v>
       </c>
-      <c r="F22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q22" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="R22" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="S22" s="43">
-        <v>2.0</v>
-      </c>
       <c r="T22" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2924,69 +2924,69 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="38" t="s">
-        <v>34</v>
+      <c r="B23" s="51" t="s">
+        <v>36</v>
       </c>
       <c r="C23" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="D23" s="40">
+        <v>16.0</v>
+      </c>
+      <c r="E23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="J23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q23" s="39">
         <v>7.0</v>
       </c>
-      <c r="D23" s="40">
-        <v>14.0</v>
-      </c>
-      <c r="E23" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="F23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J23" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="39">
-        <v>10.0</v>
-      </c>
-      <c r="M23" s="40">
-        <v>9.0</v>
-      </c>
-      <c r="N23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q23" s="39">
+      <c r="R23" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="S23" s="43">
         <v>4.0</v>
-      </c>
-      <c r="R23" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S23" s="43">
-        <v>2.0</v>
       </c>
       <c r="T23" s="41">
         <v>15.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -2999,7 +2999,7 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="48" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
@@ -3057,11 +3057,11 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1440</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3074,7 +3074,7 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="48" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
@@ -3132,11 +3132,11 @@
         <v>0.0</v>
       </c>
       <c r="T25" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3149,23 +3149,23 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="51" t="s">
-        <v>34</v>
+      <c r="B26" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="C26" s="39">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="D26" s="40">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="E26" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="40">
         <v>1.0</v>
@@ -3174,44 +3174,44 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J26" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P26" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q26" s="39">
         <v>4.0</v>
-      </c>
-      <c r="J26" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P26" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q26" s="39">
-        <v>6.0</v>
       </c>
       <c r="R26" s="40">
         <v>2.0</v>
       </c>
       <c r="S26" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T26" s="41">
         <v>15.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1410</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3224,23 +3224,23 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="51" t="s">
-        <v>34</v>
+      <c r="B27" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="C27" s="39">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="D27" s="40">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E27" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" s="40">
         <v>0.0</v>
@@ -3249,7 +3249,7 @@
         <v>0.0</v>
       </c>
       <c r="I27" s="41">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J27" s="39">
         <v>0.0</v>
@@ -3261,32 +3261,32 @@
         <v>2.0</v>
       </c>
       <c r="M27" s="40">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="N27" s="40">
         <v>1.0</v>
       </c>
       <c r="O27" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P27" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q27" s="39">
         <v>3.0</v>
       </c>
-      <c r="P27" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q27" s="39">
+      <c r="R27" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="S27" s="43">
         <v>4.0</v>
-      </c>
-      <c r="R27" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S27" s="43">
-        <v>1.0</v>
       </c>
       <c r="T27" s="41">
         <v>15.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1245</v>
+        <v>1380</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3299,69 +3299,69 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>30</v>
+      <c r="B28" s="51" t="s">
+        <v>36</v>
       </c>
       <c r="C28" s="39">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="D28" s="40">
+        <v>20.0</v>
+      </c>
+      <c r="E28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J28" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="M28" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O28" s="40">
         <v>3.0</v>
       </c>
-      <c r="E28" s="40">
+      <c r="P28" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R28" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S28" s="43">
         <v>2.0</v>
-      </c>
-      <c r="F28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J28" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P28" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q28" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="R28" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S28" s="43">
-        <v>1.0</v>
       </c>
       <c r="T28" s="41">
         <v>15.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1320</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3374,23 +3374,23 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="48" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C29" s="39">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D29" s="40">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E29" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="40">
         <v>0.0</v>
@@ -3399,7 +3399,7 @@
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3408,35 +3408,35 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M29" s="40">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O29" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P29" s="42">
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R29" s="40">
         <v>3.0</v>
       </c>
       <c r="S29" s="43">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="T29" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1170</v>
+        <v>1260</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3449,17 +3449,17 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="s">
+      <c r="A30" s="49" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D30" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E30" s="40">
         <v>0.0</v>
@@ -3468,7 +3468,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H30" s="40">
         <v>0.0</v>
@@ -3501,17 +3501,17 @@
         <v>3.0</v>
       </c>
       <c r="R30" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S30" s="43">
         <v>2.0</v>
       </c>
       <c r="T30" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1200</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3524,11 +3524,11 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="49" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C31" s="39">
         <v>8.0</v>
@@ -3603,7 +3603,7 @@
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C32" s="39">
         <v>4.0</v>
@@ -3674,11 +3674,11 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="49" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C33" s="39">
         <v>4.0</v>
@@ -3749,32 +3749,32 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="49" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C34" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D34" s="40">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="E34" s="40">
         <v>1.0</v>
       </c>
       <c r="F34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" s="40">
         <v>0.0</v>
       </c>
       <c r="H34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" s="41">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="J34" s="39">
         <v>0.0</v>
@@ -3783,16 +3783,16 @@
         <v>0.0</v>
       </c>
       <c r="L34" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M34" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P34" s="42">
         <v>0.0</v>
@@ -3801,17 +3801,17 @@
         <v>3.0</v>
       </c>
       <c r="R34" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S34" s="43">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="T34" s="41">
         <v>15.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3824,32 +3824,32 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="50" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C35" s="39">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D35" s="40">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="E35" s="40">
         <v>1.0</v>
       </c>
       <c r="F35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" s="40">
         <v>0.0</v>
       </c>
       <c r="H35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J35" s="39">
         <v>0.0</v>
@@ -3858,28 +3858,28 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M35" s="40">
         <v>3.0</v>
       </c>
-      <c r="M35" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P35" s="42">
         <v>0.0</v>
       </c>
       <c r="Q35" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R35" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="S35" s="43">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="T35" s="41">
         <v>15.0</v>
@@ -3903,13 +3903,13 @@
         <v>62</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C36" s="39">
         <v>2.0</v>
       </c>
       <c r="D36" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3948,13 +3948,13 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R36" s="40">
         <v>0.0</v>
       </c>
       <c r="S36" s="43">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T36" s="41">
         <v>15.0</v>
@@ -4032,11 +4032,11 @@
         <v>0.0</v>
       </c>
       <c r="T37" s="41">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4053,13 +4053,13 @@
         <v>64</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C38" s="39">
         <v>1.0</v>
       </c>
       <c r="D38" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E38" s="40">
         <v>0.0</v>
@@ -4098,13 +4098,13 @@
         <v>0.0</v>
       </c>
       <c r="Q38" s="52">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R38" s="53">
         <v>1.0</v>
       </c>
       <c r="S38" s="55">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T38" s="41">
         <v>15.0</v>
@@ -4362,13 +4362,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="79">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
       <c r="D4" s="80">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E4" s="80">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="F4" s="80">
         <v>0.0</v>
@@ -4404,11 +4404,11 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R4" s="83">
-        <f t="shared" ref="R4:R7" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>3795</v>
+        <f t="shared" ref="R4:R9" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>4395</v>
       </c>
     </row>
     <row r="5">
@@ -4416,7 +4416,7 @@
         <v>75</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="81">
         <v>27.0</v>
@@ -4518,11 +4518,11 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3150</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="7">
@@ -4530,19 +4530,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="81">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="D7" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E7" s="42">
         <v>15.0</v>
       </c>
       <c r="F7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G7" s="42">
         <v>0.0</v>
@@ -4551,19 +4551,19 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J7" s="42">
         <v>0.0</v>
       </c>
       <c r="K7" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N7" s="81">
         <v>0.0</v>
@@ -4572,32 +4572,32 @@
         <v>0.0</v>
       </c>
       <c r="P7" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q7" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>3030</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>34</v>
+      <c r="B8" s="78" t="s">
+        <v>30</v>
       </c>
       <c r="C8" s="81">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="D8" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="E8" s="42">
         <v>13.0</v>
       </c>
-      <c r="E8" s="42">
-        <v>14.0</v>
-      </c>
       <c r="F8" s="42">
         <v>0.0</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="80">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J8" s="42">
         <v>0.0</v>
@@ -4617,7 +4617,7 @@
         <v>0.0</v>
       </c>
       <c r="L8" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M8" s="82">
         <v>0.0</v>
@@ -4629,52 +4629,52 @@
         <v>0.0</v>
       </c>
       <c r="P8" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q8" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R8" s="83">
-        <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
-        <v>3030</v>
+        <f t="shared" si="1"/>
+        <v>3060</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="77" t="s">
         <v>79</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C9" s="81">
         <v>22.0</v>
       </c>
       <c r="D9" s="42">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="E9" s="42">
         <v>15.0</v>
       </c>
       <c r="F9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" s="42">
         <v>0.0</v>
       </c>
       <c r="H9" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I9" s="80">
         <v>0.0</v>
       </c>
       <c r="J9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K9" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M9" s="82">
         <v>0.0</v>
@@ -4689,28 +4689,28 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="82">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="R9" s="83">
-        <f t="shared" ref="R9:R36" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
-        <v>2850</v>
+        <f t="shared" si="1"/>
+        <v>3030</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="86" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="81">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="D10" s="42">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="E10" s="42">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
@@ -4722,19 +4722,19 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
       </c>
       <c r="K10" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L10" s="42">
         <v>0.0</v>
       </c>
       <c r="M10" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="81">
         <v>0.0</v>
@@ -4749,154 +4749,154 @@
         <v>15.0</v>
       </c>
       <c r="R10" s="83">
-        <f t="shared" si="2"/>
-        <v>2760</v>
+        <f>C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2</f>
+        <v>3030</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="85" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C11" s="81">
         <v>22.0</v>
       </c>
       <c r="D11" s="42">
+        <v>12.0</v>
+      </c>
+      <c r="E11" s="42">
+        <v>15.0</v>
+      </c>
+      <c r="F11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="80">
+        <v>1.0</v>
+      </c>
+      <c r="I11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="K11" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="L11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="82">
+        <v>17.0</v>
+      </c>
+      <c r="R11" s="83">
+        <f t="shared" ref="R11:R36" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="81">
+        <v>24.0</v>
+      </c>
+      <c r="D12" s="42">
         <v>8.0</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E12" s="42">
         <v>13.0</v>
       </c>
-      <c r="F11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="82">
+      <c r="F12" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q12" s="82">
         <v>12.0</v>
-      </c>
-      <c r="R11" s="83">
-        <f t="shared" si="2"/>
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="81">
-        <v>18.0</v>
-      </c>
-      <c r="D12" s="42">
-        <v>6.0</v>
-      </c>
-      <c r="E12" s="42">
-        <v>12.0</v>
-      </c>
-      <c r="F12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="80">
-        <v>2.0</v>
-      </c>
-      <c r="J12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="M12" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="82">
-        <v>16.0</v>
       </c>
       <c r="R12" s="83">
         <f t="shared" si="2"/>
-        <v>2610</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="85" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13" s="81">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="D13" s="42">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E13" s="42">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="F13" s="42">
         <v>0.0</v>
       </c>
       <c r="G13" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H13" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="80">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="81">
         <v>0.0</v>
@@ -4917,43 +4917,43 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>2415</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="77" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="D14" s="42">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E14" s="42">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="F14" s="42">
         <v>0.0</v>
       </c>
       <c r="G14" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H14" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I14" s="80">
         <v>0.0</v>
       </c>
       <c r="J14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K14" s="81">
         <v>0.0</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="R14" s="83">
         <f t="shared" si="2"/>
-        <v>2295</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="15">
@@ -5031,11 +5031,11 @@
         <v>1.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2220</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="16">
@@ -5043,7 +5043,7 @@
         <v>86</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="81">
         <v>18.0</v>
@@ -5145,11 +5145,11 @@
         <v>1.0</v>
       </c>
       <c r="Q17" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>1965</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="18">
@@ -5202,11 +5202,11 @@
         <v>0.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>1950</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="19">
@@ -5259,11 +5259,11 @@
         <v>1.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>1905</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="20">
@@ -5316,11 +5316,11 @@
         <v>0.0</v>
       </c>
       <c r="Q20" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>1905</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="21">
@@ -5373,11 +5373,11 @@
         <v>1.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>1905</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="22">
@@ -5385,16 +5385,16 @@
         <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" s="81">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="D22" s="42">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E22" s="42">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="F22" s="42">
         <v>0.0</v>
@@ -5403,13 +5403,13 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I22" s="80">
         <v>0.0</v>
       </c>
       <c r="J22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K22" s="81">
         <v>0.0</v>
@@ -5427,14 +5427,14 @@
         <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q22" s="82">
         <v>15.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>1650</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="23">
@@ -5442,16 +5442,16 @@
         <v>93</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" s="81">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="D23" s="42">
         <v>17.0</v>
       </c>
       <c r="E23" s="42">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="F23" s="42">
         <v>0.0</v>
@@ -5460,13 +5460,13 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I23" s="80">
         <v>0.0</v>
       </c>
       <c r="J23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K23" s="81">
         <v>0.0</v>
@@ -5484,14 +5484,14 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="82">
         <v>15.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>1605</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="24">
@@ -5499,25 +5499,25 @@
         <v>94</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24" s="81">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="D24" s="42">
         <v>7.0</v>
       </c>
       <c r="E24" s="42">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
       </c>
       <c r="G24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
@@ -5541,14 +5541,14 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1605</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="25">
@@ -5601,11 +5601,11 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1590</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="26">
@@ -5613,25 +5613,25 @@
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C26" s="81">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D26" s="42">
         <v>7.0</v>
       </c>
       <c r="E26" s="42">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
       </c>
       <c r="G26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I26" s="80">
         <v>0.0</v>
@@ -5655,14 +5655,14 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q26" s="82">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1455</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="27">
@@ -5715,11 +5715,11 @@
         <v>1.0</v>
       </c>
       <c r="Q27" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1410</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="28">
@@ -5772,11 +5772,11 @@
         <v>1.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
-        <v>1320</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="29">
@@ -5784,7 +5784,7 @@
         <v>99</v>
       </c>
       <c r="B29" s="78" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C29" s="81">
         <v>12.0</v>
@@ -5886,11 +5886,11 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>1035</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="31">
@@ -5898,7 +5898,7 @@
         <v>101</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C31" s="81">
         <v>10.0</v>
@@ -5955,13 +5955,13 @@
         <v>102</v>
       </c>
       <c r="B32" s="78" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C32" s="81">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D32" s="42">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E32" s="42">
         <v>2.0</v>
@@ -5997,14 +5997,14 @@
         <v>0.0</v>
       </c>
       <c r="P32" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q32" s="82">
         <v>15.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>945</v>
+        <v>930</v>
       </c>
     </row>
     <row r="33">
@@ -6012,16 +6012,16 @@
         <v>103</v>
       </c>
       <c r="B33" s="78" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C33" s="81">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D33" s="42">
         <v>12.0</v>
       </c>
       <c r="E33" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="42">
         <v>0.0</v>
@@ -6054,14 +6054,14 @@
         <v>0.0</v>
       </c>
       <c r="P33" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q33" s="82">
         <v>17.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="34">
@@ -6069,7 +6069,7 @@
         <v>104</v>
       </c>
       <c r="B34" s="90" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C34" s="91">
         <v>2.0</v>
@@ -6171,11 +6171,11 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="92">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R35" s="83">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36">
@@ -6183,7 +6183,7 @@
         <v>106</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C36" s="95">
         <v>1.0</v>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -128,12 +128,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>Rosario, Elian</t>
+  </si>
+  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
-    <t>Rosario, Elian</t>
-  </si>
-  <si>
     <t>Castillo, Wesly</t>
   </si>
   <si>
@@ -149,30 +149,30 @@
     <t>Gonzalez, Victor</t>
   </si>
   <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
     <t>Marcano, Jose</t>
   </si>
   <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
+    <t>Pinder, Jayln</t>
+  </si>
+  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
-    <t>Pinder, Jayln</t>
+    <t>Valdes, Abel</t>
   </si>
   <si>
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
-    <t>Valdes, Abel</t>
-  </si>
-  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
@@ -266,16 +266,22 @@
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
+    <t>Gamez, Manuel</t>
+  </si>
+  <si>
+    <t>Lara, Carlos</t>
+  </si>
+  <si>
+    <t>Peralta, Eddy</t>
+  </si>
+  <si>
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
-    <t>Gamez, Manuel</t>
-  </si>
-  <si>
-    <t>Lara, Carlos</t>
-  </si>
-  <si>
-    <t>Peralta, Eddy</t>
+    <t>Figuereo, Breyner</t>
+  </si>
+  <si>
+    <t>Granado, Argenis</t>
   </si>
   <si>
     <t>Alcantara, Jostin</t>
@@ -284,9 +290,6 @@
     <t>Fernandez, Jehiber</t>
   </si>
   <si>
-    <t>Granado, Argenis</t>
-  </si>
-  <si>
     <t>Castillo, Albert</t>
   </si>
   <si>
@@ -296,6 +299,9 @@
     <t>Ramos, Daniel</t>
   </si>
   <si>
+    <t>Perez, Juanangel</t>
+  </si>
+  <si>
     <t>Acosta, Isaac</t>
   </si>
   <si>
@@ -308,13 +314,7 @@
     <t>Ballesteros, Jean</t>
   </si>
   <si>
-    <t>Perez, Juanangel</t>
-  </si>
-  <si>
     <t>Lamu, Alex</t>
-  </si>
-  <si>
-    <t>Figuereo, Breyner</t>
   </si>
   <si>
     <t>Figuereo, Enmanuel</t>
@@ -1584,7 +1584,7 @@
         <v>28.0</v>
       </c>
       <c r="D5" s="40">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E5" s="40">
         <v>10.0</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4260</v>
+        <v>4230</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1659,7 +1659,7 @@
         <v>18.0</v>
       </c>
       <c r="D6" s="40">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E6" s="40">
         <v>12.0</v>
@@ -1683,7 +1683,7 @@
         <v>0.0</v>
       </c>
       <c r="L6" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="M6" s="40">
         <v>7.0</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>3945</v>
+        <v>3870</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1731,10 +1731,10 @@
         <v>30</v>
       </c>
       <c r="C7" s="45">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D7" s="46">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="E7" s="46">
         <v>11.0</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>3615</v>
+        <v>3660</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1806,13 +1806,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D8" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E8" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F8" s="40">
         <v>5.0</v>
@@ -1824,7 +1824,7 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="41">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J8" s="39">
         <v>0.0</v>
@@ -1833,7 +1833,7 @@
         <v>0.0</v>
       </c>
       <c r="L8" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M8" s="40">
         <v>1.0</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3480</v>
+        <v>3600</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1881,10 +1881,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="39">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="D9" s="40">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E9" s="40">
         <v>1.0</v>
@@ -1911,7 +1911,7 @@
         <v>2.0</v>
       </c>
       <c r="M9" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N9" s="40">
         <v>2.0</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3330</v>
+        <v>3360</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -2024,69 +2024,69 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C11" s="39">
-        <v>26.0</v>
+        <v>17.0</v>
       </c>
       <c r="D11" s="40">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="E11" s="40">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F11" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="G11" s="40">
         <v>6.0</v>
       </c>
-      <c r="G11" s="40">
+      <c r="H11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="M11" s="40">
         <v>2.0</v>
       </c>
-      <c r="H11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="39">
+      <c r="N11" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R11" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="S11" s="43">
         <v>4.0</v>
       </c>
-      <c r="M11" s="40">
-        <v>13.0</v>
-      </c>
-      <c r="N11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S11" s="43">
-        <v>5.0</v>
-      </c>
       <c r="T11" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2895</v>
+        <v>2910</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2099,69 +2099,69 @@
       <c r="AD11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="49" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C12" s="39">
-        <v>17.0</v>
+        <v>26.0</v>
       </c>
       <c r="D12" s="40">
+        <v>22.0</v>
+      </c>
+      <c r="E12" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F12" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J12" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M12" s="40">
         <v>14.0</v>
       </c>
-      <c r="E12" s="40">
+      <c r="N12" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P12" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="39">
         <v>6.0</v>
       </c>
-      <c r="F12" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="G12" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="H12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="39">
+      <c r="R12" s="40">
         <v>5.0</v>
       </c>
-      <c r="M12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N12" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O12" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R12" s="40">
-        <v>6.0</v>
-      </c>
       <c r="S12" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T12" s="41">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2805</v>
+        <v>2895</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2184,7 +2184,7 @@
         <v>19.0</v>
       </c>
       <c r="D13" s="40">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="E13" s="40">
         <v>3.0</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2595</v>
+        <v>2565</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2334,7 +2334,7 @@
         <v>12.0</v>
       </c>
       <c r="D15" s="40">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="E15" s="40">
         <v>9.0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2175</v>
+        <v>2145</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2549,69 +2549,69 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="48" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C18" s="39">
+        <v>13.0</v>
+      </c>
+      <c r="D18" s="40">
+        <v>32.0</v>
+      </c>
+      <c r="E18" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="F18" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="G18" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="J18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O18" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P18" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q18" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R18" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S18" s="43">
+        <v>5.0</v>
+      </c>
+      <c r="T18" s="41">
         <v>17.0</v>
-      </c>
-      <c r="D18" s="40">
-        <v>19.0</v>
-      </c>
-      <c r="E18" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="M18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P18" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="R18" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S18" s="43">
-        <v>4.0</v>
-      </c>
-      <c r="T18" s="41">
-        <v>15.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1950</v>
+        <v>1920</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2624,69 +2624,69 @@
       <c r="AD18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="49" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C19" s="39">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="D19" s="40">
-        <v>32.0</v>
+        <v>20.0</v>
       </c>
       <c r="E19" s="40">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H19" s="40">
         <v>0.0</v>
       </c>
       <c r="I19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L19" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R19" s="40">
         <v>5.0</v>
       </c>
-      <c r="J19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R19" s="40">
-        <v>7.0</v>
-      </c>
       <c r="S19" s="43">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T19" s="41">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>1845</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2706,13 +2706,13 @@
         <v>36</v>
       </c>
       <c r="C20" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D20" s="40">
         <v>3.0</v>
       </c>
       <c r="E20" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="40">
         <v>1.0</v>
@@ -2733,7 +2733,7 @@
         <v>0.0</v>
       </c>
       <c r="L20" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M20" s="40">
         <v>4.0</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1620</v>
+        <v>1740</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2799,7 +2799,7 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="41">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="J21" s="39">
         <v>0.0</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1485</v>
+        <v>1515</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2849,20 +2849,20 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>30</v>
+      <c r="B22" s="51" t="s">
+        <v>36</v>
       </c>
       <c r="C22" s="39">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="D22" s="40">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E22" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F22" s="40">
         <v>0.0</v>
@@ -2874,7 +2874,7 @@
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2883,16 +2883,16 @@
         <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M22" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="40">
         <v>0.0</v>
       </c>
       <c r="O22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P22" s="42">
         <v>0.0</v>
@@ -2901,13 +2901,13 @@
         <v>7.0</v>
       </c>
       <c r="R22" s="40">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="S22" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T22" s="41">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
@@ -2924,20 +2924,20 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="51" t="s">
-        <v>36</v>
+      <c r="B23" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C23" s="39">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="D23" s="40">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E23" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F23" s="40">
         <v>0.0</v>
@@ -2949,7 +2949,7 @@
         <v>0.0</v>
       </c>
       <c r="I23" s="41">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="J23" s="39">
         <v>0.0</v>
@@ -2958,16 +2958,16 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="M23" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="42">
         <v>0.0</v>
@@ -2976,17 +2976,17 @@
         <v>7.0</v>
       </c>
       <c r="R23" s="40">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="S23" s="43">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="T23" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3006,16 +3006,16 @@
         <v>30</v>
       </c>
       <c r="C24" s="39">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="D24" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E24" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G24" s="40">
         <v>0.0</v>
@@ -3024,7 +3024,7 @@
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3033,35 +3033,35 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M24" s="40">
         <v>0.0</v>
       </c>
       <c r="N24" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O24" s="40">
         <v>1.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="R24" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="S24" s="43">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="T24" s="41">
         <v>17.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1440</v>
+        <v>1425</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3081,62 +3081,62 @@
         <v>30</v>
       </c>
       <c r="C25" s="39">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="D25" s="40">
         <v>6.0</v>
       </c>
       <c r="E25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
         <v>3.0</v>
       </c>
-      <c r="F25" s="40">
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="R25" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S25" s="43">
         <v>3.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="R25" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="S25" s="43">
-        <v>0.0</v>
       </c>
       <c r="T25" s="41">
         <v>17.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1425</v>
+        <v>1410</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3231,10 +3231,10 @@
         <v>36</v>
       </c>
       <c r="C27" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D27" s="40">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E27" s="40">
         <v>3.0</v>
@@ -3258,10 +3258,10 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M27" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="N27" s="40">
         <v>1.0</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1395</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3309,7 +3309,7 @@
         <v>13.0</v>
       </c>
       <c r="D28" s="40">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="E28" s="40">
         <v>1.0</v>
@@ -3336,7 +3336,7 @@
         <v>2.0</v>
       </c>
       <c r="M28" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="N28" s="40">
         <v>1.0</v>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1305</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3534,10 +3534,10 @@
         <v>8.0</v>
       </c>
       <c r="D31" s="40">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E31" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F31" s="40">
         <v>1.0</v>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1005</v>
+        <v>1035</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3612,7 +3612,7 @@
         <v>3.0</v>
       </c>
       <c r="E32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F32" s="40">
         <v>1.0</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>825</v>
+        <v>885</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3759,7 +3759,7 @@
         <v>5.0</v>
       </c>
       <c r="D34" s="40">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="E34" s="40">
         <v>1.0</v>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>765</v>
+        <v>735</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -4533,7 +4533,7 @@
         <v>36</v>
       </c>
       <c r="C7" s="81">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="D7" s="42">
         <v>10.0</v>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>3075</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="8">
@@ -4868,35 +4868,35 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="77" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C13" s="81">
         <v>19.0</v>
       </c>
       <c r="D13" s="42">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E13" s="42">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="F13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H13" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="80">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="81">
         <v>0.0</v>
@@ -4917,43 +4917,43 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>2430</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="87" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C14" s="81">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
       <c r="D14" s="42">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E14" s="42">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="F14" s="42">
         <v>0.0</v>
       </c>
       <c r="G14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I14" s="80">
         <v>0.0</v>
       </c>
       <c r="J14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K14" s="81">
         <v>0.0</v>
@@ -4974,37 +4974,37 @@
         <v>1.0</v>
       </c>
       <c r="Q14" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R14" s="83">
         <f t="shared" si="2"/>
-        <v>2415</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="77" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C15" s="81">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="D15" s="42">
         <v>10.0</v>
       </c>
       <c r="E15" s="42">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F15" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" s="42">
         <v>0.0</v>
       </c>
       <c r="H15" s="80">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="42">
         <v>0.0</v>
@@ -5013,7 +5013,7 @@
         <v>0.0</v>
       </c>
       <c r="K15" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L15" s="42">
         <v>0.0</v>
@@ -5028,28 +5028,28 @@
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2250</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="85" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C16" s="81">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D16" s="42">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E16" s="42">
         <v>6.0</v>
@@ -5058,10 +5058,10 @@
         <v>0.0</v>
       </c>
       <c r="G16" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H16" s="80">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I16" s="80">
         <v>0.0</v>
@@ -5070,7 +5070,7 @@
         <v>0.0</v>
       </c>
       <c r="K16" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L16" s="42">
         <v>0.0</v>
@@ -5085,46 +5085,46 @@
         <v>0.0</v>
       </c>
       <c r="P16" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>2070</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>30</v>
+      <c r="B17" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C17" s="81">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="D17" s="42">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="E17" s="42">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K17" s="81">
         <v>0.0</v>
@@ -5145,22 +5145,22 @@
         <v>1.0</v>
       </c>
       <c r="Q17" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>1995</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="84" t="s">
         <v>88</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="81">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D18" s="42">
         <v>13.0</v>
@@ -5175,10 +5175,10 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5199,31 +5199,31 @@
         <v>0.0</v>
       </c>
       <c r="P18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>1980</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="86" t="s">
         <v>89</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="81">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="D19" s="42">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E19" s="42">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="F19" s="42">
         <v>0.0</v>
@@ -5235,7 +5235,7 @@
         <v>0.0</v>
       </c>
       <c r="I19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J19" s="42">
         <v>0.0</v>
@@ -5259,40 +5259,40 @@
         <v>1.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="85" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="81">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="D20" s="42">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="E20" s="42">
         <v>7.0</v>
       </c>
       <c r="F20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" s="42">
         <v>0.0</v>
       </c>
       <c r="H20" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J20" s="42">
         <v>0.0</v>
@@ -5320,21 +5320,21 @@
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="88" t="s">
+      <c r="A21" s="77" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="81">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="D21" s="42">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="E21" s="42">
         <v>7.0</v>
@@ -5370,7 +5370,7 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q21" s="82">
         <v>17.0</v>
@@ -5381,23 +5381,23 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="88" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C22" s="81">
         <v>19.0</v>
       </c>
       <c r="D22" s="42">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="E22" s="42">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="F22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="42">
         <v>0.0</v>
@@ -5427,14 +5427,14 @@
         <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>1875</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="23">
@@ -5445,13 +5445,13 @@
         <v>36</v>
       </c>
       <c r="C23" s="81">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="D23" s="42">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E23" s="42">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="F23" s="42">
         <v>0.0</v>
@@ -5460,13 +5460,13 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I23" s="80">
         <v>0.0</v>
       </c>
       <c r="J23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K23" s="81">
         <v>0.0</v>
@@ -5484,37 +5484,37 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q23" s="82">
         <v>15.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>1650</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C24" s="81">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="D24" s="42">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="E24" s="42">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
       </c>
       <c r="G24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H24" s="80">
         <v>0.0</v>
@@ -5544,49 +5544,49 @@
         <v>1.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1635</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="77" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C25" s="81">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D25" s="42">
         <v>17.0</v>
       </c>
       <c r="E25" s="42">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="F25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" s="42">
         <v>0.0</v>
       </c>
       <c r="H25" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I25" s="42">
         <v>0.0</v>
       </c>
       <c r="J25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K25" s="81">
         <v>0.0</v>
       </c>
       <c r="L25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M25" s="82">
         <v>0.0</v>
@@ -5601,11 +5601,11 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="26">
@@ -5613,25 +5613,25 @@
         <v>96</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C26" s="81">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="D26" s="42">
         <v>7.0</v>
       </c>
       <c r="E26" s="42">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
       </c>
       <c r="G26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I26" s="80">
         <v>0.0</v>
@@ -5655,34 +5655,34 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1605</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="81">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="D27" s="42">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="E27" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" s="42">
         <v>0.0</v>
@@ -5700,7 +5700,7 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M27" s="82">
         <v>0.0</v>
@@ -5715,29 +5715,29 @@
         <v>1.0</v>
       </c>
       <c r="Q27" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1440</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="86" t="s">
         <v>98</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C28" s="81">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D28" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="E28" s="42">
         <v>8.0</v>
       </c>
-      <c r="E28" s="42">
-        <v>5.0</v>
-      </c>
       <c r="F28" s="42">
         <v>0.0</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I28" s="42">
         <v>0.0</v>
@@ -5769,31 +5769,31 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
-        <v>1350</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="88" t="s">
+      <c r="A29" s="85" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="78" t="s">
-        <v>36</v>
+      <c r="B29" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C29" s="81">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="D29" s="42">
         <v>8.0</v>
       </c>
       <c r="E29" s="42">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F29" s="42">
         <v>0.0</v>
@@ -5802,13 +5802,13 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29" s="42">
         <v>0.0</v>
       </c>
       <c r="J29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K29" s="81">
         <v>0.0</v>
@@ -5829,11 +5829,11 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1290</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="30">
@@ -6146,7 +6146,7 @@
       <c r="H35" s="80">
         <v>0.0</v>
       </c>
-      <c r="I35" s="90">
+      <c r="I35" s="42">
         <v>0.0</v>
       </c>
       <c r="J35" s="42">

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Pitchers" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$38</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Position Players'!$A$4:$U$37</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Pitchers!$A$3:$R$36</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
   <si>
     <t>INCENTIVOS DSL 2026</t>
   </si>
@@ -104,21 +104,18 @@
     <t>$RD</t>
   </si>
   <si>
+    <t>Mateo, Cesar</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>Celesten, Yeisy</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>Mateo, Cesar</t>
-  </si>
-  <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
-    <t>Cavero, Braulio</t>
-  </si>
-  <si>
     <t>Rodriguez, Alex</t>
   </si>
   <si>
@@ -140,72 +137,72 @@
     <t>Benitez, Frainker</t>
   </si>
   <si>
+    <t>Gonzalez, Victor</t>
+  </si>
+  <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Gonzalez, Victor</t>
-  </si>
-  <si>
     <t>Done, Carlos</t>
   </si>
   <si>
+    <t>Marcano, Jose</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
-    <t>Marcano, Jose</t>
+    <t>Pinder, Jayln</t>
+  </si>
+  <si>
+    <t>Volquez, Fabelin</t>
   </si>
   <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
-    <t>Pinder, Jayln</t>
-  </si>
-  <si>
-    <t>Volquez, Fabelin</t>
+    <t>Alarcon, Rosnel</t>
   </si>
   <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
-    <t>Alarcon, Rosnel</t>
+    <t>Montero, Darling</t>
   </si>
   <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
+    <t>Ortiz Jr, David</t>
   </si>
   <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
-    <t>Ortiz Jr, David</t>
-  </si>
-  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
+    <t>Genao, Jhostin</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
+    <t>Colina, Felix</t>
+  </si>
+  <si>
+    <t>Simon, Jhon</t>
+  </si>
+  <si>
     <t>Coronado, Francisco</t>
   </si>
   <si>
-    <t>Genao, Jhostin</t>
-  </si>
-  <si>
-    <t>Colina, Felix</t>
-  </si>
-  <si>
-    <t>Simon, Jhon</t>
-  </si>
-  <si>
     <t>Seminiel, Cristian</t>
   </si>
   <si>
@@ -242,9 +239,15 @@
     <t>Silvestre, Jose</t>
   </si>
   <si>
+    <t>Medina, Juan</t>
+  </si>
+  <si>
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Fukuda, Masahiro</t>
+  </si>
+  <si>
     <t>Roquez, Yadiel</t>
   </si>
   <si>
@@ -254,18 +257,12 @@
     <t>Gomez, Manuel</t>
   </si>
   <si>
-    <t>Medina, Juan</t>
-  </si>
-  <si>
     <t>Santos, Aneudy</t>
   </si>
   <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
-    <t>Fukuda, Masahiro</t>
-  </si>
-  <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
@@ -278,40 +275,40 @@
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
+    <t>Alcantara, Jostin</t>
+  </si>
+  <si>
     <t>Figuereo, Breyner</t>
   </si>
   <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
+    <t>Castillo, Albert</t>
+  </si>
+  <si>
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Alcantara, Jostin</t>
-  </si>
-  <si>
-    <t>Fernandez, Jehiber</t>
-  </si>
-  <si>
-    <t>Castillo, Albert</t>
+    <t>Acosta, Isaac</t>
+  </si>
+  <si>
+    <t>Liriano, Edgar</t>
   </si>
   <si>
     <t>Pena, Dariel</t>
   </si>
   <si>
-    <t>Ramos, Daniel</t>
+    <t>Ballesteros, Jean</t>
+  </si>
+  <si>
+    <t>Cordero, Albert</t>
   </si>
   <si>
     <t>Perez, Juanangel</t>
-  </si>
-  <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
-    <t>Cordero, Albert</t>
-  </si>
-  <si>
-    <t>Liriano, Edgar</t>
-  </si>
-  <si>
-    <t>Ballesteros, Jean</t>
   </si>
   <si>
     <t>Lamu, Alex</t>
@@ -1581,62 +1578,62 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>28.0</v>
+        <v>20.0</v>
       </c>
       <c r="D5" s="40">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="E5" s="40">
+        <v>12.0</v>
+      </c>
+      <c r="F5" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="G5" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="41">
+        <v>29.0</v>
+      </c>
+      <c r="J5" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="K5" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="39">
         <v>10.0</v>
       </c>
-      <c r="F5" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="G5" s="40">
+      <c r="M5" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="N5" s="40">
         <v>4.0</v>
       </c>
-      <c r="H5" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J5" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="K5" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="M5" s="40">
-        <v>11.0</v>
-      </c>
-      <c r="N5" s="40">
-        <v>2.0</v>
-      </c>
       <c r="O5" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P5" s="42">
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="R5" s="40">
         <v>8.0</v>
       </c>
       <c r="S5" s="43">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="T5" s="41">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="U5" s="44">
-        <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4230</v>
+        <f t="shared" ref="U5:U37" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
+        <v>4425</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1656,62 +1653,62 @@
         <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="D6" s="40">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E6" s="40">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="F6" s="40">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G6" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H6" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J6" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="K6" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="39">
         <v>5.0</v>
       </c>
-      <c r="H6" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="41">
-        <v>27.0</v>
-      </c>
-      <c r="J6" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L6" s="39">
-        <v>10.0</v>
-      </c>
       <c r="M6" s="40">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="N6" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="O6" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P6" s="42">
         <v>0.0</v>
       </c>
       <c r="Q6" s="39">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="R6" s="40">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="S6" s="43">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T6" s="41">
         <v>17.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>3870</v>
+        <v>4350</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1731,10 +1728,10 @@
         <v>30</v>
       </c>
       <c r="C7" s="45">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="D7" s="46">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="E7" s="46">
         <v>11.0</v>
@@ -1773,20 +1770,20 @@
         <v>0.0</v>
       </c>
       <c r="Q7" s="39">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R7" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="S7" s="43">
         <v>5.0</v>
       </c>
       <c r="T7" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>3660</v>
+        <v>3870</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1799,26 +1796,26 @@
       <c r="AD7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="48" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="D8" s="40">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="E8" s="40">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="F8" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" s="40">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H8" s="40">
         <v>0.0</v>
@@ -1827,7 +1824,7 @@
         <v>7.0</v>
       </c>
       <c r="J8" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K8" s="41">
         <v>0.0</v>
@@ -1836,32 +1833,32 @@
         <v>2.0</v>
       </c>
       <c r="M8" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N8" s="40">
         <v>2.0</v>
       </c>
       <c r="O8" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P8" s="42">
         <v>0.0</v>
       </c>
       <c r="Q8" s="39">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="R8" s="40">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="S8" s="43">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="T8" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3600</v>
+        <v>3480</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1874,23 +1871,23 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="49" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C9" s="39">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="D9" s="40">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="E9" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F9" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G9" s="40">
         <v>4.0</v>
@@ -1899,22 +1896,22 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="41">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="J9" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K9" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="L9" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M9" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N9" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O9" s="40">
         <v>0.0</v>
@@ -1923,13 +1920,13 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="R9" s="40">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="S9" s="43">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="T9" s="41">
         <v>17.0</v>
@@ -1949,47 +1946,47 @@
       <c r="AD9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="s">
-        <v>35</v>
+      <c r="A10" s="37" t="s">
+        <v>36</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C10" s="39">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="D10" s="40">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="E10" s="40">
         <v>7.0</v>
       </c>
       <c r="F10" s="40">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G10" s="40">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="40">
         <v>0.0</v>
       </c>
       <c r="I10" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J10" s="39">
         <v>0.0</v>
       </c>
       <c r="K10" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L10" s="39">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="M10" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N10" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O10" s="40">
         <v>0.0</v>
@@ -1998,20 +1995,20 @@
         <v>0.0</v>
       </c>
       <c r="Q10" s="39">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="R10" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S10" s="43">
         <v>4.0</v>
       </c>
       <c r="T10" s="41">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3300</v>
+        <v>3060</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2024,69 +2021,69 @@
       <c r="AD10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="49" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" s="39">
-        <v>17.0</v>
+        <v>27.0</v>
       </c>
       <c r="D11" s="40">
+        <v>24.0</v>
+      </c>
+      <c r="E11" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F11" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="G11" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J11" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M11" s="40">
         <v>14.0</v>
       </c>
-      <c r="E11" s="40">
+      <c r="N11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P11" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="39">
         <v>6.0</v>
       </c>
-      <c r="F11" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="G11" s="40">
+      <c r="R11" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S11" s="43">
         <v>6.0</v>
-      </c>
-      <c r="H11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="M11" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N11" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R11" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S11" s="43">
-        <v>4.0</v>
       </c>
       <c r="T11" s="41">
         <v>17.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>2910</v>
+        <v>3045</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2103,10 +2100,10 @@
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="39">
-        <v>26.0</v>
+        <v>22.0</v>
       </c>
       <c r="D12" s="40">
         <v>22.0</v>
@@ -2115,7 +2112,7 @@
         <v>3.0</v>
       </c>
       <c r="F12" s="40">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="40">
         <v>2.0</v>
@@ -2124,25 +2121,25 @@
         <v>0.0</v>
       </c>
       <c r="I12" s="41">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="J12" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K12" s="41">
         <v>0.0</v>
       </c>
       <c r="L12" s="39">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M12" s="40">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="N12" s="40">
         <v>0.0</v>
       </c>
       <c r="O12" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P12" s="42">
         <v>0.0</v>
@@ -2154,14 +2151,14 @@
         <v>5.0</v>
       </c>
       <c r="S12" s="43">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T12" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2895</v>
+        <v>2880</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2174,69 +2171,69 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="50" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="39">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="D13" s="40">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
       <c r="E13" s="40">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F13" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H13" s="40">
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="J13" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="41">
         <v>0.0</v>
       </c>
       <c r="L13" s="39">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M13" s="40">
         <v>0.0</v>
       </c>
       <c r="N13" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O13" s="40">
         <v>0.0</v>
       </c>
       <c r="P13" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R13" s="40">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S13" s="43">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T13" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2565</v>
+        <v>2355</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2249,69 +2246,69 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>36</v>
+      <c r="B14" s="51" t="s">
+        <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="D14" s="40">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
       <c r="E14" s="40">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="41">
+        <v>7.0</v>
+      </c>
+      <c r="J14" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M14" s="40">
         <v>4.0</v>
       </c>
-      <c r="H14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J14" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="M14" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N14" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O14" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q14" s="39">
         <v>6.0</v>
       </c>
       <c r="R14" s="40">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="S14" s="43">
         <v>4.0</v>
       </c>
       <c r="T14" s="41">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>2235</v>
+        <v>2355</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2331,7 +2328,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D15" s="40">
         <v>18.0</v>
@@ -2370,23 +2367,23 @@
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R15" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S15" s="43">
         <v>3.0</v>
       </c>
       <c r="T15" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2145</v>
+        <v>2490</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2406,10 +2403,10 @@
         <v>30</v>
       </c>
       <c r="C16" s="39">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D16" s="40">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E16" s="40">
         <v>2.0</v>
@@ -2433,7 +2430,7 @@
         <v>0.0</v>
       </c>
       <c r="L16" s="39">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M16" s="40">
         <v>10.0</v>
@@ -2448,20 +2445,20 @@
         <v>0.0</v>
       </c>
       <c r="Q16" s="39">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R16" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S16" s="43">
         <v>3.0</v>
       </c>
       <c r="T16" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2145</v>
+        <v>2250</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2474,32 +2471,32 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="39">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="D17" s="40">
-        <v>25.0</v>
+        <v>34.0</v>
       </c>
       <c r="E17" s="40">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G17" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" s="40">
         <v>0.0</v>
       </c>
       <c r="I17" s="41">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="J17" s="39">
         <v>0.0</v>
@@ -2508,31 +2505,31 @@
         <v>0.0</v>
       </c>
       <c r="L17" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M17" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="N17" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O17" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P17" s="42">
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
+        <v>13.0</v>
+      </c>
+      <c r="R17" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="S17" s="43">
         <v>5.0</v>
       </c>
-      <c r="R17" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="S17" s="43">
-        <v>4.0</v>
-      </c>
       <c r="T17" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
@@ -2549,69 +2546,69 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="49" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C18" s="39">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="D18" s="40">
-        <v>32.0</v>
+        <v>4.0</v>
       </c>
       <c r="E18" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M18" s="40">
         <v>6.0</v>
       </c>
-      <c r="F18" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G18" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="J18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O18" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P18" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="R18" s="40">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="S18" s="43">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="T18" s="41">
         <v>17.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>1965</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2628,7 +2625,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="39">
         <v>16.0</v>
@@ -2682,11 +2679,11 @@
         <v>4.0</v>
       </c>
       <c r="T19" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1845</v>
+        <v>1905</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2702,66 +2699,66 @@
       <c r="A20" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>36</v>
+      <c r="B20" s="51" t="s">
+        <v>35</v>
       </c>
       <c r="C20" s="39">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="D20" s="40">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="E20" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="41">
+        <v>6.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="R20" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="S20" s="43">
         <v>5.0</v>
       </c>
-      <c r="F20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="Q20" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="R20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="S20" s="43">
-        <v>1.0</v>
-      </c>
       <c r="T20" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1740</v>
+        <v>1695</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2774,20 +2771,20 @@
       <c r="AD20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="37" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C21" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D21" s="40">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E21" s="40">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="F21" s="40">
         <v>0.0</v>
@@ -2799,44 +2796,44 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M21" s="40">
         <v>4.0</v>
       </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>10.0</v>
-      </c>
-      <c r="M21" s="40">
-        <v>10.0</v>
-      </c>
       <c r="N21" s="40">
         <v>0.0</v>
       </c>
       <c r="O21" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P21" s="42">
         <v>0.0</v>
       </c>
       <c r="Q21" s="39">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="R21" s="40">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="S21" s="43">
         <v>3.0</v>
       </c>
       <c r="T21" s="41">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1515</v>
+        <v>1620</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2852,17 +2849,17 @@
       <c r="A22" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="51" t="s">
-        <v>36</v>
+      <c r="B22" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="C22" s="39">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="D22" s="40">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E22" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F22" s="40">
         <v>0.0</v>
@@ -2874,7 +2871,7 @@
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2883,10 +2880,10 @@
         <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="M22" s="40">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="N22" s="40">
         <v>0.0</v>
@@ -2898,20 +2895,20 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="R22" s="40">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="S22" s="43">
         <v>4.0</v>
       </c>
       <c r="T22" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1470</v>
+        <v>1605</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2924,69 +2921,69 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="48" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="39">
+        <v>9.0</v>
+      </c>
+      <c r="D23" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="E23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="41">
+        <v>3.0</v>
+      </c>
+      <c r="J23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q23" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R23" s="40">
         <v>7.0</v>
-      </c>
-      <c r="D23" s="40">
-        <v>11.0</v>
-      </c>
-      <c r="E23" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M23" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="N23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q23" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="R23" s="40">
-        <v>6.0</v>
       </c>
       <c r="S23" s="43">
         <v>3.0</v>
       </c>
       <c r="T23" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1455</v>
+        <v>1605</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3006,7 +3003,7 @@
         <v>30</v>
       </c>
       <c r="C24" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D24" s="40">
         <v>6.0</v>
@@ -3051,17 +3048,17 @@
         <v>7.0</v>
       </c>
       <c r="R24" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S24" s="43">
         <v>0.0</v>
       </c>
       <c r="T24" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1425</v>
+        <v>1560</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3074,69 +3071,69 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="50" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C25" s="39">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D25" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M25" s="40">
         <v>6.0</v>
       </c>
-      <c r="E25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
+      <c r="N25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
         <v>3.0</v>
       </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>4.0</v>
-      </c>
       <c r="R25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="S25" s="43">
         <v>5.0</v>
-      </c>
-      <c r="S25" s="43">
-        <v>3.0</v>
       </c>
       <c r="T25" s="41">
         <v>17.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1545</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3153,7 +3150,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="39">
         <v>8.0</v>
@@ -3207,11 +3204,11 @@
         <v>2.0</v>
       </c>
       <c r="T26" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3224,23 +3221,23 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="48" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C27" s="39">
         <v>9.0</v>
       </c>
       <c r="D27" s="40">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E27" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" s="40">
         <v>0.0</v>
@@ -3249,7 +3246,7 @@
         <v>0.0</v>
       </c>
       <c r="I27" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="39">
         <v>0.0</v>
@@ -3258,31 +3255,31 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="40">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P27" s="42">
         <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="R27" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S27" s="43">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="T27" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
@@ -3303,13 +3300,13 @@
         <v>54</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="39">
         <v>13.0</v>
       </c>
       <c r="D28" s="40">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="E28" s="40">
         <v>1.0</v>
@@ -3336,7 +3333,7 @@
         <v>2.0</v>
       </c>
       <c r="M28" s="40">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="N28" s="40">
         <v>1.0</v>
@@ -3348,7 +3345,7 @@
         <v>0.0</v>
       </c>
       <c r="Q28" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R28" s="40">
         <v>5.0</v>
@@ -3357,11 +3354,11 @@
         <v>2.0</v>
       </c>
       <c r="T28" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1365</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3374,32 +3371,32 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="49" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="39">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D29" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E29" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F29" s="40">
         <v>0.0</v>
       </c>
       <c r="G29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="40">
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3408,35 +3405,35 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="M29" s="40">
         <v>0.0</v>
       </c>
       <c r="N29" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P29" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="R29" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S29" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T29" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1275</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3453,34 +3450,34 @@
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C30" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D30" s="40">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
       <c r="E30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I30" s="41">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
       </c>
       <c r="K30" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L30" s="39">
         <v>3.0</v>
@@ -3489,29 +3486,29 @@
         <v>0.0</v>
       </c>
       <c r="N30" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O30" s="40">
         <v>1.0</v>
       </c>
       <c r="P30" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R30" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S30" s="43">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="T30" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3528,13 +3525,13 @@
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D31" s="40">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E31" s="40">
         <v>3.0</v>
@@ -3567,26 +3564,26 @@
         <v>0.0</v>
       </c>
       <c r="O31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P31" s="42">
         <v>0.0</v>
       </c>
       <c r="Q31" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R31" s="40">
         <v>1.0</v>
       </c>
       <c r="S31" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T31" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1125</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3603,7 +3600,7 @@
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="39">
         <v>4.0</v>
@@ -3612,7 +3609,7 @@
         <v>3.0</v>
       </c>
       <c r="E32" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F32" s="40">
         <v>1.0</v>
@@ -3648,20 +3645,20 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R32" s="40">
         <v>0.0</v>
       </c>
       <c r="S32" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T32" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>885</v>
+        <v>1065</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3674,45 +3671,45 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="50" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="D33" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="E33" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F33" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H33" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J33" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M33" s="40">
         <v>4.0</v>
       </c>
-      <c r="D33" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="E33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J33" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M33" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N33" s="40">
         <v>0.0</v>
       </c>
@@ -3723,20 +3720,20 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="R33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S33" s="43">
         <v>2.0</v>
       </c>
       <c r="T33" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>765</v>
+        <v>1065</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3749,32 +3746,32 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="50" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="39">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="D34" s="40">
-        <v>21.0</v>
+        <v>4.0</v>
       </c>
       <c r="E34" s="40">
         <v>1.0</v>
       </c>
       <c r="F34" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" s="40">
         <v>0.0</v>
       </c>
       <c r="H34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J34" s="39">
         <v>0.0</v>
@@ -3783,13 +3780,13 @@
         <v>0.0</v>
       </c>
       <c r="L34" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M34" s="40">
         <v>0.0</v>
       </c>
       <c r="N34" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O34" s="40">
         <v>1.0</v>
@@ -3798,20 +3795,20 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="39">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R34" s="40">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="S34" s="43">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="T34" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>870</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3824,20 +3821,20 @@
       <c r="AD34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="49" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="39">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D35" s="40">
         <v>2.0</v>
       </c>
       <c r="E35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F35" s="40">
         <v>0.0</v>
@@ -3849,7 +3846,7 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J35" s="39">
         <v>0.0</v>
@@ -3861,7 +3858,7 @@
         <v>1.0</v>
       </c>
       <c r="M35" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N35" s="40">
         <v>0.0</v>
@@ -3873,20 +3870,20 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="R35" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S35" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T35" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>705</v>
+        <v>825</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3899,17 +3896,17 @@
       <c r="AD35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="37" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C36" s="39">
         <v>2.0</v>
       </c>
       <c r="D36" s="40">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="E36" s="40">
         <v>0.0</v>
@@ -3942,26 +3939,26 @@
         <v>0.0</v>
       </c>
       <c r="O36" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P36" s="42">
         <v>0.0</v>
       </c>
       <c r="Q36" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R36" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S36" s="43">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="T36" s="41">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3977,8 +3974,8 @@
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="38" t="s">
-        <v>30</v>
+      <c r="B37" s="51" t="s">
+        <v>35</v>
       </c>
       <c r="C37" s="39">
         <v>1.0</v>
@@ -4007,36 +4004,36 @@
       <c r="K37" s="41">
         <v>0.0</v>
       </c>
-      <c r="L37" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O37" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P37" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q37" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="R37" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="S37" s="43">
-        <v>0.0</v>
+      <c r="L37" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="P37" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="Q37" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="R37" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="S37" s="55">
+        <v>1.0</v>
       </c>
       <c r="T37" s="41">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4048,92 +4045,17 @@
       <c r="AC37" s="9"/>
       <c r="AD37" s="9"/>
     </row>
-    <row r="38">
-      <c r="A38" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="D38" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="E38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H38" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I38" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J38" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="52">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="P38" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="Q38" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="R38" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="S38" s="55">
-        <v>1.0</v>
-      </c>
-      <c r="T38" s="41">
-        <v>15.0</v>
-      </c>
-      <c r="U38" s="44">
-        <f t="shared" si="1"/>
-        <v>495</v>
-      </c>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-      <c r="AA38" s="9"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
-      <c r="AD38" s="9"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$4:$U$38">
-    <sortState ref="A4:U38">
-      <sortCondition descending="1" ref="U4:U38"/>
-      <sortCondition descending="1" ref="O4:O38"/>
-      <sortCondition ref="B4:B38"/>
-      <sortCondition descending="1" ref="G4:G38"/>
-      <sortCondition ref="A4:A38"/>
-      <sortCondition descending="1" ref="F4:F38"/>
-      <sortCondition descending="1" ref="M4:M38"/>
-      <sortCondition descending="1" ref="I4:I38"/>
+  <autoFilter ref="$A$4:$U$37">
+    <sortState ref="A4:U37">
+      <sortCondition descending="1" ref="U4:U37"/>
+      <sortCondition descending="1" ref="O4:O37"/>
+      <sortCondition ref="B4:B37"/>
+      <sortCondition descending="1" ref="G4:G37"/>
+      <sortCondition ref="A4:A37"/>
+      <sortCondition descending="1" ref="F4:F37"/>
+      <sortCondition descending="1" ref="M4:M37"/>
+      <sortCondition descending="1" ref="I4:I37"/>
     </sortState>
   </autoFilter>
   <mergeCells count="9">
@@ -4147,7 +4069,7 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="U5:U38">
+  <conditionalFormatting sqref="U5:U37">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4159,12 +4081,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B38">
+  <conditionalFormatting sqref="B5:B37">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH(("B"),(B5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B38">
+  <conditionalFormatting sqref="B5:B37">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH(("R"),(B5))))</formula>
     </cfRule>
@@ -4292,7 +4214,7 @@
     </row>
     <row r="3">
       <c r="A3" s="71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="72" t="s">
         <v>9</v>
@@ -4304,13 +4226,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="G3" s="73" t="s">
         <v>67</v>
-      </c>
-      <c r="G3" s="73" t="s">
-        <v>68</v>
       </c>
       <c r="H3" s="73" t="s">
         <v>19</v>
@@ -4322,19 +4244,19 @@
         <v>22</v>
       </c>
       <c r="K3" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="72" t="s">
+      <c r="M3" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="N3" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="O3" s="72" t="s">
         <v>72</v>
-      </c>
-      <c r="O3" s="72" t="s">
-        <v>73</v>
       </c>
       <c r="P3" s="72" t="s">
         <v>26</v>
@@ -4356,7 +4278,7 @@
     </row>
     <row r="4">
       <c r="A4" s="77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="78" t="s">
         <v>30</v>
@@ -4404,28 +4326,28 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R4" s="83">
-        <f t="shared" ref="R4:R9" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>4395</v>
+        <f t="shared" ref="R4:R10" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>4425</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>36</v>
+      <c r="A5" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>35</v>
       </c>
       <c r="C5" s="81">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="D5" s="42">
         <v>9.0</v>
       </c>
       <c r="E5" s="42">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="F5" s="42">
         <v>1.0</v>
@@ -4443,7 +4365,7 @@
         <v>0.0</v>
       </c>
       <c r="K5" s="81">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L5" s="42">
         <v>1.0</v>
@@ -4461,37 +4383,37 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="82">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="R5" s="83">
         <f t="shared" si="1"/>
-        <v>3525</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="85" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>30</v>
+      <c r="A6" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>35</v>
       </c>
       <c r="C6" s="81">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="D6" s="42">
         <v>9.0</v>
       </c>
       <c r="E6" s="42">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="F6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H6" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I6" s="80">
         <v>0.0</v>
@@ -4500,13 +4422,13 @@
         <v>0.0</v>
       </c>
       <c r="K6" s="81">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M6" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N6" s="81">
         <v>0.0</v>
@@ -4518,31 +4440,31 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3180</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="s">
-        <v>77</v>
+      <c r="A7" s="84" t="s">
+        <v>76</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="81">
-        <v>22.0</v>
+        <v>28.0</v>
       </c>
       <c r="D7" s="42">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E7" s="42">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" s="42">
         <v>0.0</v>
@@ -4551,19 +4473,19 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J7" s="42">
         <v>0.0</v>
       </c>
       <c r="K7" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" s="42">
         <v>0.0</v>
       </c>
       <c r="M7" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N7" s="81">
         <v>0.0</v>
@@ -4572,31 +4494,31 @@
         <v>0.0</v>
       </c>
       <c r="P7" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q7" s="82">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>3150</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="85" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="81">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="D8" s="42">
         <v>9.0</v>
       </c>
       <c r="E8" s="42">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F8" s="42">
         <v>0.0</v>
@@ -4605,22 +4527,22 @@
         <v>0.0</v>
       </c>
       <c r="H8" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I8" s="80">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J8" s="42">
         <v>0.0</v>
       </c>
       <c r="K8" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L8" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M8" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N8" s="81">
         <v>0.0</v>
@@ -4629,34 +4551,34 @@
         <v>0.0</v>
       </c>
       <c r="P8" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q8" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R8" s="83">
         <f t="shared" si="1"/>
-        <v>3060</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="81">
         <v>22.0</v>
       </c>
       <c r="D9" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E9" s="42">
         <v>15.0</v>
       </c>
       <c r="F9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G9" s="42">
         <v>0.0</v>
@@ -4665,19 +4587,19 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J9" s="42">
         <v>0.0</v>
       </c>
       <c r="K9" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N9" s="81">
         <v>0.0</v>
@@ -4686,89 +4608,89 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q9" s="82">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="R9" s="83">
         <f t="shared" si="1"/>
-        <v>3030</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="81">
+        <v>24.0</v>
+      </c>
+      <c r="D10" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="E10" s="42">
+        <v>13.0</v>
+      </c>
+      <c r="F10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="80">
+        <v>2.0</v>
+      </c>
+      <c r="J10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="M10" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" s="82">
+        <v>18.0</v>
+      </c>
+      <c r="R10" s="83">
+        <f t="shared" si="1"/>
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="81">
+      <c r="B11" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="81">
         <v>28.0</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D11" s="42">
         <v>13.0</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E11" s="42">
         <v>14.0</v>
       </c>
-      <c r="F10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q10" s="82">
-        <v>15.0</v>
-      </c>
-      <c r="R10" s="83">
-        <f>C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2</f>
-        <v>3030</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="85" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="81">
-        <v>22.0</v>
-      </c>
-      <c r="D11" s="42">
-        <v>12.0</v>
-      </c>
-      <c r="E11" s="42">
-        <v>15.0</v>
-      </c>
       <c r="F11" s="42">
         <v>0.0</v>
       </c>
@@ -4776,16 +4698,16 @@
         <v>0.0</v>
       </c>
       <c r="H11" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I11" s="42">
         <v>0.0</v>
       </c>
       <c r="J11" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K11" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L11" s="42">
         <v>0.0</v>
@@ -4806,43 +4728,43 @@
         <v>17.0</v>
       </c>
       <c r="R11" s="83">
-        <f t="shared" ref="R11:R36" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
-        <v>2880</v>
+        <f>C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2</f>
+        <v>3090</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="s">
-        <v>82</v>
+      <c r="A12" s="85" t="s">
+        <v>81</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C12" s="81">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="D12" s="42">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E12" s="42">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="F12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" s="42">
         <v>0.0</v>
       </c>
       <c r="H12" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I12" s="80">
         <v>0.0</v>
       </c>
       <c r="J12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K12" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L12" s="42">
         <v>0.0</v>
@@ -4860,19 +4782,19 @@
         <v>1.0</v>
       </c>
       <c r="Q12" s="82">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="R12" s="83">
-        <f t="shared" si="2"/>
-        <v>2820</v>
+        <f t="shared" ref="R12:R36" si="2">C12*$C$2+D12*$D$2+E12*$E$2+F12*$F$2+G12*$G$2+H12*$H$2+K12*$K$2+L12*$L$2+M12*$M$2+N12*$N$2+O12*$O$2+P12*$P$2+Q12*$Q$2+I12*$I$2+J12*$J$2</f>
+        <v>2910</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="81">
         <v>19.0</v>
@@ -4917,16 +4839,16 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>2820</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="87" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B14" s="42" t="s">
         <v>30</v>
@@ -4974,19 +4896,19 @@
         <v>1.0</v>
       </c>
       <c r="Q14" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R14" s="83">
         <f t="shared" si="2"/>
-        <v>2730</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="81">
         <v>23.0</v>
@@ -5031,28 +4953,28 @@
         <v>2.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2595</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="81">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D16" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E16" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="42">
         <v>0.0</v>
@@ -5088,43 +5010,43 @@
         <v>1.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>2430</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="78" t="s">
-        <v>36</v>
+      <c r="A17" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C17" s="81">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="D17" s="42">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="E17" s="42">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="F17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I17" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K17" s="81">
         <v>0.0</v>
@@ -5145,43 +5067,43 @@
         <v>1.0</v>
       </c>
       <c r="Q17" s="82">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>2385</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>30</v>
+      <c r="A18" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>35</v>
       </c>
       <c r="C18" s="81">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="D18" s="42">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="E18" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I18" s="42">
         <v>0.0</v>
       </c>
       <c r="J18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K18" s="81">
         <v>0.0</v>
@@ -5202,25 +5124,25 @@
         <v>1.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>2010</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="86" t="s">
-        <v>89</v>
+      <c r="A19" s="85" t="s">
+        <v>88</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="81">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="D19" s="42">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E19" s="42">
         <v>9.0</v>
@@ -5232,7 +5154,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I19" s="42">
         <v>1.0</v>
@@ -5256,31 +5178,31 @@
         <v>0.0</v>
       </c>
       <c r="P19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>1995</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="85" t="s">
-        <v>90</v>
+      <c r="A20" s="77" t="s">
+        <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C20" s="81">
+        <v>18.0</v>
+      </c>
+      <c r="D20" s="42">
         <v>19.0</v>
       </c>
-      <c r="D20" s="42">
-        <v>13.0</v>
-      </c>
       <c r="E20" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5289,10 +5211,10 @@
         <v>0.0</v>
       </c>
       <c r="H20" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="42">
         <v>0.0</v>
@@ -5301,10 +5223,10 @@
         <v>0.0</v>
       </c>
       <c r="L20" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M20" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N20" s="81">
         <v>0.0</v>
@@ -5313,31 +5235,31 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q20" s="82">
         <v>17.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>1980</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="81">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D21" s="42">
         <v>7.0</v>
       </c>
       <c r="E21" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F21" s="42">
         <v>1.0</v>
@@ -5373,31 +5295,31 @@
         <v>0.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="88" t="s">
-        <v>92</v>
+      <c r="A22" s="84" t="s">
+        <v>91</v>
       </c>
       <c r="B22" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="81">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D22" s="42">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E22" s="42">
         <v>7.0</v>
       </c>
       <c r="F22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" s="42">
         <v>0.0</v>
@@ -5430,28 +5352,28 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="81">
         <v>18.0</v>
       </c>
       <c r="D23" s="42">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E23" s="42">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="F23" s="42">
         <v>0.0</v>
@@ -5460,13 +5382,13 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I23" s="80">
         <v>0.0</v>
       </c>
       <c r="J23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K23" s="81">
         <v>0.0</v>
@@ -5484,34 +5406,34 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>1800</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="78" t="s">
+      <c r="A24" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C24" s="81">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="D24" s="42">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="E24" s="42">
         <v>8.0</v>
       </c>
       <c r="F24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" s="42">
         <v>0.0</v>
@@ -5529,7 +5451,7 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M24" s="82">
         <v>0.0</v>
@@ -5544,43 +5466,43 @@
         <v>1.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1785</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="s">
-        <v>95</v>
+      <c r="A25" s="88" t="s">
+        <v>94</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C25" s="81">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="D25" s="42">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="E25" s="42">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="F25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" s="42">
         <v>0.0</v>
       </c>
       <c r="H25" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I25" s="42">
         <v>0.0</v>
       </c>
       <c r="J25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K25" s="81">
         <v>0.0</v>
@@ -5601,37 +5523,37 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1650</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C26" s="81">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="D26" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E26" s="42">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
       </c>
       <c r="G26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I26" s="80">
         <v>0.0</v>
@@ -5655,19 +5577,19 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q26" s="82">
         <v>17.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1635</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="s">
-        <v>97</v>
+      <c r="A27" s="86" t="s">
+        <v>96</v>
       </c>
       <c r="B27" s="42" t="s">
         <v>30</v>
@@ -5676,16 +5598,16 @@
         <v>12.0</v>
       </c>
       <c r="D27" s="42">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="E27" s="42">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" s="80">
         <v>0.0</v>
@@ -5697,10 +5619,10 @@
         <v>0.0</v>
       </c>
       <c r="K27" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="82">
         <v>0.0</v>
@@ -5715,25 +5637,25 @@
         <v>1.0</v>
       </c>
       <c r="Q27" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1620</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>36</v>
+      <c r="A28" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="78" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="81">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="D28" s="42">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="E28" s="42">
         <v>8.0</v>
@@ -5745,7 +5667,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28" s="42">
         <v>0.0</v>
@@ -5769,19 +5691,19 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
-        <v>1605</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B29" s="42" t="s">
         <v>30</v>
@@ -5790,7 +5712,7 @@
         <v>10.0</v>
       </c>
       <c r="D29" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E29" s="42">
         <v>5.0</v>
@@ -5829,28 +5751,28 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1350</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B30" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="81">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D30" s="42">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E30" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F30" s="42">
         <v>0.0</v>
@@ -5886,19 +5808,19 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="82">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>1065</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="81">
         <v>10.0</v>
@@ -5907,7 +5829,7 @@
         <v>19.0</v>
       </c>
       <c r="E31" s="42">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -5943,19 +5865,19 @@
         <v>1.0</v>
       </c>
       <c r="Q31" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="81">
         <v>10.0</v>
@@ -6000,19 +5922,19 @@
         <v>2.0</v>
       </c>
       <c r="Q32" s="82">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>930</v>
+        <v>990</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" s="78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="81">
         <v>7.0</v>
@@ -6057,19 +5979,19 @@
         <v>2.0</v>
       </c>
       <c r="Q33" s="82">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="89" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="90" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="91">
         <v>2.0</v>
@@ -6114,16 +6036,16 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="92">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="R34" s="83">
         <f t="shared" si="2"/>
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="89" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="93" t="s">
         <v>30</v>
@@ -6171,28 +6093,28 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="92">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R35" s="83">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="95">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D36" s="54">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E36" s="54">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F36" s="54">
         <v>0.0</v>
@@ -6228,11 +6150,11 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="97">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R36" s="98">
         <f t="shared" si="2"/>
-        <v>-45</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -119,30 +119,30 @@
     <t>Rodriguez, Alex</t>
   </si>
   <si>
+    <t>Rosario, Elian</t>
+  </si>
+  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>Rosario, Elian</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
     <t>Castillo, Wesly</t>
   </si>
   <si>
+    <t>Gonzalez, Victor</t>
+  </si>
+  <si>
+    <t>Ramirez, Santiago</t>
+  </si>
+  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
-    <t>Gonzalez, Victor</t>
-  </si>
-  <si>
-    <t>Ramirez, Santiago</t>
-  </si>
-  <si>
     <t>Diaz, David</t>
   </si>
   <si>
@@ -152,6 +152,12 @@
     <t>Marcano, Jose</t>
   </si>
   <si>
+    <t>Valdes, Abel</t>
+  </si>
+  <si>
+    <t>Jaquez, Luis</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
@@ -161,42 +167,36 @@
     <t>Volquez, Fabelin</t>
   </si>
   <si>
-    <t>Jaquez, Luis</t>
+    <t>Montero, Darling</t>
   </si>
   <si>
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
-    <t>Valdes, Abel</t>
-  </si>
-  <si>
-    <t>Montero, Darling</t>
+    <t>Ortiz Jr, David</t>
+  </si>
+  <si>
+    <t>Pereira, Raul</t>
+  </si>
+  <si>
+    <t>Genao, Jhostin</t>
   </si>
   <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Ortiz Jr, David</t>
-  </si>
-  <si>
-    <t>Pereira, Raul</t>
+    <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
-    <t>Genao, Jhostin</t>
-  </si>
-  <si>
-    <t>Chavez, Jesus</t>
+    <t>Colina, Felix</t>
   </si>
   <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
-    <t>Colina, Felix</t>
-  </si>
-  <si>
     <t>Simon, Jhon</t>
   </si>
   <si>
@@ -245,21 +245,21 @@
     <t>Colmenares, Kevin</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
+    <t>Santos, Aneudy</t>
+  </si>
+  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Pineda, Frandel</t>
   </si>
   <si>
     <t>Gomez, Manuel</t>
   </si>
   <si>
-    <t>Santos, Aneudy</t>
-  </si>
-  <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
@@ -302,10 +302,10 @@
     <t>Pena, Dariel</t>
   </si>
   <si>
+    <t>Cordero, Albert</t>
+  </si>
+  <si>
     <t>Ballesteros, Jean</t>
-  </si>
-  <si>
-    <t>Cordero, Albert</t>
   </si>
   <si>
     <t>Perez, Juanangel</t>
@@ -928,11 +928,11 @@
     <xf borderId="20" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1046,16 +1046,16 @@
     <xf borderId="16" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="34" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1578,10 +1578,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="D5" s="40">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="E5" s="40">
         <v>12.0</v>
@@ -1596,7 +1596,7 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="41">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="J5" s="39">
         <v>1.0</v>
@@ -1605,7 +1605,7 @@
         <v>0.0</v>
       </c>
       <c r="L5" s="39">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="M5" s="40">
         <v>7.0</v>
@@ -1620,20 +1620,20 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="R5" s="40">
         <v>8.0</v>
       </c>
       <c r="S5" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T5" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U37" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4425</v>
+        <v>4860</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1653,16 +1653,16 @@
         <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="D6" s="40">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="E6" s="40">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="F6" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G6" s="40">
         <v>4.0</v>
@@ -1683,7 +1683,7 @@
         <v>5.0</v>
       </c>
       <c r="M6" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="N6" s="40">
         <v>2.0</v>
@@ -1695,20 +1695,20 @@
         <v>0.0</v>
       </c>
       <c r="Q6" s="39">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R6" s="40">
         <v>9.0</v>
       </c>
       <c r="S6" s="43">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T6" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>4350</v>
+        <v>4725</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1728,16 +1728,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="45">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="D7" s="46">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="E7" s="46">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F7" s="46">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="G7" s="46">
         <v>3.0</v>
@@ -1770,20 +1770,20 @@
         <v>0.0</v>
       </c>
       <c r="Q7" s="39">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="R7" s="40">
         <v>10.0</v>
       </c>
       <c r="S7" s="43">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T7" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>3870</v>
+        <v>4275</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1803,10 +1803,10 @@
         <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="D8" s="40">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E8" s="40">
         <v>1.0</v>
@@ -1821,7 +1821,7 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="41">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J8" s="39">
         <v>2.0</v>
@@ -1845,20 +1845,20 @@
         <v>0.0</v>
       </c>
       <c r="Q8" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R8" s="40">
         <v>9.0</v>
       </c>
       <c r="S8" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T8" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3480</v>
+        <v>3720</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1871,47 +1871,47 @@
       <c r="AD8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="37" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C9" s="39">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="D9" s="40">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="E9" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="F9" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="G9" s="40">
         <v>7.0</v>
       </c>
-      <c r="F9" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G9" s="40">
-        <v>4.0</v>
-      </c>
       <c r="H9" s="40">
         <v>0.0</v>
       </c>
       <c r="I9" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J9" s="39">
         <v>0.0</v>
       </c>
       <c r="K9" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L9" s="39">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="M9" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N9" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O9" s="40">
         <v>0.0</v>
@@ -1920,20 +1920,20 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="R9" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S9" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T9" s="41">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3360</v>
+        <v>3600</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1946,59 +1946,59 @@
       <c r="AD9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>30</v>
-      </c>
       <c r="C10" s="39">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="D10" s="40">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="E10" s="40">
         <v>7.0</v>
       </c>
       <c r="F10" s="40">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G10" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J10" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L10" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" s="39">
         <v>6.0</v>
       </c>
-      <c r="H10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="M10" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="N10" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q10" s="39">
-        <v>13.0</v>
-      </c>
       <c r="R10" s="40">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="S10" s="43">
         <v>4.0</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3060</v>
+        <v>3390</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2025,13 +2025,13 @@
         <v>37</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="39">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="D11" s="40">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="E11" s="40">
         <v>3.0</v>
@@ -2055,35 +2055,35 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M11" s="40">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="N11" s="40">
         <v>0.0</v>
       </c>
       <c r="O11" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="P11" s="42">
         <v>0.0</v>
       </c>
       <c r="Q11" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R11" s="40">
         <v>5.0</v>
       </c>
       <c r="S11" s="43">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="T11" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>3045</v>
+        <v>3060</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2100,16 +2100,16 @@
         <v>38</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="39">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="D12" s="40">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="E12" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F12" s="40">
         <v>1.0</v>
@@ -2121,7 +2121,7 @@
         <v>0.0</v>
       </c>
       <c r="I12" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="J12" s="39">
         <v>2.0</v>
@@ -2145,20 +2145,20 @@
         <v>0.0</v>
       </c>
       <c r="Q12" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R12" s="40">
         <v>5.0</v>
       </c>
       <c r="S12" s="43">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="T12" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2171,69 +2171,69 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>35</v>
+      <c r="B13" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C13" s="39">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
       <c r="D13" s="40">
+        <v>27.0</v>
+      </c>
+      <c r="E13" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F13" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="41">
         <v>9.0</v>
       </c>
-      <c r="E13" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="F13" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="40">
+      <c r="J13" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M13" s="40">
         <v>4.0</v>
       </c>
-      <c r="H13" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J13" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="M13" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N13" s="40">
         <v>1.0</v>
       </c>
       <c r="O13" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q13" s="39">
         <v>7.0</v>
       </c>
       <c r="R13" s="40">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="S13" s="43">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T13" s="41">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2355</v>
+        <v>2745</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2246,69 +2246,69 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
       <c r="D14" s="40">
-        <v>26.0</v>
+        <v>18.0</v>
       </c>
       <c r="E14" s="40">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="F14" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G14" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M14" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N14" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q14" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="R14" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S14" s="43">
         <v>3.0</v>
       </c>
-      <c r="H14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="41">
-        <v>7.0</v>
-      </c>
-      <c r="J14" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M14" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="N14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P14" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q14" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R14" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="S14" s="43">
-        <v>4.0</v>
-      </c>
       <c r="T14" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>2355</v>
+        <v>2550</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2321,32 +2321,32 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="51" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C15" s="39">
         <v>13.0</v>
       </c>
       <c r="D15" s="40">
-        <v>18.0</v>
+        <v>9.0</v>
       </c>
       <c r="E15" s="40">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="F15" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2358,10 +2358,10 @@
         <v>4.0</v>
       </c>
       <c r="M15" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O15" s="40">
         <v>0.0</v>
@@ -2370,20 +2370,20 @@
         <v>1.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="R15" s="40">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="S15" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T15" s="41">
         <v>18.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2490</v>
+        <v>2385</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2454,11 +2454,11 @@
         <v>3.0</v>
       </c>
       <c r="T16" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2250</v>
+        <v>2310</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2474,23 +2474,23 @@
       <c r="A17" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>30</v>
+      <c r="B17" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C17" s="39">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D17" s="40">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="E17" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F17" s="40">
         <v>3.0</v>
       </c>
       <c r="G17" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H17" s="40">
         <v>0.0</v>
@@ -2520,20 +2520,20 @@
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R17" s="40">
         <v>9.0</v>
       </c>
       <c r="S17" s="43">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T17" s="41">
         <v>18.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>2070</v>
+        <v>2220</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2550,10 +2550,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="39">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D18" s="40">
         <v>4.0</v>
@@ -2601,14 +2601,14 @@
         <v>1.0</v>
       </c>
       <c r="S18" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>1965</v>
+        <v>2100</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2621,69 +2621,69 @@
       <c r="AD18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="48" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C19" s="39">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="D19" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="E19" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F19" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="G19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N19" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O19" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>9.0</v>
+      </c>
+      <c r="R19" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="S19" s="43">
+        <v>1.0</v>
+      </c>
+      <c r="T19" s="41">
         <v>20.0</v>
-      </c>
-      <c r="E19" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L19" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="M19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N19" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P19" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="R19" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="S19" s="43">
-        <v>4.0</v>
-      </c>
-      <c r="T19" s="41">
-        <v>17.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>1905</v>
+        <v>2040</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2699,17 +2699,17 @@
       <c r="A20" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="51" t="s">
-        <v>35</v>
+      <c r="B20" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="C20" s="39">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="D20" s="40">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="E20" s="40">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="F20" s="40">
         <v>0.0</v>
@@ -2721,44 +2721,44 @@
         <v>0.0</v>
       </c>
       <c r="I20" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J20" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="M20" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="N20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O20" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q20" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R20" s="40">
         <v>6.0</v>
-      </c>
-      <c r="J20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P20" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="R20" s="40">
-        <v>2.0</v>
       </c>
       <c r="S20" s="43">
         <v>5.0</v>
       </c>
       <c r="T20" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1695</v>
+        <v>1920</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2771,69 +2771,69 @@
       <c r="AD20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="49" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C21" s="39">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="D21" s="40">
+        <v>23.0</v>
+      </c>
+      <c r="E21" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L21" s="39">
         <v>12.0</v>
       </c>
-      <c r="E21" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>3.0</v>
-      </c>
       <c r="M21" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="N21" s="40">
         <v>0.0</v>
       </c>
       <c r="O21" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P21" s="42">
         <v>0.0</v>
       </c>
       <c r="Q21" s="39">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="R21" s="40">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="S21" s="43">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T21" s="41">
         <v>18.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1620</v>
+        <v>1875</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2849,29 +2849,29 @@
       <c r="A22" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>35</v>
+      <c r="B22" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C22" s="39">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="D22" s="40">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="E22" s="40">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F22" s="40">
         <v>0.0</v>
       </c>
       <c r="G22" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H22" s="40">
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2880,10 +2880,10 @@
         <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="M22" s="40">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="40">
         <v>0.0</v>
@@ -2895,20 +2895,20 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="R22" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="S22" s="43">
         <v>6.0</v>
       </c>
-      <c r="R22" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="S22" s="43">
-        <v>4.0</v>
-      </c>
       <c r="T22" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1605</v>
+        <v>1785</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2921,69 +2921,69 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="37" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="39">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D23" s="40">
+        <v>16.0</v>
+      </c>
+      <c r="E23" s="40">
         <v>6.0</v>
       </c>
-      <c r="E23" s="40">
-        <v>0.0</v>
-      </c>
       <c r="F23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H23" s="40">
         <v>0.0</v>
       </c>
       <c r="I23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="39">
         <v>3.0</v>
       </c>
-      <c r="J23" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="39">
-        <v>0.0</v>
-      </c>
       <c r="M23" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="42">
         <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="R23" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="S23" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T23" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1605</v>
+        <v>1770</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -2996,33 +2996,33 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="51" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C24" s="39">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="D24" s="40">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="E24" s="40">
         <v>3.0</v>
       </c>
       <c r="F24" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G24" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H24" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="41">
         <v>3.0</v>
       </c>
-      <c r="G24" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J24" s="39">
         <v>0.0</v>
       </c>
@@ -3030,35 +3030,35 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="39">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M24" s="40">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="N24" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O24" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="R24" s="40">
         <v>3.0</v>
       </c>
       <c r="S24" s="43">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="T24" s="41">
         <v>18.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1560</v>
+        <v>1710</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3071,33 +3071,33 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="48" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C25" s="39">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D25" s="40">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="E25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
         <v>3.0</v>
       </c>
-      <c r="F25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>2.0</v>
-      </c>
       <c r="J25" s="39">
         <v>0.0</v>
       </c>
@@ -3105,35 +3105,35 @@
         <v>0.0</v>
       </c>
       <c r="L25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="R25" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S25" s="43">
         <v>3.0</v>
       </c>
-      <c r="M25" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="R25" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S25" s="43">
-        <v>5.0</v>
-      </c>
       <c r="T25" s="41">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1545</v>
+        <v>1695</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3146,32 +3146,32 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="48" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D26" s="40">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="E26" s="40">
         <v>3.0</v>
       </c>
       <c r="F26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="40">
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3180,13 +3180,13 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="39">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="40">
         <v>0.0</v>
@@ -3195,20 +3195,20 @@
         <v>0.0</v>
       </c>
       <c r="Q26" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R26" s="40">
         <v>4.0</v>
       </c>
-      <c r="R26" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S26" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T26" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1470</v>
+        <v>1590</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3221,69 +3221,69 @@
       <c r="AD26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>30</v>
+      <c r="B27" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C27" s="39">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="D27" s="40">
+        <v>25.0</v>
+      </c>
+      <c r="E27" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G27" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J27" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="39">
         <v>3.0</v>
       </c>
-      <c r="E27" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="F27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="39">
-        <v>0.0</v>
-      </c>
       <c r="M27" s="40">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="N27" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O27" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="P27" s="42">
         <v>0.0</v>
       </c>
       <c r="Q27" s="39">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="R27" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S27" s="43">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T27" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1545</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3296,14 +3296,14 @@
       <c r="AD27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>35</v>
+      <c r="B28" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C28" s="39">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="D28" s="40">
         <v>23.0</v>
@@ -3312,34 +3312,34 @@
         <v>1.0</v>
       </c>
       <c r="F28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" s="40">
         <v>0.0</v>
       </c>
       <c r="H28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I28" s="41">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="J28" s="39">
         <v>0.0</v>
       </c>
       <c r="K28" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L28" s="39">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M28" s="40">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="40">
         <v>1.0</v>
       </c>
       <c r="O28" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="P28" s="42">
         <v>0.0</v>
@@ -3351,14 +3351,14 @@
         <v>5.0</v>
       </c>
       <c r="S28" s="43">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="T28" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1365</v>
+        <v>1545</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3375,19 +3375,19 @@
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C29" s="39">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D29" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E29" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G29" s="40">
         <v>1.0</v>
@@ -3396,7 +3396,7 @@
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3405,35 +3405,35 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N29" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q29" s="39">
         <v>4.0</v>
       </c>
       <c r="R29" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="S29" s="43">
         <v>2.0</v>
       </c>
       <c r="T29" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1275</v>
+        <v>1500</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3450,43 +3450,43 @@
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" s="39">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="D30" s="40">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="E30" s="40">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F30" s="40">
         <v>1.0</v>
       </c>
       <c r="G30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
       </c>
       <c r="K30" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L30" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M30" s="40">
         <v>0.0</v>
       </c>
       <c r="N30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O30" s="40">
         <v>1.0</v>
@@ -3495,20 +3495,20 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R30" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="S30" s="43">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="T30" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1140</v>
+        <v>1320</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3524,20 +3524,20 @@
       <c r="A31" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="38" t="s">
-        <v>35</v>
+      <c r="B31" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C31" s="39">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="D31" s="40">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="E31" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G31" s="40">
         <v>1.0</v>
@@ -3546,7 +3546,7 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3555,35 +3555,35 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="M31" s="40">
         <v>0.0</v>
       </c>
       <c r="N31" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O31" s="40">
         <v>1.0</v>
       </c>
       <c r="P31" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q31" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R31" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S31" s="43">
         <v>2.0</v>
       </c>
       <c r="T31" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1125</v>
+        <v>1290</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3596,26 +3596,26 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="51" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D32" s="40">
         <v>3.0</v>
       </c>
       <c r="E32" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F32" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G32" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H32" s="40">
         <v>0.0</v>
@@ -3633,7 +3633,7 @@
         <v>1.0</v>
       </c>
       <c r="M32" s="40">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="N32" s="40">
         <v>0.0</v>
@@ -3645,20 +3645,20 @@
         <v>0.0</v>
       </c>
       <c r="Q32" s="39">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S32" s="43">
         <v>2.0</v>
       </c>
       <c r="T32" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1245</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3671,14 +3671,14 @@
       <c r="AD32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="s">
+      <c r="A33" s="51" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D33" s="40">
         <v>3.0</v>
@@ -3687,10 +3687,10 @@
         <v>2.0</v>
       </c>
       <c r="F33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" s="40">
         <v>0.0</v>
@@ -3708,7 +3708,7 @@
         <v>1.0</v>
       </c>
       <c r="M33" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="N33" s="40">
         <v>0.0</v>
@@ -3720,20 +3720,20 @@
         <v>0.0</v>
       </c>
       <c r="Q33" s="39">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R33" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S33" s="43">
         <v>2.0</v>
       </c>
       <c r="T33" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1095</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3746,57 +3746,57 @@
       <c r="AD33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="51" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="D34" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="E34" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="G34" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J34" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P34" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="39">
         <v>3.0</v>
       </c>
-      <c r="D34" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="E34" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F34" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="G34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P34" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="39">
-        <v>2.0</v>
-      </c>
       <c r="R34" s="40">
         <v>0.0</v>
       </c>
@@ -3804,11 +3804,11 @@
         <v>2.0</v>
       </c>
       <c r="T34" s="41">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>870</v>
+        <v>960</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3824,8 +3824,8 @@
       <c r="A35" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="38" t="s">
-        <v>35</v>
+      <c r="B35" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C35" s="39">
         <v>4.0</v>
@@ -3879,11 +3879,11 @@
         <v>2.0</v>
       </c>
       <c r="T35" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>825</v>
+        <v>885</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3954,11 +3954,11 @@
         <v>0.0</v>
       </c>
       <c r="T36" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>630</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -3974,8 +3974,8 @@
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="51" t="s">
-        <v>35</v>
+      <c r="B37" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C37" s="39">
         <v>1.0</v>
@@ -4029,11 +4029,11 @@
         <v>1.0</v>
       </c>
       <c r="T37" s="41">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4284,13 +4284,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="79">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
       <c r="D4" s="80">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="E4" s="80">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="F4" s="80">
         <v>0.0</v>
@@ -4299,7 +4299,7 @@
         <v>1.0</v>
       </c>
       <c r="H4" s="80">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I4" s="80">
         <v>0.0</v>
@@ -4326,19 +4326,19 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R4" s="83">
-        <f t="shared" ref="R4:R10" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>4425</v>
+        <f t="shared" ref="R4:R7" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>5025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>35</v>
+      <c r="B5" s="78" t="s">
+        <v>30</v>
       </c>
       <c r="C5" s="81">
         <v>29.0</v>
@@ -4383,11 +4383,11 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="82">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="R5" s="83">
         <f t="shared" si="1"/>
-        <v>3885</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="6">
@@ -4395,16 +4395,16 @@
         <v>75</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="81">
         <v>27.0</v>
       </c>
       <c r="D6" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E6" s="42">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F6" s="42">
         <v>1.0</v>
@@ -4437,40 +4437,40 @@
         <v>0.0</v>
       </c>
       <c r="P6" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3585</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="85" t="s">
         <v>76</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C7" s="81">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="D7" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E7" s="42">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G7" s="42">
         <v>0.0</v>
       </c>
       <c r="H7" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I7" s="80">
         <v>0.0</v>
@@ -4479,13 +4479,13 @@
         <v>0.0</v>
       </c>
       <c r="K7" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="42">
         <v>0.0</v>
       </c>
       <c r="M7" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N7" s="81">
         <v>0.0</v>
@@ -4494,31 +4494,31 @@
         <v>0.0</v>
       </c>
       <c r="P7" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q7" s="82">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>3330</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="86" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C8" s="81">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
       <c r="D8" s="42">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="E8" s="42">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="F8" s="42">
         <v>0.0</v>
@@ -4527,7 +4527,7 @@
         <v>0.0</v>
       </c>
       <c r="H8" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I8" s="80">
         <v>0.0</v>
@@ -4536,13 +4536,13 @@
         <v>0.0</v>
       </c>
       <c r="K8" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L8" s="42">
         <v>0.0</v>
       </c>
       <c r="M8" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N8" s="81">
         <v>0.0</v>
@@ -4551,88 +4551,88 @@
         <v>0.0</v>
       </c>
       <c r="P8" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q8" s="82">
         <v>18.0</v>
       </c>
       <c r="R8" s="83">
-        <f t="shared" si="1"/>
-        <v>3210</v>
+        <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
+        <v>3390</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="84" t="s">
         <v>78</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="81">
-        <v>22.0</v>
+        <v>28.0</v>
       </c>
       <c r="D9" s="42">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E9" s="42">
+        <v>16.0</v>
+      </c>
+      <c r="F9" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q9" s="82">
         <v>15.0</v>
       </c>
-      <c r="F9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="80">
-        <v>1.0</v>
-      </c>
-      <c r="J9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="L9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="82">
-        <v>1.0</v>
-      </c>
-      <c r="N9" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="Q9" s="82">
-        <v>17.0</v>
-      </c>
       <c r="R9" s="83">
-        <f t="shared" si="1"/>
-        <v>3210</v>
+        <f t="shared" ref="R9:R36" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
+        <v>3360</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="78" t="s">
-        <v>30</v>
+      <c r="B10" s="42" t="s">
+        <v>36</v>
       </c>
       <c r="C10" s="81">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="D10" s="42">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E10" s="42">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
@@ -4644,19 +4644,19 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="80">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
       </c>
       <c r="K10" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L10" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M10" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="81">
         <v>0.0</v>
@@ -4665,31 +4665,31 @@
         <v>0.0</v>
       </c>
       <c r="P10" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q10" s="82">
         <v>18.0</v>
       </c>
       <c r="R10" s="83">
-        <f t="shared" si="1"/>
-        <v>3090</v>
+        <f t="shared" si="2"/>
+        <v>3465</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>35</v>
+      <c r="B11" s="78" t="s">
+        <v>30</v>
       </c>
       <c r="C11" s="81">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
       <c r="D11" s="42">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="E11" s="42">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="F11" s="42">
         <v>0.0</v>
@@ -4701,7 +4701,7 @@
         <v>0.0</v>
       </c>
       <c r="I11" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J11" s="42">
         <v>0.0</v>
@@ -4710,7 +4710,7 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M11" s="82">
         <v>0.0</v>
@@ -4722,14 +4722,14 @@
         <v>0.0</v>
       </c>
       <c r="P11" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q11" s="82">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="R11" s="83">
-        <f>C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2</f>
-        <v>3090</v>
+        <f t="shared" si="2"/>
+        <v>3450</v>
       </c>
     </row>
     <row r="12">
@@ -4743,10 +4743,10 @@
         <v>22.0</v>
       </c>
       <c r="D12" s="42">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E12" s="42">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="F12" s="42">
         <v>0.0</v>
@@ -4779,14 +4779,14 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q12" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R12" s="83">
-        <f t="shared" ref="R12:R36" si="2">C12*$C$2+D12*$D$2+E12*$E$2+F12*$F$2+G12*$G$2+H12*$H$2+K12*$K$2+L12*$L$2+M12*$M$2+N12*$N$2+O12*$O$2+P12*$P$2+Q12*$Q$2+I12*$I$2+J12*$J$2</f>
-        <v>2910</v>
+        <f t="shared" si="2"/>
+        <v>3120</v>
       </c>
     </row>
     <row r="13">
@@ -4794,7 +4794,7 @@
         <v>82</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="81">
         <v>19.0</v>
@@ -4839,11 +4839,11 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>2880</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="14">
@@ -4896,11 +4896,11 @@
         <v>1.0</v>
       </c>
       <c r="Q14" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R14" s="83">
         <f t="shared" si="2"/>
-        <v>2760</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="15">
@@ -4908,7 +4908,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="81">
         <v>23.0</v>
@@ -4953,11 +4953,11 @@
         <v>2.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2655</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="16">
@@ -4971,7 +4971,7 @@
         <v>20.0</v>
       </c>
       <c r="D16" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E16" s="42">
         <v>7.0</v>
@@ -5010,11 +5010,11 @@
         <v>1.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>2565</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="17">
@@ -5067,11 +5067,11 @@
         <v>1.0</v>
       </c>
       <c r="Q17" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>2520</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="18">
@@ -5079,7 +5079,7 @@
         <v>87</v>
       </c>
       <c r="B18" s="78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="81">
         <v>19.0</v>
@@ -5124,11 +5124,11 @@
         <v>1.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>2445</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="19">
@@ -5181,11 +5181,11 @@
         <v>0.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>2220</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="20">
@@ -5193,16 +5193,16 @@
         <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" s="81">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D20" s="42">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E20" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5238,11 +5238,11 @@
         <v>3.0</v>
       </c>
       <c r="Q20" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>2220</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="21">
@@ -5295,11 +5295,11 @@
         <v>0.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>2100</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="22">
@@ -5352,11 +5352,11 @@
         <v>1.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>2040</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="23">
@@ -5364,7 +5364,7 @@
         <v>92</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" s="81">
         <v>18.0</v>
@@ -5409,11 +5409,11 @@
         <v>1.0</v>
       </c>
       <c r="Q23" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>2040</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="24">
@@ -5466,11 +5466,11 @@
         <v>1.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1890</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="25">
@@ -5523,11 +5523,11 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1875</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="26">
@@ -5535,25 +5535,25 @@
         <v>95</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C26" s="81">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="D26" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E26" s="42">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="42">
         <v>0.0</v>
       </c>
       <c r="G26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H26" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I26" s="80">
         <v>0.0</v>
@@ -5562,7 +5562,7 @@
         <v>0.0</v>
       </c>
       <c r="K26" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L26" s="42">
         <v>0.0</v>
@@ -5577,14 +5577,14 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q26" s="82">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1845</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="27">
@@ -5592,25 +5592,25 @@
         <v>96</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C27" s="81">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="D27" s="42">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E27" s="42">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
       </c>
       <c r="G27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I27" s="42">
         <v>0.0</v>
@@ -5619,7 +5619,7 @@
         <v>0.0</v>
       </c>
       <c r="K27" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L27" s="42">
         <v>0.0</v>
@@ -5634,14 +5634,14 @@
         <v>0.0</v>
       </c>
       <c r="P27" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q27" s="82">
         <v>18.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1830</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="28">
@@ -5655,7 +5655,7 @@
         <v>17.0</v>
       </c>
       <c r="D28" s="42">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="E28" s="42">
         <v>8.0</v>
@@ -5691,10 +5691,10 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
@@ -5751,11 +5751,11 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1320</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="30">
@@ -5808,11 +5808,11 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="82">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="31">
@@ -5820,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" s="81">
         <v>10.0</v>
@@ -5865,11 +5865,11 @@
         <v>1.0</v>
       </c>
       <c r="Q31" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="32">
@@ -5877,13 +5877,13 @@
         <v>101</v>
       </c>
       <c r="B32" s="78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" s="81">
         <v>10.0</v>
       </c>
       <c r="D32" s="42">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E32" s="42">
         <v>2.0</v>
@@ -5919,14 +5919,14 @@
         <v>0.0</v>
       </c>
       <c r="P32" s="42">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q32" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="33">
@@ -5934,7 +5934,7 @@
         <v>102</v>
       </c>
       <c r="B33" s="78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="81">
         <v>7.0</v>
@@ -5979,11 +5979,11 @@
         <v>2.0</v>
       </c>
       <c r="Q33" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>840</v>
+        <v>870</v>
       </c>
     </row>
     <row r="34">
@@ -5991,27 +5991,27 @@
         <v>103</v>
       </c>
       <c r="B34" s="90" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" s="91">
         <v>2.0</v>
       </c>
-      <c r="D34" s="90">
-        <v>1.0</v>
-      </c>
-      <c r="E34" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="90">
+      <c r="D34" s="92">
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="92">
         <v>0.0</v>
       </c>
       <c r="H34" s="80">
         <v>0.0</v>
       </c>
-      <c r="I34" s="90">
+      <c r="I34" s="92">
         <v>0.0</v>
       </c>
       <c r="J34" s="42">
@@ -6020,49 +6020,49 @@
       <c r="K34" s="91">
         <v>0.0</v>
       </c>
-      <c r="L34" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="92">
+      <c r="L34" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="93">
         <v>0.0</v>
       </c>
       <c r="N34" s="91">
         <v>0.0</v>
       </c>
-      <c r="O34" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="92">
-        <v>16.0</v>
+      <c r="O34" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="93">
+        <v>17.0</v>
       </c>
       <c r="R34" s="83">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="93" t="s">
+      <c r="B35" s="90" t="s">
         <v>30</v>
       </c>
       <c r="C35" s="91">
         <v>0.0</v>
       </c>
-      <c r="D35" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="90">
+      <c r="D35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="92">
         <v>0.0</v>
       </c>
       <c r="H35" s="80">
@@ -6077,27 +6077,27 @@
       <c r="K35" s="91">
         <v>0.0</v>
       </c>
-      <c r="L35" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="92">
+      <c r="L35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="93">
         <v>0.0</v>
       </c>
       <c r="N35" s="91">
         <v>0.0</v>
       </c>
-      <c r="O35" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="90">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="92">
-        <v>16.0</v>
+      <c r="O35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="92">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="93">
+        <v>18.0</v>
       </c>
       <c r="R35" s="83">
         <f t="shared" si="2"/>
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="36">
@@ -6105,7 +6105,7 @@
         <v>105</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36" s="95">
         <v>2.0</v>
@@ -6150,11 +6150,11 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="97">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R36" s="98">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -128,12 +128,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>Castillo, Wesly</t>
+  </si>
+  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
-    <t>Castillo, Wesly</t>
-  </si>
-  <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
@@ -143,12 +143,12 @@
     <t>Benitez, Frainker</t>
   </si>
   <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
     <t>Marcano, Jose</t>
   </si>
   <si>
@@ -185,15 +185,15 @@
     <t>Rodriguez, Victor</t>
   </si>
   <si>
+    <t>Colina, Felix</t>
+  </si>
+  <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
-    <t>Colina, Felix</t>
-  </si>
-  <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
@@ -248,28 +248,31 @@
     <t>Roquez, Yadiel</t>
   </si>
   <si>
+    <t>Pineda, Frandel</t>
+  </si>
+  <si>
+    <t>Gomez, Manuel</t>
+  </si>
+  <si>
     <t>Santos, Aneudy</t>
   </si>
   <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
-    <t>Pineda, Frandel</t>
-  </si>
-  <si>
-    <t>Gomez, Manuel</t>
-  </si>
-  <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
+    <t>Peralta, Eddy</t>
+  </si>
+  <si>
     <t>Lara, Carlos</t>
   </si>
   <si>
-    <t>Peralta, Eddy</t>
+    <t>Figuereo, Breyner</t>
   </si>
   <si>
     <t>Encarnacion, Jefferson</t>
@@ -278,21 +281,21 @@
     <t>Alcantara, Jostin</t>
   </si>
   <si>
-    <t>Figuereo, Breyner</t>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
+    <t>Granado, Argenis</t>
   </si>
   <si>
     <t>Fernandez, Jehiber</t>
   </si>
   <si>
-    <t>Ramos, Daniel</t>
+    <t>Ballesteros, Jean</t>
   </si>
   <si>
     <t>Castillo, Albert</t>
   </si>
   <si>
-    <t>Granado, Argenis</t>
-  </si>
-  <si>
     <t>Acosta, Isaac</t>
   </si>
   <si>
@@ -303,9 +306,6 @@
   </si>
   <si>
     <t>Cordero, Albert</t>
-  </si>
-  <si>
-    <t>Ballesteros, Jean</t>
   </si>
   <si>
     <t>Perez, Juanangel</t>
@@ -2004,11 +2004,11 @@
         <v>4.0</v>
       </c>
       <c r="T10" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3390</v>
+        <v>3420</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2028,43 +2028,43 @@
         <v>36</v>
       </c>
       <c r="C11" s="39">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="D11" s="40">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="E11" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F11" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="40">
         <v>3.0</v>
       </c>
-      <c r="F11" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="G11" s="40">
-        <v>2.0</v>
-      </c>
       <c r="H11" s="40">
         <v>0.0</v>
       </c>
       <c r="I11" s="41">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="J11" s="39">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K11" s="41">
         <v>0.0</v>
       </c>
       <c r="L11" s="39">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="M11" s="40">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="40">
         <v>0.0</v>
       </c>
       <c r="O11" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="P11" s="42">
         <v>0.0</v>
@@ -2079,11 +2079,11 @@
         <v>7.0</v>
       </c>
       <c r="T11" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>3060</v>
+        <v>3255</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2103,16 +2103,16 @@
         <v>36</v>
       </c>
       <c r="C12" s="39">
-        <v>23.0</v>
+        <v>29.0</v>
       </c>
       <c r="D12" s="40">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
       <c r="E12" s="40">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F12" s="40">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G12" s="40">
         <v>2.0</v>
@@ -2121,25 +2121,25 @@
         <v>0.0</v>
       </c>
       <c r="I12" s="41">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="J12" s="39">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="41">
         <v>0.0</v>
       </c>
       <c r="L12" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="M12" s="40">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="N12" s="40">
         <v>0.0</v>
       </c>
       <c r="O12" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="P12" s="42">
         <v>0.0</v>
@@ -2154,11 +2154,11 @@
         <v>7.0</v>
       </c>
       <c r="T12" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>3045</v>
+        <v>3120</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2379,11 +2379,11 @@
         <v>4.0</v>
       </c>
       <c r="T15" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2385</v>
+        <v>2415</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2396,23 +2396,23 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>30</v>
+      <c r="B16" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="39">
         <v>15.0</v>
       </c>
       <c r="D16" s="40">
-        <v>17.0</v>
+        <v>37.0</v>
       </c>
       <c r="E16" s="40">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F16" s="40">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G16" s="40">
         <v>3.0</v>
@@ -2421,7 +2421,7 @@
         <v>0.0</v>
       </c>
       <c r="I16" s="41">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="J16" s="39">
         <v>0.0</v>
@@ -2430,35 +2430,35 @@
         <v>0.0</v>
       </c>
       <c r="L16" s="39">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="M16" s="40">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="N16" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="O16" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P16" s="42">
         <v>0.0</v>
       </c>
       <c r="Q16" s="39">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="R16" s="40">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="S16" s="43">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T16" s="41">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2310</v>
+        <v>2370</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2471,23 +2471,23 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="50" t="s">
-        <v>36</v>
+      <c r="B17" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C17" s="39">
         <v>15.0</v>
       </c>
       <c r="D17" s="40">
-        <v>36.0</v>
+        <v>17.0</v>
       </c>
       <c r="E17" s="40">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F17" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" s="40">
         <v>3.0</v>
@@ -2496,7 +2496,7 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="41">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="J17" s="39">
         <v>0.0</v>
@@ -2505,35 +2505,35 @@
         <v>0.0</v>
       </c>
       <c r="L17" s="39">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="M17" s="40">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="N17" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O17" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P17" s="42">
         <v>0.0</v>
       </c>
       <c r="Q17" s="39">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="R17" s="40">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="S17" s="43">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="T17" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>2220</v>
+        <v>2310</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2553,7 +2553,7 @@
         <v>36</v>
       </c>
       <c r="C18" s="39">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D18" s="40">
         <v>4.0</v>
@@ -2604,11 +2604,11 @@
         <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>2100</v>
+        <v>2205</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2754,11 +2754,11 @@
         <v>5.0</v>
       </c>
       <c r="T20" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>1950</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2829,11 +2829,11 @@
         <v>5.0</v>
       </c>
       <c r="T21" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1875</v>
+        <v>1905</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2856,7 +2856,7 @@
         <v>14.0</v>
       </c>
       <c r="D22" s="40">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E22" s="40">
         <v>2.0</v>
@@ -2871,7 +2871,7 @@
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
@@ -2904,7 +2904,7 @@
         <v>6.0</v>
       </c>
       <c r="T22" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
@@ -3021,7 +3021,7 @@
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3054,11 +3054,11 @@
         <v>5.0</v>
       </c>
       <c r="T24" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1710</v>
+        <v>1770</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3258,7 +3258,7 @@
         <v>3.0</v>
       </c>
       <c r="M27" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="N27" s="40">
         <v>1.0</v>
@@ -3279,11 +3279,11 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1545</v>
+        <v>1590</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3336,7 +3336,7 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O28" s="40">
         <v>1.0</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1545</v>
+        <v>1575</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3429,11 +3429,11 @@
         <v>2.0</v>
       </c>
       <c r="T29" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1530</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3446,32 +3446,32 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="51" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C30" s="39">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="D30" s="40">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="E30" s="40">
         <v>4.0</v>
       </c>
       <c r="F30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H30" s="40">
         <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
@@ -3483,13 +3483,13 @@
         <v>1.0</v>
       </c>
       <c r="M30" s="40">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="N30" s="40">
         <v>0.0</v>
       </c>
       <c r="O30" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P30" s="42">
         <v>0.0</v>
@@ -3504,11 +3504,11 @@
         <v>2.0</v>
       </c>
       <c r="T30" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3524,20 +3524,20 @@
       <c r="A31" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="39">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D31" s="40">
-        <v>7.0</v>
+        <v>17.0</v>
       </c>
       <c r="E31" s="40">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F31" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="40">
         <v>1.0</v>
@@ -3546,7 +3546,7 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3555,25 +3555,25 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="M31" s="40">
         <v>0.0</v>
       </c>
       <c r="N31" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="40">
         <v>1.0</v>
       </c>
       <c r="P31" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q31" s="39">
         <v>5.0</v>
       </c>
       <c r="R31" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="S31" s="43">
         <v>2.0</v>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1320</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3596,26 +3596,26 @@
       <c r="AD31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="50" t="s">
         <v>36</v>
       </c>
       <c r="C32" s="39">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="D32" s="40">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E32" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F32" s="40">
         <v>0.0</v>
       </c>
       <c r="G32" s="40">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" s="40">
         <v>0.0</v>
@@ -3630,35 +3630,35 @@
         <v>0.0</v>
       </c>
       <c r="L32" s="39">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="M32" s="40">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O32" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P32" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q32" s="39">
         <v>5.0</v>
       </c>
       <c r="R32" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S32" s="43">
         <v>2.0</v>
       </c>
       <c r="T32" s="41">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>1245</v>
+        <v>1320</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3729,11 +3729,11 @@
         <v>2.0</v>
       </c>
       <c r="T33" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3804,11 +3804,11 @@
         <v>2.0</v>
       </c>
       <c r="T34" s="41">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -4329,7 +4329,7 @@
         <v>20.0</v>
       </c>
       <c r="R4" s="83">
-        <f t="shared" ref="R4:R7" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <f t="shared" ref="R4:R9" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
         <v>5025</v>
       </c>
     </row>
@@ -4440,11 +4440,11 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3645</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="7">
@@ -4505,20 +4505,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="77" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="81">
-        <v>30.0</v>
+        <v>23.0</v>
       </c>
       <c r="D8" s="42">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="E8" s="42">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="F8" s="42">
         <v>0.0</v>
@@ -4530,19 +4530,19 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J8" s="42">
         <v>0.0</v>
       </c>
       <c r="K8" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L8" s="42">
         <v>0.0</v>
       </c>
       <c r="M8" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N8" s="81">
         <v>0.0</v>
@@ -4554,31 +4554,31 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R8" s="83">
-        <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
-        <v>3390</v>
+        <f t="shared" si="1"/>
+        <v>3495</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>36</v>
+      <c r="B9" s="78" t="s">
+        <v>30</v>
       </c>
       <c r="C9" s="81">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
       <c r="D9" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E9" s="42">
         <v>16.0</v>
       </c>
       <c r="F9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G9" s="42">
         <v>0.0</v>
@@ -4587,7 +4587,7 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="80">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J9" s="42">
         <v>0.0</v>
@@ -4596,7 +4596,7 @@
         <v>0.0</v>
       </c>
       <c r="L9" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M9" s="82">
         <v>0.0</v>
@@ -4608,31 +4608,31 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q9" s="82">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="R9" s="83">
-        <f t="shared" ref="R9:R36" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
-        <v>3360</v>
+        <f t="shared" si="1"/>
+        <v>3450</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="86" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="81">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
       <c r="D10" s="42">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E10" s="42">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="F10" s="42">
         <v>0.0</v>
@@ -4644,19 +4644,19 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
       </c>
       <c r="K10" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L10" s="42">
         <v>0.0</v>
       </c>
       <c r="M10" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="81">
         <v>0.0</v>
@@ -4668,31 +4668,31 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R10" s="83">
-        <f t="shared" si="2"/>
-        <v>3465</v>
+        <f>C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2</f>
+        <v>3420</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="78" t="s">
-        <v>30</v>
+      <c r="B11" s="42" t="s">
+        <v>36</v>
       </c>
       <c r="C11" s="81">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="D11" s="42">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E11" s="42">
         <v>16.0</v>
       </c>
       <c r="F11" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" s="42">
         <v>0.0</v>
@@ -4701,7 +4701,7 @@
         <v>0.0</v>
       </c>
       <c r="I11" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J11" s="42">
         <v>0.0</v>
@@ -4710,7 +4710,7 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="82">
         <v>0.0</v>
@@ -4722,14 +4722,14 @@
         <v>0.0</v>
       </c>
       <c r="P11" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q11" s="82">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="R11" s="83">
-        <f t="shared" si="2"/>
-        <v>3450</v>
+        <f t="shared" ref="R11:R36" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
+        <v>3390</v>
       </c>
     </row>
     <row r="12">
@@ -4839,37 +4839,37 @@
         <v>1.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>2910</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="77" t="s">
         <v>83</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C14" s="81">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="D14" s="42">
         <v>12.0</v>
       </c>
       <c r="E14" s="42">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="F14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="42">
         <v>0.0</v>
       </c>
       <c r="H14" s="80">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I14" s="80">
         <v>0.0</v>
@@ -4878,7 +4878,7 @@
         <v>0.0</v>
       </c>
       <c r="K14" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L14" s="42">
         <v>0.0</v>
@@ -4893,40 +4893,40 @@
         <v>0.0</v>
       </c>
       <c r="P14" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q14" s="82">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R14" s="83">
         <f t="shared" si="2"/>
-        <v>2820</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="87" t="s">
         <v>84</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C15" s="81">
         <v>23.0</v>
       </c>
       <c r="D15" s="42">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E15" s="42">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="F15" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="42">
         <v>0.0</v>
       </c>
       <c r="H15" s="80">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I15" s="42">
         <v>0.0</v>
@@ -4935,7 +4935,7 @@
         <v>0.0</v>
       </c>
       <c r="K15" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15" s="42">
         <v>0.0</v>
@@ -4950,34 +4950,34 @@
         <v>0.0</v>
       </c>
       <c r="P15" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2685</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="42" t="s">
-        <v>30</v>
+      <c r="B16" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="81">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="D16" s="42">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E16" s="42">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="42">
         <v>2.0</v>
@@ -4989,7 +4989,7 @@
         <v>0.0</v>
       </c>
       <c r="J16" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K16" s="81">
         <v>0.0</v>
@@ -5010,40 +5010,40 @@
         <v>1.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>2595</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="85" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="81">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="D17" s="42">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="E17" s="42">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="F17" s="42">
         <v>0.0</v>
       </c>
       <c r="G17" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5071,39 +5071,39 @@
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>2580</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="88" t="s">
+      <c r="A18" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="78" t="s">
-        <v>36</v>
+      <c r="B18" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C18" s="81">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="D18" s="42">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="E18" s="42">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="F18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H18" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K18" s="81">
         <v>0.0</v>
@@ -5124,28 +5124,28 @@
         <v>1.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>2475</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="77" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C19" s="81">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="D19" s="42">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="E19" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="42">
         <v>0.0</v>
@@ -5154,10 +5154,10 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J19" s="42">
         <v>0.0</v>
@@ -5166,10 +5166,10 @@
         <v>0.0</v>
       </c>
       <c r="L19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M19" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N19" s="81">
         <v>0.0</v>
@@ -5178,31 +5178,31 @@
         <v>0.0</v>
       </c>
       <c r="P19" s="42">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>2280</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="78" t="s">
         <v>36</v>
       </c>
       <c r="C20" s="81">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="D20" s="42">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="E20" s="42">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="F20" s="42">
         <v>0.0</v>
@@ -5211,7 +5211,7 @@
         <v>0.0</v>
       </c>
       <c r="H20" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="42">
         <v>0.0</v>
@@ -5223,10 +5223,10 @@
         <v>0.0</v>
       </c>
       <c r="L20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M20" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="81">
         <v>0.0</v>
@@ -5235,43 +5235,43 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q20" s="82">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>2415</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="85" t="s">
         <v>90</v>
       </c>
       <c r="B21" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="81">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="D21" s="42">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="E21" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" s="42">
         <v>0.0</v>
       </c>
       <c r="H21" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I21" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J21" s="42">
         <v>0.0</v>
@@ -5299,24 +5299,24 @@
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>2160</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="86" t="s">
         <v>91</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" s="81">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="D22" s="42">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="E22" s="42">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="F22" s="42">
         <v>0.0</v>
@@ -5325,7 +5325,7 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I22" s="80">
         <v>0.0</v>
@@ -5349,14 +5349,14 @@
         <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>2160</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="23">
@@ -5364,94 +5364,94 @@
         <v>92</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C23" s="81">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="D23" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="E23" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="F23" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q23" s="82">
         <v>20.0</v>
-      </c>
-      <c r="E23" s="42">
-        <v>13.0</v>
-      </c>
-      <c r="F23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="80">
-        <v>1.0</v>
-      </c>
-      <c r="I23" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="K23" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M23" s="82">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q23" s="82">
-        <v>18.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>2070</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="81" t="s">
+      <c r="A24" s="77" t="s">
         <v>93</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C24" s="81">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D24" s="42">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="E24" s="42">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="F24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" s="42">
         <v>0.0</v>
       </c>
       <c r="H24" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="42">
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="81">
         <v>0.0</v>
       </c>
       <c r="L24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M24" s="82">
         <v>0.0</v>
@@ -5466,28 +5466,28 @@
         <v>1.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>1950</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="s">
+      <c r="A25" s="81" t="s">
         <v>94</v>
       </c>
       <c r="B25" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="81">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="D25" s="42">
         <v>21.0</v>
       </c>
       <c r="E25" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F25" s="42">
         <v>1.0</v>
@@ -5508,7 +5508,7 @@
         <v>0.0</v>
       </c>
       <c r="L25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M25" s="82">
         <v>0.0</v>
@@ -5527,30 +5527,30 @@
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="88" t="s">
         <v>95</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="81">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="D26" s="42">
-        <v>10.0</v>
+        <v>21.0</v>
       </c>
       <c r="E26" s="42">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H26" s="80">
         <v>0.0</v>
@@ -5562,7 +5562,7 @@
         <v>0.0</v>
       </c>
       <c r="K26" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L26" s="42">
         <v>0.0</v>
@@ -5577,14 +5577,14 @@
         <v>0.0</v>
       </c>
       <c r="P26" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q26" s="82">
         <v>20.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1920</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="27">
@@ -5592,25 +5592,25 @@
         <v>96</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C27" s="81">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="D27" s="42">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E27" s="42">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
       </c>
       <c r="G27" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I27" s="42">
         <v>0.0</v>
@@ -5619,7 +5619,7 @@
         <v>0.0</v>
       </c>
       <c r="K27" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L27" s="42">
         <v>0.0</v>
@@ -5634,14 +5634,14 @@
         <v>0.0</v>
       </c>
       <c r="P27" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q27" s="82">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>2145</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="28">
@@ -5865,11 +5865,11 @@
         <v>1.0</v>
       </c>
       <c r="Q31" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>1140</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="32">
@@ -5922,11 +5922,11 @@
         <v>3.0</v>
       </c>
       <c r="Q32" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>1020</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="33">
@@ -5937,10 +5937,10 @@
         <v>36</v>
       </c>
       <c r="C33" s="81">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D33" s="42">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E33" s="42">
         <v>1.0</v>
@@ -5979,11 +5979,11 @@
         <v>2.0</v>
       </c>
       <c r="Q33" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>870</v>
+        <v>915</v>
       </c>
     </row>
     <row r="34">
@@ -6036,11 +6036,11 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="93">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R34" s="83">
         <f t="shared" si="2"/>
-        <v>630</v>
+        <v>660</v>
       </c>
     </row>
     <row r="35">
@@ -6150,11 +6150,11 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="97">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R36" s="98">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 6/5/2026</t>
+    <t>Actualización: 7/17/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -140,24 +140,27 @@
     <t>Ramirez, Santiago</t>
   </si>
   <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
-    <t>Done, Carlos</t>
+    <t>Marcano, Jose</t>
   </si>
   <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Marcano, Jose</t>
-  </si>
-  <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
+    <t>Genao, Jhostin</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
@@ -173,24 +176,21 @@
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Pereira, Raul</t>
+  </si>
+  <si>
+    <t>Rodriguez, Victor</t>
+  </si>
+  <si>
     <t>Ortiz Jr, David</t>
   </si>
   <si>
-    <t>Pereira, Raul</t>
-  </si>
-  <si>
-    <t>Genao, Jhostin</t>
-  </si>
-  <si>
-    <t>Rodriguez, Victor</t>
+    <t>Chavez, Jesus</t>
   </si>
   <si>
     <t>Colina, Felix</t>
   </si>
   <si>
-    <t>Chavez, Jesus</t>
-  </si>
-  <si>
     <t>Mosqueda, Juan</t>
   </si>
   <si>
@@ -242,12 +242,12 @@
     <t>Medina, Juan</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
     <t>Colmenares, Kevin</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
-  </si>
-  <si>
     <t>Pineda, Frandel</t>
   </si>
   <si>
@@ -257,15 +257,15 @@
     <t>Santos, Aneudy</t>
   </si>
   <si>
+    <t>Gamez, Manuel</t>
+  </si>
+  <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
-    <t>Gamez, Manuel</t>
-  </si>
-  <si>
     <t>Peralta, Eddy</t>
   </si>
   <si>
@@ -275,34 +275,34 @@
     <t>Figuereo, Breyner</t>
   </si>
   <si>
+    <t>Alcantara, Jostin</t>
+  </si>
+  <si>
     <t>Encarnacion, Jefferson</t>
   </si>
   <si>
-    <t>Alcantara, Jostin</t>
-  </si>
-  <si>
     <t>Ramos, Daniel</t>
   </si>
   <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Fernandez, Jehiber</t>
+    <t>Castillo, Albert</t>
+  </si>
+  <si>
+    <t>Pena, Dariel</t>
   </si>
   <si>
     <t>Ballesteros, Jean</t>
   </si>
   <si>
-    <t>Castillo, Albert</t>
-  </si>
-  <si>
     <t>Acosta, Isaac</t>
   </si>
   <si>
     <t>Liriano, Edgar</t>
-  </si>
-  <si>
-    <t>Pena, Dariel</t>
   </si>
   <si>
     <t>Cordero, Albert</t>
@@ -1028,10 +1028,10 @@
     <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="32" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="32" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="32" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="32" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1578,10 +1578,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="D5" s="40">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="E5" s="40">
         <v>12.0</v>
@@ -1599,7 +1599,7 @@
         <v>33.0</v>
       </c>
       <c r="J5" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K5" s="41">
         <v>0.0</v>
@@ -1608,7 +1608,7 @@
         <v>11.0</v>
       </c>
       <c r="M5" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="N5" s="40">
         <v>4.0</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U37" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>4860</v>
+        <v>5100</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1653,19 +1653,19 @@
         <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="D6" s="40">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="E6" s="40">
         <v>13.0</v>
       </c>
       <c r="F6" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G6" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H6" s="40">
         <v>0.0</v>
@@ -1683,7 +1683,7 @@
         <v>5.0</v>
       </c>
       <c r="M6" s="40">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="N6" s="40">
         <v>2.0</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>4725</v>
+        <v>4890</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1731,7 +1731,7 @@
         <v>22.0</v>
       </c>
       <c r="D7" s="46">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E7" s="46">
         <v>12.0</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>4275</v>
+        <v>4215</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1806,7 +1806,7 @@
         <v>27.0</v>
       </c>
       <c r="D8" s="40">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E8" s="40">
         <v>1.0</v>
@@ -1821,7 +1821,7 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="41">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="J8" s="39">
         <v>2.0</v>
@@ -1839,7 +1839,7 @@
         <v>2.0</v>
       </c>
       <c r="O8" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P8" s="42">
         <v>0.0</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3720</v>
+        <v>3705</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1881,13 +1881,13 @@
         <v>21.0</v>
       </c>
       <c r="D9" s="40">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E9" s="40">
         <v>8.0</v>
       </c>
       <c r="F9" s="40">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G9" s="40">
         <v>7.0</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3600</v>
+        <v>3585</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -2028,10 +2028,10 @@
         <v>36</v>
       </c>
       <c r="C11" s="39">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="D11" s="40">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="E11" s="40">
         <v>5.0</v>
@@ -2076,14 +2076,14 @@
         <v>5.0</v>
       </c>
       <c r="S11" s="43">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T11" s="41">
         <v>19.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>3255</v>
+        <v>3300</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2181,7 +2181,7 @@
         <v>24.0</v>
       </c>
       <c r="D13" s="40">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="E13" s="40">
         <v>2.0</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2745</v>
+        <v>2715</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2259,7 +2259,7 @@
         <v>18.0</v>
       </c>
       <c r="E14" s="40">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F14" s="40">
         <v>2.0</v>
@@ -2289,7 +2289,7 @@
         <v>2.0</v>
       </c>
       <c r="O14" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P14" s="42">
         <v>1.0</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>2550</v>
+        <v>2595</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2321,69 +2321,69 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="50" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="39">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D15" s="40">
+        <v>39.0</v>
+      </c>
+      <c r="E15" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="F15" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="G15" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H15" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="41">
+        <v>6.0</v>
+      </c>
+      <c r="J15" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L15" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N15" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O15" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P15" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q15" s="39">
+        <v>14.0</v>
+      </c>
+      <c r="R15" s="40">
         <v>9.0</v>
       </c>
-      <c r="E15" s="40">
+      <c r="S15" s="43">
         <v>7.0</v>
-      </c>
-      <c r="F15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="H15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J15" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="M15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q15" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="R15" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="S15" s="43">
-        <v>4.0</v>
       </c>
       <c r="T15" s="41">
         <v>19.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2415</v>
+        <v>2550</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2396,69 +2396,69 @@
       <c r="AD15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C16" s="39">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="D16" s="40">
-        <v>37.0</v>
+        <v>10.0</v>
       </c>
       <c r="E16" s="40">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J16" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O16" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R16" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="S16" s="43">
         <v>5.0</v>
-      </c>
-      <c r="G16" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="41">
-        <v>5.0</v>
-      </c>
-      <c r="J16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N16" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O16" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P16" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="39">
-        <v>14.0</v>
-      </c>
-      <c r="R16" s="40">
-        <v>9.0</v>
-      </c>
-      <c r="S16" s="43">
-        <v>6.0</v>
       </c>
       <c r="T16" s="41">
         <v>19.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2370</v>
+        <v>2415</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2471,69 +2471,69 @@
       <c r="AD16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="49" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C17" s="39">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="D17" s="40">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
       <c r="E17" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F17" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="40">
         <v>2.0</v>
       </c>
-      <c r="F17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="40">
+      <c r="H17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="J17" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M17" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="N17" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P17" s="42">
         <v>3.0</v>
       </c>
-      <c r="H17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J17" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="M17" s="40">
-        <v>10.0</v>
-      </c>
-      <c r="N17" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="O17" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P17" s="42">
-        <v>0.0</v>
-      </c>
       <c r="Q17" s="39">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="R17" s="40">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="S17" s="43">
         <v>3.0</v>
       </c>
       <c r="T17" s="41">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>2310</v>
+        <v>2385</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2546,69 +2546,69 @@
       <c r="AD17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="37" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C18" s="39">
+        <v>15.0</v>
+      </c>
+      <c r="D18" s="40">
+        <v>20.0</v>
+      </c>
+      <c r="E18" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H18" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="41">
+        <v>3.0</v>
+      </c>
+      <c r="J18" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M18" s="40">
         <v>10.0</v>
       </c>
-      <c r="D18" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="E18" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="F18" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H18" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="J18" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M18" s="40">
-        <v>6.0</v>
-      </c>
       <c r="N18" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="O18" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P18" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q18" s="39">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="R18" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="S18" s="43">
         <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>2205</v>
+        <v>2220</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2628,7 +2628,7 @@
         <v>30</v>
       </c>
       <c r="C19" s="39">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D19" s="40">
         <v>7.0</v>
@@ -2637,7 +2637,7 @@
         <v>4.0</v>
       </c>
       <c r="F19" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G19" s="40">
         <v>0.0</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>2040</v>
+        <v>2160</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2751,14 +2751,14 @@
         <v>6.0</v>
       </c>
       <c r="S20" s="43">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T20" s="41">
         <v>19.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1950</v>
+        <v>1980</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2774,44 +2774,44 @@
       <c r="A21" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="38" t="s">
-        <v>36</v>
+      <c r="B21" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C21" s="39">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="D21" s="40">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="E21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="F21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G21" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="I21" s="41">
+        <v>9.0</v>
+      </c>
+      <c r="J21" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L21" s="39">
         <v>5.0</v>
       </c>
-      <c r="F21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H21" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L21" s="39">
-        <v>12.0</v>
-      </c>
       <c r="M21" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N21" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O21" s="40">
         <v>1.0</v>
@@ -2820,20 +2820,20 @@
         <v>0.0</v>
       </c>
       <c r="Q21" s="39">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="R21" s="40">
         <v>5.0</v>
       </c>
       <c r="S21" s="43">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T21" s="41">
         <v>19.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1905</v>
+        <v>1920</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2849,56 +2849,56 @@
       <c r="A22" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="39">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="D22" s="40">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="E22" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F22" s="40">
         <v>0.0</v>
       </c>
       <c r="G22" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="40">
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L22" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="M22" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q22" s="39">
         <v>7.0</v>
       </c>
-      <c r="J22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P22" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q22" s="39">
-        <v>8.0</v>
-      </c>
       <c r="R22" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S22" s="43">
         <v>6.0</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1785</v>
+        <v>1905</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2921,33 +2921,33 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="38" t="s">
-        <v>30</v>
+      <c r="B23" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C23" s="39">
+        <v>15.0</v>
+      </c>
+      <c r="D23" s="40">
+        <v>23.0</v>
+      </c>
+      <c r="E23" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H23" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="41">
         <v>8.0</v>
       </c>
-      <c r="D23" s="40">
-        <v>16.0</v>
-      </c>
-      <c r="E23" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="F23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J23" s="39">
         <v>0.0</v>
       </c>
@@ -2955,35 +2955,35 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
       </c>
       <c r="O23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P23" s="42">
         <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R23" s="40">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="S23" s="43">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="T23" s="41">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1770</v>
+        <v>1890</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -2996,23 +2996,23 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="37" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C24" s="39">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="D24" s="40">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E24" s="40">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" s="40">
         <v>1.0</v>
@@ -3021,7 +3021,7 @@
         <v>0.0</v>
       </c>
       <c r="I24" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J24" s="39">
         <v>0.0</v>
@@ -3033,28 +3033,28 @@
         <v>3.0</v>
       </c>
       <c r="M24" s="40">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="N24" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O24" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P24" s="42">
         <v>0.0</v>
       </c>
       <c r="Q24" s="39">
+        <v>10.0</v>
+      </c>
+      <c r="R24" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="S24" s="43">
         <v>4.0</v>
       </c>
-      <c r="R24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S24" s="43">
-        <v>5.0</v>
-      </c>
       <c r="T24" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
@@ -3071,69 +3071,69 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="51" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C25" s="39">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D25" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M25" s="40">
         <v>6.0</v>
       </c>
-      <c r="E25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
+      <c r="N25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="R25" s="40">
         <v>3.0</v>
       </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R25" s="40">
-        <v>7.0</v>
-      </c>
       <c r="S25" s="43">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T25" s="41">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1695</v>
+        <v>1770</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3153,26 +3153,26 @@
         <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="D26" s="40">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="F26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="41">
         <v>3.0</v>
       </c>
-      <c r="F26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J26" s="39">
         <v>0.0</v>
       </c>
@@ -3189,26 +3189,26 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P26" s="42">
         <v>0.0</v>
       </c>
       <c r="Q26" s="39">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="R26" s="40">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="S26" s="43">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T26" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1590</v>
+        <v>1695</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3299,66 +3299,66 @@
       <c r="A28" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="50" t="s">
-        <v>30</v>
+      <c r="B28" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="C28" s="39">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D28" s="40">
-        <v>23.0</v>
+        <v>7.0</v>
       </c>
       <c r="E28" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F28" s="40">
         <v>1.0</v>
       </c>
       <c r="G28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28" s="41">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="J28" s="39">
         <v>0.0</v>
       </c>
       <c r="K28" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L28" s="39">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O28" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P28" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="R28" s="40">
         <v>2.0</v>
       </c>
-      <c r="O28" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P28" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q28" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R28" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S28" s="43">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="T28" s="41">
         <v>19.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1575</v>
+        <v>1530</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3371,14 +3371,14 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="48" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C29" s="39">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D29" s="40">
         <v>7.0</v>
@@ -3387,53 +3387,53 @@
         <v>3.0</v>
       </c>
       <c r="F29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="40">
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J29" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P29" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q29" s="39">
         <v>2.0</v>
       </c>
-      <c r="J29" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M29" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N29" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O29" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P29" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q29" s="39">
+      <c r="R29" s="40">
         <v>4.0</v>
       </c>
-      <c r="R29" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S29" s="43">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="T29" s="41">
         <v>19.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3446,32 +3446,32 @@
       <c r="AD29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="49" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C30" s="39">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="D30" s="40">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="E30" s="40">
         <v>4.0</v>
       </c>
       <c r="F30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="40">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H30" s="40">
         <v>0.0</v>
       </c>
       <c r="I30" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J30" s="39">
         <v>0.0</v>
@@ -3483,13 +3483,13 @@
         <v>1.0</v>
       </c>
       <c r="M30" s="40">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="40">
         <v>0.0</v>
       </c>
       <c r="O30" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P30" s="42">
         <v>0.0</v>
@@ -3501,14 +3501,14 @@
         <v>1.0</v>
       </c>
       <c r="S30" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T30" s="41">
         <v>19.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1485</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3521,32 +3521,32 @@
       <c r="AD30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="51" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="39">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="D31" s="40">
-        <v>17.0</v>
+        <v>3.0</v>
       </c>
       <c r="E31" s="40">
         <v>4.0</v>
       </c>
       <c r="F31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G31" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H31" s="40">
         <v>0.0</v>
       </c>
       <c r="I31" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J31" s="39">
         <v>0.0</v>
@@ -3558,13 +3558,13 @@
         <v>1.0</v>
       </c>
       <c r="M31" s="40">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="N31" s="40">
         <v>0.0</v>
       </c>
       <c r="O31" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P31" s="42">
         <v>0.0</v>
@@ -3576,14 +3576,14 @@
         <v>1.0</v>
       </c>
       <c r="S31" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T31" s="41">
         <v>19.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1395</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3606,7 +3606,7 @@
         <v>5.0</v>
       </c>
       <c r="D32" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E32" s="40">
         <v>0.0</v>
@@ -3651,7 +3651,7 @@
         <v>5.0</v>
       </c>
       <c r="S32" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T32" s="41">
         <v>20.0</v>
@@ -3678,7 +3678,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D33" s="40">
         <v>3.0</v>
@@ -3708,7 +3708,7 @@
         <v>1.0</v>
       </c>
       <c r="M33" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="N33" s="40">
         <v>0.0</v>
@@ -3726,14 +3726,14 @@
         <v>0.0</v>
       </c>
       <c r="S33" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T33" s="41">
         <v>19.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>1125</v>
+        <v>1260</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3831,7 +3831,7 @@
         <v>4.0</v>
       </c>
       <c r="D35" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E35" s="40">
         <v>0.0</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>885</v>
+        <v>825</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -4341,13 +4341,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="81">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
       <c r="D5" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E5" s="42">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="F5" s="42">
         <v>1.0</v>
@@ -4365,7 +4365,7 @@
         <v>0.0</v>
       </c>
       <c r="K5" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L5" s="42">
         <v>1.0</v>
@@ -4387,33 +4387,33 @@
       </c>
       <c r="R5" s="83">
         <f t="shared" si="1"/>
-        <v>3945</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="78" t="s">
-        <v>36</v>
+      <c r="B6" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C6" s="81">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
       <c r="D6" s="42">
         <v>11.0</v>
       </c>
       <c r="E6" s="42">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="F6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I6" s="80">
         <v>0.0</v>
@@ -4422,13 +4422,13 @@
         <v>0.0</v>
       </c>
       <c r="K6" s="81">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L6" s="42">
         <v>1.0</v>
       </c>
       <c r="M6" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N6" s="81">
         <v>0.0</v>
@@ -4440,37 +4440,37 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3675</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>30</v>
+      <c r="B7" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C7" s="81">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="D7" s="42">
         <v>11.0</v>
       </c>
       <c r="E7" s="42">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="F7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H7" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="80">
         <v>0.0</v>
@@ -4479,13 +4479,13 @@
         <v>0.0</v>
       </c>
       <c r="K7" s="81">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L7" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M7" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N7" s="81">
         <v>0.0</v>
@@ -4497,11 +4497,11 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="82">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>3570</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="8">
@@ -4542,7 +4542,7 @@
         <v>0.0</v>
       </c>
       <c r="M8" s="82">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N8" s="81">
         <v>0.0</v>
@@ -4558,11 +4558,11 @@
       </c>
       <c r="R8" s="83">
         <f t="shared" si="1"/>
-        <v>3495</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="84" t="s">
         <v>78</v>
       </c>
       <c r="B9" s="78" t="s">
@@ -4676,17 +4676,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="77" t="s">
         <v>80</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C11" s="81">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="D11" s="42">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E11" s="42">
         <v>16.0</v>
@@ -4695,7 +4695,7 @@
         <v>1.0</v>
       </c>
       <c r="G11" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H11" s="80">
         <v>0.0</v>
@@ -4704,7 +4704,7 @@
         <v>0.0</v>
       </c>
       <c r="J11" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K11" s="81">
         <v>0.0</v>
@@ -4725,11 +4725,11 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="82">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="R11" s="83">
         <f t="shared" ref="R11:R36" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
-        <v>3390</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="12">
@@ -4737,34 +4737,34 @@
         <v>81</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C12" s="81">
-        <v>22.0</v>
+        <v>28.0</v>
       </c>
       <c r="D12" s="42">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="E12" s="42">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="F12" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="42">
         <v>0.0</v>
       </c>
       <c r="H12" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="80">
         <v>0.0</v>
       </c>
       <c r="J12" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="81">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L12" s="42">
         <v>0.0</v>
@@ -4779,40 +4779,40 @@
         <v>0.0</v>
       </c>
       <c r="P12" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q12" s="82">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="R12" s="83">
         <f t="shared" si="2"/>
-        <v>3120</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="84" t="s">
         <v>82</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C13" s="81">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="D13" s="42">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E13" s="42">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="F13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H13" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="80">
         <v>0.0</v>
@@ -4821,7 +4821,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="42">
         <v>0.0</v>
@@ -4836,14 +4836,14 @@
         <v>0.0</v>
       </c>
       <c r="P13" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>2940</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="14">
@@ -4911,13 +4911,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="81">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="D15" s="42">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="E15" s="42">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="F15" s="42">
         <v>0.0</v>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2820</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="16">
@@ -5018,32 +5018,32 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="86" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="81">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="D17" s="42">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E17" s="42">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="F17" s="42">
         <v>0.0</v>
       </c>
       <c r="G17" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I17" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J17" s="42">
         <v>0.0</v>
@@ -5071,36 +5071,36 @@
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>2595</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="84" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="81">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="D18" s="42">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="E18" s="42">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="F18" s="42">
         <v>0.0</v>
       </c>
       <c r="G18" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>2580</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="19">
@@ -5192,14 +5192,14 @@
       <c r="A20" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="78" t="s">
-        <v>36</v>
+      <c r="B20" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="81">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="D20" s="42">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E20" s="42">
         <v>9.0</v>
@@ -5214,7 +5214,7 @@
         <v>1.0</v>
       </c>
       <c r="I20" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J20" s="42">
         <v>0.0</v>
@@ -5235,28 +5235,28 @@
         <v>0.0</v>
       </c>
       <c r="P20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="82">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>2340</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="42" t="s">
-        <v>30</v>
+      <c r="B21" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C21" s="81">
         <v>21.0</v>
       </c>
       <c r="D21" s="42">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="E21" s="42">
         <v>9.0</v>
@@ -5271,7 +5271,7 @@
         <v>1.0</v>
       </c>
       <c r="I21" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J21" s="42">
         <v>0.0</v>
@@ -5292,40 +5292,40 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>2280</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="77" t="s">
         <v>91</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C22" s="81">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D22" s="42">
+        <v>9.0</v>
+      </c>
+      <c r="E22" s="42">
         <v>8.0</v>
       </c>
-      <c r="E22" s="42">
-        <v>11.0</v>
-      </c>
       <c r="F22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="42">
         <v>0.0</v>
       </c>
       <c r="H22" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I22" s="80">
         <v>0.0</v>
@@ -5352,28 +5352,28 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>2175</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="s">
+      <c r="A23" s="88" t="s">
         <v>92</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="81">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="D23" s="42">
-        <v>7.0</v>
+        <v>24.0</v>
       </c>
       <c r="E23" s="42">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F23" s="42">
         <v>1.0</v>
@@ -5406,31 +5406,31 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q23" s="82">
         <v>20.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>2160</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="86" t="s">
         <v>93</v>
       </c>
       <c r="B24" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="81">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="D24" s="42">
-        <v>20.0</v>
+        <v>8.0</v>
       </c>
       <c r="E24" s="42">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5445,7 +5445,7 @@
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="81">
         <v>0.0</v>
@@ -5463,52 +5463,52 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="82">
         <v>19.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>2100</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="77" t="s">
         <v>94</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C25" s="81">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="D25" s="42">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="E25" s="42">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="F25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" s="42">
         <v>0.0</v>
       </c>
       <c r="H25" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I25" s="42">
         <v>0.0</v>
       </c>
       <c r="J25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K25" s="81">
         <v>0.0</v>
       </c>
       <c r="L25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M25" s="82">
         <v>0.0</v>
@@ -5523,28 +5523,28 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>1950</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="81" t="s">
         <v>95</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="81">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="D26" s="42">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="E26" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F26" s="42">
         <v>1.0</v>
@@ -5565,7 +5565,7 @@
         <v>0.0</v>
       </c>
       <c r="L26" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M26" s="82">
         <v>0.0</v>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="27">
@@ -5702,20 +5702,20 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="85" t="s">
+      <c r="A29" s="84" t="s">
         <v>98</v>
       </c>
       <c r="B29" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="81">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D29" s="42">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E29" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F29" s="42">
         <v>0.0</v>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1380</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="30">
@@ -5769,7 +5769,7 @@
         <v>11.0</v>
       </c>
       <c r="D30" s="42">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="E30" s="42">
         <v>6.0</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>1305</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="31">
@@ -5823,13 +5823,13 @@
         <v>36</v>
       </c>
       <c r="C31" s="81">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D31" s="42">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="E31" s="42">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F31" s="42">
         <v>0.0</v>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="32">
@@ -6108,13 +6108,13 @@
         <v>36</v>
       </c>
       <c r="C36" s="95">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D36" s="54">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E36" s="54">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F36" s="54">
         <v>0.0</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="R36" s="98">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 7/17/2026</t>
+    <t>Actualización: 7/20/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -122,27 +122,27 @@
     <t>Rosario, Elian</t>
   </si>
   <si>
+    <t>Castillo, Wesly</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Castillo, Wesly</t>
-  </si>
-  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
+    <t>Done, Carlos</t>
+  </si>
+  <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
-    <t>Done, Carlos</t>
-  </si>
-  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
@@ -155,10 +155,13 @@
     <t>Valdes, Abel</t>
   </si>
   <si>
+    <t>Genao, Jhostin</t>
+  </si>
+  <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
-    <t>Genao, Jhostin</t>
+    <t>Alarcon, Rosnel</t>
   </si>
   <si>
     <t>Abreu, Ariel</t>
@@ -173,9 +176,6 @@
     <t>Montero, Darling</t>
   </si>
   <si>
-    <t>Alarcon, Rosnel</t>
-  </si>
-  <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
@@ -242,10 +242,13 @@
     <t>Medina, Juan</t>
   </si>
   <si>
+    <t>Colmenares, Kevin</t>
+  </si>
+  <si>
     <t>Roquez, Yadiel</t>
   </si>
   <si>
-    <t>Colmenares, Kevin</t>
+    <t>Santos, Aneudy</t>
   </si>
   <si>
     <t>Pineda, Frandel</t>
@@ -254,19 +257,19 @@
     <t>Gomez, Manuel</t>
   </si>
   <si>
-    <t>Santos, Aneudy</t>
-  </si>
-  <si>
     <t>Gamez, Manuel</t>
   </si>
   <si>
     <t>Fukuda, Masahiro</t>
   </si>
   <si>
+    <t>Peralta, Eddy</t>
+  </si>
+  <si>
     <t>Dolsi, Frederik</t>
   </si>
   <si>
-    <t>Peralta, Eddy</t>
+    <t>Encarnacion, Jefferson</t>
   </si>
   <si>
     <t>Lara, Carlos</t>
@@ -276,9 +279,6 @@
   </si>
   <si>
     <t>Alcantara, Jostin</t>
-  </si>
-  <si>
-    <t>Encarnacion, Jefferson</t>
   </si>
   <si>
     <t>Ramos, Daniel</t>
@@ -1028,10 +1028,10 @@
     <xf borderId="33" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="32" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="32" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="32" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1578,13 +1578,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="39">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="D5" s="40">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="E5" s="40">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F5" s="40">
         <v>7.0</v>
@@ -1596,7 +1596,7 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="41">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="J5" s="39">
         <v>2.0</v>
@@ -1605,7 +1605,7 @@
         <v>0.0</v>
       </c>
       <c r="L5" s="39">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="M5" s="40">
         <v>8.0</v>
@@ -1620,7 +1620,7 @@
         <v>0.0</v>
       </c>
       <c r="Q5" s="39">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R5" s="40">
         <v>8.0</v>
@@ -1629,11 +1629,11 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U37" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>5100</v>
+        <v>5400</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1653,10 +1653,10 @@
         <v>30</v>
       </c>
       <c r="C6" s="39">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="D6" s="40">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="E6" s="40">
         <v>13.0</v>
@@ -1695,7 +1695,7 @@
         <v>0.0</v>
       </c>
       <c r="Q6" s="39">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R6" s="40">
         <v>9.0</v>
@@ -1704,11 +1704,11 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>4890</v>
+        <v>4965</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1737,7 +1737,7 @@
         <v>12.0</v>
       </c>
       <c r="F7" s="46">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G7" s="46">
         <v>3.0</v>
@@ -1770,7 +1770,7 @@
         <v>0.0</v>
       </c>
       <c r="Q7" s="39">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R7" s="40">
         <v>10.0</v>
@@ -1779,11 +1779,11 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>4215</v>
+        <v>4320</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1803,7 +1803,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="39">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="D8" s="40">
         <v>15.0</v>
@@ -1845,7 +1845,7 @@
         <v>0.0</v>
       </c>
       <c r="Q8" s="39">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="R8" s="40">
         <v>9.0</v>
@@ -1854,11 +1854,11 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U8" s="44">
         <f t="shared" si="1"/>
-        <v>3705</v>
+        <v>3915</v>
       </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
@@ -1884,10 +1884,10 @@
         <v>17.0</v>
       </c>
       <c r="E9" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F9" s="40">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G9" s="40">
         <v>7.0</v>
@@ -1920,7 +1920,7 @@
         <v>0.0</v>
       </c>
       <c r="Q9" s="39">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R9" s="40">
         <v>7.0</v>
@@ -1929,11 +1929,11 @@
         <v>5.0</v>
       </c>
       <c r="T9" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3585</v>
+        <v>3750</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1953,62 +1953,62 @@
         <v>36</v>
       </c>
       <c r="C10" s="39">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="D10" s="40">
-        <v>9.0</v>
+        <v>28.0</v>
       </c>
       <c r="E10" s="40">
+        <v>6.0</v>
+      </c>
+      <c r="F10" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="41">
+        <v>11.0</v>
+      </c>
+      <c r="J10" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="K10" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="M10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O10" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q10" s="39">
         <v>7.0</v>
-      </c>
-      <c r="F10" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G10" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="H10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="J10" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="L10" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q10" s="39">
-        <v>6.0</v>
       </c>
       <c r="R10" s="40">
         <v>6.0</v>
       </c>
       <c r="S10" s="43">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="T10" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3420</v>
+        <v>3495</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2028,35 +2028,35 @@
         <v>36</v>
       </c>
       <c r="C11" s="39">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="D11" s="40">
-        <v>27.0</v>
+        <v>9.0</v>
       </c>
       <c r="E11" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F11" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G11" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="J11" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="L11" s="39">
         <v>3.0</v>
       </c>
-      <c r="H11" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="41">
-        <v>11.0</v>
-      </c>
-      <c r="J11" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="K11" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="39">
-        <v>1.0</v>
-      </c>
       <c r="M11" s="40">
         <v>0.0</v>
       </c>
@@ -2070,20 +2070,20 @@
         <v>0.0</v>
       </c>
       <c r="Q11" s="39">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="R11" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S11" s="43">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="T11" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>3300</v>
+        <v>3450</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2106,7 +2106,7 @@
         <v>29.0</v>
       </c>
       <c r="D12" s="40">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="E12" s="40">
         <v>3.0</v>
@@ -2148,17 +2148,17 @@
         <v>7.0</v>
       </c>
       <c r="R12" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S12" s="43">
         <v>7.0</v>
       </c>
       <c r="T12" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>3120</v>
+        <v>3090</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2171,23 +2171,23 @@
       <c r="AD12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="48" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C13" s="39">
-        <v>24.0</v>
+        <v>18.0</v>
       </c>
       <c r="D13" s="40">
-        <v>28.0</v>
+        <v>39.0</v>
       </c>
       <c r="E13" s="40">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F13" s="40">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G13" s="40">
         <v>3.0</v>
@@ -2196,19 +2196,19 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="J13" s="39">
         <v>0.0</v>
       </c>
       <c r="K13" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" s="40">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="N13" s="40">
         <v>1.0</v>
@@ -2220,20 +2220,20 @@
         <v>0.0</v>
       </c>
       <c r="Q13" s="39">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="R13" s="40">
         <v>10.0</v>
       </c>
       <c r="S13" s="43">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="T13" s="41">
         <v>20.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2715</v>
+        <v>2865</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2246,69 +2246,69 @@
       <c r="AD13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="39">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
       <c r="D14" s="40">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="E14" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F14" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G14" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="H14" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="41">
+        <v>9.0</v>
+      </c>
+      <c r="J14" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M14" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="N14" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O14" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P14" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q14" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R14" s="40">
         <v>10.0</v>
       </c>
-      <c r="F14" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="G14" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H14" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="M14" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N14" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="O14" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P14" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="Q14" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="R14" s="40">
-        <v>7.0</v>
-      </c>
       <c r="S14" s="43">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T14" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="1"/>
-        <v>2595</v>
+        <v>2745</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
@@ -2321,69 +2321,69 @@
       <c r="AD14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="50" t="s">
-        <v>36</v>
+      <c r="B15" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="39">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="D15" s="40">
-        <v>39.0</v>
+        <v>19.0</v>
       </c>
       <c r="E15" s="40">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="F15" s="40">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H15" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L15" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="M15" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="N15" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="O15" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P15" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="Q15" s="39">
+        <v>13.0</v>
+      </c>
+      <c r="R15" s="40">
+        <v>7.0</v>
+      </c>
+      <c r="S15" s="43">
         <v>3.0</v>
       </c>
-      <c r="H15" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="41">
-        <v>6.0</v>
-      </c>
-      <c r="J15" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="L15" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M15" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="N15" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="O15" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="P15" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q15" s="39">
-        <v>14.0</v>
-      </c>
-      <c r="R15" s="40">
-        <v>9.0</v>
-      </c>
-      <c r="S15" s="43">
-        <v>7.0</v>
-      </c>
       <c r="T15" s="41">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2550</v>
+        <v>2685</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2403,7 +2403,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="39">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D16" s="40">
         <v>10.0</v>
@@ -2448,17 +2448,17 @@
         <v>7.0</v>
       </c>
       <c r="R16" s="40">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S16" s="43">
         <v>5.0</v>
       </c>
       <c r="T16" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2415</v>
+        <v>2550</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2529,11 +2529,11 @@
         <v>3.0</v>
       </c>
       <c r="T17" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>2385</v>
+        <v>2415</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2604,11 +2604,11 @@
         <v>3.0</v>
       </c>
       <c r="T18" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>2220</v>
+        <v>2250</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2679,11 +2679,11 @@
         <v>1.0</v>
       </c>
       <c r="T19" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>2160</v>
+        <v>2190</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2699,44 +2699,44 @@
       <c r="A20" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>36</v>
+      <c r="B20" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="39">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="D20" s="40">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="E20" s="40">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F20" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G20" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H20" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="41">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="J20" s="39">
         <v>0.0</v>
       </c>
       <c r="K20" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L20" s="39">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="M20" s="40">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="40">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O20" s="40">
         <v>1.0</v>
@@ -2748,17 +2748,17 @@
         <v>7.0</v>
       </c>
       <c r="R20" s="40">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="S20" s="43">
         <v>6.0</v>
       </c>
       <c r="T20" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>1980</v>
+        <v>2145</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2774,44 +2774,44 @@
       <c r="A21" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="50" t="s">
-        <v>30</v>
+      <c r="B21" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="C21" s="39">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="D21" s="40">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="E21" s="40">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F21" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H21" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21" s="41">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="J21" s="39">
         <v>0.0</v>
       </c>
       <c r="K21" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L21" s="39">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="M21" s="40">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="N21" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O21" s="40">
         <v>1.0</v>
@@ -2820,20 +2820,20 @@
         <v>0.0</v>
       </c>
       <c r="Q21" s="39">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R21" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S21" s="43">
         <v>6.0</v>
       </c>
       <c r="T21" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>2115</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2846,23 +2846,23 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="48" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C22" s="39">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="D22" s="40">
-        <v>25.0</v>
+        <v>6.0</v>
       </c>
       <c r="E22" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="40">
         <v>1.0</v>
@@ -2871,19 +2871,19 @@
         <v>0.0</v>
       </c>
       <c r="I22" s="41">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="J22" s="39">
         <v>0.0</v>
       </c>
       <c r="K22" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L22" s="39">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="M22" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="40">
         <v>0.0</v>
@@ -2898,17 +2898,17 @@
         <v>7.0</v>
       </c>
       <c r="R22" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S22" s="43">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="T22" s="41">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1905</v>
+        <v>1980</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2924,41 +2924,41 @@
       <c r="A23" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="39">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D23" s="40">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="E23" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="40">
         <v>0.0</v>
       </c>
       <c r="G23" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H23" s="40">
         <v>0.0</v>
       </c>
       <c r="I23" s="41">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="J23" s="39">
         <v>0.0</v>
       </c>
       <c r="K23" s="41">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L23" s="39">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="M23" s="40">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
@@ -2970,20 +2970,20 @@
         <v>0.0</v>
       </c>
       <c r="Q23" s="39">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="R23" s="40">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S23" s="43">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="T23" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1890</v>
+        <v>1935</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -2996,33 +2996,33 @@
       <c r="AD23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>30</v>
+      <c r="B24" s="50" t="s">
+        <v>36</v>
       </c>
       <c r="C24" s="39">
+        <v>15.0</v>
+      </c>
+      <c r="D24" s="40">
+        <v>23.0</v>
+      </c>
+      <c r="E24" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="F24" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="H24" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="41">
         <v>8.0</v>
       </c>
-      <c r="D24" s="40">
-        <v>16.0</v>
-      </c>
-      <c r="E24" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="F24" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H24" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="41">
-        <v>0.0</v>
-      </c>
       <c r="J24" s="39">
         <v>0.0</v>
       </c>
@@ -3030,35 +3030,35 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="39">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="M24" s="40">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="40">
         <v>0.0</v>
       </c>
       <c r="O24" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P24" s="42">
         <v>0.0</v>
       </c>
       <c r="Q24" s="39">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="R24" s="40">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="S24" s="43">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="T24" s="41">
         <v>20.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1770</v>
+        <v>1920</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3071,23 +3071,23 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="37" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C25" s="39">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="D25" s="40">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="E25" s="40">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F25" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" s="40">
         <v>1.0</v>
@@ -3096,7 +3096,7 @@
         <v>0.0</v>
       </c>
       <c r="I25" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J25" s="39">
         <v>0.0</v>
@@ -3108,32 +3108,32 @@
         <v>3.0</v>
       </c>
       <c r="M25" s="40">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="N25" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O25" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P25" s="42">
         <v>0.0</v>
       </c>
       <c r="Q25" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R25" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="S25" s="43">
         <v>4.0</v>
       </c>
-      <c r="R25" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S25" s="43">
-        <v>5.0</v>
-      </c>
       <c r="T25" s="41">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1770</v>
+        <v>1845</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3146,69 +3146,69 @@
       <c r="AD25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="51" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C26" s="39">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D26" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E26" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="41">
+        <v>4.0</v>
+      </c>
+      <c r="J26" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="M26" s="40">
         <v>6.0</v>
       </c>
-      <c r="E26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="F26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="41">
+      <c r="N26" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="O26" s="40">
+        <v>2.0</v>
+      </c>
+      <c r="P26" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q26" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="R26" s="40">
         <v>3.0</v>
       </c>
-      <c r="J26" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P26" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q26" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="R26" s="40">
-        <v>7.0</v>
-      </c>
       <c r="S26" s="43">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T26" s="41">
         <v>20.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1695</v>
+        <v>1800</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3228,10 +3228,10 @@
         <v>36</v>
       </c>
       <c r="C27" s="39">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="D27" s="40">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="E27" s="40">
         <v>2.0</v>
@@ -3273,17 +3273,17 @@
         <v>7.0</v>
       </c>
       <c r="R27" s="40">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S27" s="43">
         <v>3.0</v>
       </c>
       <c r="T27" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1590</v>
+        <v>1740</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3354,11 +3354,11 @@
         <v>2.0</v>
       </c>
       <c r="T28" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1560</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3429,11 +3429,11 @@
         <v>1.0</v>
       </c>
       <c r="T29" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1530</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3456,7 +3456,7 @@
         <v>12.0</v>
       </c>
       <c r="D30" s="40">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E30" s="40">
         <v>4.0</v>
@@ -3498,17 +3498,17 @@
         <v>5.0</v>
       </c>
       <c r="R30" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S30" s="43">
         <v>3.0</v>
       </c>
       <c r="T30" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1485</v>
+        <v>1515</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3531,7 +3531,7 @@
         <v>3.0</v>
       </c>
       <c r="D31" s="40">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E31" s="40">
         <v>4.0</v>
@@ -3555,7 +3555,7 @@
         <v>0.0</v>
       </c>
       <c r="L31" s="39">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M31" s="40">
         <v>8.0</v>
@@ -3573,17 +3573,17 @@
         <v>5.0</v>
       </c>
       <c r="R31" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S31" s="43">
         <v>3.0</v>
       </c>
       <c r="T31" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1380</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3729,11 +3729,11 @@
         <v>3.0</v>
       </c>
       <c r="T33" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1290</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3756,10 +3756,10 @@
         <v>4.0</v>
       </c>
       <c r="D34" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E34" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F34" s="40">
         <v>2.0</v>
@@ -3798,17 +3798,17 @@
         <v>3.0</v>
       </c>
       <c r="R34" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S34" s="43">
         <v>2.0</v>
       </c>
       <c r="T34" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1080</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3879,11 +3879,11 @@
         <v>2.0</v>
       </c>
       <c r="T35" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U35" s="44">
         <f t="shared" si="1"/>
-        <v>825</v>
+        <v>855</v>
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
@@ -3954,11 +3954,11 @@
         <v>0.0</v>
       </c>
       <c r="T36" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U36" s="44">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -4029,11 +4029,11 @@
         <v>1.0</v>
       </c>
       <c r="T37" s="41">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="U37" s="44">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
@@ -4049,8 +4049,8 @@
   <autoFilter ref="$A$4:$U$37">
     <sortState ref="A4:U37">
       <sortCondition descending="1" ref="U4:U37"/>
+      <sortCondition descending="1" ref="B4:B37"/>
       <sortCondition descending="1" ref="O4:O37"/>
-      <sortCondition ref="B4:B37"/>
       <sortCondition descending="1" ref="G4:G37"/>
       <sortCondition ref="A4:A37"/>
       <sortCondition descending="1" ref="F4:F37"/>
@@ -4326,11 +4326,11 @@
         <v>0.0</v>
       </c>
       <c r="Q4" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R4" s="83">
-        <f t="shared" ref="R4:R9" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
-        <v>5025</v>
+        <f t="shared" ref="R4:R7" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <v>5055</v>
       </c>
     </row>
     <row r="5">
@@ -4383,52 +4383,52 @@
         <v>1.0</v>
       </c>
       <c r="Q5" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R5" s="83">
         <f t="shared" si="1"/>
-        <v>4800</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="42" t="s">
-        <v>30</v>
+      <c r="B6" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C6" s="81">
-        <v>25.0</v>
+        <v>34.0</v>
       </c>
       <c r="D6" s="42">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E6" s="42">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="F6" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H6" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I6" s="80">
         <v>0.0</v>
       </c>
       <c r="J6" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K6" s="81">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L6" s="42">
         <v>1.0</v>
       </c>
       <c r="M6" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N6" s="81">
         <v>0.0</v>
@@ -4440,37 +4440,37 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>3750</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="78" t="s">
-        <v>36</v>
+      <c r="B7" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C7" s="81">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="D7" s="42">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E7" s="42">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
       <c r="F7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G7" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H7" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I7" s="80">
         <v>0.0</v>
@@ -4479,13 +4479,13 @@
         <v>0.0</v>
       </c>
       <c r="K7" s="81">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="42">
         <v>1.0</v>
       </c>
       <c r="M7" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N7" s="81">
         <v>0.0</v>
@@ -4497,86 +4497,86 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="82">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="R7" s="83">
         <f t="shared" si="1"/>
-        <v>3675</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="86" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="81">
+        <v>35.0</v>
+      </c>
+      <c r="D8" s="42">
+        <v>17.0</v>
+      </c>
+      <c r="E8" s="42">
+        <v>19.0</v>
+      </c>
+      <c r="F8" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="80">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="81">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="Q8" s="82">
+        <v>20.0</v>
+      </c>
+      <c r="R8" s="83">
+        <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="81">
         <v>23.0</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D9" s="42">
         <v>11.0</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E9" s="42">
         <v>18.0</v>
       </c>
-      <c r="F8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="80">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="80">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="L8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="82">
-        <v>2.0</v>
-      </c>
-      <c r="N8" s="81">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="Q8" s="82">
-        <v>19.0</v>
-      </c>
-      <c r="R8" s="83">
-        <f t="shared" si="1"/>
-        <v>3675</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="81">
-        <v>26.0</v>
-      </c>
-      <c r="D9" s="42">
-        <v>10.0</v>
-      </c>
-      <c r="E9" s="42">
-        <v>16.0</v>
-      </c>
       <c r="F9" s="42">
         <v>0.0</v>
       </c>
@@ -4587,19 +4587,19 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="80">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J9" s="42">
         <v>0.0</v>
       </c>
       <c r="K9" s="81">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L9" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="82">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N9" s="81">
         <v>0.0</v>
@@ -4608,28 +4608,28 @@
         <v>0.0</v>
       </c>
       <c r="P9" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q9" s="82">
         <v>20.0</v>
       </c>
       <c r="R9" s="83">
-        <f t="shared" si="1"/>
-        <v>3450</v>
+        <f t="shared" ref="R9:R36" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
+        <v>3705</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>36</v>
+      <c r="B10" s="78" t="s">
+        <v>30</v>
       </c>
       <c r="C10" s="81">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
       <c r="D10" s="42">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E10" s="42">
         <v>16.0</v>
@@ -4644,7 +4644,7 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="80">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J10" s="42">
         <v>0.0</v>
@@ -4653,7 +4653,7 @@
         <v>0.0</v>
       </c>
       <c r="L10" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M10" s="82">
         <v>0.0</v>
@@ -4665,14 +4665,14 @@
         <v>0.0</v>
       </c>
       <c r="P10" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q10" s="82">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="R10" s="83">
-        <f>C10*$C$2+D10*$D$2+E10*$E$2+F10*$F$2+G10*$G$2+H10*$H$2+K10*$K$2+L10*$L$2+M10*$M$2+N10*$N$2+O10*$O$2+P10*$P$2+Q10*$Q$2</f>
-        <v>3420</v>
+        <f t="shared" si="2"/>
+        <v>3480</v>
       </c>
     </row>
     <row r="11">
@@ -4725,15 +4725,15 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R11" s="83">
-        <f t="shared" ref="R11:R36" si="2">C11*$C$2+D11*$D$2+E11*$E$2+F11*$F$2+G11*$G$2+H11*$H$2+K11*$K$2+L11*$L$2+M11*$M$2+N11*$N$2+O11*$O$2+P11*$P$2+Q11*$Q$2+I11*$I$2+J11*$J$2</f>
-        <v>3405</v>
+        <f t="shared" si="2"/>
+        <v>3435</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="84" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="42" t="s">
@@ -4782,43 +4782,43 @@
         <v>1.0</v>
       </c>
       <c r="Q12" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R12" s="83">
         <f t="shared" si="2"/>
-        <v>3390</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="77" t="s">
         <v>82</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C13" s="81">
-        <v>22.0</v>
+        <v>28.0</v>
       </c>
       <c r="D13" s="42">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="E13" s="42">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="F13" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G13" s="42">
         <v>0.0</v>
       </c>
       <c r="H13" s="80">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I13" s="80">
         <v>0.0</v>
       </c>
       <c r="J13" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="81">
         <v>1.0</v>
@@ -4843,39 +4843,39 @@
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>3120</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="85" t="s">
         <v>83</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C14" s="81">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="D14" s="42">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E14" s="42">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
       <c r="F14" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="42">
         <v>0.0</v>
       </c>
       <c r="H14" s="80">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I14" s="80">
         <v>0.0</v>
       </c>
       <c r="J14" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K14" s="81">
         <v>1.0</v>
@@ -4896,34 +4896,34 @@
         <v>2.0</v>
       </c>
       <c r="Q14" s="82">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="R14" s="83">
         <f t="shared" si="2"/>
-        <v>2910</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="85" t="s">
         <v>84</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="81">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="D15" s="42">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E15" s="42">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="42">
         <v>0.0</v>
       </c>
       <c r="G15" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="80">
         <v>1.0</v>
@@ -4953,34 +4953,34 @@
         <v>1.0</v>
       </c>
       <c r="Q15" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R15" s="83">
         <f t="shared" si="2"/>
-        <v>2910</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="78" t="s">
-        <v>36</v>
+      <c r="B16" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="81">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="D16" s="42">
-        <v>8.0</v>
+        <v>18.0</v>
       </c>
       <c r="E16" s="42">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="F16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" s="80">
         <v>1.0</v>
@@ -4989,7 +4989,7 @@
         <v>0.0</v>
       </c>
       <c r="J16" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K16" s="81">
         <v>0.0</v>
@@ -5010,43 +5010,43 @@
         <v>1.0</v>
       </c>
       <c r="Q16" s="82">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="R16" s="83">
         <f t="shared" si="2"/>
-        <v>2790</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>30</v>
+      <c r="B17" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C17" s="81">
         <v>22.0</v>
       </c>
       <c r="D17" s="42">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E17" s="42">
-        <v>14.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K17" s="81">
         <v>0.0</v>
@@ -5071,36 +5071,36 @@
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>2610</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="86" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="81">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="D18" s="42">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E18" s="42">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="F18" s="42">
         <v>0.0</v>
       </c>
       <c r="G18" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H18" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J18" s="42">
         <v>0.0</v>
@@ -5124,11 +5124,11 @@
         <v>1.0</v>
       </c>
       <c r="Q18" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>2595</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="19">
@@ -5181,15 +5181,15 @@
         <v>3.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>2445</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="85" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
@@ -5238,15 +5238,15 @@
         <v>0.0</v>
       </c>
       <c r="Q20" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>2370</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="84" t="s">
         <v>90</v>
       </c>
       <c r="B21" s="78" t="s">
@@ -5295,11 +5295,11 @@
         <v>1.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>2340</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="22">
@@ -5352,11 +5352,11 @@
         <v>0.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>2250</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="23">
@@ -5409,11 +5409,11 @@
         <v>1.0</v>
       </c>
       <c r="Q23" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>2190</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="24">
@@ -5466,11 +5466,11 @@
         <v>0.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>2175</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="25">
@@ -5523,11 +5523,11 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>2100</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="26">
@@ -5580,11 +5580,11 @@
         <v>1.0</v>
       </c>
       <c r="Q26" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R26" s="83">
         <f t="shared" si="2"/>
-        <v>2070</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="27">
@@ -5601,7 +5601,7 @@
         <v>10.0</v>
       </c>
       <c r="E27" s="42">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F27" s="42">
         <v>0.0</v>
@@ -5637,11 +5637,11 @@
         <v>2.0</v>
       </c>
       <c r="Q27" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R27" s="83">
         <f t="shared" si="2"/>
-        <v>1920</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="28">
@@ -5694,15 +5694,15 @@
         <v>2.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
-        <v>1815</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="84" t="s">
+      <c r="A29" s="85" t="s">
         <v>98</v>
       </c>
       <c r="B29" s="42" t="s">
@@ -5751,11 +5751,11 @@
         <v>1.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="30">
@@ -5808,11 +5808,11 @@
         <v>0.0</v>
       </c>
       <c r="Q30" s="82">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>1245</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="31">
@@ -5865,11 +5865,11 @@
         <v>1.0</v>
       </c>
       <c r="Q31" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>1230</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="32">
@@ -5922,11 +5922,11 @@
         <v>3.0</v>
       </c>
       <c r="Q32" s="82">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="33">
@@ -5979,11 +5979,11 @@
         <v>2.0</v>
       </c>
       <c r="Q33" s="82">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>915</v>
+        <v>945</v>
       </c>
     </row>
     <row r="34">
@@ -6036,11 +6036,11 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="93">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R34" s="83">
         <f t="shared" si="2"/>
-        <v>660</v>
+        <v>690</v>
       </c>
     </row>
     <row r="35">
@@ -6093,11 +6093,11 @@
         <v>0.0</v>
       </c>
       <c r="Q35" s="93">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R35" s="83">
         <f t="shared" si="2"/>
-        <v>540</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36">
@@ -6150,11 +6150,11 @@
         <v>0.0</v>
       </c>
       <c r="Q36" s="97">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R36" s="98">
         <f t="shared" si="2"/>
-        <v>285</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -38,7 +38,7 @@
     <t>WEEKLY</t>
   </si>
   <si>
-    <t>Actualización: 7/20/2026</t>
+    <t>Actualización: 7/21/2026</t>
   </si>
   <si>
     <t>Players</t>
@@ -140,12 +140,12 @@
     <t>Gonzalez, Victor</t>
   </si>
   <si>
+    <t>Benitez, Frainker</t>
+  </si>
+  <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
-    <t>Benitez, Frainker</t>
-  </si>
-  <si>
     <t>Marcano, Jose</t>
   </si>
   <si>
@@ -161,33 +161,33 @@
     <t>Jaquez, Luis</t>
   </si>
   <si>
+    <t>Montero, Darling</t>
+  </si>
+  <si>
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Pinder, Jayln</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
-    <t>Pinder, Jayln</t>
-  </si>
-  <si>
     <t>Volquez, Fabelin</t>
   </si>
   <si>
-    <t>Montero, Darling</t>
-  </si>
-  <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
+    <t>Chavez, Jesus</t>
+  </si>
+  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
     <t>Ortiz Jr, David</t>
   </si>
   <si>
-    <t>Chavez, Jesus</t>
-  </si>
-  <si>
     <t>Colina, Felix</t>
   </si>
   <si>
@@ -275,13 +275,16 @@
     <t>Lara, Carlos</t>
   </si>
   <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
     <t>Figuereo, Breyner</t>
   </si>
   <si>
     <t>Alcantara, Jostin</t>
   </si>
   <si>
-    <t>Ramos, Daniel</t>
+    <t>Castillo, Albert</t>
   </si>
   <si>
     <t>Fernandez, Jehiber</t>
@@ -290,28 +293,25 @@
     <t>Granado, Argenis</t>
   </si>
   <si>
-    <t>Castillo, Albert</t>
+    <t>Ballesteros, Jean</t>
+  </si>
+  <si>
+    <t>Acosta, Isaac</t>
   </si>
   <si>
     <t>Pena, Dariel</t>
   </si>
   <si>
-    <t>Ballesteros, Jean</t>
-  </si>
-  <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
     <t>Liriano, Edgar</t>
   </si>
   <si>
     <t>Cordero, Albert</t>
   </si>
   <si>
+    <t>Lamu, Alex</t>
+  </si>
+  <si>
     <t>Perez, Juanangel</t>
-  </si>
-  <si>
-    <t>Lamu, Alex</t>
   </si>
   <si>
     <t>Figuereo, Enmanuel</t>
@@ -799,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1060,6 +1060,9 @@
     </xf>
     <xf borderId="34" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1581,7 +1584,7 @@
         <v>27.0</v>
       </c>
       <c r="D5" s="40">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="E5" s="40">
         <v>13.0</v>
@@ -1605,7 +1608,7 @@
         <v>0.0</v>
       </c>
       <c r="L5" s="39">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="M5" s="40">
         <v>8.0</v>
@@ -1633,7 +1636,7 @@
       </c>
       <c r="U5" s="44">
         <f t="shared" ref="U5:U37" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -1659,7 +1662,7 @@
         <v>25.0</v>
       </c>
       <c r="E6" s="40">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F6" s="40">
         <v>10.0</v>
@@ -1708,7 +1711,7 @@
       </c>
       <c r="U6" s="44">
         <f t="shared" si="1"/>
-        <v>4965</v>
+        <v>5025</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1734,7 +1737,7 @@
         <v>30.0</v>
       </c>
       <c r="E7" s="46">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F7" s="46">
         <v>14.0</v>
@@ -1746,7 +1749,7 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="47">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J7" s="39">
         <v>0.0</v>
@@ -1783,7 +1786,7 @@
       </c>
       <c r="U7" s="44">
         <f t="shared" si="1"/>
-        <v>4320</v>
+        <v>4410</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1795,7 +1798,7 @@
       <c r="AC7" s="9"/>
       <c r="AD7" s="9"/>
     </row>
-    <row r="8">
+    <row r="8" hidden="1">
       <c r="A8" s="48" t="s">
         <v>33</v>
       </c>
@@ -1881,7 +1884,7 @@
         <v>21.0</v>
       </c>
       <c r="D9" s="40">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="E9" s="40">
         <v>9.0</v>
@@ -1905,7 +1908,7 @@
         <v>0.0</v>
       </c>
       <c r="L9" s="39">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="M9" s="40">
         <v>2.0</v>
@@ -1933,7 +1936,7 @@
       </c>
       <c r="U9" s="44">
         <f t="shared" si="1"/>
-        <v>3750</v>
+        <v>3690</v>
       </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
@@ -1953,10 +1956,10 @@
         <v>36</v>
       </c>
       <c r="C10" s="39">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="D10" s="40">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="E10" s="40">
         <v>6.0</v>
@@ -1998,17 +2001,17 @@
         <v>7.0</v>
       </c>
       <c r="R10" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S10" s="43">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T10" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U10" s="44">
         <f t="shared" si="1"/>
-        <v>3495</v>
+        <v>3705</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -2079,11 +2082,11 @@
         <v>4.0</v>
       </c>
       <c r="T11" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="1"/>
-        <v>3450</v>
+        <v>3480</v>
       </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
@@ -2103,10 +2106,10 @@
         <v>36</v>
       </c>
       <c r="C12" s="39">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="D12" s="40">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="E12" s="40">
         <v>3.0</v>
@@ -2130,7 +2133,7 @@
         <v>0.0</v>
       </c>
       <c r="L12" s="39">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="M12" s="40">
         <v>17.0</v>
@@ -2148,17 +2151,17 @@
         <v>7.0</v>
       </c>
       <c r="R12" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S12" s="43">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T12" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U12" s="44">
         <f t="shared" si="1"/>
-        <v>3090</v>
+        <v>3225</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2178,10 +2181,10 @@
         <v>36</v>
       </c>
       <c r="C13" s="39">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="D13" s="40">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="E13" s="40">
         <v>8.0</v>
@@ -2196,7 +2199,7 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="41">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J13" s="39">
         <v>0.0</v>
@@ -2223,17 +2226,17 @@
         <v>14.0</v>
       </c>
       <c r="R13" s="40">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="S13" s="43">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T13" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U13" s="44">
         <f t="shared" si="1"/>
-        <v>2865</v>
+        <v>3105</v>
       </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
@@ -2325,28 +2328,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C15" s="39">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="D15" s="40">
-        <v>19.0</v>
+        <v>10.0</v>
       </c>
       <c r="E15" s="40">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="F15" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="40">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H15" s="40">
         <v>0.0</v>
       </c>
       <c r="I15" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J15" s="39">
         <v>0.0</v>
@@ -2355,35 +2358,35 @@
         <v>0.0</v>
       </c>
       <c r="L15" s="39">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M15" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="40">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O15" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="42">
         <v>1.0</v>
       </c>
       <c r="Q15" s="39">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="R15" s="40">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="S15" s="43">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T15" s="41">
         <v>21.0</v>
       </c>
       <c r="U15" s="44">
         <f t="shared" si="1"/>
-        <v>2685</v>
+        <v>2700</v>
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
@@ -2400,28 +2403,28 @@
         <v>42</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C16" s="39">
         <v>14.0</v>
       </c>
       <c r="D16" s="40">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="E16" s="40">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="F16" s="40">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H16" s="40">
         <v>0.0</v>
       </c>
       <c r="I16" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="39">
         <v>0.0</v>
@@ -2433,32 +2436,32 @@
         <v>4.0</v>
       </c>
       <c r="M16" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N16" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O16" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P16" s="42">
         <v>1.0</v>
       </c>
       <c r="Q16" s="39">
+        <v>13.0</v>
+      </c>
+      <c r="R16" s="40">
         <v>7.0</v>
       </c>
-      <c r="R16" s="40">
-        <v>5.0</v>
-      </c>
       <c r="S16" s="43">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="T16" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U16" s="44">
         <f t="shared" si="1"/>
-        <v>2550</v>
+        <v>2760</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -2529,11 +2532,11 @@
         <v>3.0</v>
       </c>
       <c r="T17" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="1"/>
-        <v>2415</v>
+        <v>2445</v>
       </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
@@ -2553,10 +2556,10 @@
         <v>30</v>
       </c>
       <c r="C18" s="39">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D18" s="40">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="E18" s="40">
         <v>2.0</v>
@@ -2608,7 +2611,7 @@
       </c>
       <c r="U18" s="44">
         <f t="shared" si="1"/>
-        <v>2250</v>
+        <v>2235</v>
       </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
@@ -2631,7 +2634,7 @@
         <v>8.0</v>
       </c>
       <c r="D19" s="40">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E19" s="40">
         <v>4.0</v>
@@ -2683,7 +2686,7 @@
       </c>
       <c r="U19" s="44">
         <f t="shared" si="1"/>
-        <v>2190</v>
+        <v>2160</v>
       </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
@@ -2709,7 +2712,7 @@
         <v>24.0</v>
       </c>
       <c r="E20" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F20" s="40">
         <v>1.0</v>
@@ -2721,7 +2724,7 @@
         <v>1.0</v>
       </c>
       <c r="I20" s="41">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="J20" s="39">
         <v>0.0</v>
@@ -2758,7 +2761,7 @@
       </c>
       <c r="U20" s="44">
         <f t="shared" si="1"/>
-        <v>2145</v>
+        <v>2235</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
@@ -2790,7 +2793,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H21" s="40">
         <v>0.0</v>
@@ -2811,7 +2814,7 @@
         <v>10.0</v>
       </c>
       <c r="N21" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O21" s="40">
         <v>1.0</v>
@@ -2829,11 +2832,11 @@
         <v>6.0</v>
       </c>
       <c r="T21" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
-        <v>2115</v>
+        <v>2190</v>
       </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
@@ -2846,69 +2849,69 @@
       <c r="AD21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="51" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" s="39">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D22" s="40">
+        <v>13.0</v>
+      </c>
+      <c r="E22" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G22" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="41">
+        <v>5.0</v>
+      </c>
+      <c r="J22" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="M22" s="40">
         <v>6.0</v>
       </c>
-      <c r="E22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="41">
-        <v>3.0</v>
-      </c>
-      <c r="J22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="40">
-        <v>0.0</v>
-      </c>
       <c r="N22" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O22" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P22" s="42">
         <v>0.0</v>
       </c>
       <c r="Q22" s="39">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="R22" s="40">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="S22" s="43">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T22" s="41">
         <v>21.0</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
-        <v>1980</v>
+        <v>2025</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -2921,23 +2924,23 @@
       <c r="AD22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="48" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C23" s="39">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="D23" s="40">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
       <c r="E23" s="40">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F23" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="40">
         <v>1.0</v>
@@ -2946,19 +2949,19 @@
         <v>0.0</v>
       </c>
       <c r="I23" s="41">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="J23" s="39">
         <v>0.0</v>
       </c>
       <c r="K23" s="41">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L23" s="39">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="40">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="40">
         <v>0.0</v>
@@ -2973,17 +2976,17 @@
         <v>7.0</v>
       </c>
       <c r="R23" s="40">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S23" s="43">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="T23" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
-        <v>1935</v>
+        <v>2055</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -3006,7 +3009,7 @@
         <v>15.0</v>
       </c>
       <c r="D24" s="40">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="E24" s="40">
         <v>2.0</v>
@@ -3048,17 +3051,17 @@
         <v>8.0</v>
       </c>
       <c r="R24" s="40">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S24" s="43">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T24" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>1920</v>
+        <v>1980</v>
       </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -3071,69 +3074,69 @@
       <c r="AD24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="49" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C25" s="39">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
       <c r="D25" s="40">
-        <v>18.0</v>
+        <v>25.0</v>
       </c>
       <c r="E25" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="F25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="L25" s="39">
+        <v>12.0</v>
+      </c>
+      <c r="M25" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="N25" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="R25" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="S25" s="43">
         <v>6.0</v>
-      </c>
-      <c r="F25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="M25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="N25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q25" s="39">
-        <v>11.0</v>
-      </c>
-      <c r="R25" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="S25" s="43">
-        <v>4.0</v>
       </c>
       <c r="T25" s="41">
         <v>21.0</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
-        <v>1845</v>
+        <v>1965</v>
       </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
@@ -3145,24 +3148,24 @@
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
     </row>
-    <row r="26">
-      <c r="A26" s="51" t="s">
+    <row r="26" hidden="1">
+      <c r="A26" s="37" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C26" s="39">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="D26" s="40">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="E26" s="40">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" s="40">
         <v>1.0</v>
@@ -3171,7 +3174,7 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="41">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="39">
         <v>0.0</v>
@@ -3183,32 +3186,32 @@
         <v>3.0</v>
       </c>
       <c r="M26" s="40">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="N26" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="40">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P26" s="42">
         <v>0.0</v>
       </c>
       <c r="Q26" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="R26" s="40">
+        <v>8.0</v>
+      </c>
+      <c r="S26" s="43">
         <v>4.0</v>
       </c>
-      <c r="R26" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="S26" s="43">
-        <v>5.0</v>
-      </c>
       <c r="T26" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>1845</v>
       </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
@@ -3231,7 +3234,7 @@
         <v>16.0</v>
       </c>
       <c r="D27" s="40">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="E27" s="40">
         <v>2.0</v>
@@ -3255,7 +3258,7 @@
         <v>0.0</v>
       </c>
       <c r="L27" s="39">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M27" s="40">
         <v>11.0</v>
@@ -3273,17 +3276,17 @@
         <v>7.0</v>
       </c>
       <c r="R27" s="40">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S27" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T27" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U27" s="44">
         <f t="shared" si="1"/>
-        <v>1740</v>
+        <v>1785</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
@@ -3303,25 +3306,25 @@
         <v>36</v>
       </c>
       <c r="C28" s="39">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="D28" s="40">
-        <v>7.0</v>
+        <v>19.0</v>
       </c>
       <c r="E28" s="40">
+        <v>4.0</v>
+      </c>
+      <c r="F28" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="40">
         <v>3.0</v>
       </c>
-      <c r="F28" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G28" s="40">
-        <v>1.0</v>
-      </c>
       <c r="H28" s="40">
         <v>0.0</v>
       </c>
       <c r="I28" s="41">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J28" s="39">
         <v>0.0</v>
@@ -3333,32 +3336,32 @@
         <v>1.0</v>
       </c>
       <c r="M28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P28" s="42">
         <v>0.0</v>
       </c>
       <c r="Q28" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="R28" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="S28" s="43">
         <v>4.0</v>
       </c>
-      <c r="R28" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="S28" s="43">
-        <v>2.0</v>
-      </c>
       <c r="T28" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U28" s="44">
         <f t="shared" si="1"/>
-        <v>1560</v>
+        <v>1695</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -3371,14 +3374,14 @@
       <c r="AD28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="49" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C29" s="39">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="D29" s="40">
         <v>7.0</v>
@@ -3387,16 +3390,16 @@
         <v>3.0</v>
       </c>
       <c r="F29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="40">
         <v>0.0</v>
       </c>
       <c r="I29" s="41">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J29" s="39">
         <v>0.0</v>
@@ -3405,13 +3408,13 @@
         <v>0.0</v>
       </c>
       <c r="L29" s="39">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N29" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O29" s="40">
         <v>0.0</v>
@@ -3420,20 +3423,20 @@
         <v>0.0</v>
       </c>
       <c r="Q29" s="39">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R29" s="40">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="S29" s="43">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T29" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1590</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
@@ -3445,70 +3448,70 @@
       <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
     </row>
-    <row r="30">
-      <c r="A30" s="49" t="s">
+    <row r="30" hidden="1">
+      <c r="A30" s="48" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C30" s="39">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="D30" s="40">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
       <c r="E30" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="F30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="J30" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="41">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="M30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="40">
+        <v>0.0</v>
+      </c>
+      <c r="P30" s="42">
+        <v>0.0</v>
+      </c>
+      <c r="Q30" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="R30" s="40">
         <v>4.0</v>
       </c>
-      <c r="F30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="G30" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="H30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="J30" s="39">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="M30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="40">
-        <v>0.0</v>
-      </c>
-      <c r="O30" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="P30" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="Q30" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="R30" s="40">
-        <v>2.0</v>
-      </c>
       <c r="S30" s="43">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="T30" s="41">
         <v>20.0</v>
       </c>
       <c r="U30" s="44">
         <f t="shared" si="1"/>
-        <v>1515</v>
+        <v>1530</v>
       </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
@@ -3579,11 +3582,11 @@
         <v>3.0</v>
       </c>
       <c r="T31" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U31" s="44">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
@@ -3600,13 +3603,13 @@
         <v>58</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" s="39">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D32" s="40">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E32" s="40">
         <v>0.0</v>
@@ -3654,11 +3657,11 @@
         <v>3.0</v>
       </c>
       <c r="T32" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U32" s="44">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1395</v>
       </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3681,7 +3684,7 @@
         <v>5.0</v>
       </c>
       <c r="D33" s="40">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E33" s="40">
         <v>2.0</v>
@@ -3723,17 +3726,17 @@
         <v>3.0</v>
       </c>
       <c r="R33" s="40">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S33" s="43">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T33" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U33" s="44">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1350</v>
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
@@ -3756,7 +3759,7 @@
         <v>4.0</v>
       </c>
       <c r="D34" s="40">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E34" s="40">
         <v>2.0</v>
@@ -3798,17 +3801,17 @@
         <v>3.0</v>
       </c>
       <c r="R34" s="40">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S34" s="43">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T34" s="41">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="U34" s="44">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3820,7 +3823,7 @@
       <c r="AC34" s="9"/>
       <c r="AD34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" hidden="1">
       <c r="A35" s="49" t="s">
         <v>61</v>
       </c>
@@ -3895,7 +3898,7 @@
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" hidden="1">
       <c r="A36" s="37" t="s">
         <v>62</v>
       </c>
@@ -3970,7 +3973,7 @@
       <c r="AC36" s="9"/>
       <c r="AD36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" hidden="1">
       <c r="A37" s="37" t="s">
         <v>63</v>
       </c>
@@ -4047,6 +4050,37 @@
     </row>
   </sheetData>
   <autoFilter ref="$A$4:$U$37">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Pereira, Raul"/>
+        <filter val="Santa, Fraimy"/>
+        <filter val="Mateo, Cesar"/>
+        <filter val="Jaquez, Luis"/>
+        <filter val="Valdes, Abel"/>
+        <filter val="Genao, Jhostin"/>
+        <filter val="Guerrero, Oliver"/>
+        <filter val="Zayas, Saivel"/>
+        <filter val="Celesten, Yeisy"/>
+        <filter val="Montero, Darling"/>
+        <filter val="Pinder, Jayln"/>
+        <filter val="Chavez, Jesus"/>
+        <filter val="Gonzalez, Victor"/>
+        <filter val="Rosario, Elian"/>
+        <filter val="Alarcon, Rosnel"/>
+        <filter val="Benitez, Frainker"/>
+        <filter val="Flores, Jesus"/>
+        <filter val="Abreu, Ariel"/>
+        <filter val="Colina, Felix"/>
+        <filter val="Simon, Jhon"/>
+        <filter val="Done, Carlos"/>
+        <filter val="Ramirez, Santiago"/>
+        <filter val="Diaz, David"/>
+        <filter val="Mosqueda, Juan"/>
+        <filter val="Castillo, Wesly"/>
+        <filter val="Rodriguez, Victor"/>
+        <filter val="Marcano, Jose"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A4:U37">
       <sortCondition descending="1" ref="U4:U37"/>
       <sortCondition descending="1" ref="B4:B37"/>
@@ -4440,11 +4474,11 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="82">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R6" s="83">
         <f t="shared" si="1"/>
-        <v>4305</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="7">
@@ -4554,11 +4588,11 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R8" s="83">
         <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
-        <v>4005</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="9">
@@ -4611,11 +4645,11 @@
         <v>2.0</v>
       </c>
       <c r="Q9" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R9" s="83">
         <f t="shared" ref="R9:R36" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
-        <v>3705</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="10">
@@ -4725,11 +4759,11 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R11" s="83">
         <f t="shared" si="2"/>
-        <v>3435</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="12">
@@ -4782,11 +4816,11 @@
         <v>1.0</v>
       </c>
       <c r="Q12" s="82">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R12" s="83">
         <f t="shared" si="2"/>
-        <v>3420</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="13">
@@ -4839,11 +4873,11 @@
         <v>2.0</v>
       </c>
       <c r="Q13" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R13" s="83">
         <f t="shared" si="2"/>
-        <v>3345</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="14">
@@ -5018,44 +5052,44 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C17" s="81">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="D17" s="42">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E17" s="42">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="F17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" s="42">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H17" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I17" s="80">
         <v>0.0</v>
       </c>
       <c r="J17" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K17" s="81">
         <v>0.0</v>
       </c>
       <c r="L17" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M17" s="82">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N17" s="81">
         <v>0.0</v>
@@ -5064,46 +5098,46 @@
         <v>0.0</v>
       </c>
       <c r="P17" s="42">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q17" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R17" s="83">
         <f t="shared" si="2"/>
-        <v>2820</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="42" t="s">
-        <v>30</v>
+      <c r="B18" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C18" s="81">
         <v>22.0</v>
       </c>
       <c r="D18" s="42">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E18" s="42">
-        <v>14.0</v>
+        <v>6.0</v>
       </c>
       <c r="F18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="42">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I18" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J18" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K18" s="81">
         <v>0.0</v>
@@ -5128,24 +5162,24 @@
       </c>
       <c r="R18" s="83">
         <f t="shared" si="2"/>
-        <v>2640</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="86" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C19" s="81">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="D19" s="42">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E19" s="42">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="F19" s="42">
         <v>0.0</v>
@@ -5157,7 +5191,7 @@
         <v>0.0</v>
       </c>
       <c r="I19" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J19" s="42">
         <v>0.0</v>
@@ -5166,10 +5200,10 @@
         <v>0.0</v>
       </c>
       <c r="L19" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M19" s="82">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N19" s="81">
         <v>0.0</v>
@@ -5178,43 +5212,43 @@
         <v>0.0</v>
       </c>
       <c r="P19" s="42">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q19" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R19" s="83">
         <f t="shared" si="2"/>
-        <v>2475</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="85" t="s">
+      <c r="A20" s="77" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="81">
-        <v>23.0</v>
+        <v>20.0</v>
       </c>
       <c r="D20" s="42">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="E20" s="42">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G20" s="42">
         <v>0.0</v>
       </c>
       <c r="H20" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="42">
         <v>0.0</v>
@@ -5242,21 +5276,21 @@
       </c>
       <c r="R20" s="83">
         <f t="shared" si="2"/>
-        <v>2400</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="78" t="s">
-        <v>36</v>
+      <c r="B21" s="42" t="s">
+        <v>30</v>
       </c>
       <c r="C21" s="81">
-        <v>21.0</v>
+        <v>25.0</v>
       </c>
       <c r="D21" s="42">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="E21" s="42">
         <v>9.0</v>
@@ -5271,7 +5305,7 @@
         <v>1.0</v>
       </c>
       <c r="I21" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="J21" s="42">
         <v>0.0</v>
@@ -5292,40 +5326,40 @@
         <v>0.0</v>
       </c>
       <c r="P21" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q21" s="82">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="R21" s="83">
         <f t="shared" si="2"/>
-        <v>2370</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="84" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="42" t="s">
-        <v>30</v>
+      <c r="B22" s="78" t="s">
+        <v>36</v>
       </c>
       <c r="C22" s="81">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="D22" s="42">
+        <v>14.0</v>
+      </c>
+      <c r="E22" s="42">
         <v>9.0</v>
       </c>
-      <c r="E22" s="42">
-        <v>8.0</v>
-      </c>
       <c r="F22" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" s="42">
         <v>0.0</v>
       </c>
       <c r="H22" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I22" s="80">
         <v>0.0</v>
@@ -5349,40 +5383,40 @@
         <v>0.0</v>
       </c>
       <c r="P22" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q22" s="82">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="R22" s="83">
         <f t="shared" si="2"/>
-        <v>2280</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="88" t="s">
+      <c r="A23" s="86" t="s">
         <v>92</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C23" s="81">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="D23" s="42">
-        <v>24.0</v>
+        <v>10.0</v>
       </c>
       <c r="E23" s="42">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="F23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" s="42">
         <v>0.0</v>
       </c>
       <c r="H23" s="80">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I23" s="80">
         <v>0.0</v>
@@ -5406,31 +5440,31 @@
         <v>0.0</v>
       </c>
       <c r="P23" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="82">
         <v>21.0</v>
       </c>
       <c r="R23" s="83">
         <f t="shared" si="2"/>
-        <v>2220</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="77" t="s">
         <v>93</v>
       </c>
       <c r="B24" s="42" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="81">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="D24" s="42">
-        <v>8.0</v>
+        <v>23.0</v>
       </c>
       <c r="E24" s="42">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="F24" s="42">
         <v>0.0</v>
@@ -5445,7 +5479,7 @@
         <v>0.0</v>
       </c>
       <c r="J24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="81">
         <v>0.0</v>
@@ -5463,46 +5497,46 @@
         <v>0.0</v>
       </c>
       <c r="P24" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q24" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R24" s="83">
         <f t="shared" si="2"/>
-        <v>2205</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="s">
+      <c r="A25" s="88" t="s">
         <v>94</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C25" s="81">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="D25" s="42">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="E25" s="42">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="F25" s="42">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" s="42">
         <v>0.0</v>
       </c>
       <c r="H25" s="80">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I25" s="42">
         <v>0.0</v>
       </c>
       <c r="J25" s="42">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K25" s="81">
         <v>0.0</v>
@@ -5523,11 +5557,11 @@
         <v>1.0</v>
       </c>
       <c r="Q25" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R25" s="83">
         <f t="shared" si="2"/>
-        <v>2130</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="26">
@@ -5645,17 +5679,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="42" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="81">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="D28" s="42">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="E28" s="42">
         <v>8.0</v>
@@ -5691,31 +5725,31 @@
         <v>0.0</v>
       </c>
       <c r="P28" s="42">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q28" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R28" s="83">
         <f t="shared" si="2"/>
-        <v>1845</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="85" t="s">
+      <c r="A29" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="78" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="81">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="D29" s="42">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
       <c r="E29" s="42">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F29" s="42">
         <v>0.0</v>
@@ -5748,14 +5782,14 @@
         <v>0.0</v>
       </c>
       <c r="P29" s="42">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q29" s="82">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="R29" s="83">
         <f t="shared" si="2"/>
-        <v>1590</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="30">
@@ -5766,7 +5800,7 @@
         <v>30</v>
       </c>
       <c r="C30" s="81">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D30" s="42">
         <v>16.0</v>
@@ -5812,7 +5846,7 @@
       </c>
       <c r="R30" s="83">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="31">
@@ -5865,11 +5899,11 @@
         <v>1.0</v>
       </c>
       <c r="Q31" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R31" s="83">
         <f t="shared" si="2"/>
-        <v>1260</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="32">
@@ -5922,11 +5956,11 @@
         <v>3.0</v>
       </c>
       <c r="Q32" s="82">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R32" s="83">
         <f t="shared" si="2"/>
-        <v>1080</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="33">
@@ -5979,11 +6013,11 @@
         <v>2.0</v>
       </c>
       <c r="Q33" s="82">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="R33" s="83">
         <f t="shared" si="2"/>
-        <v>945</v>
+        <v>975</v>
       </c>
     </row>
     <row r="34">
@@ -6036,11 +6070,11 @@
         <v>0.0</v>
       </c>
       <c r="Q34" s="93">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R34" s="83">
         <f t="shared" si="2"/>
-        <v>690</v>
+        <v>720</v>
       </c>
     </row>
     <row r="35">
@@ -6104,17 +6138,17 @@
       <c r="A36" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="95">
-        <v>3.0</v>
+      <c r="B36" s="95" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="96">
+        <v>4.0</v>
       </c>
       <c r="D36" s="54">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E36" s="54">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="54">
         <v>0.0</v>
@@ -6122,25 +6156,25 @@
       <c r="G36" s="54">
         <v>0.0</v>
       </c>
-      <c r="H36" s="96">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="96">
+      <c r="H36" s="97">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="97">
         <v>0.0</v>
       </c>
       <c r="J36" s="54">
         <v>0.0</v>
       </c>
-      <c r="K36" s="95">
+      <c r="K36" s="96">
         <v>0.0</v>
       </c>
       <c r="L36" s="54">
         <v>0.0</v>
       </c>
-      <c r="M36" s="97">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="95">
+      <c r="M36" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="96">
         <v>0.0</v>
       </c>
       <c r="O36" s="54">
@@ -6149,12 +6183,12 @@
       <c r="P36" s="54">
         <v>0.0</v>
       </c>
-      <c r="Q36" s="97">
-        <v>7.0</v>
-      </c>
-      <c r="R36" s="98">
+      <c r="Q36" s="98">
+        <v>8.0</v>
+      </c>
+      <c r="R36" s="99">
         <f t="shared" si="2"/>
-        <v>315</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Incentives System - DR TEX 2026.xlsx
+++ b/Incentives System - DR TEX 2026.xlsx
@@ -20,18 +20,18 @@
     <t>INCENTIVOS DSL 2026</t>
   </si>
   <si>
+    <t>HITTING</t>
+  </si>
+  <si>
     <t>DAILY</t>
   </si>
   <si>
-    <t>HITTING</t>
+    <t>WEEKLY</t>
   </si>
   <si>
     <t>DEFENSE</t>
   </si>
   <si>
-    <t>WEEKLY</t>
-  </si>
-  <si>
     <t>TEAM</t>
   </si>
   <si>
@@ -80,12 +80,12 @@
     <t>R2K%</t>
   </si>
   <si>
+    <t>0R</t>
+  </si>
+  <si>
     <t>Players</t>
   </si>
   <si>
-    <t>0R</t>
-  </si>
-  <si>
     <t>0H</t>
   </si>
   <si>
@@ -101,10 +101,13 @@
     <t>2H+</t>
   </si>
   <si>
+    <t>Silvestre, Jose</t>
+  </si>
+  <si>
     <t>EV100 FLY&amp;LD</t>
   </si>
   <si>
-    <t>Silvestre, Jose</t>
+    <t>B</t>
   </si>
   <si>
     <t>Avance 2 Bases</t>
@@ -113,9 +116,6 @@
     <t>1er/3er Out 3B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>SB</t>
   </si>
   <si>
@@ -140,22 +140,28 @@
     <t>Mateo, Cesar</t>
   </si>
   <si>
+    <t>Colmenares, Kevin</t>
+  </si>
+  <si>
+    <t>Celesten, Yeisy</t>
+  </si>
+  <si>
     <t>Medina, Juan</t>
   </si>
   <si>
-    <t>Celesten, Yeisy</t>
-  </si>
-  <si>
-    <t>Colmenares, Kevin</t>
+    <t>Rodriguez, Alex</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Santos, Aneudy</t>
   </si>
   <si>
     <t>Zayas, Saivel</t>
   </si>
   <si>
-    <t>Rodriguez, Alex</t>
-  </si>
-  <si>
-    <t>R</t>
+    <t>Peralta, Eddy</t>
   </si>
   <si>
     <t>Castillo, Wesly</t>
@@ -164,178 +170,172 @@
     <t>Rosario, Elian</t>
   </si>
   <si>
+    <t>Gamez, Manuel</t>
+  </si>
+  <si>
     <t>Done, Carlos</t>
   </si>
   <si>
+    <t>Pineda, Frandel</t>
+  </si>
+  <si>
     <t>Guerrero, Oliver</t>
   </si>
   <si>
+    <t>Gomez, Manuel</t>
+  </si>
+  <si>
     <t>Benitez, Frainker</t>
   </si>
   <si>
+    <t>Dolsi, Frederik</t>
+  </si>
+  <si>
     <t>Montero, Darling</t>
   </si>
   <si>
+    <t>Roquez, Yadiel</t>
+  </si>
+  <si>
     <t>Jaquez, Luis</t>
   </si>
   <si>
+    <t>Liriano, Edgar</t>
+  </si>
+  <si>
     <t>Flores, Jesus</t>
   </si>
   <si>
+    <t>Encarnacion, Jefferson</t>
+  </si>
+  <si>
     <t>Gonzalez, Victor</t>
   </si>
   <si>
+    <t>Figuereo, Breyner</t>
+  </si>
+  <si>
     <t>Marcano, Jose</t>
   </si>
   <si>
     <t>Valdes, Abel</t>
   </si>
   <si>
+    <t>Castillo, Albert</t>
+  </si>
+  <si>
     <t>Ramirez, Santiago</t>
   </si>
   <si>
+    <t>Lara, Carlos</t>
+  </si>
+  <si>
     <t>Genao, Jhostin</t>
   </si>
   <si>
     <t>Pereira, Raul</t>
   </si>
   <si>
+    <t>Ballesteros, Jean</t>
+  </si>
+  <si>
+    <t>Simon, Jhon</t>
+  </si>
+  <si>
+    <t>Acosta, Isaac</t>
+  </si>
+  <si>
     <t>Diaz, David</t>
   </si>
   <si>
-    <t>Simon, Jhon</t>
+    <t>Granado, Argenis</t>
   </si>
   <si>
     <t>Chavez, Jesus</t>
   </si>
   <si>
+    <t>Alcantara, Jostin</t>
+  </si>
+  <si>
     <t>Alarcon, Rosnel</t>
   </si>
   <si>
+    <t>Pena, Dariel</t>
+  </si>
+  <si>
     <t>Abreu, Ariel</t>
   </si>
   <si>
+    <t>Ramos, Daniel</t>
+  </si>
+  <si>
+    <t>Mosqueda, Juan</t>
+  </si>
+  <si>
+    <t>Perez, Juanangel</t>
+  </si>
+  <si>
+    <t>Volquez, Fabelin</t>
+  </si>
+  <si>
+    <t>Fernandez, Jehiber</t>
+  </si>
+  <si>
     <t>Pinder, Jayln</t>
   </si>
   <si>
-    <t>Volquez, Fabelin</t>
-  </si>
-  <si>
-    <t>Mosqueda, Juan</t>
+    <t>Cordero, Albert</t>
   </si>
   <si>
     <t>Ortiz Jr, David</t>
   </si>
   <si>
+    <t>Lamu, Alex</t>
+  </si>
+  <si>
     <t>Santa, Fraimy</t>
   </si>
   <si>
+    <t>Bautista, Jeyson</t>
+  </si>
+  <si>
     <t>Colina, Felix</t>
   </si>
   <si>
+    <t>De Jesus, Yunier</t>
+  </si>
+  <si>
     <t>Rodriguez, Victor</t>
   </si>
   <si>
-    <t>Roquez, Yadiel</t>
+    <t>Mendez, Eithan</t>
+  </si>
+  <si>
+    <t>Albarez, Alex</t>
   </si>
   <si>
     <t>Coronado, Francisco</t>
   </si>
   <si>
+    <t>Acosta, Alex</t>
+  </si>
+  <si>
     <t>Seminiel, Cristian</t>
   </si>
   <si>
-    <t>Santos, Aneudy</t>
+    <t>Ramirez, Mauricio</t>
+  </si>
+  <si>
+    <t>Fernandez, Harley</t>
   </si>
   <si>
     <t>Cedeno, Luis</t>
   </si>
   <si>
+    <t>Gonzalez, Nestor</t>
+  </si>
+  <si>
     <t>Rivas, Santiago</t>
-  </si>
-  <si>
-    <t>Peralta, Eddy</t>
-  </si>
-  <si>
-    <t>Gamez, Manuel</t>
-  </si>
-  <si>
-    <t>Pineda, Frandel</t>
-  </si>
-  <si>
-    <t>Gomez, Manuel</t>
-  </si>
-  <si>
-    <t>Liriano, Edgar</t>
-  </si>
-  <si>
-    <t>Dolsi, Frederik</t>
-  </si>
-  <si>
-    <t>Figuereo, Breyner</t>
-  </si>
-  <si>
-    <t>Encarnacion, Jefferson</t>
-  </si>
-  <si>
-    <t>Castillo, Albert</t>
-  </si>
-  <si>
-    <t>Lara, Carlos</t>
-  </si>
-  <si>
-    <t>Ballesteros, Jean</t>
-  </si>
-  <si>
-    <t>Acosta, Isaac</t>
-  </si>
-  <si>
-    <t>Granado, Argenis</t>
-  </si>
-  <si>
-    <t>Alcantara, Jostin</t>
-  </si>
-  <si>
-    <t>Pena, Dariel</t>
-  </si>
-  <si>
-    <t>Ramos, Daniel</t>
-  </si>
-  <si>
-    <t>Perez, Juanangel</t>
-  </si>
-  <si>
-    <t>Fernandez, Jehiber</t>
-  </si>
-  <si>
-    <t>Cordero, Albert</t>
-  </si>
-  <si>
-    <t>Lamu, Alex</t>
-  </si>
-  <si>
-    <t>Bautista, Jeyson</t>
-  </si>
-  <si>
-    <t>De Jesus, Yunier</t>
-  </si>
-  <si>
-    <t>Mendez, Eithan</t>
-  </si>
-  <si>
-    <t>Acosta, Alex</t>
-  </si>
-  <si>
-    <t>Albarez, Alex</t>
-  </si>
-  <si>
-    <t>Ramirez, Mauricio</t>
-  </si>
-  <si>
-    <t>Fernandez, Harley</t>
-  </si>
-  <si>
-    <t>Gonzalez, Nestor</t>
   </si>
   <si>
     <t>Bello, Abner</t>
@@ -357,12 +357,12 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
@@ -600,9 +600,88 @@
       </bottom>
     </border>
     <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -611,41 +690,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -654,6 +698,31 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -671,7 +740,7 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -682,7 +751,21 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -690,32 +773,7 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -723,64 +781,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -813,16 +813,16 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -845,77 +845,83 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="7" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="15" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="12" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="19" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="6" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="18" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="20" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="15" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -923,12 +929,6 @@
     <xf borderId="21" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="8" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -944,67 +944,76 @@
     <xf borderId="22" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="22" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="26" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="27" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="26" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="26" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="26" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="28" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="22" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="22" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="27" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="28" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="29" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="29" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="25" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1016,22 +1025,43 @@
     <xf borderId="27" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="22" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="22" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="25" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="25" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="22" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1040,49 +1070,19 @@
     <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="31" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="31" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="32" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="33" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="33" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="34" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1369,12 +1369,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -1385,13 +1385,13 @@
       <c r="J1" s="6"/>
       <c r="K1" s="3"/>
       <c r="L1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M1" s="11"/>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
       <c r="P1" s="13"/>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="R1" s="6"/>
@@ -1409,12 +1409,12 @@
       <c r="AD1" s="15"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -1423,22 +1423,22 @@
       <c r="H2" s="10"/>
       <c r="I2" s="12"/>
       <c r="J2" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="30"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="33"/>
       <c r="U2" s="14"/>
       <c r="V2" s="15"/>
       <c r="W2" s="15"/>
@@ -1451,62 +1451,62 @@
       <c r="AD2" s="15"/>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="35">
+      <c r="B3" s="21"/>
+      <c r="C3" s="38">
         <v>75.0</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="40">
         <v>-30.0</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="32">
         <v>60.0</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="32">
         <v>45.0</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="32">
         <v>15.0</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="40">
         <v>-15.0</v>
       </c>
-      <c r="I3" s="40">
+      <c r="I3" s="42">
         <v>30.0</v>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="38">
         <v>180.0</v>
       </c>
-      <c r="K3" s="40">
+      <c r="K3" s="42">
         <v>180.0</v>
       </c>
-      <c r="L3" s="42">
+      <c r="L3" s="44">
         <v>-15.0</v>
       </c>
-      <c r="M3" s="33">
+      <c r="M3" s="32">
         <v>15.0</v>
       </c>
-      <c r="N3" s="33">
+      <c r="N3" s="32">
         <v>30.0</v>
       </c>
-      <c r="O3" s="44">
+      <c r="O3" s="46">
         <v>-15.0</v>
       </c>
-      <c r="P3" s="33">
+      <c r="P3" s="32">
         <v>180.0</v>
       </c>
-      <c r="Q3" s="35">
+      <c r="Q3" s="38">
         <v>30.0</v>
       </c>
-      <c r="R3" s="45">
+      <c r="R3" s="47">
         <v>30.0</v>
       </c>
-      <c r="S3" s="33">
+      <c r="S3" s="32">
         <v>30.0</v>
       </c>
-      <c r="T3" s="40">
+      <c r="T3" s="42">
         <v>30.0</v>
       </c>
       <c r="U3" s="14"/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="4">
       <c r="A4" s="49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="50" t="s">
         <v>9</v>
@@ -1536,22 +1536,22 @@
       <c r="E4" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="53" t="s">
+      <c r="F4" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="H4" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="57" t="s">
         <v>33</v>
       </c>
       <c r="J4" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="56" t="s">
+      <c r="K4" s="57" t="s">
         <v>35</v>
       </c>
       <c r="L4" s="51" t="s">
@@ -1560,28 +1560,28 @@
       <c r="M4" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="53" t="s">
+      <c r="N4" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="53" t="s">
+      <c r="O4" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="60" t="s">
+      <c r="P4" s="59" t="s">
         <v>37</v>
       </c>
       <c r="Q4" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="53" t="s">
+      <c r="R4" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="63" t="s">
+      <c r="S4" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="56" t="s">
+      <c r="T4" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="U4" s="64" t="s">
+      <c r="U4" s="63" t="s">
         <v>26</v>
       </c>
       <c r="V4" s="15"/>
@@ -1599,13 +1599,13 @@
         <v>40</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="67">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="D5" s="68">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="E5" s="68">
         <v>19.0</v>
@@ -1632,7 +1632,7 @@
         <v>18.0</v>
       </c>
       <c r="M5" s="68">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="N5" s="68">
         <v>4.0</v>
@@ -1640,7 +1640,7 @@
       <c r="O5" s="68">
         <v>2.0</v>
       </c>
-      <c r="P5" s="59">
+      <c r="P5" s="60">
         <v>0.0</v>
       </c>
       <c r="Q5" s="67">
@@ -1655,9 +1655,9 @@
       <c r="T5" s="69">
         <v>27.0</v>
       </c>
-      <c r="U5" s="72">
+      <c r="U5" s="73">
         <f t="shared" ref="U5:U38" si="1">(C$3*C5)+(D$3*D5)+(E$3*E5)+(F$3*F5)+(G$3*G5)+(H$3*H5)+(I$3*I5)+(J$3*J5)+(K$3*K5)+(L$3*L5)+(M$3*M5)+(N$3*N5)+(O$3*O5)+(P$3*P5)+(Q$3*Q5)+(R$3*R5)+(S$3*S5)+(T$3*T5)</f>
-        <v>7050</v>
+        <v>7065</v>
       </c>
       <c r="V5" s="15"/>
       <c r="W5" s="15"/>
@@ -1674,10 +1674,10 @@
         <v>42</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="67">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="D6" s="68">
         <v>30.0</v>
@@ -1704,10 +1704,10 @@
         <v>0.0</v>
       </c>
       <c r="L6" s="67">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="M6" s="68">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="N6" s="68">
         <v>3.0</v>
@@ -1715,7 +1715,7 @@
       <c r="O6" s="68">
         <v>0.0</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="60">
         <v>0.0</v>
       </c>
       <c r="Q6" s="67">
@@ -1730,9 +1730,9 @@
       <c r="T6" s="69">
         <v>27.0</v>
       </c>
-      <c r="U6" s="72">
+      <c r="U6" s="73">
         <f t="shared" si="1"/>
-        <v>5790</v>
+        <v>5865</v>
       </c>
       <c r="V6" s="15"/>
       <c r="W6" s="15"/>
@@ -1745,69 +1745,69 @@
       <c r="AD6" s="15"/>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="74">
-        <v>28.0</v>
-      </c>
-      <c r="D7" s="75">
-        <v>50.0</v>
-      </c>
-      <c r="E7" s="75">
-        <v>18.0</v>
-      </c>
-      <c r="F7" s="75">
-        <v>19.0</v>
-      </c>
-      <c r="G7" s="75">
+      <c r="B7" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="67">
+        <v>46.0</v>
+      </c>
+      <c r="D7" s="68">
+        <v>30.0</v>
+      </c>
+      <c r="E7" s="68">
         <v>5.0</v>
       </c>
-      <c r="H7" s="75">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="76">
-        <v>10.0</v>
+      <c r="F7" s="68">
+        <v>3.0</v>
+      </c>
+      <c r="G7" s="68">
+        <v>4.0</v>
+      </c>
+      <c r="H7" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="69">
+        <v>9.0</v>
       </c>
       <c r="J7" s="67">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="K7" s="69">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" s="67">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M7" s="68">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="N7" s="68">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O7" s="68">
-        <v>4.0</v>
-      </c>
-      <c r="P7" s="59">
+        <v>2.0</v>
+      </c>
+      <c r="P7" s="60">
         <v>0.0</v>
       </c>
       <c r="Q7" s="67">
-        <v>24.0</v>
+        <v>14.0</v>
       </c>
       <c r="R7" s="68">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="S7" s="70">
         <v>11.0</v>
       </c>
       <c r="T7" s="69">
-        <v>28.0</v>
-      </c>
-      <c r="U7" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U7" s="73">
         <f t="shared" si="1"/>
-        <v>5655</v>
+        <v>5730</v>
       </c>
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
@@ -1820,69 +1820,69 @@
       <c r="AD7" s="15"/>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="78" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="67">
-        <v>46.0</v>
-      </c>
-      <c r="D8" s="68">
-        <v>30.0</v>
-      </c>
-      <c r="E8" s="68">
+      <c r="A8" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="77">
+        <v>28.0</v>
+      </c>
+      <c r="D8" s="78">
+        <v>51.0</v>
+      </c>
+      <c r="E8" s="78">
+        <v>18.0</v>
+      </c>
+      <c r="F8" s="78">
+        <v>19.0</v>
+      </c>
+      <c r="G8" s="78">
+        <v>5.0</v>
+      </c>
+      <c r="H8" s="78">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="79">
+        <v>10.0</v>
+      </c>
+      <c r="J8" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="69">
+        <v>3.0</v>
+      </c>
+      <c r="L8" s="67">
+        <v>1.0</v>
+      </c>
+      <c r="M8" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="68">
+        <v>1.0</v>
+      </c>
+      <c r="O8" s="68">
         <v>4.0</v>
       </c>
-      <c r="F8" s="68">
-        <v>2.0</v>
-      </c>
-      <c r="G8" s="68">
-        <v>4.0</v>
-      </c>
-      <c r="H8" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="69">
-        <v>9.0</v>
-      </c>
-      <c r="J8" s="67">
-        <v>3.0</v>
-      </c>
-      <c r="K8" s="69">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="67">
-        <v>2.0</v>
-      </c>
-      <c r="M8" s="68">
-        <v>6.0</v>
-      </c>
-      <c r="N8" s="68">
-        <v>2.0</v>
-      </c>
-      <c r="O8" s="68">
-        <v>2.0</v>
-      </c>
-      <c r="P8" s="59">
+      <c r="P8" s="60">
         <v>0.0</v>
       </c>
       <c r="Q8" s="67">
-        <v>14.0</v>
+        <v>24.0</v>
       </c>
       <c r="R8" s="68">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="S8" s="70">
         <v>11.0</v>
       </c>
       <c r="T8" s="69">
-        <v>24.0</v>
-      </c>
-      <c r="U8" s="72">
+        <v>28.0</v>
+      </c>
+      <c r="U8" s="73">
         <f t="shared" si="1"/>
-        <v>5580</v>
+        <v>5625</v>
       </c>
       <c r="V8" s="15"/>
       <c r="W8" s="15"/>
@@ -1895,14 +1895,14 @@
       <c r="AD8" s="15"/>
     </row>
     <row r="9">
-      <c r="A9" s="79" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>32</v>
+      <c r="A9" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C9" s="67">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="D9" s="68">
         <v>47.0</v>
@@ -1940,7 +1940,7 @@
       <c r="O9" s="68">
         <v>1.0</v>
       </c>
-      <c r="P9" s="59">
+      <c r="P9" s="60">
         <v>0.0</v>
       </c>
       <c r="Q9" s="67">
@@ -1955,9 +1955,9 @@
       <c r="T9" s="69">
         <v>31.0</v>
       </c>
-      <c r="U9" s="72">
+      <c r="U9" s="73">
         <f t="shared" si="1"/>
-        <v>5400</v>
+        <v>5475</v>
       </c>
       <c r="V9" s="15"/>
       <c r="W9" s="15"/>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="10">
       <c r="A10" s="65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="67">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="D10" s="68">
         <v>29.0</v>
@@ -1986,7 +1986,7 @@
         <v>11.0</v>
       </c>
       <c r="F10" s="68">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G10" s="68">
         <v>8.0</v>
@@ -2015,7 +2015,7 @@
       <c r="O10" s="68">
         <v>0.0</v>
       </c>
-      <c r="P10" s="59">
+      <c r="P10" s="60">
         <v>0.0</v>
       </c>
       <c r="Q10" s="67">
@@ -2030,9 +2030,9 @@
       <c r="T10" s="69">
         <v>28.0</v>
       </c>
-      <c r="U10" s="72">
+      <c r="U10" s="73">
         <f t="shared" si="1"/>
-        <v>4845</v>
+        <v>4965</v>
       </c>
       <c r="V10" s="15"/>
       <c r="W10" s="15"/>
@@ -2045,17 +2045,17 @@
       <c r="AD10" s="15"/>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="s">
-        <v>49</v>
+      <c r="A11" s="74" t="s">
+        <v>52</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="67">
         <v>32.0</v>
       </c>
       <c r="D11" s="68">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="E11" s="68">
         <v>12.0</v>
@@ -2090,7 +2090,7 @@
       <c r="O11" s="68">
         <v>5.0</v>
       </c>
-      <c r="P11" s="59">
+      <c r="P11" s="60">
         <v>0.0</v>
       </c>
       <c r="Q11" s="67">
@@ -2105,9 +2105,9 @@
       <c r="T11" s="69">
         <v>31.0</v>
       </c>
-      <c r="U11" s="72">
+      <c r="U11" s="73">
         <f t="shared" si="1"/>
-        <v>4620</v>
+        <v>4590</v>
       </c>
       <c r="V11" s="15"/>
       <c r="W11" s="15"/>
@@ -2120,11 +2120,11 @@
       <c r="AD11" s="15"/>
     </row>
     <row r="12">
-      <c r="A12" s="79" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="78" t="s">
-        <v>32</v>
+      <c r="A12" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C12" s="67">
         <v>40.0</v>
@@ -2165,7 +2165,7 @@
       <c r="O12" s="68">
         <v>3.0</v>
       </c>
-      <c r="P12" s="59">
+      <c r="P12" s="60">
         <v>0.0</v>
       </c>
       <c r="Q12" s="67">
@@ -2180,7 +2180,7 @@
       <c r="T12" s="69">
         <v>31.0</v>
       </c>
-      <c r="U12" s="72">
+      <c r="U12" s="73">
         <f t="shared" si="1"/>
         <v>4590</v>
       </c>
@@ -2195,11 +2195,11 @@
       <c r="AD12" s="15"/>
     </row>
     <row r="13">
-      <c r="A13" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>32</v>
+      <c r="A13" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C13" s="67">
         <v>22.0</v>
@@ -2240,7 +2240,7 @@
       <c r="O13" s="68">
         <v>0.0</v>
       </c>
-      <c r="P13" s="59">
+      <c r="P13" s="60">
         <v>1.0</v>
       </c>
       <c r="Q13" s="67">
@@ -2255,7 +2255,7 @@
       <c r="T13" s="69">
         <v>31.0</v>
       </c>
-      <c r="U13" s="72">
+      <c r="U13" s="73">
         <f t="shared" si="1"/>
         <v>4380</v>
       </c>
@@ -2270,14 +2270,14 @@
       <c r="AD13" s="15"/>
     </row>
     <row r="14">
-      <c r="A14" s="80" t="s">
-        <v>52</v>
+      <c r="A14" s="82" t="s">
+        <v>58</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="67">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="D14" s="68">
         <v>26.0</v>
@@ -2307,7 +2307,7 @@
         <v>9.0</v>
       </c>
       <c r="M14" s="68">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="N14" s="68">
         <v>1.0</v>
@@ -2315,7 +2315,7 @@
       <c r="O14" s="68">
         <v>2.0</v>
       </c>
-      <c r="P14" s="59">
+      <c r="P14" s="60">
         <v>0.0</v>
       </c>
       <c r="Q14" s="67">
@@ -2330,9 +2330,9 @@
       <c r="T14" s="69">
         <v>31.0</v>
       </c>
-      <c r="U14" s="72">
+      <c r="U14" s="73">
         <f t="shared" si="1"/>
-        <v>4260</v>
+        <v>4365</v>
       </c>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
@@ -2345,11 +2345,11 @@
       <c r="AD14" s="15"/>
     </row>
     <row r="15">
-      <c r="A15" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="78" t="s">
-        <v>32</v>
+      <c r="A15" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="67">
         <v>21.0</v>
@@ -2390,7 +2390,7 @@
       <c r="O15" s="68">
         <v>2.0</v>
       </c>
-      <c r="P15" s="59">
+      <c r="P15" s="60">
         <v>0.0</v>
       </c>
       <c r="Q15" s="67">
@@ -2405,7 +2405,7 @@
       <c r="T15" s="69">
         <v>31.0</v>
       </c>
-      <c r="U15" s="72">
+      <c r="U15" s="73">
         <f t="shared" si="1"/>
         <v>3870</v>
       </c>
@@ -2420,11 +2420,11 @@
       <c r="AD15" s="15"/>
     </row>
     <row r="16">
-      <c r="A16" s="79" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="78" t="s">
-        <v>32</v>
+      <c r="A16" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="67">
         <v>22.0</v>
@@ -2465,7 +2465,7 @@
       <c r="O16" s="68">
         <v>0.0</v>
       </c>
-      <c r="P16" s="59">
+      <c r="P16" s="60">
         <v>0.0</v>
       </c>
       <c r="Q16" s="67">
@@ -2480,7 +2480,7 @@
       <c r="T16" s="69">
         <v>31.0</v>
       </c>
-      <c r="U16" s="72">
+      <c r="U16" s="73">
         <f t="shared" si="1"/>
         <v>3780</v>
       </c>
@@ -2495,11 +2495,11 @@
       <c r="AD16" s="15"/>
     </row>
     <row r="17">
-      <c r="A17" s="79" t="s">
-        <v>55</v>
+      <c r="A17" s="80" t="s">
+        <v>64</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="67">
         <v>33.0</v>
@@ -2540,7 +2540,7 @@
       <c r="O17" s="68">
         <v>3.0</v>
       </c>
-      <c r="P17" s="59">
+      <c r="P17" s="60">
         <v>0.0</v>
       </c>
       <c r="Q17" s="67">
@@ -2555,7 +2555,7 @@
       <c r="T17" s="69">
         <v>28.0</v>
       </c>
-      <c r="U17" s="72">
+      <c r="U17" s="73">
         <f t="shared" si="1"/>
         <v>3750</v>
       </c>
@@ -2570,11 +2570,11 @@
       <c r="AD17" s="15"/>
     </row>
     <row r="18">
-      <c r="A18" s="79" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="78" t="s">
-        <v>32</v>
+      <c r="A18" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C18" s="67">
         <v>14.0</v>
@@ -2615,7 +2615,7 @@
       <c r="O18" s="68">
         <v>0.0</v>
       </c>
-      <c r="P18" s="59">
+      <c r="P18" s="60">
         <v>3.0</v>
       </c>
       <c r="Q18" s="67">
@@ -2630,7 +2630,7 @@
       <c r="T18" s="69">
         <v>31.0</v>
       </c>
-      <c r="U18" s="72">
+      <c r="U18" s="73">
         <f t="shared" si="1"/>
         <v>3690</v>
       </c>
@@ -2645,11 +2645,11 @@
       <c r="AD18" s="15"/>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="78" t="s">
-        <v>46</v>
+      <c r="A19" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="C19" s="67">
         <v>16.0</v>
@@ -2690,7 +2690,7 @@
       <c r="O19" s="68">
         <v>1.0</v>
       </c>
-      <c r="P19" s="59">
+      <c r="P19" s="60">
         <v>1.0</v>
       </c>
       <c r="Q19" s="67">
@@ -2703,11 +2703,11 @@
         <v>5.0</v>
       </c>
       <c r="T19" s="69">
-        <v>24.0</v>
-      </c>
-      <c r="U19" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U19" s="73">
         <f t="shared" si="1"/>
-        <v>3480</v>
+        <v>3510</v>
       </c>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
@@ -2720,11 +2720,11 @@
       <c r="AD19" s="15"/>
     </row>
     <row r="20">
-      <c r="A20" s="80" t="s">
-        <v>58</v>
+      <c r="A20" s="82" t="s">
+        <v>69</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="67">
         <v>17.0</v>
@@ -2765,7 +2765,7 @@
       <c r="O20" s="68">
         <v>1.0</v>
       </c>
-      <c r="P20" s="59">
+      <c r="P20" s="60">
         <v>2.0</v>
       </c>
       <c r="Q20" s="67">
@@ -2780,7 +2780,7 @@
       <c r="T20" s="69">
         <v>28.0</v>
       </c>
-      <c r="U20" s="72">
+      <c r="U20" s="73">
         <f t="shared" si="1"/>
         <v>3435</v>
       </c>
@@ -2795,17 +2795,17 @@
       <c r="AD20" s="15"/>
     </row>
     <row r="21">
-      <c r="A21" s="79" t="s">
-        <v>59</v>
+      <c r="A21" s="80" t="s">
+        <v>71</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="67">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="D21" s="68">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="E21" s="68">
         <v>3.0</v>
@@ -2820,7 +2820,7 @@
         <v>1.0</v>
       </c>
       <c r="I21" s="69">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="J21" s="67">
         <v>0.0</v>
@@ -2840,7 +2840,7 @@
       <c r="O21" s="68">
         <v>2.0</v>
       </c>
-      <c r="P21" s="59">
+      <c r="P21" s="60">
         <v>0.0</v>
       </c>
       <c r="Q21" s="67">
@@ -2853,11 +2853,11 @@
         <v>13.0</v>
       </c>
       <c r="T21" s="69">
-        <v>23.0</v>
-      </c>
-      <c r="U21" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U21" s="73">
         <f t="shared" si="1"/>
-        <v>3180</v>
+        <v>3390</v>
       </c>
       <c r="V21" s="15"/>
       <c r="W21" s="15"/>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="22">
       <c r="A22" s="65" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" s="67">
         <v>23.0</v>
@@ -2915,7 +2915,7 @@
       <c r="O22" s="68">
         <v>3.0</v>
       </c>
-      <c r="P22" s="59">
+      <c r="P22" s="60">
         <v>0.0</v>
       </c>
       <c r="Q22" s="67">
@@ -2930,7 +2930,7 @@
       <c r="T22" s="69">
         <v>31.0</v>
       </c>
-      <c r="U22" s="72">
+      <c r="U22" s="73">
         <f t="shared" si="1"/>
         <v>3090</v>
       </c>
@@ -2945,69 +2945,69 @@
       <c r="AD22" s="15"/>
     </row>
     <row r="23">
-      <c r="A23" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="78" t="s">
-        <v>46</v>
+      <c r="A23" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C23" s="67">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="D23" s="68">
-        <v>32.0</v>
+        <v>18.0</v>
       </c>
       <c r="E23" s="68">
+        <v>4.0</v>
+      </c>
+      <c r="F23" s="68">
+        <v>4.0</v>
+      </c>
+      <c r="G23" s="68">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="69">
+        <v>2.0</v>
+      </c>
+      <c r="J23" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="69">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="67">
         <v>3.0</v>
       </c>
-      <c r="F23" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="68">
-        <v>3.0</v>
-      </c>
-      <c r="H23" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="69">
-        <v>6.0</v>
-      </c>
-      <c r="J23" s="67">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="69">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="67">
-        <v>6.0</v>
-      </c>
       <c r="M23" s="68">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="68">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="O23" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="59">
+        <v>1.0</v>
+      </c>
+      <c r="P23" s="60">
         <v>0.0</v>
       </c>
       <c r="Q23" s="67">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="R23" s="68">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="S23" s="70">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="T23" s="69">
-        <v>24.0</v>
-      </c>
-      <c r="U23" s="72">
+        <v>31.0</v>
+      </c>
+      <c r="U23" s="73">
         <f t="shared" si="1"/>
-        <v>2940</v>
+        <v>3000</v>
       </c>
       <c r="V23" s="15"/>
       <c r="W23" s="15"/>
@@ -3020,32 +3020,32 @@
       <c r="AD23" s="15"/>
     </row>
     <row r="24">
-      <c r="A24" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="78" t="s">
-        <v>32</v>
+      <c r="A24" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="C24" s="67">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="D24" s="68">
-        <v>16.0</v>
+        <v>33.0</v>
       </c>
       <c r="E24" s="68">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" s="68">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" s="68">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H24" s="68">
         <v>0.0</v>
       </c>
       <c r="I24" s="69">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="J24" s="67">
         <v>0.0</v>
@@ -3054,35 +3054,35 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="67">
+        <v>8.0</v>
+      </c>
+      <c r="M24" s="68">
+        <v>12.0</v>
+      </c>
+      <c r="N24" s="68">
         <v>3.0</v>
       </c>
-      <c r="M24" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="68">
-        <v>0.0</v>
-      </c>
       <c r="O24" s="68">
-        <v>1.0</v>
-      </c>
-      <c r="P24" s="59">
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="60">
         <v>0.0</v>
       </c>
       <c r="Q24" s="67">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="R24" s="68">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="S24" s="70">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="T24" s="69">
-        <v>31.0</v>
-      </c>
-      <c r="U24" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U24" s="73">
         <f t="shared" si="1"/>
-        <v>2910</v>
+        <v>2985</v>
       </c>
       <c r="V24" s="15"/>
       <c r="W24" s="15"/>
@@ -3095,11 +3095,11 @@
       <c r="AD24" s="15"/>
     </row>
     <row r="25">
-      <c r="A25" s="79" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="78" t="s">
-        <v>32</v>
+      <c r="A25" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C25" s="67">
         <v>20.0</v>
@@ -3140,7 +3140,7 @@
       <c r="O25" s="68">
         <v>1.0</v>
       </c>
-      <c r="P25" s="59">
+      <c r="P25" s="60">
         <v>0.0</v>
       </c>
       <c r="Q25" s="67">
@@ -3155,7 +3155,7 @@
       <c r="T25" s="69">
         <v>31.0</v>
       </c>
-      <c r="U25" s="72">
+      <c r="U25" s="73">
         <f t="shared" si="1"/>
         <v>2760</v>
       </c>
@@ -3170,11 +3170,11 @@
       <c r="AD25" s="15"/>
     </row>
     <row r="26">
-      <c r="A26" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="78" t="s">
-        <v>46</v>
+      <c r="A26" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="C26" s="67">
         <v>19.0</v>
@@ -3215,7 +3215,7 @@
       <c r="O26" s="68">
         <v>1.0</v>
       </c>
-      <c r="P26" s="59">
+      <c r="P26" s="60">
         <v>0.0</v>
       </c>
       <c r="Q26" s="67">
@@ -3228,11 +3228,11 @@
         <v>6.0</v>
       </c>
       <c r="T26" s="69">
-        <v>24.0</v>
-      </c>
-      <c r="U26" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U26" s="73">
         <f t="shared" si="1"/>
-        <v>2685</v>
+        <v>2715</v>
       </c>
       <c r="V26" s="15"/>
       <c r="W26" s="15"/>
@@ -3245,11 +3245,11 @@
       <c r="AD26" s="15"/>
     </row>
     <row r="27">
-      <c r="A27" s="79" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="78" t="s">
-        <v>32</v>
+      <c r="A27" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C27" s="67">
         <v>20.0</v>
@@ -3290,7 +3290,7 @@
       <c r="O27" s="68">
         <v>1.0</v>
       </c>
-      <c r="P27" s="59">
+      <c r="P27" s="60">
         <v>0.0</v>
       </c>
       <c r="Q27" s="67">
@@ -3305,7 +3305,7 @@
       <c r="T27" s="69">
         <v>31.0</v>
       </c>
-      <c r="U27" s="72">
+      <c r="U27" s="73">
         <f t="shared" si="1"/>
         <v>2685</v>
       </c>
@@ -3320,32 +3320,32 @@
       <c r="AD27" s="15"/>
     </row>
     <row r="28">
-      <c r="A28" s="79" t="s">
-        <v>66</v>
+      <c r="A28" s="80" t="s">
+        <v>84</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="67">
+        <v>15.0</v>
+      </c>
+      <c r="D28" s="68">
         <v>20.0</v>
       </c>
-      <c r="D28" s="68">
-        <v>36.0</v>
-      </c>
       <c r="E28" s="68">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" s="68">
         <v>0.0</v>
       </c>
       <c r="G28" s="68">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H28" s="68">
         <v>0.0</v>
       </c>
       <c r="I28" s="69">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="J28" s="67">
         <v>0.0</v>
@@ -3354,35 +3354,35 @@
         <v>0.0</v>
       </c>
       <c r="L28" s="67">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="M28" s="68">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N28" s="68">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="O28" s="68">
         <v>1.0</v>
       </c>
-      <c r="P28" s="59">
-        <v>0.0</v>
+      <c r="P28" s="60">
+        <v>4.0</v>
       </c>
       <c r="Q28" s="67">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="R28" s="68">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S28" s="70">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="T28" s="69">
-        <v>27.0</v>
-      </c>
-      <c r="U28" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U28" s="73">
         <f t="shared" si="1"/>
-        <v>2565</v>
+        <v>2610</v>
       </c>
       <c r="V28" s="15"/>
       <c r="W28" s="15"/>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="29">
       <c r="A29" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="78" t="s">
-        <v>46</v>
+        <v>86</v>
+      </c>
+      <c r="B29" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="C29" s="67">
         <v>17.0</v>
@@ -3440,7 +3440,7 @@
       <c r="O29" s="68">
         <v>0.0</v>
       </c>
-      <c r="P29" s="59">
+      <c r="P29" s="60">
         <v>0.0</v>
       </c>
       <c r="Q29" s="67">
@@ -3453,11 +3453,11 @@
         <v>7.0</v>
       </c>
       <c r="T29" s="69">
-        <v>24.0</v>
-      </c>
-      <c r="U29" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="U29" s="73">
         <f t="shared" si="1"/>
-        <v>2565</v>
+        <v>2595</v>
       </c>
       <c r="V29" s="15"/>
       <c r="W29" s="15"/>
@@ -3470,69 +3470,69 @@
       <c r="AD29" s="15"/>
     </row>
     <row r="30">
-      <c r="A30" s="79" t="s">
-        <v>68</v>
+      <c r="A30" s="80" t="s">
+        <v>88</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" s="67">
+        <v>20.0</v>
+      </c>
+      <c r="D30" s="68">
+        <v>37.0</v>
+      </c>
+      <c r="E30" s="68">
+        <v>2.0</v>
+      </c>
+      <c r="F30" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="68">
+        <v>2.0</v>
+      </c>
+      <c r="H30" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="69">
+        <v>14.0</v>
+      </c>
+      <c r="J30" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="69">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="67">
+        <v>2.0</v>
+      </c>
+      <c r="M30" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="68">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="68">
+        <v>1.0</v>
+      </c>
+      <c r="P30" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="Q30" s="67">
         <v>13.0</v>
       </c>
-      <c r="D30" s="68">
-        <v>18.0</v>
-      </c>
-      <c r="E30" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="F30" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="G30" s="68">
-        <v>3.0</v>
-      </c>
-      <c r="H30" s="68">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="69">
-        <v>1.0</v>
-      </c>
-      <c r="J30" s="67">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="69">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="67">
-        <v>5.0</v>
-      </c>
-      <c r="M30" s="68">
-        <v>2.0</v>
-      </c>
-      <c r="N30" s="68">
-        <v>2.0</v>
-      </c>
-      <c r="O30" s="68">
-        <v>1.0</v>
-      </c>
-      <c r="P30" s="59">
+      <c r="R30" s="68">
         <v>4.0</v>
       </c>
-      <c r="Q30" s="67">
-        <v>6.0</v>
-      </c>
-      <c r="R30" s="68">
-        <v>5.0</v>
-      </c>
       <c r="S30" s="70">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="T30" s="69">
-        <v>24.0</v>
-      </c>
-      <c r="U30" s="72">
+        <v>28.0</v>
+      </c>
+      <c r="U30" s="73">
         <f t="shared" si="1"/>
-        <v>2460</v>
+        <v>2565</v>
       </c>
       <c r="V30" s="15"/>
       <c r="W30" s="15"/>
@@ -3545,17 +3545,17 @@
       <c r="AD30" s="15"/>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="78" t="s">
-        <v>46</v>
+      <c r="A31" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="C31" s="67">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="D31" s="68">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="E31" s="68">
         <v>4.0</v>
@@ -3590,7 +3590,7 @@
       <c r="O31" s="68">
         <v>0.0</v>
       </c>
-      <c r="P31" s="59">
+      <c r="P31" s="60">
         <v>0.0</v>
       </c>
       <c r="Q31" s="67">
@@ -3603,11 +3603,11 @@
         <v>5.0</v>
       </c>
       <c r="T31" s="69">
-        <v>23.0</v>
-      </c>
-      <c r="U31" s="72">
+        <v>24.0</v>
+      </c>
+      <c r="U31" s="73">
         <f t="shared" si="1"/>
-        <v>2100</v>
+        <v>2175</v>
       </c>
       <c r="V31" s="15"/>
       <c r="W31" s="15"/>
@@ -3620,11 +3620,11 @@
       <c r="AD31" s="15"/>
     </row>
     <row r="32">
-      <c r="A32" s="80" t="s">
-        <v>70</v>
+      <c r="A32" s="82" t="s">
+        <v>92</v>
       </c>
       <c r="B32" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="67">
         <v>10.0</v>
@@ -3665,7 +3665,7 @@
       <c r="O32" s="68">
         <v>0.0</v>
       </c>
-      <c r="P32" s="59">
+      <c r="P32" s="60">
         <v>0.0</v>
       </c>
       <c r="Q32" s="67">
@@ -3678,11 +3678,11 @@
         <v>8.0</v>
       </c>
       <c r="T32" s="69">
-        <v>27.0</v>
-      </c>
-      <c r="U32" s="72">
+        <v>28.0</v>
+      </c>
+      <c r="U32" s="73">
         <f t="shared" si="1"/>
-        <v>2025</v>
+        <v>2055</v>
       </c>
       <c r="V32" s="15"/>
       <c r="W32" s="15"/>
@@ -3695,11 +3695,11 @@
       <c r="AD32" s="15"/>
     </row>
     <row r="33">
-      <c r="A33" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="78" t="s">
-        <v>32</v>
+      <c r="A33" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="75" t="s">
+        <v>30</v>
       </c>
       <c r="C33" s="67">
         <v>5.0</v>
@@ -3740,7 +3740,7 @@
       <c r="O33" s="68">
         <v>0.0</v>
       </c>
-      <c r="P33" s="59">
+      <c r="P33" s="60">
         <v>0.0</v>
       </c>
       <c r="Q33" s="67">
@@ -3755,7 +3755,7 @@
       <c r="T33" s="69">
         <v>31.0</v>
       </c>
-      <c r="U33" s="72">
+      <c r="U33" s="73">
         <f t="shared" si="1"/>
         <v>1830</v>
       </c>
@@ -3770,11 +3770,11 @@
       <c r="AD33" s="15"/>
     </row>
     <row r="34">
-      <c r="A34" s="79" t="s">
-        <v>72</v>
+      <c r="A34" s="80" t="s">
+        <v>96</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" s="67">
         <v>8.0</v>
@@ -3815,7 +3815,7 @@
       <c r="O34" s="68">
         <v>0.0</v>
       </c>
-      <c r="P34" s="59">
+      <c r="P34" s="60">
         <v>0.0</v>
       </c>
       <c r="Q34" s="67">
@@ -3828,11 +3828,11 @@
         <v>2.0</v>
       </c>
       <c r="T34" s="69">
-        <v>27.0</v>
-      </c>
-      <c r="U34" s="72">
+        <v>28.0</v>
+      </c>
+      <c r="U34" s="73">
         <f t="shared" si="1"/>
-        <v>1770</v>
+        <v>1800</v>
       </c>
       <c r="V34" s="15"/>
       <c r="W34" s="15"/>
@@ -3845,17 +3845,17 @@
       <c r="AD34" s="15"/>
     </row>
     <row r="35">
-      <c r="A35" s="79" t="s">
-        <v>74</v>
+      <c r="A35" s="80" t="s">
+        <v>99</v>
       </c>
       <c r="B35" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="67">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D35" s="68">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="E35" s="68">
         <v>2.0</v>
@@ -3870,7 +3870,7 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="69">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J35" s="67">
         <v>0.0</v>
@@ -3879,10 +3879,10 @@
         <v>0.0</v>
       </c>
       <c r="L35" s="67">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M35" s="68">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="N35" s="68">
         <v>0.0</v>
@@ -3890,7 +3890,7 @@
       <c r="O35" s="68">
         <v>1.0</v>
       </c>
-      <c r="P35" s="59">
+      <c r="P35" s="60">
         <v>0.0</v>
       </c>
       <c r="Q35" s="67">
@@ -3903,11 +3903,11 @@
         <v>9.0</v>
       </c>
       <c r="T35" s="69">
-        <v>23.0</v>
-      </c>
-      <c r="U35" s="72">
+        <v>24.0</v>
+      </c>
+      <c r="U35" s="73">
         <f t="shared" si="1"/>
-        <v>1605</v>
+        <v>1785</v>
       </c>
       <c r="V35" s="15"/>
       <c r="W35" s="15"/>
@@ -3921,16 +3921,16 @@
     </row>
     <row r="36">
       <c r="A36" s="65" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B36" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="67">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D36" s="68">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E36" s="68">
         <v>1.0</v>
@@ -3965,7 +3965,7 @@
       <c r="O36" s="68">
         <v>1.0</v>
       </c>
-      <c r="P36" s="59">
+      <c r="P36" s="60">
         <v>0.0</v>
       </c>
       <c r="Q36" s="67">
@@ -3978,11 +3978,11 @@
         <v>4.0</v>
       </c>
       <c r="T36" s="69">
-        <v>25.0</v>
-      </c>
-      <c r="U36" s="72">
+        <v>26.0</v>
+      </c>
+      <c r="U36" s="73">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1395</v>
       </c>
       <c r="V36" s="15"/>
       <c r="W36" s="15"/>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="37">
       <c r="A37" s="65" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="B37" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="67">
         <v>1.0</v>
@@ -4040,7 +4040,7 @@
       <c r="O37" s="68">
         <v>0.0</v>
       </c>
-      <c r="P37" s="59">
+      <c r="P37" s="60">
         <v>0.0</v>
       </c>
       <c r="Q37" s="67">
@@ -4053,11 +4053,11 @@
         <v>2.0</v>
       </c>
       <c r="T37" s="69">
-        <v>23.0</v>
-      </c>
-      <c r="U37" s="72">
+        <v>24.0</v>
+      </c>
+      <c r="U37" s="73">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="V37" s="15"/>
       <c r="W37" s="15"/>
@@ -4070,23 +4070,23 @@
       <c r="AD37" s="15"/>
     </row>
     <row r="38">
-      <c r="A38" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="78" t="s">
-        <v>46</v>
+      <c r="A38" s="93" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="75" t="s">
+        <v>45</v>
       </c>
       <c r="C38" s="67">
         <v>4.0</v>
       </c>
       <c r="D38" s="68">
+        <v>4.0</v>
+      </c>
+      <c r="E38" s="68">
         <v>3.0</v>
       </c>
-      <c r="E38" s="68">
-        <v>2.0</v>
-      </c>
       <c r="F38" s="68">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G38" s="68">
         <v>0.0</v>
@@ -4103,36 +4103,36 @@
       <c r="K38" s="69">
         <v>0.0</v>
       </c>
-      <c r="L38" s="84">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="85">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="85">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="85">
-        <v>2.0</v>
-      </c>
-      <c r="P38" s="86">
-        <v>0.0</v>
-      </c>
-      <c r="Q38" s="84">
-        <v>1.0</v>
-      </c>
-      <c r="R38" s="85">
-        <v>0.0</v>
-      </c>
-      <c r="S38" s="87">
+      <c r="L38" s="94">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="96">
+        <v>2.0</v>
+      </c>
+      <c r="P38" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="Q38" s="94">
+        <v>1.0</v>
+      </c>
+      <c r="R38" s="96">
+        <v>0.0</v>
+      </c>
+      <c r="S38" s="100">
         <v>3.0</v>
       </c>
       <c r="T38" s="69">
-        <v>0.0</v>
-      </c>
-      <c r="U38" s="72">
+        <v>1.0</v>
+      </c>
+      <c r="U38" s="73">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="V38" s="15"/>
       <c r="W38" s="15"/>
@@ -4232,17 +4232,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.0" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="4"/>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
       <c r="J1" s="7"/>
       <c r="K1" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L1" s="10"/>
       <c r="M1" s="12"/>
@@ -4259,10 +4259,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="17"/>
-      <c r="C2" s="19">
+      <c r="C2" s="18">
         <v>75.0</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="20">
         <v>-30.0</v>
       </c>
       <c r="E2" s="22">
@@ -4274,90 +4274,90 @@
       <c r="G2" s="22">
         <v>180.0</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="20">
         <v>-15.0</v>
       </c>
       <c r="I2" s="23">
         <v>30.0</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="24">
         <v>-15.0</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="26">
         <v>180.0</v>
       </c>
-      <c r="L2" s="27">
+      <c r="L2" s="26">
         <v>180.0</v>
       </c>
-      <c r="M2" s="31">
+      <c r="M2" s="28">
         <v>180.0</v>
       </c>
-      <c r="N2" s="32">
+      <c r="N2" s="30">
         <v>60.0</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="32">
         <v>180.0</v>
       </c>
-      <c r="P2" s="27">
+      <c r="P2" s="26">
         <v>30.0</v>
       </c>
-      <c r="Q2" s="31">
+      <c r="Q2" s="28">
         <v>30.0</v>
       </c>
-      <c r="R2" s="36"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="46" t="s">
+      <c r="I3" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="J3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="K3" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="39" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="41" t="s">
+      <c r="N3" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="41" t="s">
+      <c r="P3" s="39" t="s">
         <v>24</v>
       </c>
       <c r="Q3" s="48" t="s">
@@ -4366,23 +4366,23 @@
       <c r="R3" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
     </row>
     <row r="4">
-      <c r="A4" s="54" t="s">
-        <v>29</v>
+      <c r="A4" s="53" t="s">
+        <v>28</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="57">
+        <v>30</v>
+      </c>
+      <c r="C4" s="56">
         <v>51.0</v>
       </c>
       <c r="D4" s="58">
@@ -4403,53 +4403,53 @@
       <c r="I4" s="58">
         <v>0.0</v>
       </c>
-      <c r="J4" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L4" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M4" s="62">
+      <c r="J4" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L4" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M4" s="64">
         <v>3.0</v>
       </c>
-      <c r="N4" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O4" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P4" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="Q4" s="62">
+      <c r="N4" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="Q4" s="64">
         <v>28.0</v>
       </c>
       <c r="R4" s="71">
-        <f t="shared" ref="R4:R7" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
+        <f t="shared" ref="R4:R6" si="1">C4*$C$2+D4*$D$2+E4*$E$2+F4*$F$2+G4*$G$2+H4*$H$2+K4*$K$2+L4*$L$2+M4*$M$2+N4*$N$2+O4*$O$2+P4*$P$2+Q4*$Q$2+I4*$I$2+J4*$J$2</f>
         <v>6765</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="72" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="57">
+        <v>30</v>
+      </c>
+      <c r="C5" s="56">
         <v>49.0</v>
       </c>
       <c r="D5" s="58">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="E5" s="58">
-        <v>26.0</v>
+        <v>22.0</v>
       </c>
       <c r="F5" s="58">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" s="58">
         <v>1.0</v>
@@ -4458,684 +4458,684 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L5" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M5" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N5" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O5" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P5" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q5" s="62">
-        <v>30.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J5" s="60">
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="62">
+        <v>4.0</v>
+      </c>
+      <c r="L5" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M5" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N5" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O5" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P5" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q5" s="64">
+        <v>27.0</v>
       </c>
       <c r="R5" s="71">
         <f t="shared" si="1"/>
-        <v>6315</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="61">
-        <v>47.0</v>
-      </c>
-      <c r="D6" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="E6" s="59">
-        <v>20.0</v>
-      </c>
-      <c r="F6" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="59">
+        <v>30</v>
+      </c>
+      <c r="C6" s="62">
+        <v>49.0</v>
+      </c>
+      <c r="D6" s="60">
+        <v>16.0</v>
+      </c>
+      <c r="E6" s="60">
+        <v>26.0</v>
+      </c>
+      <c r="F6" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="60">
         <v>1.0</v>
       </c>
       <c r="H6" s="58">
         <v>0.0</v>
       </c>
-      <c r="I6" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="J6" s="59">
-        <v>3.0</v>
-      </c>
-      <c r="K6" s="61">
-        <v>4.0</v>
-      </c>
-      <c r="L6" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M6" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O6" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P6" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q6" s="62">
-        <v>27.0</v>
+      <c r="I6" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L6" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M6" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q6" s="64">
+        <v>30.0</v>
       </c>
       <c r="R6" s="71">
         <f t="shared" si="1"/>
-        <v>6270</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="61">
-        <v>45.0</v>
-      </c>
-      <c r="D7" s="59">
+      <c r="A7" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="62">
+        <v>46.0</v>
+      </c>
+      <c r="D7" s="60">
+        <v>24.0</v>
+      </c>
+      <c r="E7" s="60">
+        <v>26.0</v>
+      </c>
+      <c r="F7" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q7" s="64">
+        <v>31.0</v>
+      </c>
+      <c r="R7" s="71">
+        <f>C7*$C$2+D7*$D$2+E7*$E$2+F7*$F$2+G7*$G$2+H7*$H$2+K7*$K$2+L7*$L$2+M7*$M$2+N7*$N$2+O7*$O$2+P7*$P$2+Q7*$Q$2</f>
+        <v>5370</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="62">
+        <v>47.0</v>
+      </c>
+      <c r="D8" s="60">
+        <v>21.0</v>
+      </c>
+      <c r="E8" s="60">
+        <v>15.0</v>
+      </c>
+      <c r="F8" s="60">
+        <v>3.0</v>
+      </c>
+      <c r="G8" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="58">
+        <v>3.0</v>
+      </c>
+      <c r="I8" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L8" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q8" s="64">
+        <v>31.0</v>
+      </c>
+      <c r="R8" s="71">
+        <f t="shared" ref="R8:R38" si="2">C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2+I8*$I$2+J8*$J$2</f>
+        <v>5190</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="62">
+        <v>37.0</v>
+      </c>
+      <c r="D9" s="60">
         <v>16.0</v>
       </c>
-      <c r="E7" s="59">
-        <v>28.0</v>
-      </c>
-      <c r="F7" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="H7" s="58">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L7" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M7" s="62">
-        <v>1.0</v>
-      </c>
-      <c r="N7" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O7" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P7" s="59">
-        <v>4.0</v>
-      </c>
-      <c r="Q7" s="62">
-        <v>28.0</v>
-      </c>
-      <c r="R7" s="71">
-        <f t="shared" si="1"/>
-        <v>6240</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="61">
-        <v>46.0</v>
-      </c>
-      <c r="D8" s="59">
-        <v>24.0</v>
-      </c>
-      <c r="E8" s="59">
+      <c r="E9" s="60">
         <v>26.0</v>
       </c>
-      <c r="F8" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q8" s="62">
+      <c r="F9" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="K9" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q9" s="64">
         <v>31.0</v>
       </c>
-      <c r="R8" s="71">
-        <f>C8*$C$2+D8*$D$2+E8*$E$2+F8*$F$2+G8*$G$2+H8*$H$2+K8*$K$2+L8*$L$2+M8*$M$2+N8*$N$2+O8*$O$2+P8*$P$2+Q8*$Q$2</f>
-        <v>5370</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="61">
-        <v>47.0</v>
-      </c>
-      <c r="D9" s="59">
-        <v>21.0</v>
-      </c>
-      <c r="E9" s="59">
-        <v>15.0</v>
-      </c>
-      <c r="F9" s="59">
+      <c r="R9" s="71">
+        <f t="shared" si="2"/>
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="62">
+        <v>32.0</v>
+      </c>
+      <c r="D10" s="60">
+        <v>18.0</v>
+      </c>
+      <c r="E10" s="60">
+        <v>22.0</v>
+      </c>
+      <c r="F10" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="58">
+        <v>1.0</v>
+      </c>
+      <c r="J10" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L10" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="64">
+        <v>2.0</v>
+      </c>
+      <c r="N10" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="60">
         <v>3.0</v>
       </c>
-      <c r="G9" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="58">
-        <v>3.0</v>
-      </c>
-      <c r="I9" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L9" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q9" s="62">
-        <v>31.0</v>
-      </c>
-      <c r="R9" s="71">
-        <f t="shared" ref="R9:R38" si="2">C9*$C$2+D9*$D$2+E9*$E$2+F9*$F$2+G9*$G$2+H9*$H$2+K9*$K$2+L9*$L$2+M9*$M$2+N9*$N$2+O9*$O$2+P9*$P$2+Q9*$Q$2+I9*$I$2+J9*$J$2</f>
-        <v>5190</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="61">
-        <v>35.0</v>
-      </c>
-      <c r="D10" s="59">
-        <v>14.0</v>
-      </c>
-      <c r="E10" s="59">
-        <v>24.0</v>
-      </c>
-      <c r="F10" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="H10" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="K10" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q10" s="62">
+      <c r="Q10" s="64">
         <v>31.0</v>
       </c>
       <c r="R10" s="71">
         <f t="shared" si="2"/>
-        <v>4890</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="61">
-        <v>32.0</v>
-      </c>
-      <c r="D11" s="59">
-        <v>18.0</v>
-      </c>
-      <c r="E11" s="59">
-        <v>22.0</v>
-      </c>
-      <c r="F11" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="59">
+      <c r="A11" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="62">
+        <v>34.0</v>
+      </c>
+      <c r="D11" s="60">
+        <v>14.0</v>
+      </c>
+      <c r="E11" s="60">
+        <v>21.0</v>
+      </c>
+      <c r="F11" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="60">
         <v>0.0</v>
       </c>
       <c r="H11" s="58">
         <v>0.0</v>
       </c>
       <c r="I11" s="58">
-        <v>1.0</v>
-      </c>
-      <c r="J11" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L11" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="62">
-        <v>2.0</v>
-      </c>
-      <c r="N11" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="59">
-        <v>3.0</v>
-      </c>
-      <c r="Q11" s="62">
-        <v>31.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="J11" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L11" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M11" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P11" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="64">
+        <v>28.0</v>
       </c>
       <c r="R11" s="71">
         <f t="shared" si="2"/>
-        <v>4770</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="81" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="61">
-        <v>34.0</v>
-      </c>
-      <c r="D12" s="59">
-        <v>14.0</v>
-      </c>
-      <c r="E12" s="59">
-        <v>21.0</v>
-      </c>
-      <c r="F12" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="59">
+        <v>57</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="62">
+        <v>36.0</v>
+      </c>
+      <c r="D12" s="60">
+        <v>26.0</v>
+      </c>
+      <c r="E12" s="60">
+        <v>27.0</v>
+      </c>
+      <c r="F12" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="60">
         <v>0.0</v>
       </c>
       <c r="H12" s="58">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="J12" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L12" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M12" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="62">
-        <v>28.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="K12" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L12" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="60">
+        <v>4.0</v>
+      </c>
+      <c r="Q12" s="64">
+        <v>25.0</v>
       </c>
       <c r="R12" s="71">
         <f t="shared" si="2"/>
-        <v>4650</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="s">
-        <v>83</v>
+      <c r="A13" s="81" t="s">
+        <v>59</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="61">
-        <v>31.0</v>
-      </c>
-      <c r="D13" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="E13" s="59">
-        <v>22.0</v>
-      </c>
-      <c r="F13" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="G13" s="59">
-        <v>0.0</v>
+        <v>30</v>
+      </c>
+      <c r="C13" s="62">
+        <v>18.0</v>
+      </c>
+      <c r="D13" s="60">
+        <v>16.0</v>
+      </c>
+      <c r="E13" s="60">
+        <v>29.0</v>
+      </c>
+      <c r="F13" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="60">
+        <v>1.0</v>
       </c>
       <c r="H13" s="58">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="58">
         <v>0.0</v>
       </c>
-      <c r="J13" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M13" s="62">
-        <v>2.0</v>
-      </c>
-      <c r="N13" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O13" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P13" s="59">
-        <v>3.0</v>
-      </c>
-      <c r="Q13" s="62">
+      <c r="J13" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L13" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M13" s="64">
+        <v>1.0</v>
+      </c>
+      <c r="N13" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P13" s="60">
+        <v>4.0</v>
+      </c>
+      <c r="Q13" s="64">
         <v>28.0</v>
       </c>
       <c r="R13" s="71">
         <f t="shared" si="2"/>
-        <v>4245</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="61">
+      <c r="A14" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="62">
         <v>31.0</v>
       </c>
-      <c r="D14" s="59">
-        <v>25.0</v>
-      </c>
-      <c r="E14" s="59">
-        <v>25.0</v>
-      </c>
-      <c r="F14" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="59">
+      <c r="D14" s="60">
+        <v>32.0</v>
+      </c>
+      <c r="E14" s="60">
+        <v>22.0</v>
+      </c>
+      <c r="F14" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G14" s="60">
         <v>0.0</v>
       </c>
       <c r="H14" s="58">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I14" s="58">
         <v>0.0</v>
       </c>
-      <c r="J14" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="K14" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L14" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M14" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N14" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P14" s="59">
-        <v>4.0</v>
-      </c>
-      <c r="Q14" s="62">
-        <v>24.0</v>
+      <c r="J14" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M14" s="64">
+        <v>2.0</v>
+      </c>
+      <c r="N14" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P14" s="60">
+        <v>3.0</v>
+      </c>
+      <c r="Q14" s="64">
+        <v>28.0</v>
       </c>
       <c r="R14" s="71">
         <f t="shared" si="2"/>
-        <v>4065</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="61">
-        <v>30.0</v>
-      </c>
-      <c r="D15" s="59">
-        <v>13.0</v>
-      </c>
-      <c r="E15" s="59">
-        <v>8.0</v>
-      </c>
-      <c r="F15" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="59">
+      <c r="A15" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="62">
+        <v>34.0</v>
+      </c>
+      <c r="D15" s="60">
+        <v>19.0</v>
+      </c>
+      <c r="E15" s="60">
+        <v>15.0</v>
+      </c>
+      <c r="F15" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="60">
         <v>2.0</v>
       </c>
       <c r="H15" s="58">
-        <v>2.0</v>
-      </c>
-      <c r="I15" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="K15" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M15" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P15" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q15" s="62">
-        <v>31.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="J15" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L15" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P15" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q15" s="64">
+        <v>25.0</v>
       </c>
       <c r="R15" s="71">
         <f t="shared" si="2"/>
-        <v>3885</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="61">
-        <v>32.0</v>
-      </c>
-      <c r="D16" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="E16" s="59">
-        <v>14.0</v>
-      </c>
-      <c r="F16" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="59">
+      <c r="A16" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="62">
+        <v>30.0</v>
+      </c>
+      <c r="D16" s="60">
+        <v>13.0</v>
+      </c>
+      <c r="E16" s="60">
+        <v>8.0</v>
+      </c>
+      <c r="F16" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="60">
         <v>2.0</v>
       </c>
       <c r="H16" s="58">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="58">
-        <v>1.0</v>
-      </c>
-      <c r="J16" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P16" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q16" s="62">
-        <v>24.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="K16" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M16" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P16" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q16" s="64">
+        <v>31.0</v>
       </c>
       <c r="R16" s="71">
         <f t="shared" si="2"/>
-        <v>3825</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="61">
+      <c r="A17" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="62">
         <v>26.0</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="60">
         <v>15.0</v>
       </c>
-      <c r="E17" s="59">
+      <c r="E17" s="60">
         <v>15.0</v>
       </c>
-      <c r="F17" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="59">
+      <c r="F17" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="60">
         <v>0.0</v>
       </c>
       <c r="H17" s="58">
@@ -5144,85 +5144,85 @@
       <c r="I17" s="58">
         <v>0.0</v>
       </c>
-      <c r="J17" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L17" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M17" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P17" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q17" s="62">
-        <v>24.0</v>
+      <c r="J17" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L17" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M17" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P17" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q17" s="64">
+        <v>25.0</v>
       </c>
       <c r="R17" s="71">
         <f t="shared" si="2"/>
-        <v>3600</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="89" t="s">
-        <v>88</v>
+      <c r="A18" s="84" t="s">
+        <v>70</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="61">
+        <v>30</v>
+      </c>
+      <c r="C18" s="62">
         <v>30.0</v>
       </c>
-      <c r="D18" s="59">
+      <c r="D18" s="60">
         <v>22.0</v>
       </c>
-      <c r="E18" s="59">
+      <c r="E18" s="60">
         <v>19.0</v>
       </c>
-      <c r="F18" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="59">
+      <c r="F18" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="60">
         <v>0.0</v>
       </c>
       <c r="H18" s="58">
         <v>1.0</v>
       </c>
-      <c r="I18" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P18" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q18" s="62">
+      <c r="I18" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q18" s="64">
         <v>24.0</v>
       </c>
       <c r="R18" s="71">
@@ -5231,55 +5231,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="61">
+      <c r="A19" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="62">
         <v>25.0</v>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="60">
         <v>15.0</v>
       </c>
-      <c r="E19" s="59">
+      <c r="E19" s="60">
         <v>17.0</v>
       </c>
-      <c r="F19" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="59">
+      <c r="F19" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="60">
         <v>0.0</v>
       </c>
       <c r="H19" s="58">
         <v>1.0</v>
       </c>
-      <c r="I19" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q19" s="62">
+      <c r="I19" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q19" s="64">
         <v>31.0</v>
       </c>
       <c r="R19" s="71">
@@ -5288,55 +5288,55 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="61">
+      <c r="A20" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="62">
         <v>28.0</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="60">
         <v>32.0</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="60">
         <v>21.0</v>
       </c>
-      <c r="F20" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="59">
+      <c r="F20" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="60">
         <v>0.0</v>
       </c>
       <c r="H20" s="58">
         <v>1.0</v>
       </c>
-      <c r="I20" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="K20" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P20" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q20" s="62">
+      <c r="I20" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="K20" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P20" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q20" s="64">
         <v>31.0</v>
       </c>
       <c r="R20" s="71">
@@ -5345,25 +5345,25 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="73" t="s">
-        <v>91</v>
+      <c r="A21" s="72" t="s">
+        <v>77</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="61">
+        <v>45</v>
+      </c>
+      <c r="C21" s="62">
         <v>31.0</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D21" s="60">
         <v>21.0</v>
       </c>
-      <c r="E21" s="59">
+      <c r="E21" s="60">
         <v>12.0</v>
       </c>
-      <c r="F21" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="59">
+      <c r="F21" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="60">
         <v>0.0</v>
       </c>
       <c r="H21" s="58">
@@ -5372,55 +5372,55 @@
       <c r="I21" s="58">
         <v>0.0</v>
       </c>
-      <c r="J21" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="K21" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P21" s="59">
+      <c r="J21" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="K21" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M21" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P21" s="60">
         <v>3.0</v>
       </c>
-      <c r="Q21" s="62">
-        <v>27.0</v>
+      <c r="Q21" s="64">
+        <v>28.0</v>
       </c>
       <c r="R21" s="71">
         <f t="shared" si="2"/>
-        <v>3285</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="82" t="s">
-        <v>92</v>
+      <c r="A22" s="76" t="s">
+        <v>79</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="61">
+        <v>30</v>
+      </c>
+      <c r="C22" s="62">
         <v>27.0</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="60">
         <v>31.0</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="60">
         <v>21.0</v>
       </c>
-      <c r="F22" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="59">
+      <c r="F22" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="60">
         <v>0.0</v>
       </c>
       <c r="H22" s="58">
@@ -5429,28 +5429,28 @@
       <c r="I22" s="58">
         <v>1.0</v>
       </c>
-      <c r="J22" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P22" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q22" s="62">
+      <c r="J22" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M22" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P22" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q22" s="64">
         <v>28.0</v>
       </c>
       <c r="R22" s="71">
@@ -5459,25 +5459,25 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="88" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="61">
+      <c r="A23" s="83" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="62">
         <v>36.0</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D23" s="60">
         <v>34.0</v>
       </c>
-      <c r="E23" s="59">
+      <c r="E23" s="60">
         <v>11.0</v>
       </c>
-      <c r="F23" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="G23" s="59">
+      <c r="F23" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="60">
         <v>0.0</v>
       </c>
       <c r="H23" s="58">
@@ -5486,85 +5486,85 @@
       <c r="I23" s="58">
         <v>0.0</v>
       </c>
-      <c r="J23" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M23" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P23" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q23" s="62">
-        <v>24.0</v>
+      <c r="J23" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q23" s="64">
+        <v>25.0</v>
       </c>
       <c r="R23" s="71">
         <f t="shared" si="2"/>
-        <v>3210</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="61">
+      <c r="A24" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="62">
         <v>23.0</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="60">
         <v>21.0</v>
       </c>
-      <c r="E24" s="59">
+      <c r="E24" s="60">
         <v>12.0</v>
       </c>
-      <c r="F24" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="59">
+      <c r="F24" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="60">
         <v>0.0</v>
       </c>
       <c r="H24" s="58">
         <v>0.0</v>
       </c>
-      <c r="I24" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="M24" s="62">
-        <v>1.0</v>
-      </c>
-      <c r="N24" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P24" s="59">
+      <c r="I24" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J24" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="M24" s="64">
+        <v>1.0</v>
+      </c>
+      <c r="N24" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P24" s="60">
         <v>3.0</v>
       </c>
-      <c r="Q24" s="62">
+      <c r="Q24" s="64">
         <v>31.0</v>
       </c>
       <c r="R24" s="71">
@@ -5573,82 +5573,82 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="s">
-        <v>95</v>
+      <c r="A25" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="61">
+        <v>45</v>
+      </c>
+      <c r="C25" s="62">
         <v>29.0</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="60">
         <v>26.0</v>
       </c>
-      <c r="E25" s="59">
+      <c r="E25" s="60">
         <v>9.0</v>
       </c>
-      <c r="F25" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="59">
+      <c r="F25" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="60">
         <v>0.0</v>
       </c>
       <c r="H25" s="58">
         <v>0.0</v>
       </c>
-      <c r="I25" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="M25" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P25" s="59">
+      <c r="I25" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J25" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="M25" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P25" s="60">
         <v>4.0</v>
       </c>
-      <c r="Q25" s="62">
-        <v>24.0</v>
+      <c r="Q25" s="64">
+        <v>25.0</v>
       </c>
       <c r="R25" s="71">
         <f t="shared" si="2"/>
-        <v>3135</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="81" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="61">
-        <v>33.0</v>
-      </c>
-      <c r="D26" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="E26" s="59">
-        <v>12.0</v>
-      </c>
-      <c r="F26" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="59">
+        <v>87</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="62">
+        <v>34.0</v>
+      </c>
+      <c r="D26" s="60">
+        <v>34.0</v>
+      </c>
+      <c r="E26" s="60">
+        <v>13.0</v>
+      </c>
+      <c r="F26" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G26" s="60">
         <v>0.0</v>
       </c>
       <c r="H26" s="58">
@@ -5657,85 +5657,85 @@
       <c r="I26" s="58">
         <v>1.0</v>
       </c>
-      <c r="J26" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M26" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P26" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q26" s="62">
-        <v>24.0</v>
+      <c r="J26" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M26" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P26" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q26" s="64">
+        <v>25.0</v>
       </c>
       <c r="R26" s="71">
         <f t="shared" si="2"/>
-        <v>3000</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="82" t="s">
-        <v>97</v>
+      <c r="A27" s="76" t="s">
+        <v>89</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="61">
+        <v>30</v>
+      </c>
+      <c r="C27" s="62">
         <v>17.0</v>
       </c>
-      <c r="D27" s="59">
+      <c r="D27" s="60">
         <v>13.0</v>
       </c>
-      <c r="E27" s="59">
+      <c r="E27" s="60">
         <v>12.0</v>
       </c>
-      <c r="F27" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="59">
+      <c r="F27" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G27" s="60">
         <v>1.0</v>
       </c>
       <c r="H27" s="58">
         <v>0.0</v>
       </c>
-      <c r="I27" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="L27" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M27" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O27" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P27" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="Q27" s="62">
+      <c r="I27" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="62">
+        <v>1.0</v>
+      </c>
+      <c r="L27" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P27" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="Q27" s="64">
         <v>28.0</v>
       </c>
       <c r="R27" s="71">
@@ -5745,195 +5745,195 @@
     </row>
     <row r="28">
       <c r="A28" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="61">
+        <v>91</v>
+      </c>
+      <c r="B28" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="62">
         <v>23.0</v>
       </c>
-      <c r="D28" s="59">
+      <c r="D28" s="60">
         <v>16.0</v>
       </c>
-      <c r="E28" s="59">
+      <c r="E28" s="60">
         <v>10.0</v>
       </c>
-      <c r="F28" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="59">
+      <c r="F28" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="60">
         <v>0.0</v>
       </c>
       <c r="H28" s="58">
         <v>1.0</v>
       </c>
-      <c r="I28" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J28" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P28" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="Q28" s="62">
-        <v>24.0</v>
+      <c r="I28" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J28" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P28" s="60">
+        <v>1.0</v>
+      </c>
+      <c r="Q28" s="64">
+        <v>25.0</v>
       </c>
       <c r="R28" s="71">
         <f t="shared" si="2"/>
-        <v>2580</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="54" t="s">
-        <v>99</v>
+      <c r="A29" s="53" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="61">
+        <v>45</v>
+      </c>
+      <c r="C29" s="62">
         <v>19.0</v>
       </c>
-      <c r="D29" s="59">
+      <c r="D29" s="60">
         <v>20.0</v>
       </c>
-      <c r="E29" s="59">
+      <c r="E29" s="60">
         <v>4.0</v>
       </c>
-      <c r="F29" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G29" s="59">
+      <c r="F29" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="60">
         <v>0.0</v>
       </c>
       <c r="H29" s="58">
         <v>0.0</v>
       </c>
-      <c r="I29" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J29" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M29" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O29" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P29" s="59">
+      <c r="I29" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J29" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M29" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P29" s="60">
         <v>4.0</v>
       </c>
-      <c r="Q29" s="62">
-        <v>27.0</v>
+      <c r="Q29" s="64">
+        <v>28.0</v>
       </c>
       <c r="R29" s="71">
         <f t="shared" si="2"/>
-        <v>1995</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="82" t="s">
-        <v>100</v>
+      <c r="A30" s="76" t="s">
+        <v>95</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="61">
+        <v>45</v>
+      </c>
+      <c r="C30" s="62">
         <v>12.0</v>
       </c>
-      <c r="D30" s="59">
+      <c r="D30" s="60">
         <v>16.0</v>
       </c>
-      <c r="E30" s="59">
-        <v>2.0</v>
-      </c>
-      <c r="F30" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G30" s="59">
+      <c r="E30" s="60">
+        <v>2.0</v>
+      </c>
+      <c r="F30" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="60">
         <v>0.0</v>
       </c>
       <c r="H30" s="58">
         <v>1.0</v>
       </c>
-      <c r="I30" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J30" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M30" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O30" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P30" s="59">
+      <c r="I30" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J30" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M30" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P30" s="60">
         <v>4.0</v>
       </c>
-      <c r="Q30" s="62">
-        <v>27.0</v>
+      <c r="Q30" s="64">
+        <v>28.0</v>
       </c>
       <c r="R30" s="71">
         <f t="shared" si="2"/>
-        <v>1455</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="90" t="s">
-        <v>101</v>
+      <c r="A31" s="85" t="s">
+        <v>97</v>
       </c>
       <c r="B31" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="61">
+        <v>45</v>
+      </c>
+      <c r="C31" s="62">
         <v>13.0</v>
       </c>
-      <c r="D31" s="59">
+      <c r="D31" s="60">
         <v>24.0</v>
       </c>
-      <c r="E31" s="59">
+      <c r="E31" s="60">
         <v>8.0</v>
       </c>
-      <c r="F31" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="59">
+      <c r="F31" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="60">
         <v>0.0</v>
       </c>
       <c r="H31" s="58">
@@ -5942,143 +5942,143 @@
       <c r="I31" s="58">
         <v>0.0</v>
       </c>
-      <c r="J31" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="L31" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="M31" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="N31" s="61">
-        <v>0.0</v>
-      </c>
-      <c r="O31" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="P31" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="Q31" s="62">
-        <v>11.0</v>
+      <c r="J31" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="M31" s="64">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="62">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="P31" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="Q31" s="64">
+        <v>12.0</v>
       </c>
       <c r="R31" s="71">
         <f t="shared" si="2"/>
-        <v>1065</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="91" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="93">
-        <v>7.0</v>
-      </c>
-      <c r="D32" s="94">
-        <v>5.0</v>
-      </c>
-      <c r="E32" s="94">
-        <v>8.0</v>
-      </c>
-      <c r="F32" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="94">
+      <c r="A32" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="88">
+        <v>9.0</v>
+      </c>
+      <c r="D32" s="89">
+        <v>4.0</v>
+      </c>
+      <c r="E32" s="89">
+        <v>4.0</v>
+      </c>
+      <c r="F32" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="89">
         <v>0.0</v>
       </c>
       <c r="H32" s="58">
         <v>0.0</v>
       </c>
-      <c r="I32" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="94">
-        <v>1.0</v>
-      </c>
-      <c r="Q32" s="95">
-        <v>6.0</v>
+      <c r="I32" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="90">
+        <v>1.0</v>
+      </c>
+      <c r="N32" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="Q32" s="90">
+        <v>3.0</v>
       </c>
       <c r="R32" s="71">
         <f t="shared" si="2"/>
-        <v>1065</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="91" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="93">
-        <v>9.0</v>
-      </c>
-      <c r="D33" s="94">
-        <v>4.0</v>
-      </c>
-      <c r="E33" s="94">
-        <v>4.0</v>
-      </c>
-      <c r="F33" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="94">
+      <c r="A33" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="88">
+        <v>7.0</v>
+      </c>
+      <c r="D33" s="89">
+        <v>5.0</v>
+      </c>
+      <c r="E33" s="89">
+        <v>8.0</v>
+      </c>
+      <c r="F33" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="89">
         <v>0.0</v>
       </c>
       <c r="H33" s="58">
         <v>0.0</v>
       </c>
-      <c r="I33" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="59">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="95">
-        <v>1.0</v>
-      </c>
-      <c r="N33" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="94">
-        <v>1.0</v>
-      </c>
-      <c r="Q33" s="95">
-        <v>2.0</v>
+      <c r="I33" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="J33" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="Q33" s="90">
+        <v>6.0</v>
       </c>
       <c r="R33" s="71">
         <f t="shared" si="2"/>
@@ -6086,25 +6086,25 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="96" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="93">
-        <v>6.0</v>
-      </c>
-      <c r="D34" s="94">
+      <c r="A34" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="88">
+        <v>9.0</v>
+      </c>
+      <c r="D34" s="89">
+        <v>10.0</v>
+      </c>
+      <c r="E34" s="89">
         <v>7.0</v>
       </c>
-      <c r="E34" s="94">
-        <v>5.0</v>
-      </c>
-      <c r="F34" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="94">
+      <c r="F34" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="89">
         <v>0.0</v>
       </c>
       <c r="H34" s="58">
@@ -6113,55 +6113,55 @@
       <c r="I34" s="58">
         <v>0.0</v>
       </c>
-      <c r="J34" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="95">
-        <v>1.0</v>
-      </c>
-      <c r="N34" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="94">
-        <v>1.0</v>
-      </c>
-      <c r="Q34" s="95">
-        <v>0.0</v>
+      <c r="J34" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="90">
+        <v>1.0</v>
+      </c>
+      <c r="N34" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="Q34" s="90">
+        <v>1.0</v>
       </c>
       <c r="R34" s="71">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="93">
-        <v>1.0</v>
-      </c>
-      <c r="D35" s="94">
+      <c r="A35" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="88">
+        <v>1.0</v>
+      </c>
+      <c r="D35" s="89">
         <v>5.0</v>
       </c>
-      <c r="E35" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="94">
+      <c r="E35" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="89">
         <v>0.0</v>
       </c>
       <c r="H35" s="58">
@@ -6170,55 +6170,55 @@
       <c r="I35" s="58">
         <v>0.0</v>
       </c>
-      <c r="J35" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="95">
-        <v>26.0</v>
+      <c r="J35" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="90">
+        <v>27.0</v>
       </c>
       <c r="R35" s="71">
         <f t="shared" si="2"/>
-        <v>705</v>
+        <v>735</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="D36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="G36" s="94">
+      <c r="A36" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="E36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="89">
         <v>0.0</v>
       </c>
       <c r="H36" s="58">
@@ -6227,55 +6227,55 @@
       <c r="I36" s="58">
         <v>0.0</v>
       </c>
-      <c r="J36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="Q36" s="95">
-        <v>22.0</v>
+      <c r="J36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="Q36" s="90">
+        <v>23.0</v>
       </c>
       <c r="R36" s="71">
         <f t="shared" si="2"/>
-        <v>660</v>
+        <v>690</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="91" t="s">
+      <c r="A37" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="93">
+      <c r="B37" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="88">
         <v>6.0</v>
       </c>
-      <c r="D37" s="94">
+      <c r="D37" s="89">
         <v>9.0</v>
       </c>
-      <c r="E37" s="94">
+      <c r="E37" s="89">
         <v>4.0</v>
       </c>
-      <c r="F37" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="G37" s="94">
+      <c r="F37" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="89">
         <v>0.0</v>
       </c>
       <c r="H37" s="58">
@@ -6284,55 +6284,55 @@
       <c r="I37" s="58">
         <v>0.0</v>
       </c>
-      <c r="J37" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M37" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="N37" s="93">
-        <v>0.0</v>
-      </c>
-      <c r="O37" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="P37" s="94">
-        <v>1.0</v>
-      </c>
-      <c r="Q37" s="95">
-        <v>5.0</v>
+      <c r="J37" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="90">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="P37" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="Q37" s="90">
+        <v>6.0</v>
       </c>
       <c r="R37" s="71">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="98" t="s">
+      <c r="A38" s="95" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="99" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="100">
+      <c r="B38" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="99">
         <v>7.0</v>
       </c>
-      <c r="D38" s="86">
+      <c r="D38" s="98">
         <v>9.0</v>
       </c>
-      <c r="E38" s="86">
+      <c r="E38" s="98">
         <v>3.0</v>
       </c>
-      <c r="F38" s="86">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="86">
+      <c r="F38" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="98">
         <v>0.0</v>
       </c>
       <c r="H38" s="101">
@@ -6341,33 +6341,33 @@
       <c r="I38" s="101">
         <v>0.0</v>
       </c>
-      <c r="J38" s="86">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="100">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="86">
+      <c r="J38" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="K38" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="98">
         <v>0.0</v>
       </c>
       <c r="M38" s="102">
         <v>0.0</v>
       </c>
-      <c r="N38" s="100">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="86">
-        <v>0.0</v>
-      </c>
-      <c r="P38" s="86">
+      <c r="N38" s="99">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="98">
+        <v>0.0</v>
+      </c>
+      <c r="P38" s="98">
         <v>2.0</v>
       </c>
       <c r="Q38" s="102">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R38" s="103">
         <f t="shared" si="2"/>
-        <v>495</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
